--- a/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
+++ b/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
@@ -59,7 +59,7 @@
     <definedName name="_s6x">OFFSET(散布図!$BJ$8,0,0,MAX(1,COUNT(散布図!$BJ$8:$BJ$67)),1)</definedName>
     <definedName name="_s6y">OFFSET(散布図!$BK$8,0,0,MAX(1,COUNT(散布図!$BJ$8:$BJ$67)),1)</definedName>
     <definedName name="_s6z">OFFSET(散布図!$BL$8,0,0,MAX(1,COUNT(散布図!$BJ$8:$BJ$67)),1)</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">印刷用!$A$1:$AA$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">印刷用!$A$1:$AA$62</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="454">
   <si>
     <t>▼ グラフ用データ　消したり非表示にしたりしないでください</t>
   </si>
@@ -2082,7 +2082,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2130,6 +2130,14 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFC55A11"/>
           <bgColor rgb="FFC55A11"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4250,6 +4258,1246 @@
                 </c:ext>
               </c:extLst>
             </c:dLbl>
+            <c:dLbl>
+              <c:idx val="19"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$22</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000019-0000-4000-8000-000000000019}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$22</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000013-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="20"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$23</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000020-0000-4000-8000-000000000020}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$23</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000014-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="21"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$24</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000021-0000-4000-8000-000000000021}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$24</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000015-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="22"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$25</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000022-0000-4000-8000-000000000022}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$25</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000016-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="23"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$26</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000023-0000-4000-8000-000000000023}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$26</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000017-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="24"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$27</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000024-0000-4000-8000-000000000024}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$27</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000018-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="25"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$28</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000025-0000-4000-8000-000000000025}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$28</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000019-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="26"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$29</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000026-0000-4000-8000-000000000026}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$29</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001A-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="27"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$30</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000027-0000-4000-8000-000000000027}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$30</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001B-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="28"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$31</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000028-0000-4000-8000-000000000028}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$31</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001C-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="29"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$32</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000029-0000-4000-8000-000000000029}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$32</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001D-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="30"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$33</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000030-0000-4000-8000-000000000030}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$33</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001E-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="31"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$34</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000031-0000-4000-8000-000000000031}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$34</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001F-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="32"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$35</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000032-0000-4000-8000-000000000032}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$35</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000020-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="33"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$36</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000033-0000-4000-8000-000000000033}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$36</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000021-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="34"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$37</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000034-0000-4000-8000-000000000034}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$37</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000022-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="35"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$38</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000035-0000-4000-8000-000000000035}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$38</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000023-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="36"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$39</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000036-0000-4000-8000-000000000036}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$39</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000024-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="37"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$40</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000037-0000-4000-8000-000000000037}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$40</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000025-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="38"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$41</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000038-0000-4000-8000-000000000038}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$41</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000026-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="39"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$42</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000039-0000-4000-8000-000000000039}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$42</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000027-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="40"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$43</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000040-0000-4000-8000-000000000040}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$43</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000028-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="41"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$44</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000041-0000-4000-8000-000000000041}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$44</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000029-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="42"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$45</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000042-0000-4000-8000-000000000042}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$45</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000002A-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="43"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$46</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000043-0000-4000-8000-000000000043}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$46</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000002B-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="44"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$47</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000044-0000-4000-8000-000000000044}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$47</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000002C-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="45"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$48</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000045-0000-4000-8000-000000000045}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$48</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000002D-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="46"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$49</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000046-0000-4000-8000-000000000046}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$49</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000002E-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="47"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$50</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000047-0000-4000-8000-000000000047}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$50</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000002F-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="48"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$51</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000048-0000-4000-8000-000000000048}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$51</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000030-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="49"/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>印刷用データ!$K$52</c:f>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900"/>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable>
+                    <c15:dlblFTEntry>
+                      <c15:txfldGUID>{PR000049-0000-4000-8000-000000000049}</c15:txfldGUID>
+                      <c15:f>印刷用データ!$K$52</c15:f>
+                    </c15:dlblFTEntry>
+                  </c15:dlblFieldTable>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000031-9A3E-489E-9801-55C342B48382}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -4272,10 +5520,10 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>印刷用データ!$L$3:$L$21</c:f>
+              <c:f>印刷用データ!$L$3:$L$52</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>136.58407297830374</c:v>
                 </c:pt>
@@ -4338,10 +5586,10 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>印刷用データ!$M$3:$M$21</c:f>
+              <c:f>印刷用データ!$M$3:$M$52</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>149.67602924201614</c:v>
                 </c:pt>
@@ -7962,9 +9210,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>印刷用データ!$AP$3:$AP$31</c:f>
+              <c:f>印刷用データ!$AP$3:$AP$52</c:f>
               <c:strCache>
-                <c:ptCount val="29"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>本吉有美子</c:v>
                 </c:pt>
@@ -8057,10 +9305,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>印刷用データ!$AS$3:$AS$31</c:f>
+              <c:f>印刷用データ!$AS$3:$AS$52</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>143.93786470715366</c:v>
                 </c:pt>
@@ -8203,9 +9451,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>印刷用データ!$AP$3:$AP$31</c:f>
+              <c:f>印刷用データ!$AP$3:$AP$52</c:f>
               <c:strCache>
-                <c:ptCount val="29"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>本吉有美子</c:v>
                 </c:pt>
@@ -8298,10 +9546,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>印刷用データ!$AV$3:$AV$31</c:f>
+              <c:f>印刷用データ!$AV$3:$AV$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="29"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>100</c:v>
                 </c:pt>
@@ -8565,9 +9813,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>印刷用データ!$R$3:$R$21</c:f>
+              <c:f>印刷用データ!$R$3:$R$52</c:f>
               <c:strCache>
-                <c:ptCount val="19"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>本吉有美子</c:v>
                 </c:pt>
@@ -8630,10 +9878,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>印刷用データ!$S$3:$S$21</c:f>
+              <c:f>印刷用データ!$S$3:$S$52</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>136.58407297830374</c:v>
                 </c:pt>
@@ -8765,9 +10013,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>印刷用データ!$R$3:$R$21</c:f>
+              <c:f>印刷用データ!$R$3:$R$52</c:f>
               <c:strCache>
-                <c:ptCount val="19"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>本吉有美子</c:v>
                 </c:pt>
@@ -8830,10 +10078,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>印刷用データ!$T$3:$T$21</c:f>
+              <c:f>印刷用データ!$T$3:$T$52</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>149.67602924201614</c:v>
                 </c:pt>
@@ -8947,9 +10195,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>印刷用データ!$R$3:$R$21</c:f>
+              <c:f>印刷用データ!$R$3:$R$52</c:f>
               <c:strCache>
-                <c:ptCount val="19"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>本吉有美子</c:v>
                 </c:pt>
@@ -9012,10 +10260,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>印刷用データ!$U$3:$U$21</c:f>
+              <c:f>印刷用データ!$U$3:$U$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>100</c:v>
                 </c:pt>
@@ -9419,7 +10667,7 @@
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -9455,7 +10703,7 @@
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -9485,13 +10733,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -9521,13 +10769,13 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -9584,13 +10832,13 @@
     <xdr:from>
       <xdr:col>20</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -9647,13 +10895,13 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -9710,13 +10958,13 @@
     <xdr:from>
       <xdr:col>20</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -9773,13 +11021,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>55</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -26619,7 +27867,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AA41"/>
+  <dimension ref="B1:AA62"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
@@ -26668,8 +27916,9 @@
     </row>
     <row r="2" spans="2:27" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="3" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="64" t="s">
-        <v>453</v>
+      <c r="B3" s="64" t="str">
+        <f>"① 個人別 総合達成率（全員 "&amp;COUNT(印刷用データ!$AS$3:$AS$62)&amp;"名）"</f>
+        <v>① 個人別 総合達成率（全員 29名）</v>
       </c>
       <c r="C3" s="64"/>
       <c r="D3" s="64"/>
@@ -26681,16 +27930,18 @@
       <c r="J3" s="64"/>
       <c r="K3" s="64"/>
       <c r="L3" s="63"/>
-      <c r="M3" s="64" t="s">
-        <v>115</v>
+      <c r="M3" s="64" t="str">
+        <f>"④ 改善優先順位（全員 "&amp;COUNT(印刷用データ!$AS$3:$AS$62)&amp;"名）"</f>
+        <v>④ 改善優先順位（全員 29名）</v>
       </c>
       <c r="N3" s="63"/>
       <c r="O3" s="63"/>
       <c r="P3" s="63"/>
       <c r="Q3" s="63"/>
       <c r="R3" s="63"/>
-      <c r="T3" s="86" t="s">
-        <v>116</v>
+      <c r="T3" s="86" t="str">
+        <f>"② ピッキング・梱包 内訳比較（両工程 "&amp;COUNT(印刷用データ!$Q$3:$Q$62)&amp;"名）"</f>
+        <v>② ピッキング・梱包 内訳比較（両工程 19名）</v>
       </c>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
@@ -26731,7 +27982,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="5" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="63"/>
       <c r="C5" s="63"/>
       <c r="D5" s="63"/>
@@ -26760,7 +28011,7 @@
         <v>56.602448979591827</v>
       </c>
       <c r="Q5" s="36">
-        <f t="shared" ref="Q5:Q33" si="0">IF(P5="","",P5-100)</f>
+        <f t="shared" ref="Q5:Q54" si="0">IF(P5="","",P5-100)</f>
         <v>-43.397551020408173</v>
       </c>
       <c r="R5" s="37" t="str">
@@ -26768,7 +28019,7 @@
         <v>ピッキング改善</v>
       </c>
     </row>
-    <row r="6" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="63"/>
       <c r="C6" s="63"/>
       <c r="D6" s="63"/>
@@ -26805,7 +28056,7 @@
         <v>両工程を見直し</v>
       </c>
     </row>
-    <row r="7" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="63"/>
       <c r="C7" s="63"/>
       <c r="D7" s="63"/>
@@ -26842,7 +28093,7 @@
         <v>両工程を見直し</v>
       </c>
     </row>
-    <row r="8" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="63"/>
       <c r="C8" s="63"/>
       <c r="D8" s="63"/>
@@ -26879,7 +28130,7 @@
         <v>ピッキング改善</v>
       </c>
     </row>
-    <row r="9" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="63"/>
       <c r="C9" s="63"/>
       <c r="D9" s="63"/>
@@ -26916,7 +28167,7 @@
         <v>両工程を見直し</v>
       </c>
     </row>
-    <row r="10" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="63"/>
       <c r="C10" s="63"/>
       <c r="D10" s="63"/>
@@ -26953,7 +28204,7 @@
         <v>ピッキング改善</v>
       </c>
     </row>
-    <row r="11" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="63"/>
       <c r="C11" s="63"/>
       <c r="D11" s="63"/>
@@ -26990,7 +28241,7 @@
         <v>ピッキング改善</v>
       </c>
     </row>
-    <row r="12" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="63"/>
       <c r="C12" s="63"/>
       <c r="D12" s="63"/>
@@ -27027,7 +28278,7 @@
         <v>ピッキング改善</v>
       </c>
     </row>
-    <row r="13" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="63"/>
       <c r="C13" s="63"/>
       <c r="D13" s="63"/>
@@ -27064,7 +28315,7 @@
         <v>梱包手順を改善</v>
       </c>
     </row>
-    <row r="14" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="63"/>
       <c r="C14" s="63"/>
       <c r="D14" s="63"/>
@@ -27101,7 +28352,7 @@
         <v>ピッキング改善</v>
       </c>
     </row>
-    <row r="15" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="63"/>
       <c r="C15" s="63"/>
       <c r="D15" s="63"/>
@@ -27138,7 +28389,7 @@
         <v>ピッキング改善</v>
       </c>
     </row>
-    <row r="16" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="63"/>
       <c r="C16" s="63"/>
       <c r="D16" s="63"/>
@@ -27175,7 +28426,7 @@
         <v>ピッキング改善</v>
       </c>
     </row>
-    <row r="17" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="63"/>
       <c r="C17" s="63"/>
       <c r="D17" s="63"/>
@@ -27212,7 +28463,7 @@
         <v>ピッキング改善</v>
       </c>
     </row>
-    <row r="18" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="63"/>
       <c r="C18" s="63"/>
       <c r="D18" s="63"/>
@@ -27249,7 +28500,7 @@
         <v>梱包手順を改善</v>
       </c>
     </row>
-    <row r="19" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="63"/>
       <c r="C19" s="63"/>
       <c r="D19" s="63"/>
@@ -27285,18 +28536,8 @@
         <f>IFERROR(INDEX(印刷用データ!$AL$3:$AL$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,15),印刷用データ!$AM$3:$AM$62,0)),"")</f>
         <v>梱包手順を改善</v>
       </c>
-      <c r="T19" s="86" t="s">
-        <v>122</v>
-      </c>
-      <c r="U19" s="77"/>
-      <c r="V19" s="77"/>
-      <c r="W19" s="77"/>
-      <c r="X19" s="77"/>
-      <c r="Y19" s="77"/>
-      <c r="Z19" s="77"/>
-      <c r="AA19" s="77"/>
-    </row>
-    <row r="20" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="20" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="63"/>
       <c r="C20" s="63"/>
       <c r="D20" s="63"/>
@@ -27333,7 +28574,7 @@
         <v>両工程を見直し</v>
       </c>
     </row>
-    <row r="21" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="63"/>
       <c r="C21" s="63"/>
       <c r="D21" s="63"/>
@@ -27370,7 +28611,7 @@
         <v>梱包手順を改善</v>
       </c>
     </row>
-    <row r="22" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="63"/>
       <c r="C22" s="63"/>
       <c r="D22" s="63"/>
@@ -27407,7 +28648,7 @@
         <v>梱包手順を改善</v>
       </c>
     </row>
-    <row r="23" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="63"/>
       <c r="C23" s="63"/>
       <c r="D23" s="63"/>
@@ -27444,7 +28685,7 @@
         <v>目標達成</v>
       </c>
     </row>
-    <row r="24" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="63"/>
       <c r="C24" s="63"/>
       <c r="D24" s="63"/>
@@ -27481,7 +28722,7 @@
         <v>梱包手順を改善</v>
       </c>
     </row>
-    <row r="25" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="63"/>
       <c r="C25" s="63"/>
       <c r="D25" s="63"/>
@@ -27518,7 +28759,7 @@
         <v>ピッキング改善</v>
       </c>
     </row>
-    <row r="26" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="63"/>
       <c r="C26" s="63"/>
       <c r="D26" s="63"/>
@@ -27554,8 +28795,19 @@
         <f>IFERROR(INDEX(印刷用データ!$AL$3:$AL$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,22),印刷用データ!$AM$3:$AM$62,0)),"")</f>
         <v>ピッキング改善</v>
       </c>
-    </row>
-    <row r="27" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T26" s="86" t="str">
+        <f>"③ 改善優先度マトリクス（両工程 "&amp;COUNT(印刷用データ!$N$3:$N$62)&amp;"名）"</f>
+        <v>③ 改善優先度マトリクス（両工程 19名）</v>
+      </c>
+      <c r="U26" s="77"/>
+      <c r="V26" s="77"/>
+      <c r="W26" s="77"/>
+      <c r="X26" s="77"/>
+      <c r="Y26" s="77"/>
+      <c r="Z26" s="77"/>
+      <c r="AA26" s="77"/>
+    </row>
+    <row r="27" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="63"/>
       <c r="C27" s="63"/>
       <c r="D27" s="63"/>
@@ -27592,7 +28844,7 @@
         <v>目標達成</v>
       </c>
     </row>
-    <row r="28" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="63"/>
       <c r="C28" s="63"/>
       <c r="D28" s="63"/>
@@ -27629,7 +28881,7 @@
         <v>目標達成</v>
       </c>
     </row>
-    <row r="29" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="63"/>
       <c r="C29" s="63"/>
       <c r="D29" s="63"/>
@@ -27666,7 +28918,7 @@
         <v>目標達成</v>
       </c>
     </row>
-    <row r="30" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="63"/>
       <c r="C30" s="63"/>
       <c r="D30" s="63"/>
@@ -27703,7 +28955,7 @@
         <v>目標達成</v>
       </c>
     </row>
-    <row r="31" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="63"/>
       <c r="C31" s="63"/>
       <c r="D31" s="63"/>
@@ -27740,7 +28992,7 @@
         <v>目標達成</v>
       </c>
     </row>
-    <row r="32" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="63"/>
       <c r="C32" s="63"/>
       <c r="D32" s="63"/>
@@ -27777,7 +29029,7 @@
         <v>目標達成</v>
       </c>
     </row>
-    <row r="33" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="63"/>
       <c r="C33" s="63"/>
       <c r="D33" s="63"/>
@@ -27814,7 +29066,7 @@
         <v>目標達成</v>
       </c>
     </row>
-    <row r="34" spans="2:27" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="63"/>
       <c r="C34" s="63"/>
       <c r="D34" s="63"/>
@@ -27826,91 +29078,873 @@
       <c r="J34" s="63"/>
       <c r="K34" s="63"/>
       <c r="L34" s="63"/>
-      <c r="M34" s="63"/>
-      <c r="N34" s="63"/>
-      <c r="O34" s="63"/>
-      <c r="P34" s="63"/>
-      <c r="Q34" s="63"/>
-      <c r="R34" s="63"/>
-    </row>
-    <row r="35" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="36" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="37" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="38" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="39" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="40" spans="2:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="85" t="s">
+      <c r="M34" s="38" t="str">
+        <f>IFERROR(IF(SMALL(印刷用データ!$AM$3:$AM$62,30)&gt;0,30,""),"")</f>
+        <v/>
+      </c>
+      <c r="N34" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AG$3:$AG$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,30),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O34" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AK$3:$AK$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,30),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="P34" s="35" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AJ$3:$AJ$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,30),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Q34" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="R34" s="37" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AL$3:$AL$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,30),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B35" s="63"/>
+      <c r="C35" s="63"/>
+      <c r="D35" s="63"/>
+      <c r="E35" s="63"/>
+      <c r="F35" s="63"/>
+      <c r="G35" s="63"/>
+      <c r="H35" s="63"/>
+      <c r="I35" s="63"/>
+      <c r="J35" s="63"/>
+      <c r="K35" s="63"/>
+      <c r="L35" s="63"/>
+      <c r="M35" s="38" t="str">
+        <f>IFERROR(IF(SMALL(印刷用データ!$AM$3:$AM$62,31)&gt;0,31,""),"")</f>
+        <v/>
+      </c>
+      <c r="N35" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AG$3:$AG$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,31),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O35" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AK$3:$AK$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,31),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="P35" s="35" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AJ$3:$AJ$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,31),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Q35" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="R35" s="37" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AL$3:$AL$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,31),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="63"/>
+      <c r="C36" s="63"/>
+      <c r="D36" s="63"/>
+      <c r="E36" s="63"/>
+      <c r="F36" s="63"/>
+      <c r="G36" s="63"/>
+      <c r="H36" s="63"/>
+      <c r="I36" s="63"/>
+      <c r="J36" s="63"/>
+      <c r="K36" s="63"/>
+      <c r="L36" s="63"/>
+      <c r="M36" s="38" t="str">
+        <f>IFERROR(IF(SMALL(印刷用データ!$AM$3:$AM$62,32)&gt;0,32,""),"")</f>
+        <v/>
+      </c>
+      <c r="N36" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AG$3:$AG$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,32),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O36" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AK$3:$AK$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,32),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="P36" s="35" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AJ$3:$AJ$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,32),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Q36" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="R36" s="37" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AL$3:$AL$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,32),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B37" s="63"/>
+      <c r="C37" s="63"/>
+      <c r="D37" s="63"/>
+      <c r="E37" s="63"/>
+      <c r="F37" s="63"/>
+      <c r="G37" s="63"/>
+      <c r="H37" s="63"/>
+      <c r="I37" s="63"/>
+      <c r="J37" s="63"/>
+      <c r="K37" s="63"/>
+      <c r="L37" s="63"/>
+      <c r="M37" s="38" t="str">
+        <f>IFERROR(IF(SMALL(印刷用データ!$AM$3:$AM$62,33)&gt;0,33,""),"")</f>
+        <v/>
+      </c>
+      <c r="N37" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AG$3:$AG$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,33),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O37" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AK$3:$AK$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,33),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="P37" s="35" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AJ$3:$AJ$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,33),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Q37" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="R37" s="37" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AL$3:$AL$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,33),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B38" s="63"/>
+      <c r="C38" s="63"/>
+      <c r="D38" s="63"/>
+      <c r="E38" s="63"/>
+      <c r="F38" s="63"/>
+      <c r="G38" s="63"/>
+      <c r="H38" s="63"/>
+      <c r="I38" s="63"/>
+      <c r="J38" s="63"/>
+      <c r="K38" s="63"/>
+      <c r="L38" s="63"/>
+      <c r="M38" s="38" t="str">
+        <f>IFERROR(IF(SMALL(印刷用データ!$AM$3:$AM$62,34)&gt;0,34,""),"")</f>
+        <v/>
+      </c>
+      <c r="N38" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AG$3:$AG$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,34),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O38" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AK$3:$AK$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,34),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="P38" s="35" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AJ$3:$AJ$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,34),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Q38" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="R38" s="37" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AL$3:$AL$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,34),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B39" s="63"/>
+      <c r="C39" s="63"/>
+      <c r="D39" s="63"/>
+      <c r="E39" s="63"/>
+      <c r="F39" s="63"/>
+      <c r="G39" s="63"/>
+      <c r="H39" s="63"/>
+      <c r="I39" s="63"/>
+      <c r="J39" s="63"/>
+      <c r="K39" s="63"/>
+      <c r="L39" s="63"/>
+      <c r="M39" s="38" t="str">
+        <f>IFERROR(IF(SMALL(印刷用データ!$AM$3:$AM$62,35)&gt;0,35,""),"")</f>
+        <v/>
+      </c>
+      <c r="N39" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AG$3:$AG$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,35),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O39" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AK$3:$AK$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,35),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="P39" s="35" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AJ$3:$AJ$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,35),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Q39" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="R39" s="37" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AL$3:$AL$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,35),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="63"/>
+      <c r="C40" s="63"/>
+      <c r="D40" s="63"/>
+      <c r="E40" s="63"/>
+      <c r="F40" s="63"/>
+      <c r="G40" s="63"/>
+      <c r="H40" s="63"/>
+      <c r="I40" s="63"/>
+      <c r="J40" s="63"/>
+      <c r="K40" s="63"/>
+      <c r="L40" s="63"/>
+      <c r="M40" s="38" t="str">
+        <f>IFERROR(IF(SMALL(印刷用データ!$AM$3:$AM$62,36)&gt;0,36,""),"")</f>
+        <v/>
+      </c>
+      <c r="N40" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AG$3:$AG$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,36),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O40" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AK$3:$AK$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,36),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="P40" s="35" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AJ$3:$AJ$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,36),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Q40" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="R40" s="37" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AL$3:$AL$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,36),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B41" s="63"/>
+      <c r="C41" s="63"/>
+      <c r="D41" s="63"/>
+      <c r="E41" s="63"/>
+      <c r="F41" s="63"/>
+      <c r="G41" s="63"/>
+      <c r="H41" s="63"/>
+      <c r="I41" s="63"/>
+      <c r="J41" s="63"/>
+      <c r="K41" s="63"/>
+      <c r="L41" s="63"/>
+      <c r="M41" s="38" t="str">
+        <f>IFERROR(IF(SMALL(印刷用データ!$AM$3:$AM$62,37)&gt;0,37,""),"")</f>
+        <v/>
+      </c>
+      <c r="N41" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AG$3:$AG$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,37),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O41" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AK$3:$AK$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,37),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="P41" s="35" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AJ$3:$AJ$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,37),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Q41" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="R41" s="37" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AL$3:$AL$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,37),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B42" s="63"/>
+      <c r="C42" s="63"/>
+      <c r="D42" s="63"/>
+      <c r="E42" s="63"/>
+      <c r="F42" s="63"/>
+      <c r="G42" s="63"/>
+      <c r="H42" s="63"/>
+      <c r="I42" s="63"/>
+      <c r="J42" s="63"/>
+      <c r="K42" s="63"/>
+      <c r="L42" s="63"/>
+      <c r="M42" s="38" t="str">
+        <f>IFERROR(IF(SMALL(印刷用データ!$AM$3:$AM$62,38)&gt;0,38,""),"")</f>
+        <v/>
+      </c>
+      <c r="N42" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AG$3:$AG$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,38),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O42" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AK$3:$AK$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,38),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="P42" s="35" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AJ$3:$AJ$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,38),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Q42" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="R42" s="37" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AL$3:$AL$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,38),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B43" s="63"/>
+      <c r="C43" s="63"/>
+      <c r="D43" s="63"/>
+      <c r="E43" s="63"/>
+      <c r="F43" s="63"/>
+      <c r="G43" s="63"/>
+      <c r="H43" s="63"/>
+      <c r="I43" s="63"/>
+      <c r="J43" s="63"/>
+      <c r="K43" s="63"/>
+      <c r="L43" s="63"/>
+      <c r="M43" s="38" t="str">
+        <f>IFERROR(IF(SMALL(印刷用データ!$AM$3:$AM$62,39)&gt;0,39,""),"")</f>
+        <v/>
+      </c>
+      <c r="N43" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AG$3:$AG$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,39),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O43" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AK$3:$AK$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,39),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="P43" s="35" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AJ$3:$AJ$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,39),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Q43" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="R43" s="37" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AL$3:$AL$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,39),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B44" s="63"/>
+      <c r="C44" s="63"/>
+      <c r="D44" s="63"/>
+      <c r="E44" s="63"/>
+      <c r="F44" s="63"/>
+      <c r="G44" s="63"/>
+      <c r="H44" s="63"/>
+      <c r="I44" s="63"/>
+      <c r="J44" s="63"/>
+      <c r="K44" s="63"/>
+      <c r="L44" s="63"/>
+      <c r="M44" s="38" t="str">
+        <f>IFERROR(IF(SMALL(印刷用データ!$AM$3:$AM$62,40)&gt;0,40,""),"")</f>
+        <v/>
+      </c>
+      <c r="N44" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AG$3:$AG$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,40),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O44" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AK$3:$AK$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,40),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="P44" s="35" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AJ$3:$AJ$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,40),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Q44" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="R44" s="37" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AL$3:$AL$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,40),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B45" s="63"/>
+      <c r="C45" s="63"/>
+      <c r="D45" s="63"/>
+      <c r="E45" s="63"/>
+      <c r="F45" s="63"/>
+      <c r="G45" s="63"/>
+      <c r="H45" s="63"/>
+      <c r="I45" s="63"/>
+      <c r="J45" s="63"/>
+      <c r="K45" s="63"/>
+      <c r="L45" s="63"/>
+      <c r="M45" s="38" t="str">
+        <f>IFERROR(IF(SMALL(印刷用データ!$AM$3:$AM$62,41)&gt;0,41,""),"")</f>
+        <v/>
+      </c>
+      <c r="N45" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AG$3:$AG$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,41),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O45" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AK$3:$AK$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,41),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="P45" s="35" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AJ$3:$AJ$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,41),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Q45" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="R45" s="37" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AL$3:$AL$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,41),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B46" s="63"/>
+      <c r="C46" s="63"/>
+      <c r="D46" s="63"/>
+      <c r="E46" s="63"/>
+      <c r="F46" s="63"/>
+      <c r="G46" s="63"/>
+      <c r="H46" s="63"/>
+      <c r="I46" s="63"/>
+      <c r="J46" s="63"/>
+      <c r="K46" s="63"/>
+      <c r="L46" s="63"/>
+      <c r="M46" s="38" t="str">
+        <f>IFERROR(IF(SMALL(印刷用データ!$AM$3:$AM$62,42)&gt;0,42,""),"")</f>
+        <v/>
+      </c>
+      <c r="N46" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AG$3:$AG$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,42),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O46" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AK$3:$AK$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,42),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="P46" s="35" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AJ$3:$AJ$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,42),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Q46" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="R46" s="37" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AL$3:$AL$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,42),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B47" s="63"/>
+      <c r="C47" s="63"/>
+      <c r="D47" s="63"/>
+      <c r="E47" s="63"/>
+      <c r="F47" s="63"/>
+      <c r="G47" s="63"/>
+      <c r="H47" s="63"/>
+      <c r="I47" s="63"/>
+      <c r="J47" s="63"/>
+      <c r="K47" s="63"/>
+      <c r="L47" s="63"/>
+      <c r="M47" s="38" t="str">
+        <f>IFERROR(IF(SMALL(印刷用データ!$AM$3:$AM$62,43)&gt;0,43,""),"")</f>
+        <v/>
+      </c>
+      <c r="N47" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AG$3:$AG$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,43),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O47" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AK$3:$AK$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,43),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="P47" s="35" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AJ$3:$AJ$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,43),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Q47" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="R47" s="37" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AL$3:$AL$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,43),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B48" s="63"/>
+      <c r="C48" s="63"/>
+      <c r="D48" s="63"/>
+      <c r="E48" s="63"/>
+      <c r="F48" s="63"/>
+      <c r="G48" s="63"/>
+      <c r="H48" s="63"/>
+      <c r="I48" s="63"/>
+      <c r="J48" s="63"/>
+      <c r="K48" s="63"/>
+      <c r="L48" s="63"/>
+      <c r="M48" s="38" t="str">
+        <f>IFERROR(IF(SMALL(印刷用データ!$AM$3:$AM$62,44)&gt;0,44,""),"")</f>
+        <v/>
+      </c>
+      <c r="N48" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AG$3:$AG$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,44),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O48" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AK$3:$AK$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,44),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="P48" s="35" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AJ$3:$AJ$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,44),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Q48" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="R48" s="37" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AL$3:$AL$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,44),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B49" s="63"/>
+      <c r="C49" s="63"/>
+      <c r="D49" s="63"/>
+      <c r="E49" s="63"/>
+      <c r="F49" s="63"/>
+      <c r="G49" s="63"/>
+      <c r="H49" s="63"/>
+      <c r="I49" s="63"/>
+      <c r="J49" s="63"/>
+      <c r="K49" s="63"/>
+      <c r="L49" s="63"/>
+      <c r="M49" s="38" t="str">
+        <f>IFERROR(IF(SMALL(印刷用データ!$AM$3:$AM$62,45)&gt;0,45,""),"")</f>
+        <v/>
+      </c>
+      <c r="N49" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AG$3:$AG$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,45),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O49" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AK$3:$AK$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,45),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="P49" s="35" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AJ$3:$AJ$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,45),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Q49" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="R49" s="37" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AL$3:$AL$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,45),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B50" s="63"/>
+      <c r="C50" s="63"/>
+      <c r="D50" s="63"/>
+      <c r="E50" s="63"/>
+      <c r="F50" s="63"/>
+      <c r="G50" s="63"/>
+      <c r="H50" s="63"/>
+      <c r="I50" s="63"/>
+      <c r="J50" s="63"/>
+      <c r="K50" s="63"/>
+      <c r="L50" s="63"/>
+      <c r="M50" s="38" t="str">
+        <f>IFERROR(IF(SMALL(印刷用データ!$AM$3:$AM$62,46)&gt;0,46,""),"")</f>
+        <v/>
+      </c>
+      <c r="N50" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AG$3:$AG$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,46),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O50" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AK$3:$AK$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,46),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="P50" s="35" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AJ$3:$AJ$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,46),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Q50" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="R50" s="37" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AL$3:$AL$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,46),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B51" s="63"/>
+      <c r="C51" s="63"/>
+      <c r="D51" s="63"/>
+      <c r="E51" s="63"/>
+      <c r="F51" s="63"/>
+      <c r="G51" s="63"/>
+      <c r="H51" s="63"/>
+      <c r="I51" s="63"/>
+      <c r="J51" s="63"/>
+      <c r="K51" s="63"/>
+      <c r="L51" s="63"/>
+      <c r="M51" s="38" t="str">
+        <f>IFERROR(IF(SMALL(印刷用データ!$AM$3:$AM$62,47)&gt;0,47,""),"")</f>
+        <v/>
+      </c>
+      <c r="N51" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AG$3:$AG$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,47),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O51" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AK$3:$AK$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,47),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="P51" s="35" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AJ$3:$AJ$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,47),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Q51" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="R51" s="37" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AL$3:$AL$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,47),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B52" s="63"/>
+      <c r="C52" s="63"/>
+      <c r="D52" s="63"/>
+      <c r="E52" s="63"/>
+      <c r="F52" s="63"/>
+      <c r="G52" s="63"/>
+      <c r="H52" s="63"/>
+      <c r="I52" s="63"/>
+      <c r="J52" s="63"/>
+      <c r="K52" s="63"/>
+      <c r="L52" s="63"/>
+      <c r="M52" s="38" t="str">
+        <f>IFERROR(IF(SMALL(印刷用データ!$AM$3:$AM$62,48)&gt;0,48,""),"")</f>
+        <v/>
+      </c>
+      <c r="N52" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AG$3:$AG$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,48),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O52" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AK$3:$AK$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,48),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="P52" s="35" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AJ$3:$AJ$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,48),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Q52" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="R52" s="37" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AL$3:$AL$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,48),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B53" s="63"/>
+      <c r="C53" s="63"/>
+      <c r="D53" s="63"/>
+      <c r="E53" s="63"/>
+      <c r="F53" s="63"/>
+      <c r="G53" s="63"/>
+      <c r="H53" s="63"/>
+      <c r="I53" s="63"/>
+      <c r="J53" s="63"/>
+      <c r="K53" s="63"/>
+      <c r="L53" s="63"/>
+      <c r="M53" s="38" t="str">
+        <f>IFERROR(IF(SMALL(印刷用データ!$AM$3:$AM$62,49)&gt;0,49,""),"")</f>
+        <v/>
+      </c>
+      <c r="N53" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AG$3:$AG$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,49),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O53" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AK$3:$AK$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,49),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="P53" s="35" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AJ$3:$AJ$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,49),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Q53" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="R53" s="37" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AL$3:$AL$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,49),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B54" s="63"/>
+      <c r="C54" s="63"/>
+      <c r="D54" s="63"/>
+      <c r="E54" s="63"/>
+      <c r="F54" s="63"/>
+      <c r="G54" s="63"/>
+      <c r="H54" s="63"/>
+      <c r="I54" s="63"/>
+      <c r="J54" s="63"/>
+      <c r="K54" s="63"/>
+      <c r="L54" s="63"/>
+      <c r="M54" s="38" t="str">
+        <f>IFERROR(IF(SMALL(印刷用データ!$AM$3:$AM$62,50)&gt;0,50,""),"")</f>
+        <v/>
+      </c>
+      <c r="N54" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AG$3:$AG$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,50),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O54" s="34" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AK$3:$AK$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,50),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="P54" s="35" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AJ$3:$AJ$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,50),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Q54" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="R54" s="37" t="str">
+        <f>IFERROR(INDEX(印刷用データ!$AL$3:$AL$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,50),印刷用データ!$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="2:27" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B55" s="63"/>
+      <c r="C55" s="63"/>
+      <c r="D55" s="63"/>
+      <c r="E55" s="63"/>
+      <c r="F55" s="63"/>
+      <c r="G55" s="63"/>
+      <c r="H55" s="63"/>
+      <c r="I55" s="63"/>
+      <c r="J55" s="63"/>
+      <c r="K55" s="63"/>
+      <c r="L55" s="63"/>
+      <c r="M55" s="63"/>
+      <c r="N55" s="63"/>
+      <c r="O55" s="63"/>
+      <c r="P55" s="63"/>
+      <c r="Q55" s="63"/>
+      <c r="R55" s="63"/>
+    </row>
+    <row r="56" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="57" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="58" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="59" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="60" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="61" spans="2:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B61" s="85" t="s">
         <v>123</v>
       </c>
-      <c r="C40" s="77"/>
-      <c r="D40" s="77"/>
-      <c r="E40" s="77"/>
-      <c r="F40" s="77"/>
-      <c r="G40" s="77"/>
-      <c r="H40" s="77"/>
-      <c r="I40" s="77"/>
-      <c r="J40" s="77"/>
-      <c r="K40" s="77"/>
-      <c r="L40" s="77"/>
-      <c r="M40" s="77"/>
-      <c r="N40" s="77"/>
-      <c r="O40" s="77"/>
-      <c r="P40" s="77"/>
-      <c r="Q40" s="77"/>
-      <c r="R40" s="77"/>
-      <c r="S40" s="77"/>
-      <c r="T40" s="77"/>
-      <c r="U40" s="77"/>
-      <c r="V40" s="77"/>
-      <c r="W40" s="77"/>
-      <c r="X40" s="77"/>
-      <c r="Y40" s="77"/>
-      <c r="Z40" s="77"/>
-      <c r="AA40" s="77"/>
-    </row>
-    <row r="41" spans="2:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="85" t="str">
+      <c r="C61" s="77"/>
+      <c r="D61" s="77"/>
+      <c r="E61" s="77"/>
+      <c r="F61" s="77"/>
+      <c r="G61" s="77"/>
+      <c r="H61" s="77"/>
+      <c r="I61" s="77"/>
+      <c r="J61" s="77"/>
+      <c r="K61" s="77"/>
+      <c r="L61" s="77"/>
+      <c r="M61" s="77"/>
+      <c r="N61" s="77"/>
+      <c r="O61" s="77"/>
+      <c r="P61" s="77"/>
+      <c r="Q61" s="77"/>
+      <c r="R61" s="77"/>
+      <c r="S61" s="77"/>
+      <c r="T61" s="77"/>
+      <c r="U61" s="77"/>
+      <c r="V61" s="77"/>
+      <c r="W61" s="77"/>
+      <c r="X61" s="77"/>
+      <c r="Y61" s="77"/>
+      <c r="Z61" s="77"/>
+      <c r="AA61" s="77"/>
+    </row>
+    <row r="62" spans="2:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B62" s="85" t="str">
         <f>"※ ①④ は実績のある全員 "&amp;COUNT(印刷用データ!AS3:AS62)&amp;" 名。「工程」が PKのみ の人は、その工程だけの標準時間 ÷ 実測時間です。②③ は両工程に実績のある "&amp;COUNT(印刷用データ!N3:N62)&amp;" 名。出典: 2026年4月 実績。"</f>
         <v>※ ①④ は実績のある全員 29 名。「工程」が PKのみ の人は、その工程だけの標準時間 ÷ 実測時間です。②③ は両工程に実績のある 19 名。出典: 2026年4月 実績。</v>
       </c>
-      <c r="C41" s="77"/>
-      <c r="D41" s="77"/>
-      <c r="E41" s="77"/>
-      <c r="F41" s="77"/>
-      <c r="G41" s="77"/>
-      <c r="H41" s="77"/>
-      <c r="I41" s="77"/>
-      <c r="J41" s="77"/>
-      <c r="K41" s="77"/>
-      <c r="L41" s="77"/>
-      <c r="M41" s="77"/>
-      <c r="N41" s="77"/>
-      <c r="O41" s="77"/>
-      <c r="P41" s="77"/>
-      <c r="Q41" s="77"/>
-      <c r="R41" s="77"/>
-      <c r="S41" s="77"/>
-      <c r="T41" s="77"/>
-      <c r="U41" s="77"/>
-      <c r="V41" s="77"/>
-      <c r="W41" s="77"/>
-      <c r="X41" s="77"/>
-      <c r="Y41" s="77"/>
-      <c r="Z41" s="77"/>
-      <c r="AA41" s="77"/>
+      <c r="C62" s="77"/>
+      <c r="D62" s="77"/>
+      <c r="E62" s="77"/>
+      <c r="F62" s="77"/>
+      <c r="G62" s="77"/>
+      <c r="H62" s="77"/>
+      <c r="I62" s="77"/>
+      <c r="J62" s="77"/>
+      <c r="K62" s="77"/>
+      <c r="L62" s="77"/>
+      <c r="M62" s="77"/>
+      <c r="N62" s="77"/>
+      <c r="O62" s="77"/>
+      <c r="P62" s="77"/>
+      <c r="Q62" s="77"/>
+      <c r="R62" s="77"/>
+      <c r="S62" s="77"/>
+      <c r="T62" s="77"/>
+      <c r="U62" s="77"/>
+      <c r="V62" s="77"/>
+      <c r="W62" s="77"/>
+      <c r="X62" s="77"/>
+      <c r="Y62" s="77"/>
+      <c r="Z62" s="77"/>
+      <c r="AA62" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B41:AA41"/>
-    <mergeCell ref="T19:AA19"/>
+    <mergeCell ref="B62:AA62"/>
+    <mergeCell ref="T26:AA26"/>
     <mergeCell ref="T1:AA1"/>
     <mergeCell ref="B1:R1"/>
     <mergeCell ref="T3:AA3"/>
-    <mergeCell ref="B40:AA40"/>
+    <mergeCell ref="B61:AA61"/>
   </mergeCells>
   <phoneticPr fontId="34"/>
-  <conditionalFormatting sqref="M5:M33">
-    <cfRule type="expression" dxfId="6" priority="1">
+  <conditionalFormatting sqref="M5:M54">
+    <cfRule type="expression" dxfId="7" priority="1" stopIfTrue="1">
+      <formula>$M5=""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M5:M54">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>AND($M5&lt;&gt;"",$M5&gt;4,$P5&lt;100)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
+++ b/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
@@ -60,6 +60,7 @@
     <definedName name="_s6y">OFFSET(散布図!$BK$8,0,0,MAX(1,COUNT(散布図!$BJ$8:$BJ$67)),1)</definedName>
     <definedName name="_s6z">OFFSET(散布図!$BL$8,0,0,MAX(1,COUNT(散布図!$BJ$8:$BJ$67)),1)</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">印刷用!$A$1:$AA$62</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">印刷用!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3289,7 +3290,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
@@ -3341,7 +3342,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
@@ -3393,7 +3394,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
@@ -3445,7 +3446,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
@@ -3497,7 +3498,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
@@ -3549,7 +3550,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
@@ -3601,7 +3602,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
@@ -3653,7 +3654,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
@@ -3705,7 +3706,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
@@ -3757,7 +3758,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
@@ -3809,7 +3810,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
@@ -3861,7 +3862,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
@@ -3913,7 +3914,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
@@ -3965,7 +3966,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
@@ -4017,7 +4018,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
@@ -4069,7 +4070,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
@@ -4121,7 +4122,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
@@ -4173,7 +4174,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
@@ -4225,7 +4226,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
@@ -4271,12 +4272,12 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
-              <c:dLblPos val="r"/>
+              <c:dLblPos val="b"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="0"/>
               <c:showCatName val="0"/>
@@ -4311,7 +4312,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
@@ -4351,12 +4352,12 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
-              <c:dLblPos val="r"/>
+              <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="0"/>
               <c:showCatName val="0"/>
@@ -4391,12 +4392,12 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
-              <c:dLblPos val="r"/>
+              <c:dLblPos val="l"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="0"/>
               <c:showCatName val="0"/>
@@ -4431,12 +4432,12 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
-              <c:dLblPos val="r"/>
+              <c:dLblPos val="b"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="0"/>
               <c:showCatName val="0"/>
@@ -4471,7 +4472,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
@@ -4511,12 +4512,12 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
-              <c:dLblPos val="r"/>
+              <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="0"/>
               <c:showCatName val="0"/>
@@ -4551,12 +4552,12 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
-              <c:dLblPos val="r"/>
+              <c:dLblPos val="l"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="0"/>
               <c:showCatName val="0"/>
@@ -4591,12 +4592,12 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
-              <c:dLblPos val="r"/>
+              <c:dLblPos val="b"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="0"/>
               <c:showCatName val="0"/>
@@ -4631,7 +4632,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
@@ -4671,12 +4672,12 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
-              <c:dLblPos val="r"/>
+              <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="0"/>
               <c:showCatName val="0"/>
@@ -4711,12 +4712,12 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
-              <c:dLblPos val="r"/>
+              <c:dLblPos val="l"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="0"/>
               <c:showCatName val="0"/>
@@ -4751,12 +4752,12 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
-              <c:dLblPos val="r"/>
+              <c:dLblPos val="b"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="0"/>
               <c:showCatName val="0"/>
@@ -4791,7 +4792,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
@@ -4831,12 +4832,12 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
-              <c:dLblPos val="r"/>
+              <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="0"/>
               <c:showCatName val="0"/>
@@ -4871,12 +4872,12 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
-              <c:dLblPos val="r"/>
+              <c:dLblPos val="l"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="0"/>
               <c:showCatName val="0"/>
@@ -4911,12 +4912,12 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
-              <c:dLblPos val="r"/>
+              <c:dLblPos val="b"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="0"/>
               <c:showCatName val="0"/>
@@ -4951,7 +4952,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
@@ -4991,12 +4992,12 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
-              <c:dLblPos val="r"/>
+              <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="0"/>
               <c:showCatName val="0"/>
@@ -5031,12 +5032,12 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
-              <c:dLblPos val="r"/>
+              <c:dLblPos val="l"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="0"/>
               <c:showCatName val="0"/>
@@ -5071,12 +5072,12 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
-              <c:dLblPos val="r"/>
+              <c:dLblPos val="b"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="0"/>
               <c:showCatName val="0"/>
@@ -5111,7 +5112,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
@@ -5151,12 +5152,12 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
-              <c:dLblPos val="r"/>
+              <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="0"/>
               <c:showCatName val="0"/>
@@ -5191,12 +5192,12 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
-              <c:dLblPos val="r"/>
+              <c:dLblPos val="l"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="0"/>
               <c:showCatName val="0"/>
@@ -5231,12 +5232,12 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
-              <c:dLblPos val="r"/>
+              <c:dLblPos val="b"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="0"/>
               <c:showCatName val="0"/>
@@ -5271,7 +5272,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
@@ -5311,12 +5312,12 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
-              <c:dLblPos val="r"/>
+              <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="0"/>
               <c:showCatName val="0"/>
@@ -5351,12 +5352,12 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
-              <c:dLblPos val="r"/>
+              <c:dLblPos val="l"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="0"/>
               <c:showCatName val="0"/>
@@ -5391,12 +5392,12 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
-              <c:dLblPos val="r"/>
+              <c:dLblPos val="b"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="0"/>
               <c:showCatName val="0"/>
@@ -5431,7 +5432,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
@@ -5471,12 +5472,12 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900"/>
+                    <a:defRPr sz="600"/>
                   </a:pPr>
                   <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
-              <c:dLblPos val="r"/>
+              <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="0"/>
               <c:showCatName val="0"/>
@@ -9676,7 +9677,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="800"/>
             </a:pPr>
             <a:endParaRPr lang="ja-JP"/>
           </a:p>
@@ -10661,13 +10662,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -10697,13 +10698,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -10733,13 +10734,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -10769,13 +10770,13 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -10832,13 +10833,13 @@
     <xdr:from>
       <xdr:col>20</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -10895,13 +10896,13 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -10958,13 +10959,13 @@
     <xdr:from>
       <xdr:col>20</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -27982,7 +27983,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="5" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="63"/>
       <c r="C5" s="63"/>
       <c r="D5" s="63"/>
@@ -28019,7 +28020,7 @@
         <v>ピッキング改善</v>
       </c>
     </row>
-    <row r="6" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="63"/>
       <c r="C6" s="63"/>
       <c r="D6" s="63"/>
@@ -28056,7 +28057,7 @@
         <v>両工程を見直し</v>
       </c>
     </row>
-    <row r="7" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="63"/>
       <c r="C7" s="63"/>
       <c r="D7" s="63"/>
@@ -28093,7 +28094,7 @@
         <v>両工程を見直し</v>
       </c>
     </row>
-    <row r="8" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="63"/>
       <c r="C8" s="63"/>
       <c r="D8" s="63"/>
@@ -28130,7 +28131,7 @@
         <v>ピッキング改善</v>
       </c>
     </row>
-    <row r="9" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="63"/>
       <c r="C9" s="63"/>
       <c r="D9" s="63"/>
@@ -28167,7 +28168,7 @@
         <v>両工程を見直し</v>
       </c>
     </row>
-    <row r="10" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="63"/>
       <c r="C10" s="63"/>
       <c r="D10" s="63"/>
@@ -28204,7 +28205,7 @@
         <v>ピッキング改善</v>
       </c>
     </row>
-    <row r="11" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="63"/>
       <c r="C11" s="63"/>
       <c r="D11" s="63"/>
@@ -28241,7 +28242,7 @@
         <v>ピッキング改善</v>
       </c>
     </row>
-    <row r="12" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="63"/>
       <c r="C12" s="63"/>
       <c r="D12" s="63"/>
@@ -28278,7 +28279,7 @@
         <v>ピッキング改善</v>
       </c>
     </row>
-    <row r="13" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="63"/>
       <c r="C13" s="63"/>
       <c r="D13" s="63"/>
@@ -28315,7 +28316,7 @@
         <v>梱包手順を改善</v>
       </c>
     </row>
-    <row r="14" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="63"/>
       <c r="C14" s="63"/>
       <c r="D14" s="63"/>
@@ -28352,7 +28353,7 @@
         <v>ピッキング改善</v>
       </c>
     </row>
-    <row r="15" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="63"/>
       <c r="C15" s="63"/>
       <c r="D15" s="63"/>
@@ -28389,7 +28390,7 @@
         <v>ピッキング改善</v>
       </c>
     </row>
-    <row r="16" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="63"/>
       <c r="C16" s="63"/>
       <c r="D16" s="63"/>
@@ -28426,7 +28427,7 @@
         <v>ピッキング改善</v>
       </c>
     </row>
-    <row r="17" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="63"/>
       <c r="C17" s="63"/>
       <c r="D17" s="63"/>
@@ -28462,8 +28463,19 @@
         <f>IFERROR(INDEX(印刷用データ!$AL$3:$AL$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,13),印刷用データ!$AM$3:$AM$62,0)),"")</f>
         <v>ピッキング改善</v>
       </c>
-    </row>
-    <row r="18" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T17" s="86" t="str">
+        <f>"③ 改善優先度マトリクス（両工程 "&amp;COUNT(印刷用データ!$N$3:$N$62)&amp;"名）"</f>
+        <v>③ 改善優先度マトリクス（両工程 19名）</v>
+      </c>
+      <c r="U17" s="77"/>
+      <c r="V17" s="77"/>
+      <c r="W17" s="77"/>
+      <c r="X17" s="77"/>
+      <c r="Y17" s="77"/>
+      <c r="Z17" s="77"/>
+      <c r="AA17" s="77"/>
+    </row>
+    <row r="18" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="63"/>
       <c r="C18" s="63"/>
       <c r="D18" s="63"/>
@@ -28500,7 +28512,7 @@
         <v>梱包手順を改善</v>
       </c>
     </row>
-    <row r="19" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="63"/>
       <c r="C19" s="63"/>
       <c r="D19" s="63"/>
@@ -28537,7 +28549,7 @@
         <v>梱包手順を改善</v>
       </c>
     </row>
-    <row r="20" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="63"/>
       <c r="C20" s="63"/>
       <c r="D20" s="63"/>
@@ -28574,7 +28586,7 @@
         <v>両工程を見直し</v>
       </c>
     </row>
-    <row r="21" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="63"/>
       <c r="C21" s="63"/>
       <c r="D21" s="63"/>
@@ -28611,7 +28623,7 @@
         <v>梱包手順を改善</v>
       </c>
     </row>
-    <row r="22" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="63"/>
       <c r="C22" s="63"/>
       <c r="D22" s="63"/>
@@ -28648,7 +28660,7 @@
         <v>梱包手順を改善</v>
       </c>
     </row>
-    <row r="23" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="63"/>
       <c r="C23" s="63"/>
       <c r="D23" s="63"/>
@@ -28685,7 +28697,7 @@
         <v>目標達成</v>
       </c>
     </row>
-    <row r="24" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="63"/>
       <c r="C24" s="63"/>
       <c r="D24" s="63"/>
@@ -28722,7 +28734,7 @@
         <v>梱包手順を改善</v>
       </c>
     </row>
-    <row r="25" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="63"/>
       <c r="C25" s="63"/>
       <c r="D25" s="63"/>
@@ -28759,7 +28771,7 @@
         <v>ピッキング改善</v>
       </c>
     </row>
-    <row r="26" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="63"/>
       <c r="C26" s="63"/>
       <c r="D26" s="63"/>
@@ -28795,19 +28807,8 @@
         <f>IFERROR(INDEX(印刷用データ!$AL$3:$AL$62,MATCH(SMALL(印刷用データ!$AM$3:$AM$62,22),印刷用データ!$AM$3:$AM$62,0)),"")</f>
         <v>ピッキング改善</v>
       </c>
-      <c r="T26" s="86" t="str">
-        <f>"③ 改善優先度マトリクス（両工程 "&amp;COUNT(印刷用データ!$N$3:$N$62)&amp;"名）"</f>
-        <v>③ 改善優先度マトリクス（両工程 19名）</v>
-      </c>
-      <c r="U26" s="77"/>
-      <c r="V26" s="77"/>
-      <c r="W26" s="77"/>
-      <c r="X26" s="77"/>
-      <c r="Y26" s="77"/>
-      <c r="Z26" s="77"/>
-      <c r="AA26" s="77"/>
-    </row>
-    <row r="27" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="27" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="63"/>
       <c r="C27" s="63"/>
       <c r="D27" s="63"/>
@@ -28844,7 +28845,7 @@
         <v>目標達成</v>
       </c>
     </row>
-    <row r="28" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="63"/>
       <c r="C28" s="63"/>
       <c r="D28" s="63"/>
@@ -28881,7 +28882,7 @@
         <v>目標達成</v>
       </c>
     </row>
-    <row r="29" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="63"/>
       <c r="C29" s="63"/>
       <c r="D29" s="63"/>
@@ -28918,7 +28919,7 @@
         <v>目標達成</v>
       </c>
     </row>
-    <row r="30" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="63"/>
       <c r="C30" s="63"/>
       <c r="D30" s="63"/>
@@ -28955,7 +28956,7 @@
         <v>目標達成</v>
       </c>
     </row>
-    <row r="31" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="63"/>
       <c r="C31" s="63"/>
       <c r="D31" s="63"/>
@@ -28992,7 +28993,7 @@
         <v>目標達成</v>
       </c>
     </row>
-    <row r="32" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="63"/>
       <c r="C32" s="63"/>
       <c r="D32" s="63"/>
@@ -29029,7 +29030,7 @@
         <v>目標達成</v>
       </c>
     </row>
-    <row r="33" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="63"/>
       <c r="C33" s="63"/>
       <c r="D33" s="63"/>
@@ -29066,7 +29067,7 @@
         <v>目標達成</v>
       </c>
     </row>
-    <row r="34" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="63"/>
       <c r="C34" s="63"/>
       <c r="D34" s="63"/>
@@ -29103,7 +29104,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="63"/>
       <c r="C35" s="63"/>
       <c r="D35" s="63"/>
@@ -29140,7 +29141,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="63"/>
       <c r="C36" s="63"/>
       <c r="D36" s="63"/>
@@ -29177,7 +29178,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="63"/>
       <c r="C37" s="63"/>
       <c r="D37" s="63"/>
@@ -29214,7 +29215,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="63"/>
       <c r="C38" s="63"/>
       <c r="D38" s="63"/>
@@ -29251,7 +29252,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="63"/>
       <c r="C39" s="63"/>
       <c r="D39" s="63"/>
@@ -29288,7 +29289,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="63"/>
       <c r="C40" s="63"/>
       <c r="D40" s="63"/>
@@ -29325,7 +29326,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="63"/>
       <c r="C41" s="63"/>
       <c r="D41" s="63"/>
@@ -29362,7 +29363,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="63"/>
       <c r="C42" s="63"/>
       <c r="D42" s="63"/>
@@ -29399,7 +29400,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="63"/>
       <c r="C43" s="63"/>
       <c r="D43" s="63"/>
@@ -29436,7 +29437,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="63"/>
       <c r="C44" s="63"/>
       <c r="D44" s="63"/>
@@ -29473,7 +29474,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="63"/>
       <c r="C45" s="63"/>
       <c r="D45" s="63"/>
@@ -29510,7 +29511,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="63"/>
       <c r="C46" s="63"/>
       <c r="D46" s="63"/>
@@ -29547,7 +29548,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="63"/>
       <c r="C47" s="63"/>
       <c r="D47" s="63"/>
@@ -29584,7 +29585,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B48" s="63"/>
       <c r="C48" s="63"/>
       <c r="D48" s="63"/>
@@ -29621,7 +29622,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="63"/>
       <c r="C49" s="63"/>
       <c r="D49" s="63"/>
@@ -29658,7 +29659,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="63"/>
       <c r="C50" s="63"/>
       <c r="D50" s="63"/>
@@ -29695,7 +29696,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="63"/>
       <c r="C51" s="63"/>
       <c r="D51" s="63"/>
@@ -29732,7 +29733,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B52" s="63"/>
       <c r="C52" s="63"/>
       <c r="D52" s="63"/>
@@ -29769,7 +29770,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="63"/>
       <c r="C53" s="63"/>
       <c r="D53" s="63"/>
@@ -29806,7 +29807,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="63"/>
       <c r="C54" s="63"/>
       <c r="D54" s="63"/>
@@ -29931,7 +29932,7 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B62:AA62"/>
-    <mergeCell ref="T26:AA26"/>
+    <mergeCell ref="T17:AA17"/>
     <mergeCell ref="T1:AA1"/>
     <mergeCell ref="B1:R1"/>
     <mergeCell ref="T3:AA3"/>
@@ -29950,7 +29951,10 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0" footer="0"/>
-  <pageSetup paperSize="8" orientation="landscape" fitToWidth="1" fitToHeight="1" horizontalDpi="600" verticalDpi="600"/>
+  <pageSetup paperSize="8" orientation="landscape" fitToWidth="1" fitToHeight="2" horizontalDpi="600" verticalDpi="600"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="36" max="16383" man="1"/>
+  </rowBreaks>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>

--- a/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
+++ b/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
@@ -3250,7 +3250,15 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>担当者</c:v>
+            <c:strRef>
+              <c:f>印刷用データ!$K$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>本吉有美子</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
             <a:ln>
@@ -3271,2396 +3279,3754 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
-            <c:dLbl>
-              <c:idx val="0"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$3</c:f>
-                  <c:strCache>
-                    <c:ptCount val="1"/>
-                    <c:pt idx="0">
-                      <c:v>本吉有美子</c:v>
-                    </c:pt>
-                  </c:strCache>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="r"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{3232EA5B-5E5E-4759-9243-2C8B7ED71FAF}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$3</c15:f>
-                      <c15:dlblFieldTableCache>
-                        <c:ptCount val="1"/>
-                        <c:pt idx="0">
-                          <c:v>本吉有美子</c:v>
-                        </c:pt>
-                      </c15:dlblFieldTableCache>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000000-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="1"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$4</c:f>
-                  <c:strCache>
-                    <c:ptCount val="1"/>
-                    <c:pt idx="0">
-                      <c:v>澤田凌</c:v>
-                    </c:pt>
-                  </c:strCache>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="b"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{BF451EBA-EE08-4C16-B64B-B12A9C3DB19B}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$4</c15:f>
-                      <c15:dlblFieldTableCache>
-                        <c:ptCount val="1"/>
-                        <c:pt idx="0">
-                          <c:v>澤田凌</c:v>
-                        </c:pt>
-                      </c15:dlblFieldTableCache>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000001-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="2"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$5</c:f>
-                  <c:strCache>
-                    <c:ptCount val="1"/>
-                    <c:pt idx="0">
-                      <c:v>大江美記子</c:v>
-                    </c:pt>
-                  </c:strCache>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="l"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{83BFFDEF-22F1-429C-B1BB-706DDA648402}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$5</c15:f>
-                      <c15:dlblFieldTableCache>
-                        <c:ptCount val="1"/>
-                        <c:pt idx="0">
-                          <c:v>大江美記子</c:v>
-                        </c:pt>
-                      </c15:dlblFieldTableCache>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000002-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="3"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$6</c:f>
-                  <c:strCache>
-                    <c:ptCount val="1"/>
-                    <c:pt idx="0">
-                      <c:v>佐藤辰成</c:v>
-                    </c:pt>
-                  </c:strCache>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="r"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{B9882535-D73F-43A9-B7EA-41222C5C892E}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$6</c15:f>
-                      <c15:dlblFieldTableCache>
-                        <c:ptCount val="1"/>
-                        <c:pt idx="0">
-                          <c:v>佐藤辰成</c:v>
-                        </c:pt>
-                      </c15:dlblFieldTableCache>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000003-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="4"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$7</c:f>
-                  <c:strCache>
-                    <c:ptCount val="1"/>
-                    <c:pt idx="0">
-                      <c:v>後藤克行</c:v>
-                    </c:pt>
-                  </c:strCache>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="l"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{C09CEFB4-250C-4F91-96F1-8049E497CC4F}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$7</c15:f>
-                      <c15:dlblFieldTableCache>
-                        <c:ptCount val="1"/>
-                        <c:pt idx="0">
-                          <c:v>後藤克行</c:v>
-                        </c:pt>
-                      </c15:dlblFieldTableCache>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000004-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="5"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$8</c:f>
-                  <c:strCache>
-                    <c:ptCount val="1"/>
-                    <c:pt idx="0">
-                      <c:v>中村美佳</c:v>
-                    </c:pt>
-                  </c:strCache>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="t"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{D8A764C5-8E5A-4A83-A961-8A5EC71609FC}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$8</c15:f>
-                      <c15:dlblFieldTableCache>
-                        <c:ptCount val="1"/>
-                        <c:pt idx="0">
-                          <c:v>中村美佳</c:v>
-                        </c:pt>
-                      </c15:dlblFieldTableCache>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000005-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="6"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$9</c:f>
-                  <c:strCache>
-                    <c:ptCount val="1"/>
-                    <c:pt idx="0">
-                      <c:v>晩田恵美</c:v>
-                    </c:pt>
-                  </c:strCache>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="l"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{AA367976-211C-4B01-94A2-18DA97FC9A19}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$9</c15:f>
-                      <c15:dlblFieldTableCache>
-                        <c:ptCount val="1"/>
-                        <c:pt idx="0">
-                          <c:v>晩田恵美</c:v>
-                        </c:pt>
-                      </c15:dlblFieldTableCache>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000006-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="7"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$10</c:f>
-                  <c:strCache>
-                    <c:ptCount val="1"/>
-                    <c:pt idx="0">
-                      <c:v>高橋佐織</c:v>
-                    </c:pt>
-                  </c:strCache>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="t"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{5542C6B9-F688-404C-A75B-BB7E89822EB6}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$10</c15:f>
-                      <c15:dlblFieldTableCache>
-                        <c:ptCount val="1"/>
-                        <c:pt idx="0">
-                          <c:v>高橋佐織</c:v>
-                        </c:pt>
-                      </c15:dlblFieldTableCache>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000007-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="8"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$11</c:f>
-                  <c:strCache>
-                    <c:ptCount val="1"/>
-                    <c:pt idx="0">
-                      <c:v>山本祥吉</c:v>
-                    </c:pt>
-                  </c:strCache>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="r"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{C0832A6B-B5EB-4C8B-B10C-CAEE41C831F3}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$11</c15:f>
-                      <c15:dlblFieldTableCache>
-                        <c:ptCount val="1"/>
-                        <c:pt idx="0">
-                          <c:v>山本祥吉</c:v>
-                        </c:pt>
-                      </c15:dlblFieldTableCache>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000008-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="9"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$12</c:f>
-                  <c:strCache>
-                    <c:ptCount val="1"/>
-                    <c:pt idx="0">
-                      <c:v>佐々木千恵</c:v>
-                    </c:pt>
-                  </c:strCache>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="t"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{8DE6A35B-607B-4781-B5EB-CDF1F24E0F84}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$12</c15:f>
-                      <c15:dlblFieldTableCache>
-                        <c:ptCount val="1"/>
-                        <c:pt idx="0">
-                          <c:v>佐々木千恵</c:v>
-                        </c:pt>
-                      </c15:dlblFieldTableCache>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000009-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="10"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$13</c:f>
-                  <c:strCache>
-                    <c:ptCount val="1"/>
-                    <c:pt idx="0">
-                      <c:v>北田倫子</c:v>
-                    </c:pt>
-                  </c:strCache>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="t"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{E183E4AE-30AE-449E-B036-7BF5900978B3}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$13</c15:f>
-                      <c15:dlblFieldTableCache>
-                        <c:ptCount val="1"/>
-                        <c:pt idx="0">
-                          <c:v>北田倫子</c:v>
-                        </c:pt>
-                      </c15:dlblFieldTableCache>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000A-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="11"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$14</c:f>
-                  <c:strCache>
-                    <c:ptCount val="1"/>
-                    <c:pt idx="0">
-                      <c:v>中納沙織</c:v>
-                    </c:pt>
-                  </c:strCache>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="b"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{C1AE3F55-9F9B-46AB-B0AF-156488203905}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$14</c15:f>
-                      <c15:dlblFieldTableCache>
-                        <c:ptCount val="1"/>
-                        <c:pt idx="0">
-                          <c:v>中納沙織</c:v>
-                        </c:pt>
-                      </c15:dlblFieldTableCache>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000B-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="12"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$15</c:f>
-                  <c:strCache>
-                    <c:ptCount val="1"/>
-                    <c:pt idx="0">
-                      <c:v>森田美加</c:v>
-                    </c:pt>
-                  </c:strCache>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="l"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{07D0962E-079E-4F07-902F-F4935EE8222B}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$15</c15:f>
-                      <c15:dlblFieldTableCache>
-                        <c:ptCount val="1"/>
-                        <c:pt idx="0">
-                          <c:v>森田美加</c:v>
-                        </c:pt>
-                      </c15:dlblFieldTableCache>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000C-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="13"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$16</c:f>
-                  <c:strCache>
-                    <c:ptCount val="1"/>
-                    <c:pt idx="0">
-                      <c:v>河野忠</c:v>
-                    </c:pt>
-                  </c:strCache>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="r"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{EF0DA3B8-14A8-4650-A8BB-91AFD94348CF}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$16</c15:f>
-                      <c15:dlblFieldTableCache>
-                        <c:ptCount val="1"/>
-                        <c:pt idx="0">
-                          <c:v>河野忠</c:v>
-                        </c:pt>
-                      </c15:dlblFieldTableCache>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000D-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="14"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$17</c:f>
-                  <c:strCache>
-                    <c:ptCount val="1"/>
-                    <c:pt idx="0">
-                      <c:v>木村千鶴</c:v>
-                    </c:pt>
-                  </c:strCache>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="l"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{C3141AB3-8532-4590-9CC1-E9EED6E5D330}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$17</c15:f>
-                      <c15:dlblFieldTableCache>
-                        <c:ptCount val="1"/>
-                        <c:pt idx="0">
-                          <c:v>木村千鶴</c:v>
-                        </c:pt>
-                      </c15:dlblFieldTableCache>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000E-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="15"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$18</c:f>
-                  <c:strCache>
-                    <c:ptCount val="1"/>
-                    <c:pt idx="0">
-                      <c:v>鈴木香織</c:v>
-                    </c:pt>
-                  </c:strCache>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="l"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{6C453BA4-8B4C-45F6-8767-49A1253B0AEF}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$18</c15:f>
-                      <c15:dlblFieldTableCache>
-                        <c:ptCount val="1"/>
-                        <c:pt idx="0">
-                          <c:v>鈴木香織</c:v>
-                        </c:pt>
-                      </c15:dlblFieldTableCache>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000F-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="16"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$19</c:f>
-                  <c:strCache>
-                    <c:ptCount val="1"/>
-                    <c:pt idx="0">
-                      <c:v>森本久美</c:v>
-                    </c:pt>
-                  </c:strCache>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="l"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{D945B2C5-5ACB-48EC-9500-0683DA6D2A08}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$19</c15:f>
-                      <c15:dlblFieldTableCache>
-                        <c:ptCount val="1"/>
-                        <c:pt idx="0">
-                          <c:v>森本久美</c:v>
-                        </c:pt>
-                      </c15:dlblFieldTableCache>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000010-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="17"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$20</c:f>
-                  <c:strCache>
-                    <c:ptCount val="1"/>
-                    <c:pt idx="0">
-                      <c:v>菊池敬</c:v>
-                    </c:pt>
-                  </c:strCache>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="l"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{85B7640A-A446-45AC-8D61-F0C998DE4300}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$20</c15:f>
-                      <c15:dlblFieldTableCache>
-                        <c:ptCount val="1"/>
-                        <c:pt idx="0">
-                          <c:v>菊池敬</c:v>
-                        </c:pt>
-                      </c15:dlblFieldTableCache>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000011-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="18"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$21</c:f>
-                  <c:strCache>
-                    <c:ptCount val="1"/>
-                    <c:pt idx="0">
-                      <c:v>飯田由加里</c:v>
-                    </c:pt>
-                  </c:strCache>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="l"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{F0FE5FEB-0222-472A-9CED-3CA984D80127}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$21</c15:f>
-                      <c15:dlblFieldTableCache>
-                        <c:ptCount val="1"/>
-                        <c:pt idx="0">
-                          <c:v>飯田由加里</c:v>
-                        </c:pt>
-                      </c15:dlblFieldTableCache>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000012-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="19"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$22</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="b"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000019-0000-4000-8000-000000000019}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$22</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000013-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="20"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$23</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="r"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000020-0000-4000-8000-000000000020}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$23</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000014-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="21"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$24</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="t"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000021-0000-4000-8000-000000000021}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$24</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000015-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="22"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$25</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="l"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000022-0000-4000-8000-000000000022}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$25</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000016-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="23"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$26</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="b"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000023-0000-4000-8000-000000000023}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$26</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000017-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="24"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$27</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="r"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000024-0000-4000-8000-000000000024}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$27</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000018-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="25"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$28</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="t"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000025-0000-4000-8000-000000000025}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$28</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000019-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="26"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$29</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="l"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000026-0000-4000-8000-000000000026}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$29</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001A-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="27"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$30</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="b"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000027-0000-4000-8000-000000000027}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$30</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001B-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="28"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$31</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="r"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000028-0000-4000-8000-000000000028}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$31</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001C-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="29"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$32</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="t"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000029-0000-4000-8000-000000000029}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$32</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001D-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="30"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$33</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="l"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000030-0000-4000-8000-000000000030}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$33</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001E-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="31"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$34</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="b"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000031-0000-4000-8000-000000000031}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$34</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000001F-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="32"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$35</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="r"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000032-0000-4000-8000-000000000032}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$35</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000020-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="33"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$36</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="t"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000033-0000-4000-8000-000000000033}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$36</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000021-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="34"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$37</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="l"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000034-0000-4000-8000-000000000034}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$37</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000022-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="35"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$38</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="b"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000035-0000-4000-8000-000000000035}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$38</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000023-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="36"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$39</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="r"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000036-0000-4000-8000-000000000036}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$39</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000024-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="37"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$40</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="t"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000037-0000-4000-8000-000000000037}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$40</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000025-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="38"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$41</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="l"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000038-0000-4000-8000-000000000038}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$41</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000026-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="39"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$42</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="b"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000039-0000-4000-8000-000000000039}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$42</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000027-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="40"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$43</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="r"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000040-0000-4000-8000-000000000040}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$43</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000028-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="41"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$44</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="t"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000041-0000-4000-8000-000000000041}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$44</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000029-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="42"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$45</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="l"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000042-0000-4000-8000-000000000042}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$45</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002A-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="43"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$46</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="b"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000043-0000-4000-8000-000000000043}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$46</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002B-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="44"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$47</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="r"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000044-0000-4000-8000-000000000044}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$47</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002C-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="45"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$48</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="t"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000045-0000-4000-8000-000000000045}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$48</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002D-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="46"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$49</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="l"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000046-0000-4000-8000-000000000046}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$49</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002E-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="47"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$50</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="b"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000047-0000-4000-8000-000000000047}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$50</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000002F-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="48"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$51</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="r"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000048-0000-4000-8000-000000000048}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$51</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000030-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="49"/>
-              <c:tx>
-                <c:strRef>
-                  <c:f>印刷用データ!$K$52</c:f>
-                </c:strRef>
-              </c:tx>
-              <c:spPr/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="600"/>
-                  </a:pPr>
-                  <a:endParaRPr lang="ja-JP"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="t"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable>
-                    <c15:dlblFTEntry>
-                      <c15:txfldGUID>{PR000049-0000-4000-8000-000000000049}</c15:txfldGUID>
-                      <c15:f>印刷用データ!$K$52</c15:f>
-                    </c15:dlblFTEntry>
-                  </c15:dlblFieldTable>
-                  <c15:showDataLabelsRange val="0"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000031-9A3E-489E-9801-55C342B48382}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
             <c:spPr>
               <a:noFill/>
               <a:ln>
                 <a:noFill/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="1"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>印刷用データ!$L$3:$L$52</c:f>
+              <c:f>印刷用データ!$L$3</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>136.58407297830374</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>138.51606425702809</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>128.62508143322475</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>131.80246913580245</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>111.60069735006972</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>121.32499999999997</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>108.44019316493313</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>106.8047477744807</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>106.22178879910837</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>106.39972273567466</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>101.99950049950048</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>101.71352549889134</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>98.221111111111114</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>98.116847826086968</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>99.64362464183381</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>96.542574257425741</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>81.891759776536304</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>85.862631578947358</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>74.630235602094231</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>印刷用データ!$M$3:$M$52</c:f>
+              <c:f>印刷用データ!$M$3</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>149.67602924201614</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>72.980283224400878</c:v>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>澤田凌</c:v>
                 </c:pt>
-                <c:pt idx="2">
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$4</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>138.5160642570281</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$4</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>72.98028322440088</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>大江美記子</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$5</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>128.62508143322475</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$5</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>132.88643790849673</c:v>
                 </c:pt>
-                <c:pt idx="3">
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>佐藤辰成</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="b"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$6</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>131.80246913580245</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$6</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>132.51857923497266</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>80.326509661835729</c:v>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>後藤克行</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>81.792465753424665</c:v>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="b"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>111.60069735006972</c:v>
                 </c:pt>
-                <c:pt idx="6">
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>80.32650966183573</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>中村美佳</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$8</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>121.32499999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$8</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>81.79246575342466</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>晩田恵美</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>108.44019316493313</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>121.13147824640211</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>93.863706034204569</c:v>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>高橋佐織</c:v>
                 </c:pt>
-                <c:pt idx="8">
-                  <c:v>84.736739745403099</c:v>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="b"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$10</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>106.8047477744807</c:v>
                 </c:pt>
-                <c:pt idx="9">
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$10</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>93.86370603420457</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>山本祥吉</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="b"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>106.22178879910837</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>84.7367397454031</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>佐々木千恵</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$12</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>106.39972273567466</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$12</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>171.96125541125542</c:v>
                 </c:pt>
-                <c:pt idx="10">
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="10"/>
+          <c:order val="10"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>北田倫子</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>101.99950049950048</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>136.2250663632916</c:v>
                 </c:pt>
-                <c:pt idx="11">
-                  <c:v>66.904561403508765</c:v>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="11"/>
+          <c:order val="11"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>中納沙織</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>52.277377892030849</c:v>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$14</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>101.71352549889134</c:v>
                 </c:pt>
-                <c:pt idx="13">
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$14</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>66.90456140350877</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="12"/>
+          <c:order val="12"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>森田美加</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$15</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>98.22111111111111</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$15</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>52.27737789203085</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="13"/>
+          <c:order val="13"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$16</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>河野忠</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$16</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>98.11684782608697</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$16</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>116.41046228710461</c:v>
                 </c:pt>
-                <c:pt idx="14">
-                  <c:v>71.829549454417446</c:v>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="14"/>
+          <c:order val="14"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$17</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>木村千鶴</c:v>
                 </c:pt>
-                <c:pt idx="15">
-                  <c:v>97.378246753246756</c:v>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="b"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$17</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>99.64362464183381</c:v>
                 </c:pt>
-                <c:pt idx="16">
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$17</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>71.82954945441745</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="15"/>
+          <c:order val="15"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$18</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>鈴木香織</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$18</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>96.54257425742574</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$18</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>97.37824675324676</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="16"/>
+          <c:order val="16"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>森本久美</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$19</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>81.8917597765363</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$19</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>100.98448866067606</c:v>
                 </c:pt>
-                <c:pt idx="17">
-                  <c:v>65.703477177483293</c:v>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="17"/>
+          <c:order val="17"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>菊池敬</c:v>
                 </c:pt>
-                <c:pt idx="18">
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$20</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>85.86263157894736</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$20</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>65.7034771774833</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="18"/>
+          <c:order val="18"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>飯田由加里</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$21</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>74.63023560209423</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$21</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>129.17098681218735</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000013-9A3E-489E-9801-55C342B48382}"/>
-            </c:ext>
-          </c:extLst>
+          <c:smooth val="0"/>
         </c:ser>
         <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
+          <c:idx val="19"/>
+          <c:order val="19"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$22</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="l"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$22</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$22</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="20"/>
+          <c:order val="20"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$23</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$23</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$23</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="21"/>
+          <c:order val="21"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$24</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="b"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$24</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$24</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="22"/>
+          <c:order val="22"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$25</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$25</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$25</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="23"/>
+          <c:order val="23"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$26</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="l"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$26</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$26</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="24"/>
+          <c:order val="24"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$27</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$27</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$27</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="25"/>
+          <c:order val="25"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$28</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="b"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$28</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$28</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="26"/>
+          <c:order val="26"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$29</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$29</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$29</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="27"/>
+          <c:order val="27"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$30</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="l"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$30</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$30</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="28"/>
+          <c:order val="28"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$31</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$31</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$31</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="29"/>
+          <c:order val="29"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$32</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="b"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$32</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$32</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="30"/>
+          <c:order val="30"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$33</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$33</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$33</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="31"/>
+          <c:order val="31"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$34</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="l"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$34</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$34</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="32"/>
+          <c:order val="32"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$35</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$35</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$35</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="33"/>
+          <c:order val="33"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$36</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="b"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$36</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$36</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="34"/>
+          <c:order val="34"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$37</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$37</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$37</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="35"/>
+          <c:order val="35"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$38</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="l"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$38</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$38</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="36"/>
+          <c:order val="36"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$39</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$39</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$39</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="37"/>
+          <c:order val="37"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$40</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="b"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$40</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$40</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="38"/>
+          <c:order val="38"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$41</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$41</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$41</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="39"/>
+          <c:order val="39"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$42</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="l"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$42</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$42</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="40"/>
+          <c:order val="40"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$43</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$43</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$43</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="41"/>
+          <c:order val="41"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$44</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="b"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$44</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$44</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="42"/>
+          <c:order val="42"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$45</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$45</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$45</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="43"/>
+          <c:order val="43"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$46</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="l"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$46</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$46</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="44"/>
+          <c:order val="44"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$47</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$47</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$47</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="45"/>
+          <c:order val="45"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$48</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="b"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$48</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$48</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="46"/>
+          <c:order val="46"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$49</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$49</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$49</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="47"/>
+          <c:order val="47"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$50</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="l"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$50</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$50</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="48"/>
+          <c:order val="48"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$51</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$51</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$51</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="49"/>
+          <c:order val="49"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$K$52</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="600"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="b"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$L$52</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$M$52</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="50"/>
+          <c:order val="50"/>
           <c:tx>
             <c:v>基準線(縦)</c:v>
           </c:tx>
@@ -5713,8 +7079,8 @@
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
+          <c:idx val="51"/>
+          <c:order val="51"/>
           <c:tx>
             <c:v>基準線(横)</c:v>
           </c:tx>

--- a/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
+++ b/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
@@ -23107,13 +23107,13 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:BC62"/>
+  <dimension ref="A1:BD62"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="55" width="11" customWidth="1"/>
+    <col min="1" max="56" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A1" s="60" t="s">
         <v>0</v>
       </c>
@@ -23150,7 +23150,7 @@
         </is>
       </c>
     </row>
-    <row r="2" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A2" s="39" t="s">
         <v>428</v>
       </c>
@@ -23304,6 +23304,11 @@
           <t>片方通番</t>
         </is>
       </c>
+      <c r="BD2" s="39" t="inlineStr">
+        <is>
+          <t>軸外</t>
+        </is>
+      </c>
       <c r="AZ2" s="39">
         <v>10</v>
       </c>
@@ -23317,7 +23322,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A3" s="61" t="str">
         <f>IF(ピッキング!$B$7="","",ピッキング!$B$7)</f>
         <v>本吉有美子</v>
@@ -23520,8 +23525,12 @@
       <c r="BC3" s="39">
         <v>190</v>
       </c>
-    </row>
-    <row r="4" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD3" s="62">
+        <f>IF($AG3="","",IF(OR(AND(ISNUMBER($AH3),OR($AH3&lt;10,$AH3&gt;190)),AND(ISNUMBER($AI3),OR($AI3&lt;10,$AI3&gt;190))),1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A4" s="61" t="str">
         <f>IF(ピッキング!$B$8="","",ピッキング!$B$8)</f>
         <v>澤田凌</v>
@@ -23700,8 +23709,12 @@
         <f>IF($AK4="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH4)+1,IF($AK4="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI4)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="5" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD4" s="62">
+        <f>IF($AG4="","",IF(OR(AND(ISNUMBER($AH4),OR($AH4&lt;10,$AH4&gt;190)),AND(ISNUMBER($AI4),OR($AI4&lt;10,$AI4&gt;190))),1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A5" s="61" t="str">
         <f>IF(ピッキング!$B$9="","",ピッキング!$B$9)</f>
         <v>大江美記子</v>
@@ -23880,8 +23893,12 @@
         <f>IF($AK5="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH5)+1,IF($AK5="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI5)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="6" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD5" s="62">
+        <f>IF($AG5="","",IF(OR(AND(ISNUMBER($AH5),OR($AH5&lt;10,$AH5&gt;190)),AND(ISNUMBER($AI5),OR($AI5&lt;10,$AI5&gt;190))),1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A6" s="61" t="str">
         <f>IF(ピッキング!$B$10="","",ピッキング!$B$10)</f>
         <v>佐藤辰成</v>
@@ -24060,8 +24077,12 @@
         <f>IF($AK6="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH6)+1,IF($AK6="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI6)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="7" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD6" s="62">
+        <f>IF($AG6="","",IF(OR(AND(ISNUMBER($AH6),OR($AH6&lt;10,$AH6&gt;190)),AND(ISNUMBER($AI6),OR($AI6&lt;10,$AI6&gt;190))),1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A7" s="61" t="str">
         <f>IF(ピッキング!$B$11="","",ピッキング!$B$11)</f>
         <v>春谷智子</v>
@@ -24240,8 +24261,12 @@
         <f>IF($AK7="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH7)+1,IF($AK7="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI7)+1,""))</f>
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD7" s="62">
+        <f>IF($AG7="","",IF(OR(AND(ISNUMBER($AH7),OR($AH7&lt;10,$AH7&gt;190)),AND(ISNUMBER($AI7),OR($AI7&lt;10,$AI7&gt;190))),1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A8" s="61" t="str">
         <f>IF(ピッキング!$B$12="","",ピッキング!$B$12)</f>
         <v>後藤克行</v>
@@ -24420,8 +24445,12 @@
         <f>IF($AK8="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH8)+1,IF($AK8="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI8)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="9" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD8" s="62">
+        <f>IF($AG8="","",IF(OR(AND(ISNUMBER($AH8),OR($AH8&lt;10,$AH8&gt;190)),AND(ISNUMBER($AI8),OR($AI8&lt;10,$AI8&gt;190))),1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A9" s="61" t="str">
         <f>IF(ピッキング!$B$13="","",ピッキング!$B$13)</f>
         <v>中村美佳</v>
@@ -24600,8 +24629,12 @@
         <f>IF($AK9="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH9)+1,IF($AK9="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI9)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="10" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD9" s="62">
+        <f>IF($AG9="","",IF(OR(AND(ISNUMBER($AH9),OR($AH9&lt;10,$AH9&gt;190)),AND(ISNUMBER($AI9),OR($AI9&lt;10,$AI9&gt;190))),1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A10" s="61" t="str">
         <f>IF(ピッキング!$B$14="","",ピッキング!$B$14)</f>
         <v>晩田恵美</v>
@@ -24780,8 +24813,12 @@
         <f>IF($AK10="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH10)+1,IF($AK10="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI10)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="11" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD10" s="62">
+        <f>IF($AG10="","",IF(OR(AND(ISNUMBER($AH10),OR($AH10&lt;10,$AH10&gt;190)),AND(ISNUMBER($AI10),OR($AI10&lt;10,$AI10&gt;190))),1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A11" s="61" t="str">
         <f>IF(ピッキング!$B$15="","",ピッキング!$B$15)</f>
         <v>高橋佐織</v>
@@ -24960,8 +24997,12 @@
         <f>IF($AK11="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH11)+1,IF($AK11="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI11)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="12" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD11" s="62">
+        <f>IF($AG11="","",IF(OR(AND(ISNUMBER($AH11),OR($AH11&lt;10,$AH11&gt;190)),AND(ISNUMBER($AI11),OR($AI11&lt;10,$AI11&gt;190))),1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A12" s="61" t="str">
         <f>IF(ピッキング!$B$16="","",ピッキング!$B$16)</f>
         <v>山本祥吉</v>
@@ -25140,8 +25181,12 @@
         <f>IF($AK12="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH12)+1,IF($AK12="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI12)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="13" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD12" s="62">
+        <f>IF($AG12="","",IF(OR(AND(ISNUMBER($AH12),OR($AH12&lt;10,$AH12&gt;190)),AND(ISNUMBER($AI12),OR($AI12&lt;10,$AI12&gt;190))),1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A13" s="61" t="str">
         <f>IF(ピッキング!$B$17="","",ピッキング!$B$17)</f>
         <v>佐々木千恵</v>
@@ -25320,8 +25365,12 @@
         <f>IF($AK13="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH13)+1,IF($AK13="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI13)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="14" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD13" s="62">
+        <f>IF($AG13="","",IF(OR(AND(ISNUMBER($AH13),OR($AH13&lt;10,$AH13&gt;190)),AND(ISNUMBER($AI13),OR($AI13&lt;10,$AI13&gt;190))),1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A14" s="61" t="str">
         <f>IF(ピッキング!$B$18="","",ピッキング!$B$18)</f>
         <v>北田倫子</v>
@@ -25500,8 +25549,12 @@
         <f>IF($AK14="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH14)+1,IF($AK14="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI14)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="15" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD14" s="62">
+        <f>IF($AG14="","",IF(OR(AND(ISNUMBER($AH14),OR($AH14&lt;10,$AH14&gt;190)),AND(ISNUMBER($AI14),OR($AI14&lt;10,$AI14&gt;190))),1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A15" s="61" t="str">
         <f>IF(ピッキング!$B$19="","",ピッキング!$B$19)</f>
         <v>中納沙織</v>
@@ -25680,8 +25733,12 @@
         <f>IF($AK15="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH15)+1,IF($AK15="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI15)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="16" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD15" s="62">
+        <f>IF($AG15="","",IF(OR(AND(ISNUMBER($AH15),OR($AH15&lt;10,$AH15&gt;190)),AND(ISNUMBER($AI15),OR($AI15&lt;10,$AI15&gt;190))),1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A16" s="61" t="str">
         <f>IF(ピッキング!$B$20="","",ピッキング!$B$20)</f>
         <v>石戸谷亜子</v>
@@ -25860,8 +25917,12 @@
         <f>IF($AK16="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH16)+1,IF($AK16="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI16)+1,""))</f>
         <v>9</v>
       </c>
-    </row>
-    <row r="17" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD16" s="62">
+        <f>IF($AG16="","",IF(OR(AND(ISNUMBER($AH16),OR($AH16&lt;10,$AH16&gt;190)),AND(ISNUMBER($AI16),OR($AI16&lt;10,$AI16&gt;190))),1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A17" s="61" t="str">
         <f>IF(ピッキング!$B$21="","",ピッキング!$B$21)</f>
         <v>森田美加</v>
@@ -26040,8 +26101,12 @@
         <f>IF($AK17="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH17)+1,IF($AK17="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI17)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="18" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD17" s="62">
+        <f>IF($AG17="","",IF(OR(AND(ISNUMBER($AH17),OR($AH17&lt;10,$AH17&gt;190)),AND(ISNUMBER($AI17),OR($AI17&lt;10,$AI17&gt;190))),1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A18" s="61" t="str">
         <f>IF(ピッキング!$B$22="","",ピッキング!$B$22)</f>
         <v>河野忠</v>
@@ -26220,8 +26285,12 @@
         <f>IF($AK18="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH18)+1,IF($AK18="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI18)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="19" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD18" s="62">
+        <f>IF($AG18="","",IF(OR(AND(ISNUMBER($AH18),OR($AH18&lt;10,$AH18&gt;190)),AND(ISNUMBER($AI18),OR($AI18&lt;10,$AI18&gt;190))),1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A19" s="61" t="str">
         <f>IF(ピッキング!$B$23="","",ピッキング!$B$23)</f>
         <v>木村千鶴</v>
@@ -26400,8 +26469,12 @@
         <f>IF($AK19="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH19)+1,IF($AK19="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI19)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="20" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD19" s="62">
+        <f>IF($AG19="","",IF(OR(AND(ISNUMBER($AH19),OR($AH19&lt;10,$AH19&gt;190)),AND(ISNUMBER($AI19),OR($AI19&lt;10,$AI19&gt;190))),1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A20" s="61" t="str">
         <f>IF(ピッキング!$B$24="","",ピッキング!$B$24)</f>
         <v>奥野愛海</v>
@@ -26580,8 +26653,12 @@
         <f>IF($AK20="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH20)+1,IF($AK20="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI20)+1,""))</f>
         <v>8</v>
       </c>
-    </row>
-    <row r="21" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD20" s="62">
+        <f>IF($AG20="","",IF(OR(AND(ISNUMBER($AH20),OR($AH20&lt;10,$AH20&gt;190)),AND(ISNUMBER($AI20),OR($AI20&lt;10,$AI20&gt;190))),1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A21" s="61" t="str">
         <f>IF(ピッキング!$B$25="","",ピッキング!$B$25)</f>
         <v>鈴木香織</v>
@@ -26760,8 +26837,12 @@
         <f>IF($AK21="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH21)+1,IF($AK21="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI21)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="22" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD21" s="62">
+        <f>IF($AG21="","",IF(OR(AND(ISNUMBER($AH21),OR($AH21&lt;10,$AH21&gt;190)),AND(ISNUMBER($AI21),OR($AI21&lt;10,$AI21&gt;190))),1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A22" s="61" t="str">
         <f>IF(ピッキング!$B$26="","",ピッキング!$B$26)</f>
         <v>向井ひかり</v>
@@ -26940,8 +27021,12 @@
         <f>IF($AK22="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH22)+1,IF($AK22="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI22)+1,""))</f>
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD22" s="62">
+        <f>IF($AG22="","",IF(OR(AND(ISNUMBER($AH22),OR($AH22&lt;10,$AH22&gt;190)),AND(ISNUMBER($AI22),OR($AI22&lt;10,$AI22&gt;190))),1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A23" s="61" t="str">
         <f>IF(ピッキング!$B$27="","",ピッキング!$B$27)</f>
         <v>片岡達也</v>
@@ -27120,8 +27205,12 @@
         <f>IF($AK23="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH23)+1,IF($AK23="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI23)+1,""))</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD23" s="62">
+        <f>IF($AG23="","",IF(OR(AND(ISNUMBER($AH23),OR($AH23&lt;10,$AH23&gt;190)),AND(ISNUMBER($AI23),OR($AI23&lt;10,$AI23&gt;190))),1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A24" s="61" t="str">
         <f>IF(ピッキング!$B$28="","",ピッキング!$B$28)</f>
         <v>廣瀬こずえ</v>
@@ -27300,8 +27389,12 @@
         <f>IF($AK24="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH24)+1,IF($AK24="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI24)+1,""))</f>
         <v>6</v>
       </c>
-    </row>
-    <row r="25" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD24" s="62">
+        <f>IF($AG24="","",IF(OR(AND(ISNUMBER($AH24),OR($AH24&lt;10,$AH24&gt;190)),AND(ISNUMBER($AI24),OR($AI24&lt;10,$AI24&gt;190))),1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A25" s="61" t="str">
         <f>IF(ピッキング!$B$29="","",ピッキング!$B$29)</f>
         <v>森本久美</v>
@@ -27480,8 +27573,12 @@
         <f>IF($AK25="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH25)+1,IF($AK25="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI25)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="26" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD25" s="62">
+        <f>IF($AG25="","",IF(OR(AND(ISNUMBER($AH25),OR($AH25&lt;10,$AH25&gt;190)),AND(ISNUMBER($AI25),OR($AI25&lt;10,$AI25&gt;190))),1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A26" s="61" t="str">
         <f>IF(ピッキング!$B$30="","",ピッキング!$B$30)</f>
         <v>菊池敬</v>
@@ -27660,8 +27757,12 @@
         <f>IF($AK26="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH26)+1,IF($AK26="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI26)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="27" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD26" s="62">
+        <f>IF($AG26="","",IF(OR(AND(ISNUMBER($AH26),OR($AH26&lt;10,$AH26&gt;190)),AND(ISNUMBER($AI26),OR($AI26&lt;10,$AI26&gt;190))),1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A27" s="61" t="str">
         <f>IF(ピッキング!$B$31="","",ピッキング!$B$31)</f>
         <v>高橋正美</v>
@@ -27840,8 +27941,12 @@
         <f>IF($AK27="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH27)+1,IF($AK27="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI27)+1,""))</f>
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD27" s="62">
+        <f>IF($AG27="","",IF(OR(AND(ISNUMBER($AH27),OR($AH27&lt;10,$AH27&gt;190)),AND(ISNUMBER($AI27),OR($AI27&lt;10,$AI27&gt;190))),1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A28" s="61" t="str">
         <f>IF(ピッキング!$B$32="","",ピッキング!$B$32)</f>
         <v>秋草文恵</v>
@@ -28020,8 +28125,12 @@
         <f>IF($AK28="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH28)+1,IF($AK28="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI28)+1,""))</f>
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD28" s="62">
+        <f>IF($AG28="","",IF(OR(AND(ISNUMBER($AH28),OR($AH28&lt;10,$AH28&gt;190)),AND(ISNUMBER($AI28),OR($AI28&lt;10,$AI28&gt;190))),1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A29" s="61" t="str">
         <f>IF(ピッキング!$B$33="","",ピッキング!$B$33)</f>
         <v>上村和恵</v>
@@ -28200,8 +28309,12 @@
         <f>IF($AK29="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH29)+1,IF($AK29="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI29)+1,""))</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD29" s="62">
+        <f>IF($AG29="","",IF(OR(AND(ISNUMBER($AH29),OR($AH29&lt;10,$AH29&gt;190)),AND(ISNUMBER($AI29),OR($AI29&lt;10,$AI29&gt;190))),1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A30" s="61" t="str">
         <f>IF(ピッキング!$B$34="","",ピッキング!$B$34)</f>
         <v>平田学</v>
@@ -28380,8 +28493,12 @@
         <f>IF($AK30="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH30)+1,IF($AK30="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI30)+1,""))</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD30" s="62">
+        <f>IF($AG30="","",IF(OR(AND(ISNUMBER($AH30),OR($AH30&lt;10,$AH30&gt;190)),AND(ISNUMBER($AI30),OR($AI30&lt;10,$AI30&gt;190))),1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A31" s="61" t="str">
         <f>IF(ピッキング!$B$35="","",ピッキング!$B$35)</f>
         <v>飯田由加里</v>
@@ -28560,8 +28677,12 @@
         <f>IF($AK31="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH31)+1,IF($AK31="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI31)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="32" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD31" s="62">
+        <f>IF($AG31="","",IF(OR(AND(ISNUMBER($AH31),OR($AH31&lt;10,$AH31&gt;190)),AND(ISNUMBER($AI31),OR($AI31&lt;10,$AI31&gt;190))),1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A32" s="61" t="str">
         <f>IF(ピッキング!$B$36="","",ピッキング!$B$36)</f>
         <v/>
@@ -28740,8 +28861,12 @@
         <f>IF($AK32="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH32)+1,IF($AK32="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI32)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="33" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD32" s="62" t="str">
+        <f>IF($AG32="","",IF(OR(AND(ISNUMBER($AH32),OR($AH32&lt;10,$AH32&gt;190)),AND(ISNUMBER($AI32),OR($AI32&lt;10,$AI32&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A33" s="61" t="str">
         <f>IF(ピッキング!$B$37="","",ピッキング!$B$37)</f>
         <v/>
@@ -28920,8 +29045,12 @@
         <f>IF($AK33="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH33)+1,IF($AK33="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI33)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="34" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD33" s="62" t="str">
+        <f>IF($AG33="","",IF(OR(AND(ISNUMBER($AH33),OR($AH33&lt;10,$AH33&gt;190)),AND(ISNUMBER($AI33),OR($AI33&lt;10,$AI33&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A34" s="61" t="str">
         <f>IF(ピッキング!$B$38="","",ピッキング!$B$38)</f>
         <v/>
@@ -29100,8 +29229,12 @@
         <f>IF($AK34="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH34)+1,IF($AK34="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI34)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="35" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD34" s="62" t="str">
+        <f>IF($AG34="","",IF(OR(AND(ISNUMBER($AH34),OR($AH34&lt;10,$AH34&gt;190)),AND(ISNUMBER($AI34),OR($AI34&lt;10,$AI34&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A35" s="61" t="str">
         <f>IF(ピッキング!$B$39="","",ピッキング!$B$39)</f>
         <v/>
@@ -29280,8 +29413,12 @@
         <f>IF($AK35="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH35)+1,IF($AK35="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI35)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="36" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD35" s="62" t="str">
+        <f>IF($AG35="","",IF(OR(AND(ISNUMBER($AH35),OR($AH35&lt;10,$AH35&gt;190)),AND(ISNUMBER($AI35),OR($AI35&lt;10,$AI35&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A36" s="61" t="str">
         <f>IF(ピッキング!$B$40="","",ピッキング!$B$40)</f>
         <v/>
@@ -29460,8 +29597,12 @@
         <f>IF($AK36="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH36)+1,IF($AK36="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI36)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="37" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD36" s="62" t="str">
+        <f>IF($AG36="","",IF(OR(AND(ISNUMBER($AH36),OR($AH36&lt;10,$AH36&gt;190)),AND(ISNUMBER($AI36),OR($AI36&lt;10,$AI36&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A37" s="61" t="str">
         <f>IF(ピッキング!$B$41="","",ピッキング!$B$41)</f>
         <v/>
@@ -29640,8 +29781,12 @@
         <f>IF($AK37="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH37)+1,IF($AK37="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI37)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="38" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD37" s="62" t="str">
+        <f>IF($AG37="","",IF(OR(AND(ISNUMBER($AH37),OR($AH37&lt;10,$AH37&gt;190)),AND(ISNUMBER($AI37),OR($AI37&lt;10,$AI37&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A38" s="61" t="str">
         <f>IF(ピッキング!$B$42="","",ピッキング!$B$42)</f>
         <v/>
@@ -29820,8 +29965,12 @@
         <f>IF($AK38="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH38)+1,IF($AK38="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI38)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="39" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD38" s="62" t="str">
+        <f>IF($AG38="","",IF(OR(AND(ISNUMBER($AH38),OR($AH38&lt;10,$AH38&gt;190)),AND(ISNUMBER($AI38),OR($AI38&lt;10,$AI38&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A39" s="61" t="str">
         <f>IF(ピッキング!$B$43="","",ピッキング!$B$43)</f>
         <v/>
@@ -30000,8 +30149,12 @@
         <f>IF($AK39="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH39)+1,IF($AK39="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI39)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="40" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD39" s="62" t="str">
+        <f>IF($AG39="","",IF(OR(AND(ISNUMBER($AH39),OR($AH39&lt;10,$AH39&gt;190)),AND(ISNUMBER($AI39),OR($AI39&lt;10,$AI39&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A40" s="61" t="str">
         <f>IF(ピッキング!$B$44="","",ピッキング!$B$44)</f>
         <v/>
@@ -30180,8 +30333,12 @@
         <f>IF($AK40="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH40)+1,IF($AK40="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI40)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="41" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD40" s="62" t="str">
+        <f>IF($AG40="","",IF(OR(AND(ISNUMBER($AH40),OR($AH40&lt;10,$AH40&gt;190)),AND(ISNUMBER($AI40),OR($AI40&lt;10,$AI40&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A41" s="61" t="str">
         <f>IF(ピッキング!$B$45="","",ピッキング!$B$45)</f>
         <v/>
@@ -30360,8 +30517,12 @@
         <f>IF($AK41="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH41)+1,IF($AK41="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI41)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="42" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD41" s="62" t="str">
+        <f>IF($AG41="","",IF(OR(AND(ISNUMBER($AH41),OR($AH41&lt;10,$AH41&gt;190)),AND(ISNUMBER($AI41),OR($AI41&lt;10,$AI41&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A42" s="61" t="str">
         <f>IF(ピッキング!$B$46="","",ピッキング!$B$46)</f>
         <v/>
@@ -30540,8 +30701,12 @@
         <f>IF($AK42="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH42)+1,IF($AK42="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI42)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="43" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD42" s="62" t="str">
+        <f>IF($AG42="","",IF(OR(AND(ISNUMBER($AH42),OR($AH42&lt;10,$AH42&gt;190)),AND(ISNUMBER($AI42),OR($AI42&lt;10,$AI42&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A43" s="61" t="str">
         <f>IF(ピッキング!$B$47="","",ピッキング!$B$47)</f>
         <v/>
@@ -30720,8 +30885,12 @@
         <f>IF($AK43="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH43)+1,IF($AK43="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI43)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="44" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD43" s="62" t="str">
+        <f>IF($AG43="","",IF(OR(AND(ISNUMBER($AH43),OR($AH43&lt;10,$AH43&gt;190)),AND(ISNUMBER($AI43),OR($AI43&lt;10,$AI43&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A44" s="61" t="str">
         <f>IF(ピッキング!$B$48="","",ピッキング!$B$48)</f>
         <v/>
@@ -30900,8 +31069,12 @@
         <f>IF($AK44="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH44)+1,IF($AK44="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI44)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="45" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD44" s="62" t="str">
+        <f>IF($AG44="","",IF(OR(AND(ISNUMBER($AH44),OR($AH44&lt;10,$AH44&gt;190)),AND(ISNUMBER($AI44),OR($AI44&lt;10,$AI44&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A45" s="61" t="str">
         <f>IF(ピッキング!$B$49="","",ピッキング!$B$49)</f>
         <v/>
@@ -31080,8 +31253,12 @@
         <f>IF($AK45="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH45)+1,IF($AK45="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI45)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="46" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD45" s="62" t="str">
+        <f>IF($AG45="","",IF(OR(AND(ISNUMBER($AH45),OR($AH45&lt;10,$AH45&gt;190)),AND(ISNUMBER($AI45),OR($AI45&lt;10,$AI45&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A46" s="61" t="str">
         <f>IF(ピッキング!$B$50="","",ピッキング!$B$50)</f>
         <v/>
@@ -31260,8 +31437,12 @@
         <f>IF($AK46="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH46)+1,IF($AK46="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI46)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="47" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD46" s="62" t="str">
+        <f>IF($AG46="","",IF(OR(AND(ISNUMBER($AH46),OR($AH46&lt;10,$AH46&gt;190)),AND(ISNUMBER($AI46),OR($AI46&lt;10,$AI46&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A47" s="61" t="str">
         <f>IF(ピッキング!$B$51="","",ピッキング!$B$51)</f>
         <v/>
@@ -31440,8 +31621,12 @@
         <f>IF($AK47="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH47)+1,IF($AK47="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI47)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="48" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD47" s="62" t="str">
+        <f>IF($AG47="","",IF(OR(AND(ISNUMBER($AH47),OR($AH47&lt;10,$AH47&gt;190)),AND(ISNUMBER($AI47),OR($AI47&lt;10,$AI47&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A48" s="61" t="str">
         <f>IF(ピッキング!$B$52="","",ピッキング!$B$52)</f>
         <v/>
@@ -31620,8 +31805,12 @@
         <f>IF($AK48="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH48)+1,IF($AK48="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI48)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="49" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD48" s="62" t="str">
+        <f>IF($AG48="","",IF(OR(AND(ISNUMBER($AH48),OR($AH48&lt;10,$AH48&gt;190)),AND(ISNUMBER($AI48),OR($AI48&lt;10,$AI48&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A49" s="61" t="str">
         <f>IF(ピッキング!$B$53="","",ピッキング!$B$53)</f>
         <v/>
@@ -31800,8 +31989,12 @@
         <f>IF($AK49="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH49)+1,IF($AK49="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI49)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="50" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD49" s="62" t="str">
+        <f>IF($AG49="","",IF(OR(AND(ISNUMBER($AH49),OR($AH49&lt;10,$AH49&gt;190)),AND(ISNUMBER($AI49),OR($AI49&lt;10,$AI49&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A50" s="61" t="str">
         <f>IF(ピッキング!$B$54="","",ピッキング!$B$54)</f>
         <v/>
@@ -31980,8 +32173,12 @@
         <f>IF($AK50="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH50)+1,IF($AK50="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI50)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="51" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD50" s="62" t="str">
+        <f>IF($AG50="","",IF(OR(AND(ISNUMBER($AH50),OR($AH50&lt;10,$AH50&gt;190)),AND(ISNUMBER($AI50),OR($AI50&lt;10,$AI50&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A51" s="61" t="str">
         <f>IF(ピッキング!$B$55="","",ピッキング!$B$55)</f>
         <v/>
@@ -32160,8 +32357,12 @@
         <f>IF($AK51="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH51)+1,IF($AK51="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI51)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="52" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD51" s="62" t="str">
+        <f>IF($AG51="","",IF(OR(AND(ISNUMBER($AH51),OR($AH51&lt;10,$AH51&gt;190)),AND(ISNUMBER($AI51),OR($AI51&lt;10,$AI51&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A52" s="61" t="str">
         <f>IF(ピッキング!$B$56="","",ピッキング!$B$56)</f>
         <v/>
@@ -32340,8 +32541,12 @@
         <f>IF($AK52="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH52)+1,IF($AK52="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI52)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="53" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD52" s="62" t="str">
+        <f>IF($AG52="","",IF(OR(AND(ISNUMBER($AH52),OR($AH52&lt;10,$AH52&gt;190)),AND(ISNUMBER($AI52),OR($AI52&lt;10,$AI52&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A53" s="61" t="str">
         <f>IF(ピッキング!$B$57="","",ピッキング!$B$57)</f>
         <v/>
@@ -32520,8 +32725,12 @@
         <f>IF($AK53="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH53)+1,IF($AK53="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI53)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="54" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD53" s="62" t="str">
+        <f>IF($AG53="","",IF(OR(AND(ISNUMBER($AH53),OR($AH53&lt;10,$AH53&gt;190)),AND(ISNUMBER($AI53),OR($AI53&lt;10,$AI53&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A54" s="61" t="str">
         <f>IF(ピッキング!$B$58="","",ピッキング!$B$58)</f>
         <v/>
@@ -32700,8 +32909,12 @@
         <f>IF($AK54="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH54)+1,IF($AK54="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI54)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="55" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD54" s="62" t="str">
+        <f>IF($AG54="","",IF(OR(AND(ISNUMBER($AH54),OR($AH54&lt;10,$AH54&gt;190)),AND(ISNUMBER($AI54),OR($AI54&lt;10,$AI54&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A55" s="61" t="str">
         <f>IF(ピッキング!$B$59="","",ピッキング!$B$59)</f>
         <v/>
@@ -32880,8 +33093,12 @@
         <f>IF($AK55="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH55)+1,IF($AK55="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI55)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="56" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD55" s="62" t="str">
+        <f>IF($AG55="","",IF(OR(AND(ISNUMBER($AH55),OR($AH55&lt;10,$AH55&gt;190)),AND(ISNUMBER($AI55),OR($AI55&lt;10,$AI55&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A56" s="61" t="str">
         <f>IF(ピッキング!$B$60="","",ピッキング!$B$60)</f>
         <v/>
@@ -33060,8 +33277,12 @@
         <f>IF($AK56="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH56)+1,IF($AK56="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI56)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="57" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD56" s="62" t="str">
+        <f>IF($AG56="","",IF(OR(AND(ISNUMBER($AH56),OR($AH56&lt;10,$AH56&gt;190)),AND(ISNUMBER($AI56),OR($AI56&lt;10,$AI56&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A57" s="61" t="str">
         <f>IF(ピッキング!$B$61="","",ピッキング!$B$61)</f>
         <v/>
@@ -33240,8 +33461,12 @@
         <f>IF($AK57="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH57)+1,IF($AK57="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI57)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="58" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD57" s="62" t="str">
+        <f>IF($AG57="","",IF(OR(AND(ISNUMBER($AH57),OR($AH57&lt;10,$AH57&gt;190)),AND(ISNUMBER($AI57),OR($AI57&lt;10,$AI57&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A58" s="61" t="str">
         <f>IF(ピッキング!$B$62="","",ピッキング!$B$62)</f>
         <v/>
@@ -33420,8 +33645,12 @@
         <f>IF($AK58="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH58)+1,IF($AK58="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI58)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="59" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD58" s="62" t="str">
+        <f>IF($AG58="","",IF(OR(AND(ISNUMBER($AH58),OR($AH58&lt;10,$AH58&gt;190)),AND(ISNUMBER($AI58),OR($AI58&lt;10,$AI58&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A59" s="61" t="str">
         <f>IF(ピッキング!$B$63="","",ピッキング!$B$63)</f>
         <v/>
@@ -33600,8 +33829,12 @@
         <f>IF($AK59="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH59)+1,IF($AK59="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI59)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="60" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD59" s="62" t="str">
+        <f>IF($AG59="","",IF(OR(AND(ISNUMBER($AH59),OR($AH59&lt;10,$AH59&gt;190)),AND(ISNUMBER($AI59),OR($AI59&lt;10,$AI59&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A60" s="61" t="str">
         <f>IF(ピッキング!$B$64="","",ピッキング!$B$64)</f>
         <v/>
@@ -33780,8 +34013,12 @@
         <f>IF($AK60="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH60)+1,IF($AK60="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI60)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="61" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD60" s="62" t="str">
+        <f>IF($AG60="","",IF(OR(AND(ISNUMBER($AH60),OR($AH60&lt;10,$AH60&gt;190)),AND(ISNUMBER($AI60),OR($AI60&lt;10,$AI60&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A61" s="61" t="str">
         <f>IF(ピッキング!$B$65="","",ピッキング!$B$65)</f>
         <v/>
@@ -33960,8 +34197,12 @@
         <f>IF($AK61="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH61)+1,IF($AK61="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI61)+1,""))</f>
         <v/>
       </c>
-    </row>
-    <row r="62" spans="1:55" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BD61" s="62" t="str">
+        <f>IF($AG61="","",IF(OR(AND(ISNUMBER($AH61),OR($AH61&lt;10,$AH61&gt;190)),AND(ISNUMBER($AI61),OR($AI61&lt;10,$AI61&gt;190))),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A62" s="61" t="str">
         <f>IF(ピッキング!$B$66="","",ピッキング!$B$66)</f>
         <v/>
@@ -34138,6 +34379,10 @@
       </c>
       <c r="AY62" s="62" t="str">
         <f>IF($AK62="PKのみ",COUNTIFS($AK$3:$AK$62,"PKのみ",$AH$3:$AH$62,"&lt;"&amp;$AH62)+1,IF($AK62="梱包のみ",COUNTIFS($AK$3:$AK$62,"梱包のみ",$AI$3:$AI$62,"&lt;"&amp;$AI62)+1,""))</f>
+        <v/>
+      </c>
+      <c r="BD62" s="62" t="str">
+        <f>IF($AG62="","",IF(OR(AND(ISNUMBER($AH62),OR($AH62&lt;10,$AH62&gt;190)),AND(ISNUMBER($AI62),OR($AI62&lt;10,$AI62&gt;190))),1,0))</f>
         <v/>
       </c>
     </row>
@@ -36184,7 +36429,7 @@
     </row>
     <row r="62" spans="2:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="85" t="str">
-        <f>"※ ①〜④ は実績のある全員 "&amp;COUNT(印刷用データ!AS3:AS62)&amp;" 名。「工程」が PKのみ／梱包のみ の人は、その工程だけの標準時間 ÷ 実測時間です。③ でもう一方の実績が無い "&amp;(COUNT(印刷用データ!AS3:AS62)-COUNT(印刷用データ!N3:N62))&amp;" 名は、下の帯に灰色の三角で並べています。出典: 2026年4月 実績。"</f>
+        <f>"※ ①〜④ は実績のある全員 "&amp;COUNT(印刷用データ!AS3:AS62)&amp;" 名。「工程」が PKのみ／梱包のみ の人は、その工程だけの標準時間 ÷ 実測時間です。③ でもう一方の実績が無い "&amp;(COUNT(印刷用データ!AS3:AS62)-COUNT(印刷用データ!N3:N62))&amp;" 名は、下の帯に灰色の三角で並べています。出典: 2026年4月 実績。"&amp;IF(SUM(印刷用データ!BD3:BD62)&gt;0,"　【要確認】③ は縦横とも 10〜190% の範囲で描いています。範囲外のため図に出ていない人が "&amp;SUM(印刷用データ!BD3:BD62)&amp;" 名います。","")</f>
         <v>※ ①〜④ は実績のある全員 29 名。「工程」が PKのみ／梱包のみ の人は、その工程だけの標準時間 ÷ 実測時間です。③ でもう一方の実績が無い 10 名は、下の帯に灰色の三角で並べています。出典: 2026年4月 実績。</v>
       </c>
       <c r="C62" s="77"/>

--- a/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
+++ b/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
@@ -34464,11 +34464,11 @@
         <f>"④ 改善優先順位（全員 "&amp;COUNT(印刷用データ!$AS$3:$AS$62)&amp;"名）"</f>
         <v>④ 改善優先順位（全員 29名）</v>
       </c>
-      <c r="N3" s="63"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
       <c r="T3" s="86" t="str">
         <f>"② ピッキング・梱包 内訳比較（全員 "&amp;COUNT(印刷用データ!$AS$3:$AS$62)&amp;"名）"</f>
         <v>② ピッキング・梱包 内訳比較（全員 29名）</v>
@@ -36459,7 +36459,9 @@
       <c r="AA62" s="77"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="M3:R3"/>
     <mergeCell ref="B62:AA62"/>
     <mergeCell ref="T17:AA17"/>
     <mergeCell ref="T1:AA1"/>

--- a/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
+++ b/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
@@ -15112,191 +15112,137 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>印刷用データ!$AP$3:$AP$52</c:f>
+              <c:f>印刷用データ!$BF$3:$BF$22</c:f>
               <c:strCache>
-                <c:ptCount val="50"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>本吉有美子</c:v>
+                  <c:v>平田学</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>佐々木千恵</c:v>
+                  <c:v>森田美加</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>佐藤辰成</c:v>
+                  <c:v>菊池敬</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>大江美記子</c:v>
+                  <c:v>片岡達也</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>春谷智子</c:v>
+                  <c:v>木村千鶴</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>北田倫子</c:v>
+                  <c:v>上村和恵</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>晩田恵美</c:v>
+                  <c:v>秋草文恵</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>飯田由加里</c:v>
+                  <c:v>高橋正美</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>河野忠</c:v>
+                  <c:v>中村美佳</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>澤田凌</c:v>
+                  <c:v>廣瀬こずえ</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>石戸谷亜子</c:v>
+                  <c:v>向井ひかり</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>後藤克行</c:v>
+                  <c:v>奥野愛海</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>高橋佐織</c:v>
+                  <c:v>森本久美</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>鈴木香織</c:v>
+                  <c:v>中納沙織</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>山本祥吉</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>中納沙織</c:v>
+                  <c:v>鈴木香織</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>森本久美</c:v>
+                  <c:v>高橋佐織</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>奥野愛海</c:v>
+                  <c:v>後藤克行</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>向井ひかり</c:v>
+                  <c:v>石戸谷亜子</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>廣瀬こずえ</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>中村美佳</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>高橋正美</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>秋草文恵</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>上村和恵</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>木村千鶴</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>片岡達也</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>菊池敬</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>森田美加</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>平田学</c:v>
+                  <c:v>澤田凌</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>印刷用データ!$AQ$3:$AQ$52</c:f>
+              <c:f>印刷用データ!$BG$3:$BG$22</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>136.58407297830374</c:v>
+                  <c:v>56.60244897959183</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>106.39972273567466</c:v>
+                  <c:v>98.22111111111111</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>131.80246913580245</c:v>
+                  <c:v>85.86263157894736</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>128.62508143322475</c:v>
+                  <c:v>76.88366336633663</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>126.5595238095238</c:v>
+                  <c:v>99.64362464183381</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>101.99950049950048</c:v>
+                  <c:v>79.35816135084428</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>108.44019316493313</c:v>
+                  <c:v>80.2896370582617</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>74.63023560209423</c:v>
+                  <c:v>80.89163346613546</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>98.11684782608697</c:v>
+                  <c:v>121.32499999999997</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>138.5160642570281</c:v>
+                  <c:v>88.02662271805272</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>100.59261744966443</c:v>
+                  <c:v>89.99333688699362</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>111.60069735006972</c:v>
+                  <c:v>91.34864864864863</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>106.8047477744807</c:v>
+                  <c:v>81.8917597765363</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>96.54257425742574</c:v>
+                  <c:v>101.71352549889134</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>106.22178879910837</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>101.71352549889134</c:v>
+                  <c:v>96.54257425742574</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>81.8917597765363</c:v>
+                  <c:v>106.8047477744807</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>91.34864864864863</c:v>
+                  <c:v>111.60069735006972</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>89.99333688699362</c:v>
+                  <c:v>100.59261744966443</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>88.02662271805272</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>121.32499999999997</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>80.89163346613546</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>80.2896370582617</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>79.35816135084428</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>99.64362464183381</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>76.88366336633663</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>85.86263157894736</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>98.22111111111111</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>56.60244897959183</c:v>
+                  <c:v>138.5160642570281</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15372,161 +15318,110 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>印刷用データ!$AP$3:$AP$52</c:f>
+              <c:f>印刷用データ!$BF$3:$BF$22</c:f>
               <c:strCache>
-                <c:ptCount val="50"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>本吉有美子</c:v>
+                  <c:v>平田学</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>佐々木千恵</c:v>
+                  <c:v>森田美加</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>佐藤辰成</c:v>
+                  <c:v>菊池敬</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>大江美記子</c:v>
+                  <c:v>片岡達也</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>春谷智子</c:v>
+                  <c:v>木村千鶴</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>北田倫子</c:v>
+                  <c:v>上村和恵</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>晩田恵美</c:v>
+                  <c:v>秋草文恵</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>飯田由加里</c:v>
+                  <c:v>高橋正美</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>河野忠</c:v>
+                  <c:v>中村美佳</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>澤田凌</c:v>
+                  <c:v>廣瀬こずえ</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>石戸谷亜子</c:v>
+                  <c:v>向井ひかり</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>後藤克行</c:v>
+                  <c:v>奥野愛海</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>高橋佐織</c:v>
+                  <c:v>森本久美</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>鈴木香織</c:v>
+                  <c:v>中納沙織</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>山本祥吉</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>中納沙織</c:v>
+                  <c:v>鈴木香織</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>森本久美</c:v>
+                  <c:v>高橋佐織</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>奥野愛海</c:v>
+                  <c:v>後藤克行</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>向井ひかり</c:v>
+                  <c:v>石戸谷亜子</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>廣瀬こずえ</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>中村美佳</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>高橋正美</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>秋草文恵</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>上村和恵</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>木村千鶴</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>片岡達也</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>菊池敬</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>森田美加</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>平田学</c:v>
+                  <c:v>澤田凌</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>印刷用データ!$AR$3:$AR$52</c:f>
+              <c:f>印刷用データ!$BH$3:$BH$22</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
-                <c:ptCount val="50"/>
-                <c:pt idx="0">
-                  <c:v>149.67602924201614</c:v>
-                </c:pt>
+                <c:ptCount val="20"/>
                 <c:pt idx="1">
-                  <c:v>171.96125541125542</c:v>
+                  <c:v>52.27737789203085</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>132.51857923497266</c:v>
+                  <c:v>65.7034771774833</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>132.88643790849673</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>136.2250663632916</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>121.13147824640211</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>129.17098681218735</c:v>
+                <c:pt idx="4">
+                  <c:v>71.82954945441745</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>116.41046228710461</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>72.98028322440088</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>80.32650966183573</c:v>
+                  <c:v>81.79246575342466</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>93.86370603420457</c:v>
+                  <c:v>100.98448866067606</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>97.37824675324676</c:v>
+                  <c:v>66.90456140350877</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>84.7367397454031</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>66.90456140350877</c:v>
+                  <c:v>97.37824675324676</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>100.98448866067606</c:v>
+                  <c:v>93.86370603420457</c:v>
                 </c:pt>
-                <c:pt idx="20">
-                  <c:v>81.79246575342466</c:v>
+                <c:pt idx="17">
+                  <c:v>80.32650966183573</c:v>
                 </c:pt>
-                <c:pt idx="24">
-                  <c:v>71.82954945441745</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>65.7034771774833</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>52.27737789203085</c:v>
+                <c:pt idx="19">
+                  <c:v>72.98028322440088</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15584,105 +15479,78 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>印刷用データ!$AP$3:$AP$52</c:f>
+              <c:f>印刷用データ!$BF$3:$BF$22</c:f>
               <c:strCache>
-                <c:ptCount val="50"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>本吉有美子</c:v>
+                  <c:v>平田学</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>佐々木千恵</c:v>
+                  <c:v>森田美加</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>佐藤辰成</c:v>
+                  <c:v>菊池敬</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>大江美記子</c:v>
+                  <c:v>片岡達也</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>春谷智子</c:v>
+                  <c:v>木村千鶴</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>北田倫子</c:v>
+                  <c:v>上村和恵</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>晩田恵美</c:v>
+                  <c:v>秋草文恵</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>飯田由加里</c:v>
+                  <c:v>高橋正美</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>河野忠</c:v>
+                  <c:v>中村美佳</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>澤田凌</c:v>
+                  <c:v>廣瀬こずえ</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>石戸谷亜子</c:v>
+                  <c:v>向井ひかり</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>後藤克行</c:v>
+                  <c:v>奥野愛海</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>高橋佐織</c:v>
+                  <c:v>森本久美</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>鈴木香織</c:v>
+                  <c:v>中納沙織</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>山本祥吉</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>中納沙織</c:v>
+                  <c:v>鈴木香織</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>森本久美</c:v>
+                  <c:v>高橋佐織</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>奥野愛海</c:v>
+                  <c:v>後藤克行</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>向井ひかり</c:v>
+                  <c:v>石戸谷亜子</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>廣瀬こずえ</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>中村美佳</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>高橋正美</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>秋草文恵</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>上村和恵</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>木村千鶴</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>片岡達也</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>菊池敬</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>森田美加</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>平田学</c:v>
+                  <c:v>澤田凌</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>印刷用データ!$AV$3:$AV$52</c:f>
+              <c:f>印刷用データ!$BI$3:$BI$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>100</c:v>
                 </c:pt>
@@ -15741,33 +15609,6 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="28">
                   <c:v>100</c:v>
                 </c:pt>
               </c:numCache>
@@ -23107,13 +22948,13 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:BD62"/>
+  <dimension ref="A1:BI62"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="56" width="11" customWidth="1"/>
+    <col min="1" max="61" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A1" s="60" t="s">
         <v>0</v>
       </c>
@@ -23150,7 +22991,7 @@
         </is>
       </c>
     </row>
-    <row r="2" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A2" s="39" t="s">
         <v>428</v>
       </c>
@@ -23309,6 +23150,26 @@
           <t>軸外</t>
         </is>
       </c>
+      <c r="BF2" s="39" t="inlineStr">
+        <is>
+          <t>優先順 氏名</t>
+        </is>
+      </c>
+      <c r="BG2" s="39" t="inlineStr">
+        <is>
+          <t>優先順 PK</t>
+        </is>
+      </c>
+      <c r="BH2" s="39" t="inlineStr">
+        <is>
+          <t>優先順 梱包</t>
+        </is>
+      </c>
+      <c r="BI2" s="39" t="inlineStr">
+        <is>
+          <t>目標</t>
+        </is>
+      </c>
       <c r="AZ2" s="39">
         <v>10</v>
       </c>
@@ -23322,7 +23183,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A3" s="61" t="str">
         <f>IF(ピッキング!$B$7="","",ピッキング!$B$7)</f>
         <v>本吉有美子</v>
@@ -23529,8 +23390,24 @@
         <f>IF($AG3="","",IF(OR(AND(ISNUMBER($AH3),OR($AH3&lt;10,$AH3&gt;190)),AND(ISNUMBER($AI3),OR($AI3&lt;10,$AI3&gt;190))),1,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BF3" s="61" t="str">
+        <f>IFERROR(INDEX($AG$3:$AG$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>平田学</v>
+      </c>
+      <c r="BG3" s="62">
+        <f>IFERROR(INDEX($AH$3:$AH$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>56.60244897959183</v>
+      </c>
+      <c r="BH3" s="61" t="str">
+        <f>IFERROR(INDEX($AI$3:$AI$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="BI3" s="62">
+        <f>IF($BF3="","",100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A4" s="61" t="str">
         <f>IF(ピッキング!$B$8="","",ピッキング!$B$8)</f>
         <v>澤田凌</v>
@@ -23713,8 +23590,24 @@
         <f>IF($AG4="","",IF(OR(AND(ISNUMBER($AH4),OR($AH4&lt;10,$AH4&gt;190)),AND(ISNUMBER($AI4),OR($AI4&lt;10,$AI4&gt;190))),1,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BF4" s="61" t="str">
+        <f>IFERROR(INDEX($AG$3:$AG$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>森田美加</v>
+      </c>
+      <c r="BG4" s="62">
+        <f>IFERROR(INDEX($AH$3:$AH$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>98.22111111111111</v>
+      </c>
+      <c r="BH4" s="62">
+        <f>IFERROR(INDEX($AI$3:$AI$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>52.27737789203085</v>
+      </c>
+      <c r="BI4" s="62">
+        <f>IF($BF4="","",100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A5" s="61" t="str">
         <f>IF(ピッキング!$B$9="","",ピッキング!$B$9)</f>
         <v>大江美記子</v>
@@ -23897,8 +23790,24 @@
         <f>IF($AG5="","",IF(OR(AND(ISNUMBER($AH5),OR($AH5&lt;10,$AH5&gt;190)),AND(ISNUMBER($AI5),OR($AI5&lt;10,$AI5&gt;190))),1,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BF5" s="61" t="str">
+        <f>IFERROR(INDEX($AG$3:$AG$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>菊池敬</v>
+      </c>
+      <c r="BG5" s="62">
+        <f>IFERROR(INDEX($AH$3:$AH$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>85.86263157894736</v>
+      </c>
+      <c r="BH5" s="62">
+        <f>IFERROR(INDEX($AI$3:$AI$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>65.7034771774833</v>
+      </c>
+      <c r="BI5" s="62">
+        <f>IF($BF5="","",100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A6" s="61" t="str">
         <f>IF(ピッキング!$B$10="","",ピッキング!$B$10)</f>
         <v>佐藤辰成</v>
@@ -24081,8 +23990,24 @@
         <f>IF($AG6="","",IF(OR(AND(ISNUMBER($AH6),OR($AH6&lt;10,$AH6&gt;190)),AND(ISNUMBER($AI6),OR($AI6&lt;10,$AI6&gt;190))),1,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BF6" s="61" t="str">
+        <f>IFERROR(INDEX($AG$3:$AG$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>片岡達也</v>
+      </c>
+      <c r="BG6" s="62">
+        <f>IFERROR(INDEX($AH$3:$AH$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>76.88366336633663</v>
+      </c>
+      <c r="BH6" s="61" t="str">
+        <f>IFERROR(INDEX($AI$3:$AI$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="BI6" s="62">
+        <f>IF($BF6="","",100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A7" s="61" t="str">
         <f>IF(ピッキング!$B$11="","",ピッキング!$B$11)</f>
         <v>春谷智子</v>
@@ -24265,8 +24190,24 @@
         <f>IF($AG7="","",IF(OR(AND(ISNUMBER($AH7),OR($AH7&lt;10,$AH7&gt;190)),AND(ISNUMBER($AI7),OR($AI7&lt;10,$AI7&gt;190))),1,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BF7" s="61" t="str">
+        <f>IFERROR(INDEX($AG$3:$AG$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>木村千鶴</v>
+      </c>
+      <c r="BG7" s="62">
+        <f>IFERROR(INDEX($AH$3:$AH$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>99.64362464183381</v>
+      </c>
+      <c r="BH7" s="62">
+        <f>IFERROR(INDEX($AI$3:$AI$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>71.82954945441745</v>
+      </c>
+      <c r="BI7" s="62">
+        <f>IF($BF7="","",100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A8" s="61" t="str">
         <f>IF(ピッキング!$B$12="","",ピッキング!$B$12)</f>
         <v>後藤克行</v>
@@ -24449,8 +24390,24 @@
         <f>IF($AG8="","",IF(OR(AND(ISNUMBER($AH8),OR($AH8&lt;10,$AH8&gt;190)),AND(ISNUMBER($AI8),OR($AI8&lt;10,$AI8&gt;190))),1,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BF8" s="61" t="str">
+        <f>IFERROR(INDEX($AG$3:$AG$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>上村和恵</v>
+      </c>
+      <c r="BG8" s="62">
+        <f>IFERROR(INDEX($AH$3:$AH$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>79.35816135084428</v>
+      </c>
+      <c r="BH8" s="61" t="str">
+        <f>IFERROR(INDEX($AI$3:$AI$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="BI8" s="62">
+        <f>IF($BF8="","",100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A9" s="61" t="str">
         <f>IF(ピッキング!$B$13="","",ピッキング!$B$13)</f>
         <v>中村美佳</v>
@@ -24633,8 +24590,24 @@
         <f>IF($AG9="","",IF(OR(AND(ISNUMBER($AH9),OR($AH9&lt;10,$AH9&gt;190)),AND(ISNUMBER($AI9),OR($AI9&lt;10,$AI9&gt;190))),1,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BF9" s="61" t="str">
+        <f>IFERROR(INDEX($AG$3:$AG$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>秋草文恵</v>
+      </c>
+      <c r="BG9" s="62">
+        <f>IFERROR(INDEX($AH$3:$AH$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>80.2896370582617</v>
+      </c>
+      <c r="BH9" s="61" t="str">
+        <f>IFERROR(INDEX($AI$3:$AI$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="BI9" s="62">
+        <f>IF($BF9="","",100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A10" s="61" t="str">
         <f>IF(ピッキング!$B$14="","",ピッキング!$B$14)</f>
         <v>晩田恵美</v>
@@ -24817,8 +24790,24 @@
         <f>IF($AG10="","",IF(OR(AND(ISNUMBER($AH10),OR($AH10&lt;10,$AH10&gt;190)),AND(ISNUMBER($AI10),OR($AI10&lt;10,$AI10&gt;190))),1,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BF10" s="61" t="str">
+        <f>IFERROR(INDEX($AG$3:$AG$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>高橋正美</v>
+      </c>
+      <c r="BG10" s="62">
+        <f>IFERROR(INDEX($AH$3:$AH$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>80.89163346613546</v>
+      </c>
+      <c r="BH10" s="61" t="str">
+        <f>IFERROR(INDEX($AI$3:$AI$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="BI10" s="62">
+        <f>IF($BF10="","",100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A11" s="61" t="str">
         <f>IF(ピッキング!$B$15="","",ピッキング!$B$15)</f>
         <v>高橋佐織</v>
@@ -25001,8 +24990,24 @@
         <f>IF($AG11="","",IF(OR(AND(ISNUMBER($AH11),OR($AH11&lt;10,$AH11&gt;190)),AND(ISNUMBER($AI11),OR($AI11&lt;10,$AI11&gt;190))),1,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BF11" s="61" t="str">
+        <f>IFERROR(INDEX($AG$3:$AG$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>中村美佳</v>
+      </c>
+      <c r="BG11" s="62">
+        <f>IFERROR(INDEX($AH$3:$AH$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>121.32499999999997</v>
+      </c>
+      <c r="BH11" s="62">
+        <f>IFERROR(INDEX($AI$3:$AI$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>81.79246575342466</v>
+      </c>
+      <c r="BI11" s="62">
+        <f>IF($BF11="","",100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A12" s="61" t="str">
         <f>IF(ピッキング!$B$16="","",ピッキング!$B$16)</f>
         <v>山本祥吉</v>
@@ -25185,8 +25190,24 @@
         <f>IF($AG12="","",IF(OR(AND(ISNUMBER($AH12),OR($AH12&lt;10,$AH12&gt;190)),AND(ISNUMBER($AI12),OR($AI12&lt;10,$AI12&gt;190))),1,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BF12" s="61" t="str">
+        <f>IFERROR(INDEX($AG$3:$AG$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>廣瀬こずえ</v>
+      </c>
+      <c r="BG12" s="62">
+        <f>IFERROR(INDEX($AH$3:$AH$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>88.02662271805272</v>
+      </c>
+      <c r="BH12" s="61" t="str">
+        <f>IFERROR(INDEX($AI$3:$AI$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="BI12" s="62">
+        <f>IF($BF12="","",100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A13" s="61" t="str">
         <f>IF(ピッキング!$B$17="","",ピッキング!$B$17)</f>
         <v>佐々木千恵</v>
@@ -25369,8 +25390,24 @@
         <f>IF($AG13="","",IF(OR(AND(ISNUMBER($AH13),OR($AH13&lt;10,$AH13&gt;190)),AND(ISNUMBER($AI13),OR($AI13&lt;10,$AI13&gt;190))),1,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BF13" s="61" t="str">
+        <f>IFERROR(INDEX($AG$3:$AG$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>向井ひかり</v>
+      </c>
+      <c r="BG13" s="62">
+        <f>IFERROR(INDEX($AH$3:$AH$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>89.99333688699362</v>
+      </c>
+      <c r="BH13" s="61" t="str">
+        <f>IFERROR(INDEX($AI$3:$AI$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="BI13" s="62">
+        <f>IF($BF13="","",100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A14" s="61" t="str">
         <f>IF(ピッキング!$B$18="","",ピッキング!$B$18)</f>
         <v>北田倫子</v>
@@ -25553,8 +25590,24 @@
         <f>IF($AG14="","",IF(OR(AND(ISNUMBER($AH14),OR($AH14&lt;10,$AH14&gt;190)),AND(ISNUMBER($AI14),OR($AI14&lt;10,$AI14&gt;190))),1,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BF14" s="61" t="str">
+        <f>IFERROR(INDEX($AG$3:$AG$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>奥野愛海</v>
+      </c>
+      <c r="BG14" s="62">
+        <f>IFERROR(INDEX($AH$3:$AH$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>91.34864864864863</v>
+      </c>
+      <c r="BH14" s="61" t="str">
+        <f>IFERROR(INDEX($AI$3:$AI$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="BI14" s="62">
+        <f>IF($BF14="","",100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A15" s="61" t="str">
         <f>IF(ピッキング!$B$19="","",ピッキング!$B$19)</f>
         <v>中納沙織</v>
@@ -25737,8 +25790,24 @@
         <f>IF($AG15="","",IF(OR(AND(ISNUMBER($AH15),OR($AH15&lt;10,$AH15&gt;190)),AND(ISNUMBER($AI15),OR($AI15&lt;10,$AI15&gt;190))),1,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BF15" s="61" t="str">
+        <f>IFERROR(INDEX($AG$3:$AG$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>森本久美</v>
+      </c>
+      <c r="BG15" s="62">
+        <f>IFERROR(INDEX($AH$3:$AH$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>81.8917597765363</v>
+      </c>
+      <c r="BH15" s="62">
+        <f>IFERROR(INDEX($AI$3:$AI$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>100.98448866067606</v>
+      </c>
+      <c r="BI15" s="62">
+        <f>IF($BF15="","",100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A16" s="61" t="str">
         <f>IF(ピッキング!$B$20="","",ピッキング!$B$20)</f>
         <v>石戸谷亜子</v>
@@ -25921,8 +25990,24 @@
         <f>IF($AG16="","",IF(OR(AND(ISNUMBER($AH16),OR($AH16&lt;10,$AH16&gt;190)),AND(ISNUMBER($AI16),OR($AI16&lt;10,$AI16&gt;190))),1,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BF16" s="61" t="str">
+        <f>IFERROR(INDEX($AG$3:$AG$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>中納沙織</v>
+      </c>
+      <c r="BG16" s="62">
+        <f>IFERROR(INDEX($AH$3:$AH$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>101.71352549889134</v>
+      </c>
+      <c r="BH16" s="62">
+        <f>IFERROR(INDEX($AI$3:$AI$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>66.90456140350877</v>
+      </c>
+      <c r="BI16" s="62">
+        <f>IF($BF16="","",100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A17" s="61" t="str">
         <f>IF(ピッキング!$B$21="","",ピッキング!$B$21)</f>
         <v>森田美加</v>
@@ -26105,8 +26190,24 @@
         <f>IF($AG17="","",IF(OR(AND(ISNUMBER($AH17),OR($AH17&lt;10,$AH17&gt;190)),AND(ISNUMBER($AI17),OR($AI17&lt;10,$AI17&gt;190))),1,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BF17" s="61" t="str">
+        <f>IFERROR(INDEX($AG$3:$AG$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>山本祥吉</v>
+      </c>
+      <c r="BG17" s="62">
+        <f>IFERROR(INDEX($AH$3:$AH$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>106.22178879910837</v>
+      </c>
+      <c r="BH17" s="62">
+        <f>IFERROR(INDEX($AI$3:$AI$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>84.7367397454031</v>
+      </c>
+      <c r="BI17" s="62">
+        <f>IF($BF17="","",100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A18" s="61" t="str">
         <f>IF(ピッキング!$B$22="","",ピッキング!$B$22)</f>
         <v>河野忠</v>
@@ -26289,8 +26390,24 @@
         <f>IF($AG18="","",IF(OR(AND(ISNUMBER($AH18),OR($AH18&lt;10,$AH18&gt;190)),AND(ISNUMBER($AI18),OR($AI18&lt;10,$AI18&gt;190))),1,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BF18" s="61" t="str">
+        <f>IFERROR(INDEX($AG$3:$AG$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>鈴木香織</v>
+      </c>
+      <c r="BG18" s="62">
+        <f>IFERROR(INDEX($AH$3:$AH$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>96.54257425742574</v>
+      </c>
+      <c r="BH18" s="62">
+        <f>IFERROR(INDEX($AI$3:$AI$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>97.37824675324676</v>
+      </c>
+      <c r="BI18" s="62">
+        <f>IF($BF18="","",100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A19" s="61" t="str">
         <f>IF(ピッキング!$B$23="","",ピッキング!$B$23)</f>
         <v>木村千鶴</v>
@@ -26473,8 +26590,24 @@
         <f>IF($AG19="","",IF(OR(AND(ISNUMBER($AH19),OR($AH19&lt;10,$AH19&gt;190)),AND(ISNUMBER($AI19),OR($AI19&lt;10,$AI19&gt;190))),1,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BF19" s="61" t="str">
+        <f>IFERROR(INDEX($AG$3:$AG$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>高橋佐織</v>
+      </c>
+      <c r="BG19" s="62">
+        <f>IFERROR(INDEX($AH$3:$AH$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>106.8047477744807</v>
+      </c>
+      <c r="BH19" s="62">
+        <f>IFERROR(INDEX($AI$3:$AI$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>93.86370603420457</v>
+      </c>
+      <c r="BI19" s="62">
+        <f>IF($BF19="","",100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A20" s="61" t="str">
         <f>IF(ピッキング!$B$24="","",ピッキング!$B$24)</f>
         <v>奥野愛海</v>
@@ -26657,8 +26790,24 @@
         <f>IF($AG20="","",IF(OR(AND(ISNUMBER($AH20),OR($AH20&lt;10,$AH20&gt;190)),AND(ISNUMBER($AI20),OR($AI20&lt;10,$AI20&gt;190))),1,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BF20" s="61" t="str">
+        <f>IFERROR(INDEX($AG$3:$AG$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>後藤克行</v>
+      </c>
+      <c r="BG20" s="62">
+        <f>IFERROR(INDEX($AH$3:$AH$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>111.60069735006972</v>
+      </c>
+      <c r="BH20" s="62">
+        <f>IFERROR(INDEX($AI$3:$AI$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>80.32650966183573</v>
+      </c>
+      <c r="BI20" s="62">
+        <f>IF($BF20="","",100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A21" s="61" t="str">
         <f>IF(ピッキング!$B$25="","",ピッキング!$B$25)</f>
         <v>鈴木香織</v>
@@ -26841,8 +26990,24 @@
         <f>IF($AG21="","",IF(OR(AND(ISNUMBER($AH21),OR($AH21&lt;10,$AH21&gt;190)),AND(ISNUMBER($AI21),OR($AI21&lt;10,$AI21&gt;190))),1,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BF21" s="61" t="str">
+        <f>IFERROR(INDEX($AG$3:$AG$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>石戸谷亜子</v>
+      </c>
+      <c r="BG21" s="62">
+        <f>IFERROR(INDEX($AH$3:$AH$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>100.59261744966443</v>
+      </c>
+      <c r="BH21" s="61" t="str">
+        <f>IFERROR(INDEX($AI$3:$AI$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v/>
+      </c>
+      <c r="BI21" s="62">
+        <f>IF($BF21="","",100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A22" s="61" t="str">
         <f>IF(ピッキング!$B$26="","",ピッキング!$B$26)</f>
         <v>向井ひかり</v>
@@ -27025,8 +27190,24 @@
         <f>IF($AG22="","",IF(OR(AND(ISNUMBER($AH22),OR($AH22&lt;10,$AH22&gt;190)),AND(ISNUMBER($AI22),OR($AI22&lt;10,$AI22&gt;190))),1,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BF22" s="61" t="str">
+        <f>IFERROR(INDEX($AG$3:$AG$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>澤田凌</v>
+      </c>
+      <c r="BG22" s="62">
+        <f>IFERROR(INDEX($AH$3:$AH$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>138.5160642570281</v>
+      </c>
+      <c r="BH22" s="62">
+        <f>IFERROR(INDEX($AI$3:$AI$62,MATCH(SMALL($AM$3:$AM$62,ROW()-2),$AM$3:$AM$62,0)),"")</f>
+        <v>72.98028322440088</v>
+      </c>
+      <c r="BI22" s="62">
+        <f>IF($BF22="","",100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A23" s="61" t="str">
         <f>IF(ピッキング!$B$27="","",ピッキング!$B$27)</f>
         <v>片岡達也</v>
@@ -27210,7 +27391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A24" s="61" t="str">
         <f>IF(ピッキング!$B$28="","",ピッキング!$B$28)</f>
         <v>廣瀬こずえ</v>
@@ -27394,7 +27575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A25" s="61" t="str">
         <f>IF(ピッキング!$B$29="","",ピッキング!$B$29)</f>
         <v>森本久美</v>
@@ -27578,7 +27759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A26" s="61" t="str">
         <f>IF(ピッキング!$B$30="","",ピッキング!$B$30)</f>
         <v>菊池敬</v>
@@ -27762,7 +27943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A27" s="61" t="str">
         <f>IF(ピッキング!$B$31="","",ピッキング!$B$31)</f>
         <v>高橋正美</v>
@@ -27946,7 +28127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A28" s="61" t="str">
         <f>IF(ピッキング!$B$32="","",ピッキング!$B$32)</f>
         <v>秋草文恵</v>
@@ -28130,7 +28311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A29" s="61" t="str">
         <f>IF(ピッキング!$B$33="","",ピッキング!$B$33)</f>
         <v>上村和恵</v>
@@ -28314,7 +28495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A30" s="61" t="str">
         <f>IF(ピッキング!$B$34="","",ピッキング!$B$34)</f>
         <v>平田学</v>
@@ -28498,7 +28679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A31" s="61" t="str">
         <f>IF(ピッキング!$B$35="","",ピッキング!$B$35)</f>
         <v>飯田由加里</v>
@@ -28682,7 +28863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A32" s="61" t="str">
         <f>IF(ピッキング!$B$36="","",ピッキング!$B$36)</f>
         <v/>
@@ -28866,7 +29047,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A33" s="61" t="str">
         <f>IF(ピッキング!$B$37="","",ピッキング!$B$37)</f>
         <v/>
@@ -29050,7 +29231,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A34" s="61" t="str">
         <f>IF(ピッキング!$B$38="","",ピッキング!$B$38)</f>
         <v/>
@@ -29234,7 +29415,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A35" s="61" t="str">
         <f>IF(ピッキング!$B$39="","",ピッキング!$B$39)</f>
         <v/>
@@ -29418,7 +29599,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A36" s="61" t="str">
         <f>IF(ピッキング!$B$40="","",ピッキング!$B$40)</f>
         <v/>
@@ -29602,7 +29783,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A37" s="61" t="str">
         <f>IF(ピッキング!$B$41="","",ピッキング!$B$41)</f>
         <v/>
@@ -29786,7 +29967,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A38" s="61" t="str">
         <f>IF(ピッキング!$B$42="","",ピッキング!$B$42)</f>
         <v/>
@@ -29970,7 +30151,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A39" s="61" t="str">
         <f>IF(ピッキング!$B$43="","",ピッキング!$B$43)</f>
         <v/>
@@ -30154,7 +30335,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A40" s="61" t="str">
         <f>IF(ピッキング!$B$44="","",ピッキング!$B$44)</f>
         <v/>
@@ -30338,7 +30519,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A41" s="61" t="str">
         <f>IF(ピッキング!$B$45="","",ピッキング!$B$45)</f>
         <v/>
@@ -30522,7 +30703,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A42" s="61" t="str">
         <f>IF(ピッキング!$B$46="","",ピッキング!$B$46)</f>
         <v/>
@@ -30706,7 +30887,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A43" s="61" t="str">
         <f>IF(ピッキング!$B$47="","",ピッキング!$B$47)</f>
         <v/>
@@ -30890,7 +31071,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A44" s="61" t="str">
         <f>IF(ピッキング!$B$48="","",ピッキング!$B$48)</f>
         <v/>
@@ -31074,7 +31255,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A45" s="61" t="str">
         <f>IF(ピッキング!$B$49="","",ピッキング!$B$49)</f>
         <v/>
@@ -31258,7 +31439,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A46" s="61" t="str">
         <f>IF(ピッキング!$B$50="","",ピッキング!$B$50)</f>
         <v/>
@@ -31442,7 +31623,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A47" s="61" t="str">
         <f>IF(ピッキング!$B$51="","",ピッキング!$B$51)</f>
         <v/>
@@ -31626,7 +31807,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A48" s="61" t="str">
         <f>IF(ピッキング!$B$52="","",ピッキング!$B$52)</f>
         <v/>
@@ -31810,7 +31991,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A49" s="61" t="str">
         <f>IF(ピッキング!$B$53="","",ピッキング!$B$53)</f>
         <v/>
@@ -31994,7 +32175,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A50" s="61" t="str">
         <f>IF(ピッキング!$B$54="","",ピッキング!$B$54)</f>
         <v/>
@@ -32178,7 +32359,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A51" s="61" t="str">
         <f>IF(ピッキング!$B$55="","",ピッキング!$B$55)</f>
         <v/>
@@ -32362,7 +32543,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A52" s="61" t="str">
         <f>IF(ピッキング!$B$56="","",ピッキング!$B$56)</f>
         <v/>
@@ -32546,7 +32727,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A53" s="61" t="str">
         <f>IF(ピッキング!$B$57="","",ピッキング!$B$57)</f>
         <v/>
@@ -32730,7 +32911,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A54" s="61" t="str">
         <f>IF(ピッキング!$B$58="","",ピッキング!$B$58)</f>
         <v/>
@@ -32914,7 +33095,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A55" s="61" t="str">
         <f>IF(ピッキング!$B$59="","",ピッキング!$B$59)</f>
         <v/>
@@ -33098,7 +33279,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A56" s="61" t="str">
         <f>IF(ピッキング!$B$60="","",ピッキング!$B$60)</f>
         <v/>
@@ -33282,7 +33463,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A57" s="61" t="str">
         <f>IF(ピッキング!$B$61="","",ピッキング!$B$61)</f>
         <v/>
@@ -33466,7 +33647,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A58" s="61" t="str">
         <f>IF(ピッキング!$B$62="","",ピッキング!$B$62)</f>
         <v/>
@@ -33650,7 +33831,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A59" s="61" t="str">
         <f>IF(ピッキング!$B$63="","",ピッキング!$B$63)</f>
         <v/>
@@ -33834,7 +34015,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A60" s="61" t="str">
         <f>IF(ピッキング!$B$64="","",ピッキング!$B$64)</f>
         <v/>
@@ -34018,7 +34199,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A61" s="61" t="str">
         <f>IF(ピッキング!$B$65="","",ピッキング!$B$65)</f>
         <v/>
@@ -34202,7 +34383,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:56" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A62" s="61" t="str">
         <f>IF(ピッキング!$B$66="","",ピッキング!$B$66)</f>
         <v/>
@@ -34470,8 +34651,8 @@
       <c r="Q3" s="64"/>
       <c r="R3" s="64"/>
       <c r="T3" s="86" t="str">
-        <f>"② ピッキング・梱包 内訳比較（全員 "&amp;COUNT(印刷用データ!$AS$3:$AS$62)&amp;"名）"</f>
-        <v>② ピッキング・梱包 内訳比較（全員 29名）</v>
+        <f>"② ピッキング・梱包 内訳比較（改善優先 上位 "&amp;MIN(20,COUNT(印刷用データ!$AS$3:$AS$62))&amp;"名）"</f>
+        <v>② ピッキング・梱包 内訳比較（改善優先 上位 20名）</v>
       </c>
       <c r="U3" s="77"/>
       <c r="V3" s="77"/>
@@ -36429,8 +36610,8 @@
     </row>
     <row r="62" spans="2:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="85" t="str">
-        <f>"※ ①〜④ は実績のある全員 "&amp;COUNT(印刷用データ!AS3:AS62)&amp;" 名。「工程」が PKのみ／梱包のみ の人は、その工程だけの標準時間 ÷ 実測時間です。③ でもう一方の実績が無い "&amp;(COUNT(印刷用データ!AS3:AS62)-COUNT(印刷用データ!N3:N62))&amp;" 名は、下の帯に灰色の三角で並べています。出典: 2026年4月 実績。"&amp;IF(SUM(印刷用データ!BD3:BD62)&gt;0,"　【要確認】③ は縦横とも 10〜190% の範囲で描いています。範囲外のため図に出ていない人が "&amp;SUM(印刷用データ!BD3:BD62)&amp;" 名います。","")</f>
-        <v>※ ①〜④ は実績のある全員 29 名。「工程」が PKのみ／梱包のみ の人は、その工程だけの標準時間 ÷ 実測時間です。③ でもう一方の実績が無い 10 名は、下の帯に灰色の三角で並べています。出典: 2026年4月 実績。</v>
+        <f>"※ ①③④ は実績のある全員 "&amp;COUNT(印刷用データ!AS3:AS62)&amp;" 名。② は改善優先の上位 "&amp;MIN(20,COUNT(印刷用データ!$AS$3:$AS$62))&amp;" 名です（全員の順位は④の表）。「工程」が PKのみ／梱包のみ の人は、その工程だけの標準時間 ÷ 実測時間です。③ でもう一方の実績が無い "&amp;(COUNT(印刷用データ!AS3:AS62)-COUNT(印刷用データ!N3:N62))&amp;" 名は、下の帯に灰色の三角で並べています。出典: 2026年4月 実績。"&amp;IF(SUM(印刷用データ!BD3:BD62)&gt;0,"　【要確認】③ は縦横とも 10〜190% の範囲で描いています。範囲外のため図に出ていない人が "&amp;SUM(印刷用データ!BD3:BD62)&amp;" 名います。","")</f>
+        <v>※ ①③④ は実績のある全員 29 名。② は改善優先の上位 20 名です（全員の順位は④の表）。「工程」が PKのみ／梱包のみ の人は、その工程だけの標準時間 ÷ 実測時間です。③ でもう一方の実績が無い 10 名は、下の帯に灰色の三角で並べています。出典: 2026年4月 実績。</v>
       </c>
       <c r="C62" s="77"/>
       <c r="D62" s="77"/>

--- a/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
+++ b/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
@@ -59,7 +59,7 @@
     <definedName name="_s6x">OFFSET(散布図!$BJ$8,0,0,MAX(1,COUNT(散布図!$BJ$8:$BJ$67)),1)</definedName>
     <definedName name="_s6y">OFFSET(散布図!$BK$8,0,0,MAX(1,COUNT(散布図!$BJ$8:$BJ$67)),1)</definedName>
     <definedName name="_s6z">OFFSET(散布図!$BL$8,0,0,MAX(1,COUNT(散布図!$BJ$8:$BJ$67)),1)</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">印刷用!$A$1:$AA$62</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">印刷用!$A$1:$AA$63</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">印刷用!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -22325,7 +22325,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="B2:G21"/>
+  <dimension ref="B2:G27"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -22378,13 +22378,15 @@
         <v>362</v>
       </c>
       <c r="E6" s="56">
-        <v>92.1</v>
+        <v>56.05</v>
       </c>
       <c r="F6" s="21" t="s">
         <v>363</v>
       </c>
-      <c r="G6" s="24" t="s">
-        <v>364</v>
+      <c r="G6" s="24" t="inlineStr">
+        <is>
+          <t>① リストを見る 10.0 ＋ ④ 伝票を挟む 46.05</t>
+        </is>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.15">
@@ -22558,6 +22560,80 @@
       </c>
       <c r="D21" s="24" t="s">
         <v>380</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.15">
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>会社目標</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.15">
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>会社が定めた1件あたりの目標時間です。工程ごとにそれぞれ 1.6 分。ここは変更しない前提の数字です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.15">
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>工程</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>目標</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>単位</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>秒に直すと</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.15">
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>ピッキング</t>
+        </is>
+      </c>
+      <c r="C26" s="56">
+        <v>1.6</v>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>分/件</t>
+        </is>
+      </c>
+      <c r="E26" s="56">
+        <f>C26*60</f>
+        <v>96.0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.15">
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>梱包</t>
+        </is>
+      </c>
+      <c r="C27" s="56">
+        <v>1.6</v>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>分/件</t>
+        </is>
+      </c>
+      <c r="E27" s="56">
+        <f>C27*60</f>
+        <v>96.0</v>
       </c>
     </row>
   </sheetData>
@@ -22948,13 +23024,13 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:BI62"/>
+  <dimension ref="A1:BL62"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="61" width="11" customWidth="1"/>
+    <col min="1" max="64" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A1" s="60" t="s">
         <v>0</v>
       </c>
@@ -22991,7 +23067,7 @@
         </is>
       </c>
     </row>
-    <row r="2" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A2" s="39" t="s">
         <v>428</v>
       </c>
@@ -23182,8 +23258,17 @@
       <c r="BC2" s="39">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BK2" s="39" t="inlineStr">
+        <is>
+          <t>会社目標(分/件)</t>
+        </is>
+      </c>
+      <c r="BL2" s="62">
+        <f>設定!$C$26</f>
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A3" s="61" t="str">
         <f>IF(ピッキング!$B$7="","",ピッキング!$B$7)</f>
         <v>本吉有美子</v>
@@ -23406,8 +23491,17 @@
         <f>IF($BF3="","",100)</f>
         <v>100</v>
       </c>
-    </row>
-    <row r="4" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BK3" s="39" t="inlineStr">
+        <is>
+          <t>PK 総件数</t>
+        </is>
+      </c>
+      <c r="BL3" s="62">
+        <f>SUM(ピッキング!$C$7:$C$66)</f>
+        <v>21249</v>
+      </c>
+    </row>
+    <row r="4" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A4" s="61" t="str">
         <f>IF(ピッキング!$B$8="","",ピッキング!$B$8)</f>
         <v>澤田凌</v>
@@ -23606,8 +23700,17 @@
         <f>IF($BF4="","",100)</f>
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BK4" s="39" t="inlineStr">
+        <is>
+          <t>PK 総企業数</t>
+        </is>
+      </c>
+      <c r="BL4" s="62">
+        <f>SUM(ピッキング!$E$7:$E$66)</f>
+        <v>9114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A5" s="61" t="str">
         <f>IF(ピッキング!$B$9="","",ピッキング!$B$9)</f>
         <v>大江美記子</v>
@@ -23806,8 +23909,17 @@
         <f>IF($BF5="","",100)</f>
         <v>100</v>
       </c>
-    </row>
-    <row r="6" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BK5" s="39" t="inlineStr">
+        <is>
+          <t>PK 総実測(分)</t>
+        </is>
+      </c>
+      <c r="BL5" s="62">
+        <f>SUM(ピッキング!$D$7:$D$66)</f>
+        <v>40783</v>
+      </c>
+    </row>
+    <row r="6" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A6" s="61" t="str">
         <f>IF(ピッキング!$B$10="","",ピッキング!$B$10)</f>
         <v>佐藤辰成</v>
@@ -24006,8 +24118,17 @@
         <f>IF($BF6="","",100)</f>
         <v>100</v>
       </c>
-    </row>
-    <row r="7" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BK6" s="39" t="inlineStr">
+        <is>
+          <t>PK 会社目標達成率(%)</t>
+        </is>
+      </c>
+      <c r="BL6" s="62">
+        <f>IF($BL$5=0,"",$BL$2*$BL$3/$BL$5*100)</f>
+        <v>83.36414682588334</v>
+      </c>
+    </row>
+    <row r="7" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A7" s="61" t="str">
         <f>IF(ピッキング!$B$11="","",ピッキング!$B$11)</f>
         <v>春谷智子</v>
@@ -24206,8 +24327,17 @@
         <f>IF($BF7="","",100)</f>
         <v>100</v>
       </c>
-    </row>
-    <row r="8" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BK7" s="39" t="inlineStr">
+        <is>
+          <t>PK 1社あたり件数</t>
+        </is>
+      </c>
+      <c r="BL7" s="62">
+        <f>IF($BL$4=0,"",$BL$3/$BL$4)</f>
+        <v>2.3314680710994073</v>
+      </c>
+    </row>
+    <row r="8" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A8" s="61" t="str">
         <f>IF(ピッキング!$B$12="","",ピッキング!$B$12)</f>
         <v>後藤克行</v>
@@ -24406,8 +24536,17 @@
         <f>IF($BF8="","",100)</f>
         <v>100</v>
       </c>
-    </row>
-    <row r="9" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BK8" s="39" t="inlineStr">
+        <is>
+          <t>PK 段取り(秒/件)</t>
+        </is>
+      </c>
+      <c r="BL8" s="62">
+        <f>IF($BL$3=0,"",設定!$E$6*$BL$4/$BL$3)</f>
+        <v>24.040646618664404</v>
+      </c>
+    </row>
+    <row r="9" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A9" s="61" t="str">
         <f>IF(ピッキング!$B$13="","",ピッキング!$B$13)</f>
         <v>中村美佳</v>
@@ -24606,8 +24745,17 @@
         <f>IF($BF9="","",100)</f>
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BK9" s="39" t="inlineStr">
+        <is>
+          <t>PK 1.6分に必要な1社件数</t>
+        </is>
+      </c>
+      <c r="BL9" s="62">
+        <f>IF(設定!$E$26-設定!$E$7&lt;=0,"",設定!$E$6/(設定!$E$26-設定!$E$7))</f>
+        <v>2.7475490196078423</v>
+      </c>
+    </row>
+    <row r="10" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A10" s="61" t="str">
         <f>IF(ピッキング!$B$14="","",ピッキング!$B$14)</f>
         <v>晩田恵美</v>
@@ -24807,7 +24955,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A11" s="61" t="str">
         <f>IF(ピッキング!$B$15="","",ピッキング!$B$15)</f>
         <v>高橋佐織</v>
@@ -25006,8 +25154,17 @@
         <f>IF($BF11="","",100)</f>
         <v>100</v>
       </c>
-    </row>
-    <row r="12" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BK11" s="39" t="inlineStr">
+        <is>
+          <t>梱包 総件数</t>
+        </is>
+      </c>
+      <c r="BL11" s="62">
+        <f>SUM(梱包!$C$7:$C$66)</f>
+        <v>24467</v>
+      </c>
+    </row>
+    <row r="12" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A12" s="61" t="str">
         <f>IF(ピッキング!$B$16="","",ピッキング!$B$16)</f>
         <v>山本祥吉</v>
@@ -25206,8 +25363,17 @@
         <f>IF($BF12="","",100)</f>
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BK12" s="39" t="inlineStr">
+        <is>
+          <t>梱包 総実測(分)</t>
+        </is>
+      </c>
+      <c r="BL12" s="62">
+        <f>SUM(梱包!$D$7:$D$66)</f>
+        <v>39187</v>
+      </c>
+    </row>
+    <row r="13" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A13" s="61" t="str">
         <f>IF(ピッキング!$B$17="","",ピッキング!$B$17)</f>
         <v>佐々木千恵</v>
@@ -25406,8 +25572,17 @@
         <f>IF($BF13="","",100)</f>
         <v>100</v>
       </c>
-    </row>
-    <row r="14" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="BK13" s="39" t="inlineStr">
+        <is>
+          <t>梱包 会社目標達成率(%)</t>
+        </is>
+      </c>
+      <c r="BL13" s="62">
+        <f>IF($BL$12=0,"",設定!$C$27*$BL$11/$BL$12*100)</f>
+        <v>99.89843570571875</v>
+      </c>
+    </row>
+    <row r="14" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A14" s="61" t="str">
         <f>IF(ピッキング!$B$18="","",ピッキング!$B$18)</f>
         <v>北田倫子</v>
@@ -25607,7 +25782,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A15" s="61" t="str">
         <f>IF(ピッキング!$B$19="","",ピッキング!$B$19)</f>
         <v>中納沙織</v>
@@ -25807,7 +25982,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A16" s="61" t="str">
         <f>IF(ピッキング!$B$20="","",ピッキング!$B$20)</f>
         <v>石戸谷亜子</v>
@@ -26007,7 +26182,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A17" s="61" t="str">
         <f>IF(ピッキング!$B$21="","",ピッキング!$B$21)</f>
         <v>森田美加</v>
@@ -26207,7 +26382,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A18" s="61" t="str">
         <f>IF(ピッキング!$B$22="","",ピッキング!$B$22)</f>
         <v>河野忠</v>
@@ -26407,7 +26582,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A19" s="61" t="str">
         <f>IF(ピッキング!$B$23="","",ピッキング!$B$23)</f>
         <v>木村千鶴</v>
@@ -26607,7 +26782,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A20" s="61" t="str">
         <f>IF(ピッキング!$B$24="","",ピッキング!$B$24)</f>
         <v>奥野愛海</v>
@@ -26807,7 +26982,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A21" s="61" t="str">
         <f>IF(ピッキング!$B$25="","",ピッキング!$B$25)</f>
         <v>鈴木香織</v>
@@ -27007,7 +27182,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A22" s="61" t="str">
         <f>IF(ピッキング!$B$26="","",ピッキング!$B$26)</f>
         <v>向井ひかり</v>
@@ -27207,7 +27382,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A23" s="61" t="str">
         <f>IF(ピッキング!$B$27="","",ピッキング!$B$27)</f>
         <v>片岡達也</v>
@@ -27391,7 +27566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A24" s="61" t="str">
         <f>IF(ピッキング!$B$28="","",ピッキング!$B$28)</f>
         <v>廣瀬こずえ</v>
@@ -27575,7 +27750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A25" s="61" t="str">
         <f>IF(ピッキング!$B$29="","",ピッキング!$B$29)</f>
         <v>森本久美</v>
@@ -27759,7 +27934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A26" s="61" t="str">
         <f>IF(ピッキング!$B$30="","",ピッキング!$B$30)</f>
         <v>菊池敬</v>
@@ -27943,7 +28118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A27" s="61" t="str">
         <f>IF(ピッキング!$B$31="","",ピッキング!$B$31)</f>
         <v>高橋正美</v>
@@ -28127,7 +28302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A28" s="61" t="str">
         <f>IF(ピッキング!$B$32="","",ピッキング!$B$32)</f>
         <v>秋草文恵</v>
@@ -28311,7 +28486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A29" s="61" t="str">
         <f>IF(ピッキング!$B$33="","",ピッキング!$B$33)</f>
         <v>上村和恵</v>
@@ -28495,7 +28670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A30" s="61" t="str">
         <f>IF(ピッキング!$B$34="","",ピッキング!$B$34)</f>
         <v>平田学</v>
@@ -28679,7 +28854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A31" s="61" t="str">
         <f>IF(ピッキング!$B$35="","",ピッキング!$B$35)</f>
         <v>飯田由加里</v>
@@ -28863,7 +29038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A32" s="61" t="str">
         <f>IF(ピッキング!$B$36="","",ピッキング!$B$36)</f>
         <v/>
@@ -29047,7 +29222,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A33" s="61" t="str">
         <f>IF(ピッキング!$B$37="","",ピッキング!$B$37)</f>
         <v/>
@@ -29231,7 +29406,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A34" s="61" t="str">
         <f>IF(ピッキング!$B$38="","",ピッキング!$B$38)</f>
         <v/>
@@ -29415,7 +29590,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A35" s="61" t="str">
         <f>IF(ピッキング!$B$39="","",ピッキング!$B$39)</f>
         <v/>
@@ -29599,7 +29774,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A36" s="61" t="str">
         <f>IF(ピッキング!$B$40="","",ピッキング!$B$40)</f>
         <v/>
@@ -29783,7 +29958,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A37" s="61" t="str">
         <f>IF(ピッキング!$B$41="","",ピッキング!$B$41)</f>
         <v/>
@@ -29967,7 +30142,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A38" s="61" t="str">
         <f>IF(ピッキング!$B$42="","",ピッキング!$B$42)</f>
         <v/>
@@ -30151,7 +30326,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A39" s="61" t="str">
         <f>IF(ピッキング!$B$43="","",ピッキング!$B$43)</f>
         <v/>
@@ -30335,7 +30510,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A40" s="61" t="str">
         <f>IF(ピッキング!$B$44="","",ピッキング!$B$44)</f>
         <v/>
@@ -30519,7 +30694,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A41" s="61" t="str">
         <f>IF(ピッキング!$B$45="","",ピッキング!$B$45)</f>
         <v/>
@@ -30703,7 +30878,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A42" s="61" t="str">
         <f>IF(ピッキング!$B$46="","",ピッキング!$B$46)</f>
         <v/>
@@ -30887,7 +31062,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A43" s="61" t="str">
         <f>IF(ピッキング!$B$47="","",ピッキング!$B$47)</f>
         <v/>
@@ -31071,7 +31246,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A44" s="61" t="str">
         <f>IF(ピッキング!$B$48="","",ピッキング!$B$48)</f>
         <v/>
@@ -31255,7 +31430,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A45" s="61" t="str">
         <f>IF(ピッキング!$B$49="","",ピッキング!$B$49)</f>
         <v/>
@@ -31439,7 +31614,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A46" s="61" t="str">
         <f>IF(ピッキング!$B$50="","",ピッキング!$B$50)</f>
         <v/>
@@ -31623,7 +31798,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A47" s="61" t="str">
         <f>IF(ピッキング!$B$51="","",ピッキング!$B$51)</f>
         <v/>
@@ -31807,7 +31982,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A48" s="61" t="str">
         <f>IF(ピッキング!$B$52="","",ピッキング!$B$52)</f>
         <v/>
@@ -31991,7 +32166,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A49" s="61" t="str">
         <f>IF(ピッキング!$B$53="","",ピッキング!$B$53)</f>
         <v/>
@@ -32175,7 +32350,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A50" s="61" t="str">
         <f>IF(ピッキング!$B$54="","",ピッキング!$B$54)</f>
         <v/>
@@ -32359,7 +32534,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A51" s="61" t="str">
         <f>IF(ピッキング!$B$55="","",ピッキング!$B$55)</f>
         <v/>
@@ -32543,7 +32718,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A52" s="61" t="str">
         <f>IF(ピッキング!$B$56="","",ピッキング!$B$56)</f>
         <v/>
@@ -32727,7 +32902,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A53" s="61" t="str">
         <f>IF(ピッキング!$B$57="","",ピッキング!$B$57)</f>
         <v/>
@@ -32911,7 +33086,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A54" s="61" t="str">
         <f>IF(ピッキング!$B$58="","",ピッキング!$B$58)</f>
         <v/>
@@ -33095,7 +33270,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A55" s="61" t="str">
         <f>IF(ピッキング!$B$59="","",ピッキング!$B$59)</f>
         <v/>
@@ -33279,7 +33454,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A56" s="61" t="str">
         <f>IF(ピッキング!$B$60="","",ピッキング!$B$60)</f>
         <v/>
@@ -33463,7 +33638,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A57" s="61" t="str">
         <f>IF(ピッキング!$B$61="","",ピッキング!$B$61)</f>
         <v/>
@@ -33647,7 +33822,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A58" s="61" t="str">
         <f>IF(ピッキング!$B$62="","",ピッキング!$B$62)</f>
         <v/>
@@ -33831,7 +34006,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A59" s="61" t="str">
         <f>IF(ピッキング!$B$63="","",ピッキング!$B$63)</f>
         <v/>
@@ -34015,7 +34190,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A60" s="61" t="str">
         <f>IF(ピッキング!$B$64="","",ピッキング!$B$64)</f>
         <v/>
@@ -34199,7 +34374,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A61" s="61" t="str">
         <f>IF(ピッキング!$B$65="","",ピッキング!$B$65)</f>
         <v/>
@@ -34383,7 +34558,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:61" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A62" s="61" t="str">
         <f>IF(ピッキング!$B$66="","",ピッキング!$B$66)</f>
         <v/>
@@ -34578,7 +34753,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AA62"/>
+  <dimension ref="B1:AA63"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
@@ -36639,8 +36814,40 @@
       <c r="Z62" s="77"/>
       <c r="AA62" s="77"/>
     </row>
+    <row r="63" spans="2:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B63" s="85" t="str">
+        <f>"■ 会社目標（工程ごと 1.6分/件）に対する達成率は ピッキング "&amp;TEXT(印刷用データ!$BL$6,"0.0")&amp;"％・梱包 "&amp;TEXT(印刷用データ!$BL$13,"0.0")&amp;"％。ピッキングは1社あたり "&amp;TEXT(印刷用データ!$BL$7,"0.00")&amp;" 件のため段取りだけで "&amp;TEXT(印刷用データ!$BL$8,"0.0")&amp;" 秒/件かかり、1.6分に収めるには1社あたり "&amp;TEXT(印刷用データ!$BL$9,"0.00")&amp;" 件が必要です。"</f>
+        <v>■ 会社目標（工程ごと 1.6分/件）に対する達成率は ピッキング 83.4％・梱包 99.9％。ピッキングは1社あたり 2.33 件のため段取りだけで 24.0 秒/件かかり、1.6分に収めるには1社あたり 2.75 件が必要です。</v>
+      </c>
+      <c r="C63" s="77"/>
+      <c r="D63" s="77"/>
+      <c r="E63" s="77"/>
+      <c r="F63" s="77"/>
+      <c r="G63" s="77"/>
+      <c r="H63" s="77"/>
+      <c r="I63" s="77"/>
+      <c r="J63" s="77"/>
+      <c r="K63" s="77"/>
+      <c r="L63" s="77"/>
+      <c r="M63" s="77"/>
+      <c r="N63" s="77"/>
+      <c r="O63" s="77"/>
+      <c r="P63" s="77"/>
+      <c r="Q63" s="77"/>
+      <c r="R63" s="77"/>
+      <c r="S63" s="77"/>
+      <c r="T63" s="77"/>
+      <c r="U63" s="77"/>
+      <c r="V63" s="77"/>
+      <c r="W63" s="77"/>
+      <c r="X63" s="77"/>
+      <c r="Y63" s="77"/>
+      <c r="Z63" s="77"/>
+      <c r="AA63" s="77"/>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="B63:AA63"/>
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="M3:R3"/>
     <mergeCell ref="B62:AA62"/>

--- a/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
+++ b/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
@@ -25781,6 +25781,15 @@
         <f>IF($BF14="","",100)</f>
         <v>100</v>
       </c>
+      <c r="BK14" s="39" t="inlineStr">
+        <is>
+          <t>PK 実測(秒/件)</t>
+        </is>
+      </c>
+      <c r="BL14" s="62">
+        <f>IF($BL$3=0,"",$BL$5*60/$BL$3)</f>
+        <v>115.15741917266695</v>
+      </c>
     </row>
     <row r="15" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A15" s="61" t="str">
@@ -25981,6 +25990,15 @@
         <f>IF($BF15="","",100)</f>
         <v>100</v>
       </c>
+      <c r="BK15" s="39" t="inlineStr">
+        <is>
+          <t>PK 標準(秒/件)</t>
+        </is>
+      </c>
+      <c r="BL15" s="62">
+        <f>IF($BL$3=0,"",設定!$E$6*$BL$4/$BL$3+設定!$E$7)</f>
+        <v>99.64064661866439</v>
+      </c>
     </row>
     <row r="16" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A16" s="61" t="str">
@@ -26181,6 +26199,15 @@
         <f>IF($BF16="","",100)</f>
         <v>100</v>
       </c>
+      <c r="BK16" s="39" t="inlineStr">
+        <is>
+          <t>PK 未達 速さ由来</t>
+        </is>
+      </c>
+      <c r="BL16" s="62">
+        <f>IF($BL$3=0,"",$BL$14-$BL$15)</f>
+        <v>15.516772554002557</v>
+      </c>
     </row>
     <row r="17" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A17" s="61" t="str">
@@ -26381,6 +26408,15 @@
         <f>IF($BF17="","",100)</f>
         <v>100</v>
       </c>
+      <c r="BK17" s="39" t="inlineStr">
+        <is>
+          <t>PK 未達 構成由来</t>
+        </is>
+      </c>
+      <c r="BL17" s="62">
+        <f>IF($BL$3=0,"",$BL$15-設定!$E$26)</f>
+        <v>3.640646618664391</v>
+      </c>
     </row>
     <row r="18" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A18" s="61" t="str">
@@ -26580,6 +26616,15 @@
       <c r="BI18" s="62">
         <f>IF($BF18="","",100)</f>
         <v>100</v>
+      </c>
+      <c r="BK18" s="39" t="inlineStr">
+        <is>
+          <t>PK 未達 合計</t>
+        </is>
+      </c>
+      <c r="BL18" s="62">
+        <f>IF($BL$3=0,"",$BL$14-設定!$E$26)</f>
+        <v>19.15741917266695</v>
       </c>
     </row>
     <row r="19" spans="1:64" ht="16.5" x14ac:dyDescent="0.35">
@@ -36816,8 +36861,8 @@
     </row>
     <row r="63" spans="2:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B63" s="85" t="str">
-        <f>"■ 会社目標（工程ごと 1.6分/件）に対する達成率は ピッキング "&amp;TEXT(印刷用データ!$BL$6,"0.0")&amp;"％・梱包 "&amp;TEXT(印刷用データ!$BL$13,"0.0")&amp;"％。ピッキングは1社あたり "&amp;TEXT(印刷用データ!$BL$7,"0.00")&amp;" 件のため段取りだけで "&amp;TEXT(印刷用データ!$BL$8,"0.0")&amp;" 秒/件かかり、1.6分に収めるには1社あたり "&amp;TEXT(印刷用データ!$BL$9,"0.00")&amp;" 件が必要です。"</f>
-        <v>■ 会社目標（工程ごと 1.6分/件）に対する達成率は ピッキング 83.4％・梱包 99.9％。ピッキングは1社あたり 2.33 件のため段取りだけで 24.0 秒/件かかり、1.6分に収めるには1社あたり 2.75 件が必要です。</v>
+        <f>"■ 会社目標（工程ごと 1.6分/件）に対する達成率は ピッキング "&amp;TEXT(印刷用データ!$BL$6,"0.0")&amp;"％・梱包 "&amp;TEXT(印刷用データ!$BL$13,"0.0")&amp;"％。ピッキングの未達 "&amp;TEXT(印刷用データ!$BL$18,"0.0")&amp;" 秒/件の内訳は、速さ由来 "&amp;TEXT(印刷用データ!$BL$16,"0.0")&amp;" 秒・リスト構成由来 "&amp;TEXT(印刷用データ!$BL$17,"0.0")&amp;" 秒（1社あたり "&amp;TEXT(印刷用データ!$BL$7,"0.00")&amp;" 件のため。1.6分には "&amp;TEXT(印刷用データ!$BL$9,"0.00")&amp;" 件が必要）。"</f>
+        <v>■ 会社目標（工程ごと 1.6分/件）に対する達成率は ピッキング 83.4％・梱包 99.9％。ピッキングの未達 19.2 秒/件の内訳は、速さ由来 15.5 秒・リスト構成由来 3.6 秒（1社あたり 2.33 件のため。1.6分には 2.75 件が必要）。</v>
       </c>
       <c r="C63" s="77"/>
       <c r="D63" s="77"/>

--- a/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
+++ b/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
@@ -3187,12 +3187,194 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>[1]!_dbS1x</c:f>
+              <c:f>ダッシュボード!$AF$3:$AF$62</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>0.4202200825309491</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5759493670886076</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.49031600407747195</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.22188905547226387</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.5983606557377049</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.4778276033881415</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.379746835443038</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.2633979475484607</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.4250797024442083</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.3457022076092062</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.28046989720998533</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.6004273504273504</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.4864391951006124</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.3333333333333333</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.4392857142857143</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.4905933429811867</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.5024038461538461</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.5541125541125541</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.4491916859122402</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.7121212121212122</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.5286396181384249</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.3194029850746269</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.43838862559241704</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.3926605504587156</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.4557109557109557</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.4181654676258993</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.5498154981549815</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>[1]!_dbS1y</c:f>
+              <c:f>ダッシュボード!$AG$3:$AG$62</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>83.68638239339752</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>94.55696202531645</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>93.88379204892966</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>72.86356821589206</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>103.27868852459017</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>107.17488789237669</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>91.13924050632912</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>92.0866590649943</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>107.43889479277364</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>101.14607797087835</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>95.33039647577093</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>128.33333333333334</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>118.37270341207349</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>105.67375886524823</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>123.85321100917432</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>118.28571428571429</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>121.21562952243126</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>133.41346153846155</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>131.16883116883116</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>129.9769053117783</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>183.63636363636363</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>141.19331742243438</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>128.23880597014926</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>135.07109004739337</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>138.1651376146789</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>146.43356643356643</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>143.79496402877697</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>198.64864864864865</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>169.15129151291512</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
@@ -3220,7 +3402,7 @@
           <c:max val="0.8"/>
           <c:min val="0"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -3270,7 +3452,7 @@
           <c:max val="200"/>
           <c:min val="0"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -12635,12 +12817,194 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>[1]!_s1x</c:f>
+              <c:f>散布図!$AE$8:$AE$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>0.4202200825309491</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5759493670886076</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.49031600407747195</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.22188905547226387</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.5983606557377049</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.4778276033881415</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.379746835443038</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.2633979475484607</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.4250797024442083</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.3457022076092062</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.28046989720998533</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.6004273504273504</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.4864391951006124</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.3333333333333333</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.4392857142857143</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.4905933429811867</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.5024038461538461</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.5541125541125541</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.4491916859122402</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.7121212121212122</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.5286396181384249</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.3194029850746269</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.43838862559241704</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.3926605504587156</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.4557109557109557</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.4181654676258993</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.5498154981549815</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>[1]!_s1y</c:f>
+              <c:f>散布図!$AF$8:$AF$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>83.68638239339752</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>94.55696202531645</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>93.88379204892966</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>72.86356821589206</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>103.27868852459017</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>107.17488789237669</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>91.13924050632912</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>92.0866590649943</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>107.43889479277364</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>101.14607797087835</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>95.33039647577093</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>128.33333333333334</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>118.37270341207349</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>105.67375886524823</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>123.85321100917432</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>118.28571428571429</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>121.21562952243126</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>133.41346153846155</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>131.16883116883116</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>129.9769053117783</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>183.63636363636363</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>141.19331742243438</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>128.23880597014926</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>135.07109004739337</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>138.1651376146789</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>146.43356643356643</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>143.79496402877697</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>198.64864864864865</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>169.15129151291512</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
@@ -12717,7 +13081,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -12766,7 +13130,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -12904,12 +13268,194 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>[1]!_s2x</c:f>
+              <c:f>散布図!$AI$8:$AI$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>0.4202200825309491</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5759493670886076</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.49031600407747195</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.22188905547226387</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.5983606557377049</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.4778276033881415</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.379746835443038</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.2633979475484607</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.4250797024442083</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.3457022076092062</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.28046989720998533</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.6004273504273504</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.4864391951006124</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.3333333333333333</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.4392857142857143</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.4905933429811867</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.5024038461538461</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.5541125541125541</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.4491916859122402</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.7121212121212122</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.5286396181384249</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.3194029850746269</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.43838862559241704</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.3926605504587156</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.4557109557109557</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.4181654676258993</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.5498154981549815</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>[1]!_s2y</c:f>
+              <c:f>散布図!$AJ$8:$AJ$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>44.98411279229711</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>62.275</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>48.725688073394494</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>52.42758620689656</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>48.16967213114755</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>63.16696562032886</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>56.164556962025316</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>67.82770809578106</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>68.28905419766207</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>69.30690465007046</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>69.49911894273129</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>73.03397435897435</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>73.57165354330708</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>74.97375886524823</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>77.8032110091743</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>77.82750000000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>76.03198263386396</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>87.14206730769232</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>80.13506493506492</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>88.60635103926097</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>118.05000000000001</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>92.50560859188546</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>98.82179104477613</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>94.69549763033176</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>102.00110091743119</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>104.46258741258742</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>105.28192446043165</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>161.80864864864867</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>118.51328413284132</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
@@ -12935,7 +13481,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -12975,7 +13521,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -13096,11 +13642,11 @@
             <c:size val="7"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="2E75B6"/>
+                <a:srgbClr val="C55A11"/>
               </a:solidFill>
               <a:ln>
                 <a:solidFill>
-                  <a:srgbClr val="2E75B6"/>
+                  <a:srgbClr val="C55A11"/>
                 </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -13116,12 +13662,134 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>[1]!_s3x</c:f>
+              <c:f>散布図!$AM$8:$AM$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>0.2619334135579623</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.4400630914826498</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2580275229357798</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.17253521126760563</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.2617874736101337</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.2826666666666667</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.3429364803887539</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.28860445912469035</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.25387596899224807</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.21460674157303372</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.3273231622746186</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.16964285714285715</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.2968253968253968</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.12141652613827993</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.2582857142857143</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.3619047619047619</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.3020618556701031</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.31022823330515636</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.40810556079170596</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>[1]!_s3y</c:f>
+              <c:f>散布図!$AN$8:$AN$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>62.5511432009627</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>116.40378548895899</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>70.18348623853211</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>64.43661971830986</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>116.53764954257565</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>116.8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>83.45019090593544</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>102.36168455821635</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>109.6124031007752</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>51.91011235955056</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>73.14840499306518</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>127.23214285714286</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>185.23809523809524</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>69.30860033726813</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>129.87428571428572</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>105.6</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>96.37113402061856</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>149.26458157227387</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>82.90292177191328</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
@@ -13147,7 +13815,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -13187,7 +13855,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -13320,12 +13988,134 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>[1]!_s4x</c:f>
+              <c:f>散布図!$AQ$8:$AQ$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>127.03460719829701</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>109.608647015599</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>120.67691021365592</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>119.7425901187512</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>109.25811506173572</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>108.19661844228943</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>106.48628255257557</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>105.5199126114411</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>105.27874024037102</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>104.82956951103425</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>102.19941536738331</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>102.10123607448666</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>100.77903963067155</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>100.53479201324765</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>100.54560159272768</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>99.0427992117129</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>90.9750925905042</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>90.76031955021183</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>85.53848561318566</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>[1]!_s4y</c:f>
+              <c:f>散布図!$AR$8:$AR$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>146.66177155707118</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>96.6040089685315</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>131.04490021102978</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128.1824773344137</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>82.50800954832064</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>89.76235104145006</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>120.21334891697963</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>95.03098129485993</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>86.58781937105334</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>160.21330038970882</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>133.25785675591538</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>81.8195904305488</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>60.24629206624098</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>115.10131008792217</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>74.64765281846198</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>98.81317753034124</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>102.27473325768686</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>69.50855316564756</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>126.82484924085423</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
@@ -13351,7 +14141,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -13391,7 +14181,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -13512,12 +14302,194 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>[1]!_s5x</c:f>
+              <c:f>散布図!$BE$8:$BE$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>2769.925</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1420.4458333333332</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1974.395</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1067.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>265.775</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4000.8849999999993</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>145.58999999999997</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1459.605</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1799.6599999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3812.2999999999997</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1151.245</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1021.0149999999999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2293.64</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1498.83</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>441.995</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>541.605</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1391.025</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>844.9749999999999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>487.53999999999996</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1688.275</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>155.305</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1735.8849999999998</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>586.3449999999999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>815.6949999999999</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2030.38</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1681.2649999999999</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2114.895</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>693.3799999999999</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>570.175</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>[1]!_s5y</c:f>
+              <c:f>散布図!$BF$8:$BF$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1245</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1535</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>810</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3585</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1346</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1685</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3589</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1082</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2255</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1490</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>552</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1396</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>925</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>505</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1876</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>202</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1972</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>716</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>950</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2510</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2094</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2665</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1225</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>764</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
@@ -13594,7 +14566,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -13627,7 +14599,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -13720,11 +14692,11 @@
             <c:size val="7"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="2E75B6"/>
+                <a:srgbClr val="8C8C8C"/>
               </a:solidFill>
               <a:ln>
                 <a:solidFill>
-                  <a:srgbClr val="2E75B6"/>
+                  <a:srgbClr val="8C8C8C"/>
                 </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -13732,12 +14704,194 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>[1]!_s6x</c:f>
+              <c:f>散布図!$BJ$8:$BJ$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>11</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>[1]!_s6y</c:f>
+              <c:f>散布図!$BK$8:$BK$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>136.58407297830374</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>114.09203480589021</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>128.62508143322475</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>131.80246913580245</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>126.5595238095238</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>111.60069735006972</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>121.32499999999997</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>108.44019316493313</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>106.8047477744807</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>106.22178879910837</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>106.39972273567466</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>101.99950049950048</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>101.71352549889134</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>100.59261744966443</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>98.22111111111111</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>98.11684782608697</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>99.64362464183381</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>91.34864864864863</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>96.54257425742574</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>89.99333688699362</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>76.88366336633663</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>88.02662271805272</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>81.8917597765363</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>85.86263157894736</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>80.89163346613546</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>80.2896370582617</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>79.35816135084428</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>56.60244897959183</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>74.63023560209423</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
@@ -13764,11 +14918,11 @@
             <c:size val="7"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="C55A11"/>
+                <a:srgbClr val="2E75B6"/>
               </a:solidFill>
               <a:ln>
                 <a:solidFill>
-                  <a:srgbClr val="C55A11"/>
+                  <a:srgbClr val="2E75B6"/>
                 </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -13776,12 +14930,194 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>[1]!_s6x</c:f>
+              <c:f>散布図!$BJ$8:$BJ$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>11</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>[1]!_s6z</c:f>
+              <c:f>散布図!$BL$8:$BL$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>127.03460719829701</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>109.608647015599</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>120.67691021365592</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>119.7425901187512</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>111.28404540730916</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>109.25811506173572</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>108.19661844228943</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>106.48628255257557</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>105.5199126114411</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>105.27874024037102</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>104.82956951103425</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>102.19941536738331</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>102.10123607448666</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>101.53055698910751</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>100.77903963067155</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>100.53479201324765</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>100.54560159272768</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>99.23412966546182</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>99.0427992117129</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>94.65110162100073</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>93.27565646093761</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>93.41118109614357</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>90.9750925905042</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>90.76031955021183</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>88.91290688944902</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>88.53337654701247</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>87.51745426620545</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>85.92335307408533</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>85.53848561318566</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
@@ -13807,7 +15143,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -13838,7 +15174,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -14820,12 +16156,194 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>[1]!_dbS2x</c:f>
+              <c:f>ダッシュボード!$AK$3:$AK$62</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>0.4202200825309491</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5759493670886076</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.49031600407747195</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.22188905547226387</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.5983606557377049</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.4778276033881415</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.379746835443038</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.2633979475484607</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.4250797024442083</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.3457022076092062</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.28046989720998533</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.6004273504273504</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.4864391951006124</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.3333333333333333</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.4392857142857143</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.4905933429811867</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.5024038461538461</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.5541125541125541</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.4491916859122402</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.7121212121212122</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.5286396181384249</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.3194029850746269</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.43838862559241704</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.3926605504587156</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.4557109557109557</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.4181654676258993</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.5498154981549815</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>[1]!_dbS2y</c:f>
+              <c:f>ダッシュボード!$AL$3:$AL$62</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>44.98411279229711</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>62.275</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>48.725688073394494</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>52.42758620689656</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>48.16967213114755</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>63.16696562032886</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>56.164556962025316</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>67.82770809578106</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>68.28905419766207</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>69.30690465007046</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>69.49911894273129</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>73.03397435897435</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>73.57165354330708</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>74.97375886524823</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>77.8032110091743</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>77.82750000000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>76.03198263386396</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>87.14206730769232</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>80.13506493506492</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>88.60635103926097</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>118.05000000000001</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>92.50560859188546</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>98.82179104477613</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>94.69549763033176</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>102.00110091743119</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>104.46258741258742</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>105.28192446043165</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>161.80864864864867</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>118.51328413284132</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
@@ -14853,7 +16371,7 @@
           <c:max val="0.8"/>
           <c:min val="0"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -14903,7 +16421,7 @@
           <c:max val="200"/>
           <c:min val="0"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -15010,13 +16528,146 @@
             </c:spPr>
           </c:marker>
           <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>[1]!_dyLabel</c:f>
-            </c:multiLvlStrRef>
+            <c:strRef>
+              <c:f>日次!$C$8:$C$28</c:f>
+              <c:strCache>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>4/1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4/2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4/3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4/6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4/7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4/8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4/9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4/10</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4/13</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4/14</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4/15</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4/16</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4/17</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4/20</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4/21</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4/22</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4/23</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4/24</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4/27</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4/28</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4/30</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>[1]!_dyPickEff</c:f>
+              <c:f>日次!$G$8:$G$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>111.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>109.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>130.3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>106.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>108.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>126.8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>109.3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>95.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>78.9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>84.4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>83.1</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>96.3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>73.9</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>95.1</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>95.9</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>94.1</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>85.9</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>90.7</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>126.9</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -15053,13 +16704,146 @@
             </c:spPr>
           </c:marker>
           <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>[1]!_dyLabel</c:f>
-            </c:multiLvlStrRef>
+            <c:strRef>
+              <c:f>日次!$C$8:$C$28</c:f>
+              <c:strCache>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>4/1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4/2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4/3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4/6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4/7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4/8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4/9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4/10</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4/13</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4/14</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4/15</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4/16</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4/17</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4/20</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4/21</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4/22</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4/23</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4/24</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4/27</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4/28</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4/30</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>[1]!_dyPackEff</c:f>
+              <c:f>日次!$K$8:$K$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>102.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>98.8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>119.9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>102.8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>106.7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>102.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>116.2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>101.4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>90.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>87.2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>98.2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>98.6</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>102.7</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>97.2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>95.8</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>96.3</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>90.9</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>105.3</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>84.4</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>114.6</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>96.2</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
@@ -15068,6 +16852,168 @@
               <c16:uniqueId val="{00000001-4DA9-4773-85B3-B0CC4C39B132}"/>
             </c:ext>
           </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>目標 100%</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12000">
+              <a:solidFill>
+                <a:srgbClr val="595959"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>日次!$C$8:$C$28</c:f>
+              <c:strCache>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>4/1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4/2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4/3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4/6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4/7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4/8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4/9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4/10</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4/13</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4/14</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4/15</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4/16</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4/17</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4/20</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4/21</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4/22</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4/23</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4/24</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4/27</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4/28</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4/30</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>印刷用データ!$AV$3:$AV$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -15087,7 +17033,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -15122,7 +17068,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -15199,7 +17145,9 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:doughnutChart>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
@@ -15208,76 +17156,87 @@
             <c:v>時間</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="8C8C8C"/>
+            </a:solidFill>
           </c:spPr>
           <c:dPt>
             <c:idx val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="2E75B6"/>
+                <a:srgbClr val="8C8C8C"/>
               </a:solidFill>
               <a:ln>
-                <a:prstDash val="solid"/>
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-23BA-4D3B-A922-7F47AC2BDDB0}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="C55A11"/>
+                <a:srgbClr val="8C8C8C"/>
               </a:solidFill>
               <a:ln>
-                <a:prstDash val="solid"/>
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-23BA-4D3B-A922-7F47AC2BDDB0}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="1BAF7A"/>
+                <a:srgbClr val="2E75B6"/>
               </a:solidFill>
               <a:ln>
-                <a:prstDash val="solid"/>
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
               </a:ln>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-23BA-4D3B-A922-7F47AC2BDDB0}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>[1]!_dbMixLbl</c:f>
-            </c:multiLvlStrRef>
+            <c:strRef>
+              <c:f>ダッシュボード!$AZ$3:$AZ$5</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>段取り　233.2h・34.3%</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>移動　223.1h・32.8%</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>ピック　223.1h・32.8%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>[1]!_dbMixVal</c:f>
+              <c:f>ダッシュボード!$AX$3:$AX$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>233.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>223.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>223.1</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-23BA-4D3B-A922-7F47AC2BDDB0}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -15286,16 +17245,62 @@
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="1"/>
         </c:dLbls>
-        <c:firstSliceAng val="0"/>
-        <c:holeSize val="62"/>
-      </c:doughnutChart>
+        <c:gapWidth val="60"/>
+        <c:axId val="30"/>
+        <c:axId val="40"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="30"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="40"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="40"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:t>時間 (h)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="1"/>
+        </c:title>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="30"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="1"/>
-    </c:legend>
     <c:plotVisOnly val="0"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="1"/>
@@ -15347,7 +17352,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="C55A11"/>
+              <a:srgbClr val="8C8C8C"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -15356,13 +17361,92 @@
           </c:spPr>
           <c:invertIfNegative val="1"/>
           <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>[1]!_dbTopName</c:f>
-            </c:multiLvlStrRef>
+            <c:strRef>
+              <c:f>ダッシュボード!$AS$3:$AS$14</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>上村和恵</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>秋草文恵</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>高橋正美</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>向井ひかり</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>石戸谷亜子</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>中納沙織</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>山本祥吉</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>高橋佐織</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>晩田恵美</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>後藤克行</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>大江美記子</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>本吉有美子</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>[1]!_dbTopRaw</c:f>
+              <c:f>ダッシュボード!$AT$3:$AT$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>143.79496402877697</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>146.43356643356643</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>138.1651376146789</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>129.9769053117783</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>105.67375886524823</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>118.37270341207349</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>101.14607797087835</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>107.43889479277364</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>92.0866590649943</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>107.17488789237669</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>93.88379204892966</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>83.68638239339752</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -15401,13 +17485,92 @@
           </c:spPr>
           <c:invertIfNegative val="1"/>
           <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>[1]!_dbTopName</c:f>
-            </c:multiLvlStrRef>
+            <c:strRef>
+              <c:f>ダッシュボード!$AS$3:$AS$14</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>上村和恵</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>秋草文恵</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>高橋正美</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>向井ひかり</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>石戸谷亜子</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>中納沙織</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>山本祥吉</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>高橋佐織</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>晩田恵美</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>後藤克行</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>大江美記子</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>本吉有美子</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>[1]!_dbTopPure</c:f>
+              <c:f>ダッシュボード!$AU$3:$AU$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>105.28192446043165</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>104.46258741258742</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>102.00110091743119</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>88.60635103926097</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>74.97375886524823</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>73.57165354330708</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>69.30690465007046</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>68.28905419766207</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>67.82770809578106</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>63.16696562032886</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>48.725688073394494</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>44.98411279229711</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -15447,7 +17610,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:title>
           <c:tx>
@@ -15481,7 +17644,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:majorGridlines/>
         <c:title>
@@ -15573,13 +17736,194 @@
           </c:spPr>
           <c:invertIfNegative val="1"/>
           <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>[1]!_dbPkName</c:f>
-            </c:multiLvlStrRef>
+            <c:strRef>
+              <c:f>ダッシュボード!$U$3:$U$62</c:f>
+              <c:strCache>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>本吉有美子</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>大江美記子</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>佐藤辰成</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>春谷智子</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>澤田凌</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>後藤克行</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>中村美佳</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>晩田恵美</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>高橋佐織</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>山本祥吉</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>佐々木千恵</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>北田倫子</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>中納沙織</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>石戸谷亜子</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>森田美加</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>木村千鶴</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>河野忠</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>奥野愛海</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>鈴木香織</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>向井ひかり</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>廣瀬こずえ</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>片岡達也</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>森本久美</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>菊池敬</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>高橋正美</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>秋草文恵</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>上村和恵</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>平田学</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>飯田由加里</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>[1]!_dbPkVal</c:f>
+              <c:f>ダッシュボード!$V$3:$V$62</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>127.03460719829701</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>120.67691021365592</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>119.7425901187512</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>111.28404540730916</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>109.608647015599</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>109.25811506173572</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>108.19661844228943</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>106.48628255257557</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>105.5199126114411</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>105.27874024037102</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>104.82956951103425</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>102.19941536738331</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>102.10123607448666</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>101.53055698910751</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>100.77903963067155</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>100.54560159272768</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>100.53479201324765</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>99.23412966546182</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>99.0427992117129</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>94.65110162100073</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>93.41118109614357</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>93.27565646093761</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>90.9750925905042</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>90.76031955021183</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>88.91290688944902</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>88.53337654701247</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>87.51745426620545</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>85.92335307408533</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>85.53848561318566</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -15618,7 +17962,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -15636,7 +17980,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:majorGridlines/>
         <c:title>
@@ -15724,13 +18068,134 @@
           </c:spPr>
           <c:invertIfNegative val="1"/>
           <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>[1]!_dbKpName</c:f>
-            </c:multiLvlStrRef>
+            <c:strRef>
+              <c:f>ダッシュボード!$W$3:$W$62</c:f>
+              <c:strCache>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>佐々木千恵</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>本吉有美子</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>北田倫子</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>大江美記子</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>佐藤辰成</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>飯田由加里</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>晩田恵美</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>河野忠</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>森本久美</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>鈴木香織</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>澤田凌</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>高橋佐織</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>中村美佳</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>山本祥吉</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>後藤克行</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>中納沙織</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>木村千鶴</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>菊池敬</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>森田美加</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>[1]!_dbKpVal</c:f>
+              <c:f>ダッシュボード!$X$3:$X$62</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>160.21330038970882</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>146.66177155707118</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>133.25785675591538</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>131.04490021102978</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>128.1824773344137</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>126.82484924085423</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>120.21334891697963</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>115.10131008792217</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>102.27473325768686</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>98.81317753034124</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>96.6040089685315</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>95.03098129485993</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>89.76235104145006</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>86.58781937105334</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>82.50800954832064</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>81.8195904305488</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>74.64765281846198</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>69.50855316564756</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>60.24629206624098</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -15769,7 +18234,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -15787,7 +18252,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:majorGridlines/>
         <c:title>

--- a/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
+++ b/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
@@ -20712,6 +20712,60 @@
 </externalLink>
 </file>
 
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tbl_PK" displayName="Tbl_PK" ref="A6:R66" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A6:R66"/>
+  <tableColumns count="18">
+    <tableColumn id="1" name="順位"/>
+    <tableColumn id="2" name="担当者名"/>
+    <tableColumn id="3" name="件数"/>
+    <tableColumn id="4" name="時間&#10;(分)"/>
+    <tableColumn id="5" name="企業数"/>
+    <tableColumn id="6" name="件/社"/>
+    <tableColumn id="7" name="素の&#10;秒/件"/>
+    <tableColumn id="8" name="段取り&#10;(分)"/>
+    <tableColumn id="9" name="標準時間&#10;(分)"/>
+    <tableColumn id="10" name="段取り&#10;比率"/>
+    <tableColumn id="11" name="効率&#10;%"/>
+    <tableColumn id="12" name="縮小後&#10;効率%"/>
+    <tableColumn id="13" name="下限&#10;95%"/>
+    <tableColumn id="14" name="上限&#10;95%"/>
+    <tableColumn id="15" name="判定"/>
+    <tableColumn id="16" name="純速度&#10;秒/件"/>
+    <tableColumn id="17" name="公平目標&#10;分/個"/>
+    <tableColumn id="18" name="目標達成率&#10;%"/>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tbl_KP" displayName="Tbl_KP" ref="A6:R66" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A6:R66"/>
+  <tableColumns count="18">
+    <tableColumn id="1" name="順位"/>
+    <tableColumn id="2" name="担当者名"/>
+    <tableColumn id="3" name="件数"/>
+    <tableColumn id="4" name="時間&#10;(分)"/>
+    <tableColumn id="5" name="企業数"/>
+    <tableColumn id="6" name="件/社"/>
+    <tableColumn id="7" name="素の&#10;秒/件"/>
+    <tableColumn id="8" name="段取り&#10;(分)"/>
+    <tableColumn id="9" name="標準時間&#10;(分)"/>
+    <tableColumn id="10" name="段取り&#10;比率"/>
+    <tableColumn id="11" name="効率&#10;%"/>
+    <tableColumn id="12" name="縮小後&#10;効率%"/>
+    <tableColumn id="13" name="下限&#10;95%"/>
+    <tableColumn id="14" name="上限&#10;95%"/>
+    <tableColumn id="15" name="判定"/>
+    <tableColumn id="16" name="純速度&#10;秒/件"/>
+    <tableColumn id="17" name="公平目標&#10;分/個"/>
+    <tableColumn id="18" name="目標達成率&#10;%"/>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -47286,6 +47340,9 @@
     <hyperlink ref="B5" location="'ダッシュボード'!A1" display="← ダッシュボードへ戻る" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -52211,6 +52268,9 @@
     <hyperlink ref="B5" location="'ダッシュボード'!A1" display="← ダッシュボードへ戻る" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 

--- a/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
+++ b/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="496">
   <si>
     <t>▼ グラフ用データ　消したり非表示にしたりしないでください</t>
   </si>
@@ -1551,6 +1551,52 @@
   </si>
   <si>
     <t>PK 未達 合計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. 担当者ランキング　※ 目標達成率＝会社目標 1.6分/件 に対する達成率。順位も判定も、この同じ値で付けています</t>
+  </si>
+  <si>
+    <t xml:space="preserve">記録日数の少ない人は数字がブレます。ブレの大きさを見積もって、参考値（縮小後効率）と信頼区間を計算します。順位づけには使いません。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全体サマリー、目標達成率のランキング、配置マップが自動で出ます。
+段取り比率が高い月ほど、件数だけの比較は不公平になります。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">記録日数が少ない人は数字がブレるため、平均側へ寄せた参考値。順位づけには使わない。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">会社目標 1.6分/件 に対する達成率で4区分。100%以上＝◎達成、90%以上＝○あと一歩、80%以上＝△要改善、80%未満＝✕要支援。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">◎ 達成</t>
+  </si>
+  <si>
+    <t xml:space="preserve">会社目標 1.6分/件 に対する達成率が 100% 以上</t>
+  </si>
+  <si>
+    <t xml:space="preserve">○ あと一歩</t>
+  </si>
+  <si>
+    <t xml:space="preserve">達成率 90% 以上 100% 未満</t>
+  </si>
+  <si>
+    <t xml:space="preserve">△ 要改善</t>
+  </si>
+  <si>
+    <t xml:space="preserve">達成率 80% 以上 90% 未満</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✕ 要支援</t>
+  </si>
+  <si>
+    <t xml:space="preserve">達成率 80% 未満</t>
+  </si>
+  <si>
+    <t xml:space="preserve">標準時間 ＝ a × 企業数 ＋ b × 件数　（ピッキング a=56.05秒/社・b=75.6秒/件／梱包 a=92.1秒/社・b=69.5秒/件）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1社ごとに必ず発生する時間。ピッキングは 56.05秒/社（① リストを見る 10秒 ＋ ④ 伝票を挟む 46.05秒）。</t>
   </si>
 </sst>
 </file>
@@ -17705,7 +17751,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>ピッキング　縮小後効率ランキング（100 ＝ 標準どおり）</a:t>
+              <a:t>ピッキング　目標達成率ランキング（100 ＝ 目標 1.6分/件）</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -17993,7 +18039,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>効率 %</a:t>
+                  <a:t>目標達成率 %</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -18037,7 +18083,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>梱包　縮小後効率ランキング（100 ＝ 標準どおり）</a:t>
+              <a:t>梱包　目標達成率ランキング（100 ＝ 目標 1.6分/件）</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -18265,7 +18311,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>効率 %</a:t>
+                  <a:t>目標達成率 %</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -21176,19 +21222,19 @@
       </c>
       <c r="U3" t="str">
         <f>IFERROR(INDEX(ピッキング!$B$7:$B$66,MATCH($T3,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>本吉有美子</v>
+        <v>佐藤辰成</v>
       </c>
       <c r="V3">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T3,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>127.03460719829701</v>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T3,ピッキング!$A$7:$A$66,0)),"")</f>
+        <v>131.7530864197531</v>
       </c>
       <c r="W3" t="str">
         <f>IFERROR(INDEX(梱包!$B$7:$B$66,MATCH($T3,梱包!$A$7:$A$66,0)),"")</f>
         <v>佐々木千恵</v>
       </c>
       <c r="X3">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T3,梱包!$A$7:$A$66,0)),"")</f>
-        <v>160.21330038970882</v>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T3,梱包!$A$7:$A$66,0)),"")</f>
+        <v>184.93506493506493</v>
       </c>
       <c r="Z3">
         <f>IF(OR(ピッキング!$E$7="",ピッキング!$C$7=""),"",ピッキング!$E$7/ピッキング!$C$7)</f>
@@ -21290,19 +21336,19 @@
       </c>
       <c r="U4" t="str">
         <f>IFERROR(INDEX(ピッキング!$B$7:$B$66,MATCH($T4,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>大江美記子</v>
+        <v>本吉有美子</v>
       </c>
       <c r="V4">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T4,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>120.67691021365592</v>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T4,ピッキング!$A$7:$A$66,0)),"")</f>
+        <v>114.71400394477318</v>
       </c>
       <c r="W4" t="str">
         <f>IFERROR(INDEX(梱包!$B$7:$B$66,MATCH($T4,梱包!$A$7:$A$66,0)),"")</f>
         <v>本吉有美子</v>
       </c>
       <c r="X4">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T4,梱包!$A$7:$A$66,0)),"")</f>
-        <v>146.66177155707118</v>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T4,梱包!$A$7:$A$66,0)),"")</f>
+        <v>153.47441323585994</v>
       </c>
       <c r="Z4">
         <f>IF(OR(ピッキング!$E$8="",ピッキング!$C$8=""),"",ピッキング!$E$8/ピッキング!$C$8)</f>
@@ -21401,19 +21447,19 @@
       </c>
       <c r="U5" t="str">
         <f>IFERROR(INDEX(ピッキング!$B$7:$B$66,MATCH($T5,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>佐藤辰成</v>
+        <v>中村美佳</v>
       </c>
       <c r="V5">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T5,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>119.7425901187512</v>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T5,ピッキング!$A$7:$A$66,0)),"")</f>
+        <v>105.33333333333334</v>
       </c>
       <c r="W5" t="str">
         <f>IFERROR(INDEX(梱包!$B$7:$B$66,MATCH($T5,梱包!$A$7:$A$66,0)),"")</f>
-        <v>北田倫子</v>
+        <v>佐藤辰成</v>
       </c>
       <c r="X5">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T5,梱包!$A$7:$A$66,0)),"")</f>
-        <v>133.25785675591538</v>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T5,梱包!$A$7:$A$66,0)),"")</f>
+        <v>148.98360655737704</v>
       </c>
       <c r="Z5">
         <f>IF(OR(ピッキング!$E$9="",ピッキング!$C$9=""),"",ピッキング!$E$9/ピッキング!$C$9)</f>
@@ -21542,19 +21588,19 @@
       </c>
       <c r="U6" t="str">
         <f>IFERROR(INDEX(ピッキング!$B$7:$B$66,MATCH($T6,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>春谷智子</v>
+        <v>晩田恵美</v>
       </c>
       <c r="V6">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T6,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>111.28404540730916</v>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T6,ピッキング!$A$7:$A$66,0)),"")</f>
+        <v>104.24962852897475</v>
       </c>
       <c r="W6" t="str">
         <f>IFERROR(INDEX(梱包!$B$7:$B$66,MATCH($T6,梱包!$A$7:$A$66,0)),"")</f>
-        <v>大江美記子</v>
+        <v>河野忠</v>
       </c>
       <c r="X6">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T6,梱包!$A$7:$A$66,0)),"")</f>
-        <v>131.04490021102978</v>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T6,梱包!$A$7:$A$66,0)),"")</f>
+        <v>138.5109489051095</v>
       </c>
       <c r="Z6">
         <f>IF(OR(ピッキング!$E$10="",ピッキング!$C$10=""),"",ピッキング!$E$10/ピッキング!$C$10)</f>
@@ -21639,19 +21685,19 @@
       </c>
       <c r="U7" t="str">
         <f>IFERROR(INDEX(ピッキング!$B$7:$B$66,MATCH($T7,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>澤田凌</v>
+        <v>大江美記子</v>
       </c>
       <c r="V7">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T7,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>109.608647015599</v>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T7,ピッキング!$A$7:$A$66,0)),"")</f>
+        <v>102.25407166123779</v>
       </c>
       <c r="W7" t="str">
         <f>IFERROR(INDEX(梱包!$B$7:$B$66,MATCH($T7,梱包!$A$7:$A$66,0)),"")</f>
-        <v>佐藤辰成</v>
+        <v>大江美記子</v>
       </c>
       <c r="X7">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T7,梱包!$A$7:$A$66,0)),"")</f>
-        <v>128.1824773344137</v>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T7,梱包!$A$7:$A$66,0)),"")</f>
+        <v>136.7843137254902</v>
       </c>
       <c r="Z7">
         <f>IF(OR(ピッキング!$E$11="",ピッキング!$C$11=""),"",ピッキング!$E$11/ピッキング!$C$11)</f>
@@ -21747,19 +21793,19 @@
       </c>
       <c r="U8" t="str">
         <f>IFERROR(INDEX(ピッキング!$B$7:$B$66,MATCH($T8,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>後藤克行</v>
+        <v>澤田凌</v>
       </c>
       <c r="V8">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T8,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>109.25811506173572</v>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T8,ピッキング!$A$7:$A$66,0)),"")</f>
+        <v>101.5261044176707</v>
       </c>
       <c r="W8" t="str">
         <f>IFERROR(INDEX(梱包!$B$7:$B$66,MATCH($T8,梱包!$A$7:$A$66,0)),"")</f>
-        <v>飯田由加里</v>
+        <v>北田倫子</v>
       </c>
       <c r="X8">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T8,梱包!$A$7:$A$66,0)),"")</f>
-        <v>126.82484924085423</v>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T8,梱包!$A$7:$A$66,0)),"")</f>
+        <v>131.24004550625713</v>
       </c>
       <c r="Z8">
         <f>IF(OR(ピッキング!$E$12="",ピッキング!$C$12=""),"",ピッキング!$E$12/ピッキング!$C$12)</f>
@@ -21844,19 +21890,19 @@
       </c>
       <c r="U9" t="str">
         <f>IFERROR(INDEX(ピッキング!$B$7:$B$66,MATCH($T9,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>中村美佳</v>
+        <v>佐々木千恵</v>
       </c>
       <c r="V9">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T9,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>108.19661844228943</v>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T9,ピッキング!$A$7:$A$66,0)),"")</f>
+        <v>100.70240295748616</v>
       </c>
       <c r="W9" t="str">
         <f>IFERROR(INDEX(梱包!$B$7:$B$66,MATCH($T9,梱包!$A$7:$A$66,0)),"")</f>
-        <v>晩田恵美</v>
+        <v>飯田由加里</v>
       </c>
       <c r="X9">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T9,梱包!$A$7:$A$66,0)),"")</f>
-        <v>120.21334891697963</v>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T9,梱包!$A$7:$A$66,0)),"")</f>
+        <v>115.79809004092772</v>
       </c>
       <c r="Z9">
         <f>IF(OR(ピッキング!$E$13="",ピッキング!$C$13=""),"",ピッキング!$E$13/ピッキング!$C$13)</f>
@@ -21953,19 +21999,19 @@
       </c>
       <c r="U10" t="str">
         <f>IFERROR(INDEX(ピッキング!$B$7:$B$66,MATCH($T10,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>晩田恵美</v>
+        <v>山本祥吉</v>
       </c>
       <c r="V10">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T10,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>106.48628255257557</v>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T10,ピッキング!$A$7:$A$66,0)),"")</f>
+        <v>94.91223181944831</v>
       </c>
       <c r="W10" t="str">
         <f>IFERROR(INDEX(梱包!$B$7:$B$66,MATCH($T10,梱包!$A$7:$A$66,0)),"")</f>
-        <v>河野忠</v>
+        <v>晩田恵美</v>
       </c>
       <c r="X10">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T10,梱包!$A$7:$A$66,0)),"")</f>
-        <v>115.10131008792217</v>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T10,梱包!$A$7:$A$66,0)),"")</f>
+        <v>115.03868230596457</v>
       </c>
       <c r="Z10">
         <f>IF(OR(ピッキング!$E$14="",ピッキング!$C$14=""),"",ピッキング!$E$14/ピッキング!$C$14)</f>
@@ -22064,19 +22110,19 @@
       </c>
       <c r="U11" t="str">
         <f>IFERROR(INDEX(ピッキング!$B$7:$B$66,MATCH($T11,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>高橋佐織</v>
+        <v>春谷智子</v>
       </c>
       <c r="V11">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T11,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>105.5199126114411</v>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T11,ピッキング!$A$7:$A$66,0)),"")</f>
+        <v>92.95238095238096</v>
       </c>
       <c r="W11" t="str">
         <f>IFERROR(INDEX(梱包!$B$7:$B$66,MATCH($T11,梱包!$A$7:$A$66,0)),"")</f>
         <v>森本久美</v>
       </c>
       <c r="X11">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T11,梱包!$A$7:$A$66,0)),"")</f>
-        <v>102.27473325768686</v>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T11,梱包!$A$7:$A$66,0)),"")</f>
+        <v>99.61489088575097</v>
       </c>
       <c r="Z11">
         <f>IF(OR(ピッキング!$E$15="",ピッキング!$C$15=""),"",ピッキング!$E$15/ピッキング!$C$15)</f>
@@ -22173,19 +22219,19 @@
       </c>
       <c r="U12" t="str">
         <f>IFERROR(INDEX(ピッキング!$B$7:$B$66,MATCH($T12,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>山本祥吉</v>
+        <v>石戸谷亜子</v>
       </c>
       <c r="V12">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T12,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>105.27874024037102</v>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T12,ピッキング!$A$7:$A$66,0)),"")</f>
+        <v>90.84563758389262</v>
       </c>
       <c r="W12" t="str">
         <f>IFERROR(INDEX(梱包!$B$7:$B$66,MATCH($T12,梱包!$A$7:$A$66,0)),"")</f>
-        <v>鈴木香織</v>
+        <v>高橋佐織</v>
       </c>
       <c r="X12">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T12,梱包!$A$7:$A$66,0)),"")</f>
-        <v>98.813177530341235</v>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T12,梱包!$A$7:$A$66,0)),"")</f>
+        <v>93.78509196515006</v>
       </c>
       <c r="Z12">
         <f>IF(OR(ピッキング!$E$16="",ピッキング!$C$16=""),"",ピッキング!$E$16/ピッキング!$C$16)</f>
@@ -22282,19 +22328,19 @@
       </c>
       <c r="U13" t="str">
         <f>IFERROR(INDEX(ピッキング!$B$7:$B$66,MATCH($T13,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>佐々木千恵</v>
+        <v>後藤克行</v>
       </c>
       <c r="V13">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T13,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>104.82956951103425</v>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T13,ピッキング!$A$7:$A$66,0)),"")</f>
+        <v>89.57322175732219</v>
       </c>
       <c r="W13" t="str">
         <f>IFERROR(INDEX(梱包!$B$7:$B$66,MATCH($T13,梱包!$A$7:$A$66,0)),"")</f>
-        <v>澤田凌</v>
+        <v>鈴木香織</v>
       </c>
       <c r="X13">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T13,梱包!$A$7:$A$66,0)),"")</f>
-        <v>96.604008968531502</v>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T13,梱包!$A$7:$A$66,0)),"")</f>
+        <v>90.9090909090909</v>
       </c>
       <c r="Z13">
         <f>IF(OR(ピッキング!$E$17="",ピッキング!$C$17=""),"",ピッキング!$E$17/ピッキング!$C$17)</f>
@@ -22379,19 +22425,19 @@
       </c>
       <c r="U14" t="str">
         <f>IFERROR(INDEX(ピッキング!$B$7:$B$66,MATCH($T14,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>北田倫子</v>
+        <v>高橋佐織</v>
       </c>
       <c r="V14">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T14,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>102.19941536738331</v>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T14,ピッキング!$A$7:$A$66,0)),"")</f>
+        <v>89.35311572700297</v>
       </c>
       <c r="W14" t="str">
         <f>IFERROR(INDEX(梱包!$B$7:$B$66,MATCH($T14,梱包!$A$7:$A$66,0)),"")</f>
-        <v>高橋佐織</v>
+        <v>山本祥吉</v>
       </c>
       <c r="X14">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T14,梱包!$A$7:$A$66,0)),"")</f>
-        <v>95.030981294859927</v>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T14,梱包!$A$7:$A$66,0)),"")</f>
+        <v>87.58132956152758</v>
       </c>
       <c r="Z14">
         <f>IF(OR(ピッキング!$E$18="",ピッキング!$C$18=""),"",ピッキング!$E$18/ピッキング!$C$18)</f>
@@ -22488,19 +22534,19 @@
       </c>
       <c r="U15" t="str">
         <f>IFERROR(INDEX(ピッキング!$B$7:$B$66,MATCH($T15,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>中納沙織</v>
+        <v>河野忠</v>
       </c>
       <c r="V15">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T15,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>102.10123607448666</v>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T15,ピッキング!$A$7:$A$66,0)),"")</f>
+        <v>81.15942028985508</v>
       </c>
       <c r="W15" t="str">
         <f>IFERROR(INDEX(梱包!$B$7:$B$66,MATCH($T15,梱包!$A$7:$A$66,0)),"")</f>
-        <v>中村美佳</v>
+        <v>澤田凌</v>
       </c>
       <c r="X15">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T15,梱包!$A$7:$A$66,0)),"")</f>
-        <v>89.76235104145006</v>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T15,梱包!$A$7:$A$66,0)),"")</f>
+        <v>82.47154471544717</v>
       </c>
       <c r="Z15">
         <f>IF(OR(ピッキング!$E$19="",ピッキング!$C$19=""),"",ピッキング!$E$19/ピッキング!$C$19)</f>
@@ -22571,19 +22617,19 @@
       </c>
       <c r="U16" t="str">
         <f>IFERROR(INDEX(ピッキング!$B$7:$B$66,MATCH($T16,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>石戸谷亜子</v>
+        <v>中納沙織</v>
       </c>
       <c r="V16">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T16,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>101.53055698910751</v>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T16,ピッキング!$A$7:$A$66,0)),"")</f>
+        <v>81.09977827050999</v>
       </c>
       <c r="W16" t="str">
         <f>IFERROR(INDEX(梱包!$B$7:$B$66,MATCH($T16,梱包!$A$7:$A$66,0)),"")</f>
-        <v>山本祥吉</v>
+        <v>後藤克行</v>
       </c>
       <c r="X16">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T16,梱包!$A$7:$A$66,0)),"")</f>
-        <v>86.587819371053342</v>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T16,梱包!$A$7:$A$66,0)),"")</f>
+        <v>82.37681159420289</v>
       </c>
       <c r="Z16">
         <f>IF(OR(ピッキング!$E$20="",ピッキング!$C$20=""),"",ピッキング!$E$20/ピッキング!$C$20)</f>
@@ -22652,19 +22698,19 @@
       </c>
       <c r="U17" t="str">
         <f>IFERROR(INDEX(ピッキング!$B$7:$B$66,MATCH($T17,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>森田美加</v>
+        <v>木村千鶴</v>
       </c>
       <c r="V17">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T17,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>100.77903963067155</v>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T17,ピッキング!$A$7:$A$66,0)),"")</f>
+        <v>79.1977077363897</v>
       </c>
       <c r="W17" t="str">
         <f>IFERROR(INDEX(梱包!$B$7:$B$66,MATCH($T17,梱包!$A$7:$A$66,0)),"")</f>
-        <v>後藤克行</v>
+        <v>中村美佳</v>
       </c>
       <c r="X17">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T17,梱包!$A$7:$A$66,0)),"")</f>
-        <v>82.508009548320643</v>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T17,梱包!$A$7:$A$66,0)),"")</f>
+        <v>82.1917808219178</v>
       </c>
       <c r="Z17">
         <f>IF(OR(ピッキング!$E$21="",ピッキング!$C$21=""),"",ピッキング!$E$21/ピッキング!$C$21)</f>
@@ -22733,19 +22779,19 @@
       </c>
       <c r="U18" t="str">
         <f>IFERROR(INDEX(ピッキング!$B$7:$B$66,MATCH($T18,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>木村千鶴</v>
+        <v>森田美加</v>
       </c>
       <c r="V18">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T18,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>100.54560159272768</v>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T18,ピッキング!$A$7:$A$66,0)),"")</f>
+        <v>77.5111111111111</v>
       </c>
       <c r="W18" t="str">
         <f>IFERROR(INDEX(梱包!$B$7:$B$66,MATCH($T18,梱包!$A$7:$A$66,0)),"")</f>
         <v>中納沙織</v>
       </c>
       <c r="X18">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T18,梱包!$A$7:$A$66,0)),"")</f>
-        <v>81.8195904305488</v>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T18,梱包!$A$7:$A$66,0)),"")</f>
+        <v>75.45263157894738</v>
       </c>
       <c r="Z18">
         <f>IF(OR(ピッキング!$E$22="",ピッキング!$C$22=""),"",ピッキング!$E$22/ピッキング!$C$22)</f>
@@ -22802,19 +22848,19 @@
       </c>
       <c r="U19" t="str">
         <f>IFERROR(INDEX(ピッキング!$B$7:$B$66,MATCH($T19,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>河野忠</v>
+        <v>森本久美</v>
       </c>
       <c r="V19">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T19,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>100.53479201324765</v>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T19,ピッキング!$A$7:$A$66,0)),"")</f>
+        <v>74.86033519553072</v>
       </c>
       <c r="W19" t="str">
         <f>IFERROR(INDEX(梱包!$B$7:$B$66,MATCH($T19,梱包!$A$7:$A$66,0)),"")</f>
         <v>木村千鶴</v>
       </c>
       <c r="X19">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T19,梱包!$A$7:$A$66,0)),"")</f>
-        <v>74.647652818461978</v>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T19,梱包!$A$7:$A$66,0)),"")</f>
+        <v>73.91763463569166</v>
       </c>
       <c r="Z19">
         <f>IF(OR(ピッキング!$E$23="",ピッキング!$C$23=""),"",ピッキング!$E$23/ピッキング!$C$23)</f>
@@ -22874,19 +22920,19 @@
       </c>
       <c r="U20" t="str">
         <f>IFERROR(INDEX(ピッキング!$B$7:$B$66,MATCH($T20,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>奥野愛海</v>
+        <v>北田倫子</v>
       </c>
       <c r="V20">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T20,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>99.234129665461822</v>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T20,ピッキング!$A$7:$A$66,0)),"")</f>
+        <v>74.8051948051948</v>
       </c>
       <c r="W20" t="str">
         <f>IFERROR(INDEX(梱包!$B$7:$B$66,MATCH($T20,梱包!$A$7:$A$66,0)),"")</f>
         <v>菊池敬</v>
       </c>
       <c r="X20">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T20,梱包!$A$7:$A$66,0)),"")</f>
-        <v>69.508553165647555</v>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T20,梱包!$A$7:$A$66,0)),"")</f>
+        <v>64.31532449881074</v>
       </c>
       <c r="Z20">
         <f>IF(OR(ピッキング!$E$24="",ピッキング!$C$24=""),"",ピッキング!$E$24/ピッキング!$C$24)</f>
@@ -22946,19 +22992,19 @@
       </c>
       <c r="U21" t="str">
         <f>IFERROR(INDEX(ピッキング!$B$7:$B$66,MATCH($T21,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>鈴木香織</v>
+        <v>向井ひかり</v>
       </c>
       <c r="V21">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T21,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>99.042799211712904</v>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T21,ピッキング!$A$7:$A$66,0)),"")</f>
+        <v>73.85927505330491</v>
       </c>
       <c r="W21" t="str">
         <f>IFERROR(INDEX(梱包!$B$7:$B$66,MATCH($T21,梱包!$A$7:$A$66,0)),"")</f>
         <v>森田美加</v>
       </c>
       <c r="X21">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T21,梱包!$A$7:$A$66,0)),"")</f>
-        <v>60.246292066240983</v>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T21,梱包!$A$7:$A$66,0)),"")</f>
+        <v>51.82519280205655</v>
       </c>
       <c r="Z21">
         <f>IF(OR(ピッキング!$E$25="",ピッキング!$C$25=""),"",ピッキング!$E$25/ピッキング!$C$25)</f>
@@ -23018,18 +23064,18 @@
       </c>
       <c r="U22" t="str">
         <f>IFERROR(INDEX(ピッキング!$B$7:$B$66,MATCH($T22,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>向井ひかり</v>
+        <v>鈴木香織</v>
       </c>
       <c r="V22">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T22,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>94.651101621000734</v>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T22,ピッキング!$A$7:$A$66,0)),"")</f>
+        <v>73.1881188118812</v>
       </c>
       <c r="W22" t="str">
         <f>IFERROR(INDEX(梱包!$B$7:$B$66,MATCH($T22,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="X22" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T22,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T22,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z22">
@@ -23111,18 +23157,18 @@
       </c>
       <c r="U23" t="str">
         <f>IFERROR(INDEX(ピッキング!$B$7:$B$66,MATCH($T23,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>廣瀬こずえ</v>
+        <v>奥野愛海</v>
       </c>
       <c r="V23">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T23,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>93.411181096143565</v>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T23,ピッキング!$A$7:$A$66,0)),"")</f>
+        <v>71.95675675675676</v>
       </c>
       <c r="W23" t="str">
         <f>IFERROR(INDEX(梱包!$B$7:$B$66,MATCH($T23,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="X23" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T23,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T23,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z23">
@@ -23180,18 +23226,18 @@
       </c>
       <c r="U24" t="str">
         <f>IFERROR(INDEX(ピッキング!$B$7:$B$66,MATCH($T24,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>片岡達也</v>
+        <v>菊池敬</v>
       </c>
       <c r="V24">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T24,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>93.275656460937611</v>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T24,ピッキング!$A$7:$A$66,0)),"")</f>
+        <v>71.07368421052632</v>
       </c>
       <c r="W24" t="str">
         <f>IFERROR(INDEX(梱包!$B$7:$B$66,MATCH($T24,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="X24" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T24,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T24,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z24">
@@ -23249,18 +23295,18 @@
       </c>
       <c r="U25" t="str">
         <f>IFERROR(INDEX(ピッキング!$B$7:$B$66,MATCH($T25,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>森本久美</v>
+        <v>高橋正美</v>
       </c>
       <c r="V25">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T25,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>90.975092590504204</v>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T25,ピッキング!$A$7:$A$66,0)),"")</f>
+        <v>69.4820717131474</v>
       </c>
       <c r="W25" t="str">
         <f>IFERROR(INDEX(梱包!$B$7:$B$66,MATCH($T25,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="X25" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T25,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T25,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z25">
@@ -23318,18 +23364,18 @@
       </c>
       <c r="U26" t="str">
         <f>IFERROR(INDEX(ピッキング!$B$7:$B$66,MATCH($T26,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>菊池敬</v>
+        <v>廣瀬こずえ</v>
       </c>
       <c r="V26">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T26,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>90.760319550211833</v>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T26,ピッキング!$A$7:$A$66,0)),"")</f>
+        <v>67.99188640973631</v>
       </c>
       <c r="W26" t="str">
         <f>IFERROR(INDEX(梱包!$B$7:$B$66,MATCH($T26,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="X26" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T26,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T26,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z26">
@@ -23387,18 +23433,18 @@
       </c>
       <c r="U27" t="str">
         <f>IFERROR(INDEX(ピッキング!$B$7:$B$66,MATCH($T27,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>高橋正美</v>
+        <v>上村和恵</v>
       </c>
       <c r="V27">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T27,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>88.912906889449019</v>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T27,ピッキング!$A$7:$A$66,0)),"")</f>
+        <v>66.76172607879926</v>
       </c>
       <c r="W27" t="str">
         <f>IFERROR(INDEX(梱包!$B$7:$B$66,MATCH($T27,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="X27" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T27,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T27,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z27">
@@ -23459,15 +23505,15 @@
         <v>秋草文恵</v>
       </c>
       <c r="V28">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T28,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>88.533376547012466</v>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T28,ピッキング!$A$7:$A$66,0)),"")</f>
+        <v>65.55873925501433</v>
       </c>
       <c r="W28" t="str">
         <f>IFERROR(INDEX(梱包!$B$7:$B$66,MATCH($T28,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="X28" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T28,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T28,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z28">
@@ -23525,18 +23571,18 @@
       </c>
       <c r="U29" t="str">
         <f>IFERROR(INDEX(ピッキング!$B$7:$B$66,MATCH($T29,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>上村和恵</v>
+        <v>飯田由加里</v>
       </c>
       <c r="V29">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T29,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>87.517454266205448</v>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T29,ピッキング!$A$7:$A$66,0)),"")</f>
+        <v>56.75392670157068</v>
       </c>
       <c r="W29" t="str">
         <f>IFERROR(INDEX(梱包!$B$7:$B$66,MATCH($T29,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="X29" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T29,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T29,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z29">
@@ -23594,18 +23640,18 @@
       </c>
       <c r="U30" t="str">
         <f>IFERROR(INDEX(ピッキング!$B$7:$B$66,MATCH($T30,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>平田学</v>
+        <v>片岡達也</v>
       </c>
       <c r="V30">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T30,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>85.923353074085327</v>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T30,ピッキング!$A$7:$A$66,0)),"")</f>
+        <v>52.27722772277228</v>
       </c>
       <c r="W30" t="str">
         <f>IFERROR(INDEX(梱包!$B$7:$B$66,MATCH($T30,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="X30" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T30,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T30,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z30">
@@ -23663,18 +23709,18 @@
       </c>
       <c r="U31" t="str">
         <f>IFERROR(INDEX(ピッキング!$B$7:$B$66,MATCH($T31,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>飯田由加里</v>
+        <v>平田学</v>
       </c>
       <c r="V31">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T31,ピッキング!$A$7:$A$66,0)),"")</f>
-        <v>85.538485613185657</v>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T31,ピッキング!$A$7:$A$66,0)),"")</f>
+        <v>48.3265306122449</v>
       </c>
       <c r="W31" t="str">
         <f>IFERROR(INDEX(梱包!$B$7:$B$66,MATCH($T31,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="X31" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T31,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T31,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z31">
@@ -23735,7 +23781,7 @@
         <v/>
       </c>
       <c r="V32" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T32,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T32,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W32" t="str">
@@ -23743,7 +23789,7 @@
         <v/>
       </c>
       <c r="X32" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T32,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T32,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z32" t="str">
@@ -23804,7 +23850,7 @@
         <v/>
       </c>
       <c r="V33" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T33,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T33,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W33" t="str">
@@ -23812,7 +23858,7 @@
         <v/>
       </c>
       <c r="X33" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T33,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T33,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z33" t="str">
@@ -23873,7 +23919,7 @@
         <v/>
       </c>
       <c r="V34" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T34,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T34,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W34" t="str">
@@ -23881,7 +23927,7 @@
         <v/>
       </c>
       <c r="X34" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T34,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T34,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z34" t="str">
@@ -23942,7 +23988,7 @@
         <v/>
       </c>
       <c r="V35" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T35,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T35,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W35" t="str">
@@ -23950,7 +23996,7 @@
         <v/>
       </c>
       <c r="X35" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T35,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T35,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z35" t="str">
@@ -24011,7 +24057,7 @@
         <v/>
       </c>
       <c r="V36" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T36,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T36,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W36" t="str">
@@ -24019,7 +24065,7 @@
         <v/>
       </c>
       <c r="X36" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T36,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T36,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z36" t="str">
@@ -24080,7 +24126,7 @@
         <v/>
       </c>
       <c r="V37" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T37,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T37,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W37" t="str">
@@ -24088,7 +24134,7 @@
         <v/>
       </c>
       <c r="X37" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T37,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T37,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z37" t="str">
@@ -24149,7 +24195,7 @@
         <v/>
       </c>
       <c r="V38" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T38,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T38,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W38" t="str">
@@ -24157,7 +24203,7 @@
         <v/>
       </c>
       <c r="X38" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T38,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T38,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z38" t="str">
@@ -24218,7 +24264,7 @@
         <v/>
       </c>
       <c r="V39" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T39,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T39,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W39" t="str">
@@ -24226,7 +24272,7 @@
         <v/>
       </c>
       <c r="X39" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T39,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T39,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z39" t="str">
@@ -24287,7 +24333,7 @@
         <v/>
       </c>
       <c r="V40" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T40,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T40,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W40" t="str">
@@ -24295,7 +24341,7 @@
         <v/>
       </c>
       <c r="X40" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T40,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T40,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z40" t="str">
@@ -24356,7 +24402,7 @@
         <v/>
       </c>
       <c r="V41" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T41,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T41,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W41" t="str">
@@ -24364,7 +24410,7 @@
         <v/>
       </c>
       <c r="X41" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T41,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T41,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z41" t="str">
@@ -24425,7 +24471,7 @@
         <v/>
       </c>
       <c r="V42" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T42,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T42,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W42" t="str">
@@ -24433,7 +24479,7 @@
         <v/>
       </c>
       <c r="X42" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T42,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T42,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z42" t="str">
@@ -24494,7 +24540,7 @@
         <v/>
       </c>
       <c r="V43" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T43,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T43,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W43" t="str">
@@ -24502,7 +24548,7 @@
         <v/>
       </c>
       <c r="X43" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T43,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T43,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z43" t="str">
@@ -24563,7 +24609,7 @@
         <v/>
       </c>
       <c r="V44" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T44,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T44,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W44" t="str">
@@ -24571,7 +24617,7 @@
         <v/>
       </c>
       <c r="X44" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T44,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T44,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z44" t="str">
@@ -24632,7 +24678,7 @@
         <v/>
       </c>
       <c r="V45" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T45,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T45,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W45" t="str">
@@ -24640,7 +24686,7 @@
         <v/>
       </c>
       <c r="X45" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T45,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T45,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z45" t="str">
@@ -24701,7 +24747,7 @@
         <v/>
       </c>
       <c r="V46" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T46,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T46,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W46" t="str">
@@ -24709,7 +24755,7 @@
         <v/>
       </c>
       <c r="X46" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T46,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T46,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z46" t="str">
@@ -24773,7 +24819,7 @@
         <v/>
       </c>
       <c r="V47" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T47,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T47,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W47" t="str">
@@ -24781,7 +24827,7 @@
         <v/>
       </c>
       <c r="X47" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T47,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T47,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z47" t="str">
@@ -24845,7 +24891,7 @@
         <v/>
       </c>
       <c r="V48" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T48,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T48,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W48" t="str">
@@ -24853,7 +24899,7 @@
         <v/>
       </c>
       <c r="X48" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T48,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T48,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z48" t="str">
@@ -24938,7 +24984,7 @@
         <v/>
       </c>
       <c r="V49" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T49,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T49,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W49" t="str">
@@ -24946,7 +24992,7 @@
         <v/>
       </c>
       <c r="X49" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T49,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T49,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z49" t="str">
@@ -25007,7 +25053,7 @@
         <v/>
       </c>
       <c r="V50" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T50,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T50,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W50" t="str">
@@ -25015,7 +25061,7 @@
         <v/>
       </c>
       <c r="X50" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T50,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T50,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z50" t="str">
@@ -25076,7 +25122,7 @@
         <v/>
       </c>
       <c r="V51" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T51,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T51,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W51" t="str">
@@ -25084,7 +25130,7 @@
         <v/>
       </c>
       <c r="X51" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T51,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T51,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z51" t="str">
@@ -25145,7 +25191,7 @@
         <v/>
       </c>
       <c r="V52" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T52,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T52,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W52" t="str">
@@ -25153,7 +25199,7 @@
         <v/>
       </c>
       <c r="X52" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T52,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T52,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z52" t="str">
@@ -25214,7 +25260,7 @@
         <v/>
       </c>
       <c r="V53" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T53,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T53,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W53" t="str">
@@ -25222,7 +25268,7 @@
         <v/>
       </c>
       <c r="X53" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T53,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T53,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z53" t="str">
@@ -25283,7 +25329,7 @@
         <v/>
       </c>
       <c r="V54" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T54,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T54,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W54" t="str">
@@ -25291,7 +25337,7 @@
         <v/>
       </c>
       <c r="X54" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T54,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T54,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z54" t="str">
@@ -25352,7 +25398,7 @@
         <v/>
       </c>
       <c r="V55" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T55,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T55,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W55" t="str">
@@ -25360,7 +25406,7 @@
         <v/>
       </c>
       <c r="X55" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T55,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T55,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z55" t="str">
@@ -25421,7 +25467,7 @@
         <v/>
       </c>
       <c r="V56" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T56,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T56,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W56" t="str">
@@ -25429,7 +25475,7 @@
         <v/>
       </c>
       <c r="X56" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T56,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T56,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z56" t="str">
@@ -25490,7 +25536,7 @@
         <v/>
       </c>
       <c r="V57" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T57,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T57,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W57" t="str">
@@ -25498,7 +25544,7 @@
         <v/>
       </c>
       <c r="X57" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T57,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T57,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z57" t="str">
@@ -25559,7 +25605,7 @@
         <v/>
       </c>
       <c r="V58" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T58,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T58,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W58" t="str">
@@ -25567,7 +25613,7 @@
         <v/>
       </c>
       <c r="X58" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T58,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T58,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z58" t="str">
@@ -25628,7 +25674,7 @@
         <v/>
       </c>
       <c r="V59" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T59,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T59,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W59" t="str">
@@ -25636,7 +25682,7 @@
         <v/>
       </c>
       <c r="X59" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T59,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T59,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z59" t="str">
@@ -25697,7 +25743,7 @@
         <v/>
       </c>
       <c r="V60" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T60,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T60,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W60" t="str">
@@ -25705,7 +25751,7 @@
         <v/>
       </c>
       <c r="X60" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T60,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T60,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z60" t="str">
@@ -25766,7 +25812,7 @@
         <v/>
       </c>
       <c r="V61" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T61,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T61,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W61" t="str">
@@ -25774,7 +25820,7 @@
         <v/>
       </c>
       <c r="X61" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T61,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T61,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z61" t="str">
@@ -25835,7 +25881,7 @@
         <v/>
       </c>
       <c r="V62" t="str">
-        <f>IFERROR(INDEX(ピッキング!$L$7:$L$66,MATCH($T62,ピッキング!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(ピッキング!$R$7:$R$66,MATCH($T62,ピッキング!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="W62" t="str">
@@ -25843,7 +25889,7 @@
         <v/>
       </c>
       <c r="X62" t="str">
-        <f>IFERROR(INDEX(梱包!$L$7:$L$66,MATCH($T62,梱包!$A$7:$A$66,0)),"")</f>
+        <f>IFERROR(INDEX(梱包!$R$7:$R$66,MATCH($T62,梱包!$A$7:$A$66,0)),"")</f>
         <v/>
       </c>
       <c r="Z62" t="str">
@@ -26014,7 +26060,7 @@
     </row>
     <row r="148" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B148" s="9" t="s">
-        <v>79</v>
+        <v>481</v>
       </c>
     </row>
     <row r="149" spans="2:10" x14ac:dyDescent="0.15">
@@ -26240,18 +26286,18 @@
     </row>
     <row r="162" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B162" s="25" t="s">
-        <v>104</v>
+        <v>486</v>
       </c>
       <c r="C162" s="26">
         <f>ピッキング!$T$6</f>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D162" s="26">
         <f>梱包!$T$6</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E162" s="64" t="s">
-        <v>105</v>
+        <v>487</v>
       </c>
       <c r="F162" s="65"/>
       <c r="G162" s="65"/>
@@ -26261,18 +26307,18 @@
     </row>
     <row r="163" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B163" s="25" t="s">
-        <v>106</v>
+        <v>488</v>
       </c>
       <c r="C163" s="26">
         <f>ピッキング!$T$7</f>
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="D163" s="26">
         <f>梱包!$T$7</f>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E163" s="64" t="s">
-        <v>107</v>
+        <v>489</v>
       </c>
       <c r="F163" s="65"/>
       <c r="G163" s="65"/>
@@ -26282,18 +26328,18 @@
     </row>
     <row r="164" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B164" s="25" t="s">
-        <v>108</v>
+        <v>490</v>
       </c>
       <c r="C164" s="26">
         <f>ピッキング!$T$8</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D164" s="26">
         <f>梱包!$T$8</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E164" s="64" t="s">
-        <v>109</v>
+        <v>491</v>
       </c>
       <c r="F164" s="65"/>
       <c r="G164" s="65"/>
@@ -26301,6 +26347,27 @@
       <c r="I164" s="65"/>
       <c r="J164" s="65"/>
     </row>
+    <row r="165" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B165" s="25" t="s">
+        <v>492</v>
+      </c>
+      <c r="C165" s="26">
+        <f>ピッキング!$T$9</f>
+        <v>15</v>
+      </c>
+      <c r="D165" s="26">
+        <f>梱包!$T$9</f>
+        <v>4</v>
+      </c>
+      <c r="E165" s="64" t="s">
+        <v>493</v>
+      </c>
+      <c r="F165" s="65"/>
+      <c r="G165" s="65"/>
+      <c r="H165" s="65"/>
+      <c r="I165" s="65"/>
+      <c r="J165" s="65"/>
+    </row>
     <row r="166" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B166" s="3" t="s">
         <v>110</v>
@@ -26308,7 +26375,7 @@
     </row>
     <row r="234" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B234" s="3" t="s">
-        <v>111</v>
+        <v>494</v>
       </c>
     </row>
     <row r="235" spans="2:2" x14ac:dyDescent="0.15">
@@ -26503,7 +26570,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B12" s="3" t="s">
-        <v>368</v>
+        <v>482</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.15">
@@ -26800,7 +26867,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.15">
       <c r="C11" s="91" t="s">
-        <v>383</v>
+        <v>483</v>
       </c>
       <c r="D11" s="80"/>
       <c r="E11" s="80"/>
@@ -26856,7 +26923,7 @@
         <v>390</v>
       </c>
       <c r="C21" s="93" t="s">
-        <v>391</v>
+        <v>495</v>
       </c>
       <c r="D21" s="74"/>
       <c r="E21" s="74"/>
@@ -26940,7 +27007,7 @@
         <v>265</v>
       </c>
       <c r="C28" s="93" t="s">
-        <v>402</v>
+        <v>484</v>
       </c>
       <c r="D28" s="74"/>
       <c r="E28" s="74"/>
@@ -26964,7 +27031,7 @@
         <v>183</v>
       </c>
       <c r="C30" s="93" t="s">
-        <v>405</v>
+        <v>485</v>
       </c>
       <c r="D30" s="74"/>
       <c r="E30" s="74"/>
@@ -42552,8 +42619,8 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A7" s="48">
-        <f t="shared" ref="A7:A38" si="0">IF(L7="","",RANK(L7,$L$7:$L$66,0))</f>
-        <v>1</v>
+        <f t="shared" ref="A7:A38" si="0">IF(R7="","",RANK(R7,$R$7:$R$66,0))</f>
+        <v>2</v>
       </c>
       <c r="B7" s="21" t="str">
         <f>IF(入力!$B$10="","",入力!$B$10)</f>
@@ -42640,7 +42707,7 @@
     <row r="8" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A8" s="48">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" s="21" t="str">
         <f>IF(入力!$B$11="","",入力!$B$11)</f>
@@ -42727,7 +42794,7 @@
     <row r="9" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A9" s="48">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B9" s="21" t="str">
         <f>IF(入力!$B$12="","",入力!$B$12)</f>
@@ -42814,7 +42881,7 @@
     <row r="10" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A10" s="48">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B10" s="21" t="str">
         <f>IF(入力!$B$13="","",入力!$B$13)</f>
@@ -42899,7 +42966,7 @@
     <row r="11" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A11" s="48">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B11" s="21" t="str">
         <f>IF(入力!$B$14="","",入力!$B$14)</f>
@@ -42984,7 +43051,7 @@
     <row r="12" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A12" s="48">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B12" s="21" t="str">
         <f>IF(入力!$B$15="","",入力!$B$15)</f>
@@ -43069,7 +43136,7 @@
     <row r="13" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A13" s="48">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B13" s="21" t="str">
         <f>IF(入力!$B$16="","",入力!$B$16)</f>
@@ -43154,7 +43221,7 @@
     <row r="14" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A14" s="48">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B14" s="21" t="str">
         <f>IF(入力!$B$17="","",入力!$B$17)</f>
@@ -43239,7 +43306,7 @@
     <row r="15" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A15" s="48">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B15" s="21" t="str">
         <f>IF(入力!$B$18="","",入力!$B$18)</f>
@@ -43324,7 +43391,7 @@
     <row r="16" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A16" s="48">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B16" s="21" t="str">
         <f>IF(入力!$B$19="","",入力!$B$19)</f>
@@ -43409,7 +43476,7 @@
     <row r="17" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A17" s="48">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B17" s="21" t="str">
         <f>IF(入力!$B$20="","",入力!$B$20)</f>
@@ -43494,7 +43561,7 @@
     <row r="18" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A18" s="48">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B18" s="21" t="str">
         <f>IF(入力!$B$21="","",入力!$B$21)</f>
@@ -43572,7 +43639,7 @@
     <row r="19" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A19" s="48">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B19" s="21" t="str">
         <f>IF(入力!$B$22="","",入力!$B$22)</f>
@@ -43650,7 +43717,7 @@
     <row r="20" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A20" s="48">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B20" s="21" t="str">
         <f>IF(入力!$B$23="","",入力!$B$23)</f>
@@ -43728,7 +43795,7 @@
     <row r="21" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A21" s="48">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B21" s="21" t="str">
         <f>IF(入力!$B$24="","",入力!$B$24)</f>
@@ -43806,7 +43873,7 @@
     <row r="22" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A22" s="48">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B22" s="21" t="str">
         <f>IF(入力!$B$25="","",入力!$B$25)</f>
@@ -43884,7 +43951,7 @@
     <row r="23" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A23" s="48">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B23" s="21" t="str">
         <f>IF(入力!$B$26="","",入力!$B$26)</f>
@@ -43962,7 +44029,7 @@
     <row r="24" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A24" s="48">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B24" s="21" t="str">
         <f>IF(入力!$B$27="","",入力!$B$27)</f>
@@ -44040,7 +44107,7 @@
     <row r="25" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A25" s="48">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B25" s="21" t="str">
         <f>IF(入力!$B$28="","",入力!$B$28)</f>
@@ -44118,7 +44185,7 @@
     <row r="26" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A26" s="48">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B26" s="21" t="str">
         <f>IF(入力!$B$29="","",入力!$B$29)</f>
@@ -44196,7 +44263,7 @@
     <row r="27" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A27" s="48">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B27" s="21" t="str">
         <f>IF(入力!$B$30="","",入力!$B$30)</f>
@@ -44274,7 +44341,7 @@
     <row r="28" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A28" s="48">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B28" s="21" t="str">
         <f>IF(入力!$B$31="","",入力!$B$31)</f>
@@ -44352,7 +44419,7 @@
     <row r="29" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A29" s="48">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B29" s="21" t="str">
         <f>IF(入力!$B$32="","",入力!$B$32)</f>
@@ -44430,7 +44497,7 @@
     <row r="30" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A30" s="48">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B30" s="21" t="str">
         <f>IF(入力!$B$33="","",入力!$B$33)</f>
@@ -44508,7 +44575,7 @@
     <row r="31" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A31" s="48">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B31" s="21" t="str">
         <f>IF(入力!$B$34="","",入力!$B$34)</f>
@@ -44664,7 +44731,7 @@
     <row r="33" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A33" s="48">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B33" s="21" t="str">
         <f>IF(入力!$B$36="","",入力!$B$36)</f>
@@ -44742,7 +44809,7 @@
     <row r="34" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A34" s="48">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B34" s="21" t="str">
         <f>IF(入力!$B$37="","",入力!$B$37)</f>
@@ -44820,7 +44887,7 @@
     <row r="35" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A35" s="48">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B35" s="21" t="str">
         <f>IF(入力!$B$38="","",入力!$B$38)</f>
@@ -45131,7 +45198,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A39" s="48" t="str">
-        <f t="shared" ref="A39:A66" si="9">IF(L39="","",RANK(L39,$L$7:$L$66,0))</f>
+        <f t="shared" ref="A39:A66" si="9">IF(R39="","",RANK(R39,$R$7:$R$66,0))</f>
         <v/>
       </c>
       <c r="B39" s="21" t="str">
@@ -47480,7 +47547,7 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A7" s="48">
-        <f t="shared" ref="A7:A38" si="0">IF(L7="","",RANK(L7,$L$7:$L$66,0))</f>
+        <f t="shared" ref="A7:A38" si="0">IF(R7="","",RANK(R7,$R$7:$R$66,0))</f>
         <v>2</v>
       </c>
       <c r="B7" s="21" t="str">
@@ -47568,7 +47635,7 @@
     <row r="8" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A8" s="48">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B8" s="21" t="str">
         <f>IF(入力!$B$11="","",入力!$B$11)</f>
@@ -47655,7 +47722,7 @@
     <row r="9" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A9" s="48">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B9" s="21" t="str">
         <f>IF(入力!$B$12="","",入力!$B$12)</f>
@@ -47742,7 +47809,7 @@
     <row r="10" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A10" s="48">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B10" s="21" t="str">
         <f>IF(入力!$B$13="","",入力!$B$13)</f>
@@ -47912,7 +47979,7 @@
     <row r="12" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A12" s="48">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" s="21" t="str">
         <f>IF(入力!$B$15="","",入力!$B$15)</f>
@@ -47997,7 +48064,7 @@
     <row r="13" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A13" s="48">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B13" s="21" t="str">
         <f>IF(入力!$B$16="","",入力!$B$16)</f>
@@ -48082,7 +48149,7 @@
     <row r="14" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A14" s="48">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B14" s="21" t="str">
         <f>IF(入力!$B$17="","",入力!$B$17)</f>
@@ -48167,7 +48234,7 @@
     <row r="15" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A15" s="48">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B15" s="21" t="str">
         <f>IF(入力!$B$18="","",入力!$B$18)</f>
@@ -48252,7 +48319,7 @@
     <row r="16" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A16" s="48">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B16" s="21" t="str">
         <f>IF(入力!$B$19="","",入力!$B$19)</f>
@@ -48422,7 +48489,7 @@
     <row r="18" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A18" s="48">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B18" s="21" t="str">
         <f>IF(入力!$B$21="","",入力!$B$21)</f>
@@ -48734,7 +48801,7 @@
     <row r="22" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A22" s="48">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B22" s="21" t="str">
         <f>IF(入力!$B$25="","",入力!$B$25)</f>
@@ -48968,7 +49035,7 @@
     <row r="25" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A25" s="48">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B25" s="21" t="str">
         <f>IF(入力!$B$28="","",入力!$B$28)</f>
@@ -49748,7 +49815,7 @@
     <row r="35" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A35" s="48">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B35" s="21" t="str">
         <f>IF(入力!$B$38="","",入力!$B$38)</f>
@@ -50059,7 +50126,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A39" s="48" t="str">
-        <f t="shared" ref="A39:A66" si="9">IF(L39="","",RANK(L39,$L$7:$L$66,0))</f>
+        <f t="shared" ref="A39:A66" si="9">IF(R39="","",RANK(R39,$R$7:$R$66,0))</f>
         <v/>
       </c>
       <c r="B39" s="21" t="str">

--- a/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
+++ b/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="498">
   <si>
     <t>▼ グラフ用データ　消したり非表示にしたりしないでください</t>
   </si>
@@ -1597,6 +1597,12 @@
   </si>
   <si>
     <t xml:space="preserve">1社ごとに必ず発生する時間。ピッキングは 56.05秒/社（① リストを見る 10秒 ＋ ④ 伝票を挟む 46.05秒）。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">順位の再現性。1に近いほど順位が安定。ピッキング 0.40／梱包 0.87。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">・ピッキングは信頼性 0.40 と低めです。1か月の順位だけで人を決めず、数か月ならして見てください。</t>
   </si>
 </sst>
 </file>
@@ -20759,9 +20765,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tbl_PK" displayName="Tbl_PK" ref="A6:R66" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A6:R66"/>
-  <tableColumns count="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tbl_PK" displayName="Tbl_PK" ref="A6:T66" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A6:T66"/>
+  <tableColumns count="20">
     <tableColumn id="1" name="順位"/>
     <tableColumn id="2" name="担当者名"/>
     <tableColumn id="3" name="件数"/>
@@ -20780,15 +20786,17 @@
     <tableColumn id="16" name="純速度&#10;秒/件"/>
     <tableColumn id="17" name="公平目標&#10;分/個"/>
     <tableColumn id="18" name="目標達成率&#10;%"/>
+    <tableColumn id="19" name="目標まで&#10;あと"/>
+    <tableColumn id="20" name="目標到達で&#10;増やせる件数"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tbl_KP" displayName="Tbl_KP" ref="A6:R66" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A6:R66"/>
-  <tableColumns count="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tbl_KP" displayName="Tbl_KP" ref="A6:T66" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A6:T66"/>
+  <tableColumns count="20">
     <tableColumn id="1" name="順位"/>
     <tableColumn id="2" name="担当者名"/>
     <tableColumn id="3" name="件数"/>
@@ -20807,6 +20815,8 @@
     <tableColumn id="16" name="純速度&#10;秒/件"/>
     <tableColumn id="17" name="公平目標&#10;分/個"/>
     <tableColumn id="18" name="目標達成率&#10;%"/>
+    <tableColumn id="19" name="目標まで&#10;あと"/>
+    <tableColumn id="20" name="目標到達で&#10;増やせる件数"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -22092,14 +22102,14 @@
     </row>
     <row r="11" spans="2:52" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="68">
-        <f>ピッキング!$T$10+梱包!$T$10</f>
+        <f>ピッキング!$W$10+梱包!$W$10</f>
         <v>45716</v>
       </c>
       <c r="C11" s="67"/>
       <c r="D11" s="67"/>
       <c r="E11" s="67"/>
       <c r="F11" s="82">
-        <f>IFERROR((ピッキング!$T$14+梱包!$T$14)/(ピッキング!$T$12+梱包!$T$12)*100,"")</f>
+        <f>IFERROR((ピッキング!$W$14+梱包!$W$14)/(ピッキング!$W$12+梱包!$W$12)*100,"")</f>
         <v>100.0345895569223</v>
       </c>
       <c r="G11" s="67"/>
@@ -22599,14 +22609,14 @@
     </row>
     <row r="16" spans="2:52" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="83">
-        <f>IFERROR(ピッキング!$T$13/ピッキング!$T$12,"")</f>
+        <f>IFERROR(ピッキング!$W$13/ピッキング!$W$12,"")</f>
         <v>0.33557881551953839</v>
       </c>
       <c r="C16" s="67"/>
       <c r="D16" s="67"/>
       <c r="E16" s="67"/>
       <c r="F16" s="77">
-        <f>IFERROR((ピッキング!$T$12+梱包!$T$12)/60,"")</f>
+        <f>IFERROR((ピッキング!$W$12+梱包!$W$12)/60,"")</f>
         <v>1327.8333333333333</v>
       </c>
       <c r="G16" s="67"/>
@@ -26100,11 +26110,11 @@
         <v>87</v>
       </c>
       <c r="C153" s="26">
-        <f>ピッキング!$T$5</f>
+        <f>ピッキング!$W$5</f>
         <v>29</v>
       </c>
       <c r="D153" s="26">
-        <f>梱包!$T$5</f>
+        <f>梱包!$W$5</f>
         <v>19</v>
       </c>
       <c r="E153" s="64" t="s">
@@ -26121,11 +26131,11 @@
         <v>89</v>
       </c>
       <c r="C154" s="26">
-        <f>ピッキング!$T$10</f>
+        <f>ピッキング!$W$10</f>
         <v>21249</v>
       </c>
       <c r="D154" s="26">
-        <f>梱包!$T$10</f>
+        <f>梱包!$W$10</f>
         <v>24467</v>
       </c>
       <c r="E154" s="64" t="s">
@@ -26142,11 +26152,11 @@
         <v>91</v>
       </c>
       <c r="C155" s="26">
-        <f>ピッキング!$T$11</f>
+        <f>ピッキング!$W$11</f>
         <v>9094</v>
       </c>
       <c r="D155" s="26">
-        <f>梱包!$T$11</f>
+        <f>梱包!$W$11</f>
         <v>7099</v>
       </c>
       <c r="E155" s="64" t="s">
@@ -26163,11 +26173,11 @@
         <v>93</v>
       </c>
       <c r="C156" s="27">
-        <f>ピッキング!$T$16</f>
+        <f>ピッキング!$W$16</f>
         <v>2.3365955575104462</v>
       </c>
       <c r="D156" s="27">
-        <f>梱包!$T$16</f>
+        <f>梱包!$W$16</f>
         <v>3.4465417664459781</v>
       </c>
       <c r="E156" s="64" t="s">
@@ -26184,11 +26194,11 @@
         <v>95</v>
       </c>
       <c r="C157" s="28">
-        <f>IFERROR(ピッキング!$T$12/60,"")</f>
+        <f>IFERROR(ピッキング!$W$12/60,"")</f>
         <v>679.7166666666667</v>
       </c>
       <c r="D157" s="28">
-        <f>IFERROR(梱包!$T$12/60,"")</f>
+        <f>IFERROR(梱包!$W$12/60,"")</f>
         <v>648.11666666666667</v>
       </c>
       <c r="E157" s="64" t="s">
@@ -26205,11 +26215,11 @@
         <v>97</v>
       </c>
       <c r="C158" s="28">
-        <f>IFERROR(ピッキング!$T$13/60,"")</f>
+        <f>IFERROR(ピッキング!$W$13/60,"")</f>
         <v>228.0985138888889</v>
       </c>
       <c r="D158" s="28">
-        <f>IFERROR(梱包!$T$13/60,"")</f>
+        <f>IFERROR(梱包!$W$13/60,"")</f>
         <v>181.61608333333331</v>
       </c>
       <c r="E158" s="64" t="s">
@@ -26226,11 +26236,11 @@
         <v>50</v>
       </c>
       <c r="C159" s="30">
-        <f>ピッキング!$T$15</f>
+        <f>ピッキング!$W$15</f>
         <v>0.33826072522746486</v>
       </c>
       <c r="D159" s="30">
-        <f>梱包!$T$15</f>
+        <f>梱包!$W$15</f>
         <v>0.2777152484859029</v>
       </c>
       <c r="E159" s="64" t="s">
@@ -26247,11 +26257,11 @@
         <v>100</v>
       </c>
       <c r="C160" s="22">
-        <f>ピッキング!$T$17</f>
+        <f>ピッキング!$W$17</f>
         <v>115.15741917266695</v>
       </c>
       <c r="D160" s="22">
-        <f>梱包!$T$17</f>
+        <f>梱包!$W$17</f>
         <v>95.361916050190047</v>
       </c>
       <c r="E160" s="64" t="s">
@@ -26268,11 +26278,11 @@
         <v>102</v>
       </c>
       <c r="C161" s="31">
-        <f>ピッキング!$T$3</f>
+        <f>ピッキング!$W$3</f>
         <v>102.59731598413305</v>
       </c>
       <c r="D161" s="31">
-        <f>梱包!$T$3</f>
+        <f>梱包!$W$3</f>
         <v>109.44372058095747</v>
       </c>
       <c r="E161" s="64" t="s">
@@ -26289,11 +26299,11 @@
         <v>486</v>
       </c>
       <c r="C162" s="26">
-        <f>ピッキング!$T$6</f>
+        <f>ピッキング!$W$6</f>
         <v>7</v>
       </c>
       <c r="D162" s="26">
-        <f>梱包!$T$6</f>
+        <f>梱包!$W$6</f>
         <v>8</v>
       </c>
       <c r="E162" s="64" t="s">
@@ -26310,11 +26320,11 @@
         <v>488</v>
       </c>
       <c r="C163" s="26">
-        <f>ピッキング!$T$7</f>
+        <f>ピッキング!$W$7</f>
         <v>3</v>
       </c>
       <c r="D163" s="26">
-        <f>梱包!$T$7</f>
+        <f>梱包!$W$7</f>
         <v>3</v>
       </c>
       <c r="E163" s="64" t="s">
@@ -26331,11 +26341,11 @@
         <v>490</v>
       </c>
       <c r="C164" s="26">
-        <f>ピッキング!$T$8</f>
+        <f>ピッキング!$W$8</f>
         <v>4</v>
       </c>
       <c r="D164" s="26">
-        <f>梱包!$T$8</f>
+        <f>梱包!$W$8</f>
         <v>4</v>
       </c>
       <c r="E164" s="64" t="s">
@@ -26352,11 +26362,11 @@
         <v>492</v>
       </c>
       <c r="C165" s="26">
-        <f>ピッキング!$T$9</f>
+        <f>ピッキング!$W$9</f>
         <v>15</v>
       </c>
       <c r="D165" s="26">
-        <f>梱包!$T$9</f>
+        <f>梱包!$W$9</f>
         <v>4</v>
       </c>
       <c r="E165" s="64" t="s">
@@ -27055,12 +27065,44 @@
         <v>408</v>
       </c>
       <c r="C32" s="93" t="s">
-        <v>409</v>
+        <v>496</v>
       </c>
       <c r="D32" s="74"/>
       <c r="E32" s="74"/>
       <c r="F32" s="74"/>
       <c r="G32" s="75"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.15">
+      <c r="B33" s="29" t="inlineStr">
+        <is>
+          <t>目標まで あと</t>
+        </is>
+      </c>
+      <c r="C33" s="93" t="inlineStr">
+        <is>
+          <t>1件あたりの実測秒と、会社目標 96秒（1.6分）との差。到達している人は「達成済み」と出ます。</t>
+        </is>
+      </c>
+      <c r="D33" s="74"/>
+      <c r="E33" s="74"/>
+      <c r="F33" s="74"/>
+      <c r="G33" s="75"/>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.15">
+      <c r="B34" s="29" t="inlineStr">
+        <is>
+          <t>目標到達で増やせる件数</t>
+        </is>
+      </c>
+      <c r="C34" s="93" t="inlineStr">
+        <is>
+          <t>同じ時間で目標ペースなら処理できたはずの件数と、実績との差。マイナスは、目標ペースより先行している分です。</t>
+        </is>
+      </c>
+      <c r="D34" s="74"/>
+      <c r="E34" s="74"/>
+      <c r="F34" s="74"/>
+      <c r="G34" s="75"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B35" s="9" t="s">
@@ -27099,7 +27141,7 @@
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B39" s="92" t="s">
-        <v>414</v>
+        <v>497</v>
       </c>
       <c r="C39" s="80"/>
       <c r="D39" s="80"/>
@@ -27158,7 +27200,9 @@
       <c r="G44" s="80"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="26">
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
     <mergeCell ref="B42:G42"/>
     <mergeCell ref="C24:G24"/>
     <mergeCell ref="C11:G12"/>
@@ -42487,7 +42531,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A2:U66"/>
+  <dimension ref="A2:Y66"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -42503,53 +42547,56 @@
     <col min="16" max="16" width="9" customWidth="1"/>
     <col min="17" max="17" width="10" customWidth="1"/>
     <col min="18" max="18" width="10" customWidth="1"/>
-    <col min="19" max="19" width="22" customWidth="1"/>
-    <col min="20" max="20" width="12" customWidth="1"/>
-    <col min="21" max="21" width="13" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="12" customWidth="1"/>
+    <col min="20" max="20" width="14" customWidth="1"/>
+    <col min="22" max="22" width="22" customWidth="1"/>
+    <col min="23" max="23" width="12" customWidth="1"/>
+    <col min="24" max="24" width="13" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:21" ht="17.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" ht="17.25" x14ac:dyDescent="0.2">
       <c r="B2" s="44" t="s">
         <v>169</v>
       </c>
-      <c r="S2" s="9" t="s">
+      <c r="V2" s="9" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:25" ht="14.25" x14ac:dyDescent="0.15">
       <c r="B3" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="S3" s="45" t="s">
+      <c r="V3" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="T3" s="46">
-        <f>IFERROR(SUM(U7:U66)/SUMIF(I7:I66,"&gt;0",C7:C66),"")</f>
+      <c r="W3" s="46">
+        <f>IFERROR(SUM(X7:X66)/SUMIF(I7:I66,"&gt;0",C7:C66),"")</f>
         <v>102.59731598413305</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.15">
       <c r="B4" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="S4" s="47" t="s">
+      <c r="V4" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="T4" s="21"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="W4" s="21"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.15">
       <c r="B5" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="S5" s="47" t="s">
+      <c r="V5" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="T5" s="26">
+      <c r="W5" s="26">
         <f>COUNT(L7:L66)</f>
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="20" t="s">
         <v>3</v>
       </c>
@@ -42607,17 +42654,29 @@
 %</t>
         </is>
       </c>
-      <c r="S6" s="47" t="inlineStr">
+      <c r="S6" s="20" t="inlineStr">
+        <is>
+          <t>目標まで
+あと</t>
+        </is>
+      </c>
+      <c r="T6" s="20" t="inlineStr">
+        <is>
+          <t>目標到達で
+増やせる件数</t>
+        </is>
+      </c>
+      <c r="V6" s="47" t="inlineStr">
         <is>
           <t>◎ 達成</t>
         </is>
       </c>
-      <c r="T6" s="26">
+      <c r="W6" s="26">
         <f>COUNTIF(O7:O66,"◎達成")</f>
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A7" s="48">
         <f t="shared" ref="A7:A38" si="0">IF(R7="","",RANK(R7,$R$7:$R$66,0))</f>
         <v>2</v>
@@ -42663,7 +42722,7 @@
         <v>136.58407297830374</v>
       </c>
       <c r="L7" s="22">
-        <f>IF(K7="","",IF(AND(K7&lt;&gt;"",ISNUMBER(入力!$F$10),入力!$F$10&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$10))*(K7-$T$3),K7))</f>
+        <f>IF(K7="","",IF(AND(K7&lt;&gt;"",ISNUMBER(入力!$F$10),入力!$F$10&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$10))*(K7-$W$3),K7))</f>
         <v>127.03460719829701</v>
       </c>
       <c r="M7" s="22">
@@ -42690,21 +42749,33 @@
         <f>IF(C7="","",設定!$C$26*C7/D7*100)</f>
         <v>114.71400394477318</v>
       </c>
-      <c r="S7" s="47" t="inlineStr">
+      <c r="S7" s="50" t="str">
+        <f>IF(Y7="","",IF(Y7&lt;=0,"達成済み",IF(Y7&lt;60,Y7&amp;"秒",INT(Y7/60)&amp;"分"&amp;TEXT(MOD(Y7,60),"00")&amp;"秒")))</f>
+        <v>達成済み</v>
+      </c>
+      <c r="T7" s="26">
+        <f>IF(C7="","",D7/設定!$C$26-C7)</f>
+        <v>-186.5</v>
+      </c>
+      <c r="V7" s="47" t="inlineStr">
         <is>
           <t>○ あと一歩</t>
         </is>
       </c>
-      <c r="T7" s="26">
+      <c r="W7" s="26">
         <f>COUNTIF(O7:O66,"○あと一歩")</f>
         <v>3</v>
       </c>
-      <c r="U7">
-        <f t="shared" ref="U7:U38" si="8">IF(K7="",0,K7*C7)</f>
+      <c r="X7">
+        <f t="shared" ref="X7:X38" si="8">IF(K7="",0,K7*C7)</f>
         <v>198593.24211045363</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y7">
+        <f>IF(C7="","",ROUND(G7-設定!$C$26*60,0))</f>
+        <v>-12.0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A8" s="48">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -42750,7 +42821,7 @@
         <v>114.09203480589021</v>
       </c>
       <c r="L8" s="22">
-        <f>IF(K8="","",IF(AND(K8&lt;&gt;"",ISNUMBER(入力!$F$11),入力!$F$11&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$11))*(K8-$T$3),K8))</f>
+        <f>IF(K8="","",IF(AND(K8&lt;&gt;"",ISNUMBER(入力!$F$11),入力!$F$11&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$11))*(K8-$W$3),K8))</f>
         <v>109.608647015599</v>
       </c>
       <c r="M8" s="22">
@@ -42777,21 +42848,33 @@
         <f>IF(C8="","",設定!$C$26*C8/D8*100)</f>
         <v>101.5261044176707</v>
       </c>
-      <c r="S8" s="47" t="inlineStr">
+      <c r="S8" s="50" t="str">
+        <f>IF(Y8="","",IF(Y8&lt;=0,"達成済み",IF(Y8&lt;60,Y8&amp;"秒",INT(Y8/60)&amp;"分"&amp;TEXT(MOD(Y8,60),"00")&amp;"秒")))</f>
+        <v>達成済み</v>
+      </c>
+      <c r="T8" s="26">
+        <f>IF(C8="","",D8/設定!$C$26-C8)</f>
+        <v>-11.875</v>
+      </c>
+      <c r="V8" s="47" t="inlineStr">
         <is>
           <t>△ 要改善</t>
         </is>
       </c>
-      <c r="T8" s="26">
+      <c r="W8" s="26">
         <f>COUNTIF(O7:O66,"△要改善")</f>
         <v>4</v>
       </c>
-      <c r="U8">
+      <c r="X8">
         <f t="shared" si="8"/>
         <v>90132.707496653267</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y8">
+        <f>IF(C8="","",ROUND(G8-設定!$C$26*60,0))</f>
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A9" s="48">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -42837,7 +42920,7 @@
         <v>128.62508143322475</v>
       </c>
       <c r="L9" s="22">
-        <f>IF(K9="","",IF(AND(K9&lt;&gt;"",ISNUMBER(入力!$F$12),入力!$F$12&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$12))*(K9-$T$3),K9))</f>
+        <f>IF(K9="","",IF(AND(K9&lt;&gt;"",ISNUMBER(入力!$F$12),入力!$F$12&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$12))*(K9-$W$3),K9))</f>
         <v>120.67691021365592</v>
       </c>
       <c r="M9" s="22">
@@ -42864,21 +42947,33 @@
         <f>IF(C9="","",設定!$C$26*C9/D9*100)</f>
         <v>102.25407166123779</v>
       </c>
-      <c r="S9" s="47" t="inlineStr">
+      <c r="S9" s="50" t="str">
+        <f>IF(Y9="","",IF(Y9&lt;=0,"達成済み",IF(Y9&lt;60,Y9&amp;"秒",INT(Y9/60)&amp;"分"&amp;TEXT(MOD(Y9,60),"00")&amp;"秒")))</f>
+        <v>達成済み</v>
+      </c>
+      <c r="T9" s="26">
+        <f>IF(C9="","",D9/設定!$C$26-C9)</f>
+        <v>-21.625</v>
+      </c>
+      <c r="V9" s="47" t="inlineStr">
         <is>
           <t>✕ 要支援</t>
         </is>
       </c>
-      <c r="T9" s="26">
+      <c r="W9" s="26">
         <f>COUNTIF(O7:O66,"✕要支援")</f>
         <v>15</v>
       </c>
-      <c r="U9">
+      <c r="X9">
         <f t="shared" si="8"/>
         <v>126181.20488599347</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y9">
+        <f>IF(C9="","",ROUND(G9-設定!$C$26*60,0))</f>
+        <v>-2.0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A10" s="48">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -42924,7 +43019,7 @@
         <v>131.80246913580245</v>
       </c>
       <c r="L10" s="22">
-        <f>IF(K10="","",IF(AND(K10&lt;&gt;"",ISNUMBER(入力!$F$13),入力!$F$13&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$13))*(K10-$T$3),K10))</f>
+        <f>IF(K10="","",IF(AND(K10&lt;&gt;"",ISNUMBER(入力!$F$13),入力!$F$13&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$13))*(K10-$W$3),K10))</f>
         <v>119.7425901187512</v>
       </c>
       <c r="M10" s="22">
@@ -42951,19 +43046,31 @@
         <f>IF(C10="","",設定!$C$26*C10/D10*100)</f>
         <v>131.7530864197531</v>
       </c>
-      <c r="S10" s="47" t="s">
+      <c r="S10" s="50" t="str">
+        <f>IF(Y10="","",IF(Y10&lt;=0,"達成済み",IF(Y10&lt;60,Y10&amp;"秒",INT(Y10/60)&amp;"分"&amp;TEXT(MOD(Y10,60),"00")&amp;"秒")))</f>
+        <v>達成済み</v>
+      </c>
+      <c r="T10" s="26">
+        <f>IF(C10="","",D10/設定!$C$26-C10)</f>
+        <v>-160.75</v>
+      </c>
+      <c r="V10" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="T10" s="26">
+      <c r="W10" s="26">
         <f>SUMIF(I7:I66,"&gt;0",C7:C66)</f>
         <v>21249</v>
       </c>
-      <c r="U10">
+      <c r="X10">
         <f t="shared" si="8"/>
         <v>87912.246913580238</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y10">
+        <f>IF(C10="","",ROUND(G10-設定!$C$26*60,0))</f>
+        <v>-23.0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A11" s="48">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -43009,7 +43116,7 @@
         <v>126.5595238095238</v>
       </c>
       <c r="L11" s="22">
-        <f>IF(K11="","",IF(AND(K11&lt;&gt;"",ISNUMBER(入力!$F$14),入力!$F$14&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$14))*(K11-$T$3),K11))</f>
+        <f>IF(K11="","",IF(AND(K11&lt;&gt;"",ISNUMBER(入力!$F$14),入力!$F$14&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$14))*(K11-$W$3),K11))</f>
         <v>111.28404540730916</v>
       </c>
       <c r="M11" s="22">
@@ -43036,19 +43143,31 @@
         <f>IF(C11="","",設定!$C$26*C11/D11*100)</f>
         <v>92.95238095238096</v>
       </c>
-      <c r="S11" s="47" t="s">
+      <c r="S11" s="50" t="str">
+        <f>IF(Y11="","",IF(Y11&lt;=0,"達成済み",IF(Y11&lt;60,Y11&amp;"秒",INT(Y11/60)&amp;"分"&amp;TEXT(MOD(Y11,60),"00")&amp;"秒")))</f>
+        <v>7秒</v>
+      </c>
+      <c r="T11" s="26">
+        <f>IF(C11="","",D11/設定!$C$26-C11)</f>
+        <v>9.25</v>
+      </c>
+      <c r="V11" s="47" t="s">
         <v>91</v>
       </c>
-      <c r="T11" s="26">
+      <c r="W11" s="26">
         <f>SUMIF(I7:I66,"&gt;0",E7:E66)</f>
         <v>9094</v>
       </c>
-      <c r="U11">
+      <c r="X11">
         <f t="shared" si="8"/>
         <v>15440.261904761903</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y11">
+        <f>IF(C11="","",ROUND(G11-設定!$C$26*60,0))</f>
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A12" s="48">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -43094,7 +43213,7 @@
         <v>111.60069735006972</v>
       </c>
       <c r="L12" s="22">
-        <f>IF(K12="","",IF(AND(K12&lt;&gt;"",ISNUMBER(入力!$F$15),入力!$F$15&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$15))*(K12-$T$3),K12))</f>
+        <f>IF(K12="","",IF(AND(K12&lt;&gt;"",ISNUMBER(入力!$F$15),入力!$F$15&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$15))*(K12-$W$3),K12))</f>
         <v>109.25811506173572</v>
       </c>
       <c r="M12" s="22">
@@ -43121,19 +43240,31 @@
         <f>IF(C12="","",設定!$C$26*C12/D12*100)</f>
         <v>89.57322175732219</v>
       </c>
-      <c r="S12" s="47" t="s">
+      <c r="S12" s="50" t="str">
+        <f>IF(Y12="","",IF(Y12&lt;=0,"達成済み",IF(Y12&lt;60,Y12&amp;"秒",INT(Y12/60)&amp;"分"&amp;TEXT(MOD(Y12,60),"00")&amp;"秒")))</f>
+        <v>11秒</v>
+      </c>
+      <c r="T12" s="26">
+        <f>IF(C12="","",D12/設定!$C$26-C12)</f>
+        <v>233.625</v>
+      </c>
+      <c r="V12" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="T12" s="26">
+      <c r="W12" s="26">
         <f>SUMIF(I7:I66,"&gt;0",D7:D66)</f>
         <v>40783</v>
       </c>
-      <c r="U12">
+      <c r="X12">
         <f t="shared" si="8"/>
         <v>223982.59958158992</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y12">
+        <f>IF(C12="","",ROUND(G12-設定!$C$26*60,0))</f>
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A13" s="48">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -43179,7 +43310,7 @@
         <v>121.32499999999997</v>
       </c>
       <c r="L13" s="22">
-        <f>IF(K13="","",IF(AND(K13&lt;&gt;"",ISNUMBER(入力!$F$16),入力!$F$16&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$16))*(K13-$T$3),K13))</f>
+        <f>IF(K13="","",IF(AND(K13&lt;&gt;"",ISNUMBER(入力!$F$16),入力!$F$16&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$16))*(K13-$W$3),K13))</f>
         <v>108.19661844228943</v>
       </c>
       <c r="M13" s="22">
@@ -43206,19 +43337,31 @@
         <f>IF(C13="","",設定!$C$26*C13/D13*100)</f>
         <v>105.33333333333334</v>
       </c>
-      <c r="S13" s="47" t="s">
+      <c r="S13" s="50" t="str">
+        <f>IF(Y13="","",IF(Y13&lt;=0,"達成済み",IF(Y13&lt;60,Y13&amp;"秒",INT(Y13/60)&amp;"分"&amp;TEXT(MOD(Y13,60),"00")&amp;"秒")))</f>
+        <v>達成済み</v>
+      </c>
+      <c r="T13" s="26">
+        <f>IF(C13="","",D13/設定!$C$26-C13)</f>
+        <v>-4.0</v>
+      </c>
+      <c r="V13" s="47" t="s">
         <v>187</v>
       </c>
-      <c r="T13" s="26">
+      <c r="W13" s="26">
         <f>SUMIF(I7:I66,"&gt;0",H7:H66)</f>
         <v>13685.910833333333</v>
       </c>
-      <c r="U13">
+      <c r="X13">
         <f t="shared" si="8"/>
         <v>9584.6749999999975</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y13">
+        <f>IF(C13="","",ROUND(G13-設定!$C$26*60,0))</f>
+        <v>-5.0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A14" s="48">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -43264,7 +43407,7 @@
         <v>108.44019316493313</v>
       </c>
       <c r="L14" s="22">
-        <f>IF(K14="","",IF(AND(K14&lt;&gt;"",ISNUMBER(入力!$F$17),入力!$F$17&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$17))*(K14-$T$3),K14))</f>
+        <f>IF(K14="","",IF(AND(K14&lt;&gt;"",ISNUMBER(入力!$F$17),入力!$F$17&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$17))*(K14-$W$3),K14))</f>
         <v>106.48628255257557</v>
       </c>
       <c r="M14" s="22">
@@ -43291,19 +43434,31 @@
         <f>IF(C14="","",設定!$C$26*C14/D14*100)</f>
         <v>104.24962852897475</v>
       </c>
-      <c r="S14" s="47" t="s">
+      <c r="S14" s="50" t="str">
+        <f>IF(Y14="","",IF(Y14&lt;=0,"達成済み",IF(Y14&lt;60,Y14&amp;"秒",INT(Y14/60)&amp;"分"&amp;TEXT(MOD(Y14,60),"00")&amp;"秒")))</f>
+        <v>達成済み</v>
+      </c>
+      <c r="T14" s="26">
+        <f>IF(C14="","",D14/設定!$C$26-C14)</f>
+        <v>-35.75</v>
+      </c>
+      <c r="V14" s="47" t="s">
         <v>188</v>
       </c>
-      <c r="T14" s="26">
+      <c r="W14" s="26">
         <f>SUM(I7:I66)</f>
         <v>40459.650833333326</v>
       </c>
-      <c r="U14">
+      <c r="X14">
         <f t="shared" si="8"/>
         <v>95102.049405646365</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y14">
+        <f>IF(C14="","",ROUND(G14-設定!$C$26*60,0))</f>
+        <v>-4.0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A15" s="48">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -43349,7 +43504,7 @@
         <v>106.8047477744807</v>
       </c>
       <c r="L15" s="22">
-        <f>IF(K15="","",IF(AND(K15&lt;&gt;"",ISNUMBER(入力!$F$18),入力!$F$18&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$18))*(K15-$T$3),K15))</f>
+        <f>IF(K15="","",IF(AND(K15&lt;&gt;"",ISNUMBER(入力!$F$18),入力!$F$18&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$18))*(K15-$W$3),K15))</f>
         <v>105.5199126114411</v>
       </c>
       <c r="M15" s="22">
@@ -43376,19 +43531,31 @@
         <f>IF(C15="","",設定!$C$26*C15/D15*100)</f>
         <v>89.35311572700297</v>
       </c>
-      <c r="S15" s="47" t="s">
+      <c r="S15" s="50" t="str">
+        <f>IF(Y15="","",IF(Y15&lt;=0,"達成済み",IF(Y15&lt;60,Y15&amp;"秒",INT(Y15/60)&amp;"分"&amp;TEXT(MOD(Y15,60),"00")&amp;"秒")))</f>
+        <v>11秒</v>
+      </c>
+      <c r="T15" s="26">
+        <f>IF(C15="","",D15/設定!$C$26-C15)</f>
+        <v>112.125</v>
+      </c>
+      <c r="V15" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="T15" s="23">
-        <f>IFERROR(T13/T14,"")</f>
+      <c r="W15" s="23">
+        <f>IFERROR(W13/W14,"")</f>
         <v>0.33826072522746486</v>
       </c>
-      <c r="U15">
+      <c r="X15">
         <f t="shared" si="8"/>
         <v>100503.26765578635</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y15">
+        <f>IF(C15="","",ROUND(G15-設定!$C$26*60,0))</f>
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A16" s="48">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -43434,7 +43601,7 @@
         <v>106.22178879910837</v>
       </c>
       <c r="L16" s="22">
-        <f>IF(K16="","",IF(AND(K16&lt;&gt;"",ISNUMBER(入力!$F$19),入力!$F$19&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$19))*(K16-$T$3),K16))</f>
+        <f>IF(K16="","",IF(AND(K16&lt;&gt;"",ISNUMBER(入力!$F$19),入力!$F$19&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$19))*(K16-$W$3),K16))</f>
         <v>105.27874024037102</v>
       </c>
       <c r="M16" s="22">
@@ -43461,19 +43628,31 @@
         <f>IF(C16="","",設定!$C$26*C16/D16*100)</f>
         <v>94.91223181944831</v>
       </c>
-      <c r="S16" s="47" t="s">
+      <c r="S16" s="50" t="str">
+        <f>IF(Y16="","",IF(Y16&lt;=0,"達成済み",IF(Y16&lt;60,Y16&amp;"秒",INT(Y16/60)&amp;"分"&amp;TEXT(MOD(Y16,60),"00")&amp;"秒")))</f>
+        <v>5秒</v>
+      </c>
+      <c r="T16" s="26">
+        <f>IF(C16="","",D16/設定!$C$26-C16)</f>
+        <v>114.125</v>
+      </c>
+      <c r="V16" s="47" t="s">
         <v>93</v>
       </c>
-      <c r="T16" s="27">
-        <f>IFERROR(T10/T11,"")</f>
+      <c r="W16" s="27">
+        <f>IFERROR(W10/W11,"")</f>
         <v>2.3365955575104462</v>
       </c>
-      <c r="U16">
+      <c r="X16">
         <f t="shared" si="8"/>
         <v>226146.18835330172</v>
       </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y16">
+        <f>IF(C16="","",ROUND(G16-設定!$C$26*60,0))</f>
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A17" s="48">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -43519,7 +43698,7 @@
         <v>106.39972273567466</v>
       </c>
       <c r="L17" s="22">
-        <f>IF(K17="","",IF(AND(K17&lt;&gt;"",ISNUMBER(入力!$F$20),入力!$F$20&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$20))*(K17-$T$3),K17))</f>
+        <f>IF(K17="","",IF(AND(K17&lt;&gt;"",ISNUMBER(入力!$F$20),入力!$F$20&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$20))*(K17-$W$3),K17))</f>
         <v>104.82956951103425</v>
       </c>
       <c r="M17" s="22">
@@ -43546,19 +43725,31 @@
         <f>IF(C17="","",設定!$C$26*C17/D17*100)</f>
         <v>100.70240295748616</v>
       </c>
-      <c r="S17" s="47" t="s">
+      <c r="S17" s="50" t="str">
+        <f>IF(Y17="","",IF(Y17&lt;=0,"達成済み",IF(Y17&lt;60,Y17&amp;"秒",INT(Y17/60)&amp;"分"&amp;TEXT(MOD(Y17,60),"00")&amp;"秒")))</f>
+        <v>達成済み</v>
+      </c>
+      <c r="T17" s="26">
+        <f>IF(C17="","",D17/設定!$C$26-C17)</f>
+        <v>-4.75</v>
+      </c>
+      <c r="V17" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="T17" s="22">
-        <f>IFERROR(T12*60/T10,"")</f>
+      <c r="W17" s="22">
+        <f>IFERROR(W12*60/W10,"")</f>
         <v>115.15741917266695</v>
       </c>
-      <c r="U17">
+      <c r="X17">
         <f t="shared" si="8"/>
         <v>72458.211182994448</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y17">
+        <f>IF(C17="","",ROUND(G17-設定!$C$26*60,0))</f>
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A18" s="48">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -43604,7 +43795,7 @@
         <v>101.99950049950048</v>
       </c>
       <c r="L18" s="22">
-        <f>IF(K18="","",IF(AND(K18&lt;&gt;"",ISNUMBER(入力!$F$21),入力!$F$21&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$21))*(K18-$T$3),K18))</f>
+        <f>IF(K18="","",IF(AND(K18&lt;&gt;"",ISNUMBER(入力!$F$21),入力!$F$21&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$21))*(K18-$W$3),K18))</f>
         <v>102.19941536738331</v>
       </c>
       <c r="M18" s="22">
@@ -43631,12 +43822,33 @@
         <f>IF(C18="","",設定!$C$26*C18/D18*100)</f>
         <v>74.8051948051948</v>
       </c>
-      <c r="U18">
+      <c r="S18" s="50" t="str">
+        <f>IF(Y18="","",IF(Y18&lt;=0,"達成済み",IF(Y18&lt;60,Y18&amp;"秒",INT(Y18/60)&amp;"分"&amp;TEXT(MOD(Y18,60),"00")&amp;"秒")))</f>
+        <v>32秒</v>
+      </c>
+      <c r="T18" s="26">
+        <f>IF(C18="","",D18/設定!$C$26-C18)</f>
+        <v>157.625</v>
+      </c>
+      <c r="V18" s="47" t="inlineStr">
+        <is>
+          <t>1件あたり 目標まで(秒)</t>
+        </is>
+      </c>
+      <c r="W18" s="22">
+        <f>IFERROR(W17-設定!$C$26*60,"")</f>
+        <v>19.157419172667005</v>
+      </c>
+      <c r="X18">
         <f t="shared" si="8"/>
         <v>47735.766233766226</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y18">
+        <f>IF(C18="","",ROUND(G18-設定!$C$26*60,0))</f>
+        <v>32.0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A19" s="48">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -43682,7 +43894,7 @@
         <v>101.71352549889134</v>
       </c>
       <c r="L19" s="22">
-        <f>IF(K19="","",IF(AND(K19&lt;&gt;"",ISNUMBER(入力!$F$22),入力!$F$22&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$22))*(K19-$T$3),K19))</f>
+        <f>IF(K19="","",IF(AND(K19&lt;&gt;"",ISNUMBER(入力!$F$22),入力!$F$22&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$22))*(K19-$W$3),K19))</f>
         <v>102.10123607448666</v>
       </c>
       <c r="M19" s="22">
@@ -43709,12 +43921,33 @@
         <f>IF(C19="","",設定!$C$26*C19/D19*100)</f>
         <v>81.09977827050999</v>
       </c>
-      <c r="U19">
+      <c r="S19" s="50" t="str">
+        <f>IF(Y19="","",IF(Y19&lt;=0,"達成済み",IF(Y19&lt;60,Y19&amp;"秒",INT(Y19/60)&amp;"分"&amp;TEXT(MOD(Y19,60),"00")&amp;"秒")))</f>
+        <v>22秒</v>
+      </c>
+      <c r="T19" s="26">
+        <f>IF(C19="","",D19/設定!$C$26-C19)</f>
+        <v>266.375</v>
+      </c>
+      <c r="V19" s="47" t="inlineStr">
+        <is>
+          <t>目標到達で増やせる件数</t>
+        </is>
+      </c>
+      <c r="W19" s="26">
+        <f>IFERROR(W12/設定!$C$26-W10,"")</f>
+        <v>4240.375</v>
+      </c>
+      <c r="X19">
         <f t="shared" si="8"/>
         <v>116258.5596452328</v>
       </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y19">
+        <f>IF(C19="","",ROUND(G19-設定!$C$26*60,0))</f>
+        <v>22.0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A20" s="48">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -43760,7 +43993,7 @@
         <v>100.59261744966443</v>
       </c>
       <c r="L20" s="22">
-        <f>IF(K20="","",IF(AND(K20&lt;&gt;"",ISNUMBER(入力!$F$23),入力!$F$23&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$23))*(K20-$T$3),K20))</f>
+        <f>IF(K20="","",IF(AND(K20&lt;&gt;"",ISNUMBER(入力!$F$23),入力!$F$23&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$23))*(K20-$W$3),K20))</f>
         <v>101.53055698910751</v>
       </c>
       <c r="M20" s="22">
@@ -43787,12 +44020,24 @@
         <f>IF(C20="","",設定!$C$26*C20/D20*100)</f>
         <v>90.84563758389262</v>
       </c>
-      <c r="U20">
+      <c r="S20" s="50" t="str">
+        <f>IF(Y20="","",IF(Y20&lt;=0,"達成済み",IF(Y20&lt;60,Y20&amp;"秒",INT(Y20/60)&amp;"分"&amp;TEXT(MOD(Y20,60),"00")&amp;"秒")))</f>
+        <v>10秒</v>
+      </c>
+      <c r="T20" s="26">
+        <f>IF(C20="","",D20/設定!$C$26-C20)</f>
+        <v>85.25</v>
+      </c>
+      <c r="X20">
         <f t="shared" si="8"/>
         <v>85101.35436241611</v>
       </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y20">
+        <f>IF(C20="","",ROUND(G20-設定!$C$26*60,0))</f>
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A21" s="48">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -43838,7 +44083,7 @@
         <v>98.221111111111114</v>
       </c>
       <c r="L21" s="22">
-        <f>IF(K21="","",IF(AND(K21&lt;&gt;"",ISNUMBER(入力!$F$24),入力!$F$24&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$24))*(K21-$T$3),K21))</f>
+        <f>IF(K21="","",IF(AND(K21&lt;&gt;"",ISNUMBER(入力!$F$24),入力!$F$24&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$24))*(K21-$W$3),K21))</f>
         <v>100.77903963067155</v>
       </c>
       <c r="M21" s="22">
@@ -43865,12 +44110,24 @@
         <f>IF(C21="","",設定!$C$26*C21/D21*100)</f>
         <v>77.5111111111111</v>
       </c>
-      <c r="U21">
+      <c r="S21" s="50" t="str">
+        <f>IF(Y21="","",IF(Y21&lt;=0,"達成済み",IF(Y21&lt;60,Y21&amp;"秒",INT(Y21/60)&amp;"分"&amp;TEXT(MOD(Y21,60),"00")&amp;"秒")))</f>
+        <v>28秒</v>
+      </c>
+      <c r="T21" s="26">
+        <f>IF(C21="","",D21/設定!$C$26-C21)</f>
+        <v>63.25</v>
+      </c>
+      <c r="X21">
         <f t="shared" si="8"/>
         <v>21412.202222222222</v>
       </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y21">
+        <f>IF(C21="","",ROUND(G21-設定!$C$26*60,0))</f>
+        <v>28.0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A22" s="48">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -43916,7 +44173,7 @@
         <v>98.116847826086968</v>
       </c>
       <c r="L22" s="22">
-        <f>IF(K22="","",IF(AND(K22&lt;&gt;"",ISNUMBER(入力!$F$25),入力!$F$25&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$25))*(K22-$T$3),K22))</f>
+        <f>IF(K22="","",IF(AND(K22&lt;&gt;"",ISNUMBER(入力!$F$25),入力!$F$25&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$25))*(K22-$W$3),K22))</f>
         <v>100.53479201324765</v>
       </c>
       <c r="M22" s="22">
@@ -43943,12 +44200,24 @@
         <f>IF(C22="","",設定!$C$26*C22/D22*100)</f>
         <v>81.15942028985508</v>
       </c>
-      <c r="U22">
+      <c r="S22" s="50" t="str">
+        <f>IF(Y22="","",IF(Y22&lt;=0,"達成済み",IF(Y22&lt;60,Y22&amp;"秒",INT(Y22/60)&amp;"分"&amp;TEXT(MOD(Y22,60),"00")&amp;"秒")))</f>
+        <v>22秒</v>
+      </c>
+      <c r="T22" s="26">
+        <f>IF(C22="","",D22/設定!$C$26-C22)</f>
+        <v>65.0</v>
+      </c>
+      <c r="X22">
         <f t="shared" si="8"/>
         <v>27472.717391304352</v>
       </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y22">
+        <f>IF(C22="","",ROUND(G22-設定!$C$26*60,0))</f>
+        <v>22.0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A23" s="48">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -43994,7 +44263,7 @@
         <v>99.64362464183381</v>
       </c>
       <c r="L23" s="22">
-        <f>IF(K23="","",IF(AND(K23&lt;&gt;"",ISNUMBER(入力!$F$26),入力!$F$26&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$26))*(K23-$T$3),K23))</f>
+        <f>IF(K23="","",IF(AND(K23&lt;&gt;"",ISNUMBER(入力!$F$26),入力!$F$26&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$26))*(K23-$W$3),K23))</f>
         <v>100.54560159272768</v>
       </c>
       <c r="M23" s="22">
@@ -44021,12 +44290,24 @@
         <f>IF(C23="","",設定!$C$26*C23/D23*100)</f>
         <v>79.1977077363897</v>
       </c>
-      <c r="U23">
+      <c r="S23" s="50" t="str">
+        <f>IF(Y23="","",IF(Y23&lt;=0,"達成済み",IF(Y23&lt;60,Y23&amp;"秒",INT(Y23/60)&amp;"分"&amp;TEXT(MOD(Y23,60),"00")&amp;"秒")))</f>
+        <v>25秒</v>
+      </c>
+      <c r="T23" s="26">
+        <f>IF(C23="","",D23/設定!$C$26-C23)</f>
+        <v>181.5</v>
+      </c>
+      <c r="X23">
         <f t="shared" si="8"/>
         <v>68853.744627507156</v>
       </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y23">
+        <f>IF(C23="","",ROUND(G23-設定!$C$26*60,0))</f>
+        <v>25.0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A24" s="48">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -44072,7 +44353,7 @@
         <v>91.348648648648634</v>
       </c>
       <c r="L24" s="22">
-        <f>IF(K24="","",IF(AND(K24&lt;&gt;"",ISNUMBER(入力!$F$27),入力!$F$27&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$27))*(K24-$T$3),K24))</f>
+        <f>IF(K24="","",IF(AND(K24&lt;&gt;"",ISNUMBER(入力!$F$27),入力!$F$27&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$27))*(K24-$W$3),K24))</f>
         <v>99.234129665461822</v>
       </c>
       <c r="M24" s="22">
@@ -44099,12 +44380,24 @@
         <f>IF(C24="","",設定!$C$26*C24/D24*100)</f>
         <v>71.95675675675676</v>
       </c>
-      <c r="U24">
+      <c r="S24" s="50" t="str">
+        <f>IF(Y24="","",IF(Y24&lt;=0,"達成済み",IF(Y24&lt;60,Y24&amp;"秒",INT(Y24/60)&amp;"分"&amp;TEXT(MOD(Y24,60),"00")&amp;"秒")))</f>
+        <v>37秒</v>
+      </c>
+      <c r="T24" s="26">
+        <f>IF(C24="","",D24/設定!$C$26-C24)</f>
+        <v>162.125</v>
+      </c>
+      <c r="X24">
         <f t="shared" si="8"/>
         <v>38001.03783783783</v>
       </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y24">
+        <f>IF(C24="","",ROUND(G24-設定!$C$26*60,0))</f>
+        <v>37.0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A25" s="48">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -44150,7 +44443,7 @@
         <v>96.542574257425741</v>
       </c>
       <c r="L25" s="22">
-        <f>IF(K25="","",IF(AND(K25&lt;&gt;"",ISNUMBER(入力!$F$28),入力!$F$28&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$28))*(K25-$T$3),K25))</f>
+        <f>IF(K25="","",IF(AND(K25&lt;&gt;"",ISNUMBER(入力!$F$28),入力!$F$28&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$28))*(K25-$W$3),K25))</f>
         <v>99.042799211712904</v>
       </c>
       <c r="M25" s="22">
@@ -44177,12 +44470,24 @@
         <f>IF(C25="","",設定!$C$26*C25/D25*100)</f>
         <v>73.1881188118812</v>
       </c>
-      <c r="U25">
+      <c r="S25" s="50" t="str">
+        <f>IF(Y25="","",IF(Y25&lt;=0,"達成済み",IF(Y25&lt;60,Y25&amp;"秒",INT(Y25/60)&amp;"分"&amp;TEXT(MOD(Y25,60),"00")&amp;"秒")))</f>
+        <v>35秒</v>
+      </c>
+      <c r="T25" s="26">
+        <f>IF(C25="","",D25/設定!$C$26-C25)</f>
+        <v>84.625</v>
+      </c>
+      <c r="X25">
         <f t="shared" si="8"/>
         <v>22301.334653465346</v>
       </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y25">
+        <f>IF(C25="","",ROUND(G25-設定!$C$26*60,0))</f>
+        <v>35.0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A26" s="48">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -44228,7 +44533,7 @@
         <v>89.993336886993617</v>
       </c>
       <c r="L26" s="22">
-        <f>IF(K26="","",IF(AND(K26&lt;&gt;"",ISNUMBER(入力!$F$29),入力!$F$29&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$29))*(K26-$T$3),K26))</f>
+        <f>IF(K26="","",IF(AND(K26&lt;&gt;"",ISNUMBER(入力!$F$29),入力!$F$29&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$29))*(K26-$W$3),K26))</f>
         <v>94.651101621000734</v>
       </c>
       <c r="M26" s="22">
@@ -44255,12 +44560,24 @@
         <f>IF(C26="","",設定!$C$26*C26/D26*100)</f>
         <v>73.85927505330491</v>
       </c>
-      <c r="U26">
+      <c r="S26" s="50" t="str">
+        <f>IF(Y26="","",IF(Y26&lt;=0,"達成済み",IF(Y26&lt;60,Y26&amp;"秒",INT(Y26/60)&amp;"分"&amp;TEXT(MOD(Y26,60),"00")&amp;"秒")))</f>
+        <v>34秒</v>
+      </c>
+      <c r="T26" s="26">
+        <f>IF(C26="","",D26/設定!$C$26-C26)</f>
+        <v>306.5</v>
+      </c>
+      <c r="X26">
         <f t="shared" si="8"/>
         <v>77934.229744136479</v>
       </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y26">
+        <f>IF(C26="","",ROUND(G26-設定!$C$26*60,0))</f>
+        <v>34.0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A27" s="48">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -44306,7 +44623,7 @@
         <v>76.883663366336634</v>
       </c>
       <c r="L27" s="22">
-        <f>IF(K27="","",IF(AND(K27&lt;&gt;"",ISNUMBER(入力!$F$30),入力!$F$30&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$30))*(K27-$T$3),K27))</f>
+        <f>IF(K27="","",IF(AND(K27&lt;&gt;"",ISNUMBER(入力!$F$30),入力!$F$30&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$30))*(K27-$W$3),K27))</f>
         <v>93.275656460937611</v>
       </c>
       <c r="M27" s="22">
@@ -44333,12 +44650,24 @@
         <f>IF(C27="","",設定!$C$26*C27/D27*100)</f>
         <v>52.27722772277228</v>
       </c>
-      <c r="U27">
+      <c r="S27" s="50" t="str">
+        <f>IF(Y27="","",IF(Y27&lt;=0,"達成済み",IF(Y27&lt;60,Y27&amp;"秒",INT(Y27/60)&amp;"分"&amp;TEXT(MOD(Y27,60),"00")&amp;"秒")))</f>
+        <v>1分28秒</v>
+      </c>
+      <c r="T27" s="26">
+        <f>IF(C27="","",D27/設定!$C$26-C27)</f>
+        <v>60.25</v>
+      </c>
+      <c r="X27">
         <f t="shared" si="8"/>
         <v>5074.3217821782182</v>
       </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y27">
+        <f>IF(C27="","",ROUND(G27-設定!$C$26*60,0))</f>
+        <v>88.0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A28" s="48">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -44384,7 +44713,7 @@
         <v>88.026622718052721</v>
       </c>
       <c r="L28" s="22">
-        <f>IF(K28="","",IF(AND(K28&lt;&gt;"",ISNUMBER(入力!$F$31),入力!$F$31&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$31))*(K28-$T$3),K28))</f>
+        <f>IF(K28="","",IF(AND(K28&lt;&gt;"",ISNUMBER(入力!$F$31),入力!$F$31&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$31))*(K28-$W$3),K28))</f>
         <v>93.411181096143565</v>
       </c>
       <c r="M28" s="22">
@@ -44411,12 +44740,24 @@
         <f>IF(C28="","",設定!$C$26*C28/D28*100)</f>
         <v>67.99188640973631</v>
       </c>
-      <c r="U28">
+      <c r="S28" s="50" t="str">
+        <f>IF(Y28="","",IF(Y28&lt;=0,"達成済み",IF(Y28&lt;60,Y28&amp;"秒",INT(Y28/60)&amp;"分"&amp;TEXT(MOD(Y28,60),"00")&amp;"秒")))</f>
+        <v>45秒</v>
+      </c>
+      <c r="T28" s="26">
+        <f>IF(C28="","",D28/設定!$C$26-C28)</f>
+        <v>394.5</v>
+      </c>
+      <c r="X28">
         <f t="shared" si="8"/>
         <v>73766.309837728186</v>
       </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y28">
+        <f>IF(C28="","",ROUND(G28-設定!$C$26*60,0))</f>
+        <v>45.0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A29" s="48">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -44462,7 +44803,7 @@
         <v>81.891759776536304</v>
       </c>
       <c r="L29" s="22">
-        <f>IF(K29="","",IF(AND(K29&lt;&gt;"",ISNUMBER(入力!$F$32),入力!$F$32&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$32))*(K29-$T$3),K29))</f>
+        <f>IF(K29="","",IF(AND(K29&lt;&gt;"",ISNUMBER(入力!$F$32),入力!$F$32&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$32))*(K29-$W$3),K29))</f>
         <v>90.975092590504204</v>
       </c>
       <c r="M29" s="22">
@@ -44489,12 +44830,24 @@
         <f>IF(C29="","",設定!$C$26*C29/D29*100)</f>
         <v>74.86033519553072</v>
       </c>
-      <c r="U29">
+      <c r="S29" s="50" t="str">
+        <f>IF(Y29="","",IF(Y29&lt;=0,"達成済み",IF(Y29&lt;60,Y29&amp;"秒",INT(Y29/60)&amp;"分"&amp;TEXT(MOD(Y29,60),"00")&amp;"秒")))</f>
+        <v>32秒</v>
+      </c>
+      <c r="T29" s="26">
+        <f>IF(C29="","",D29/設定!$C$26-C29)</f>
+        <v>112.5</v>
+      </c>
+      <c r="X29">
         <f t="shared" si="8"/>
         <v>27433.739525139663</v>
       </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y29">
+        <f>IF(C29="","",ROUND(G29-設定!$C$26*60,0))</f>
+        <v>32.0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A30" s="48">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -44540,7 +44893,7 @@
         <v>85.862631578947358</v>
       </c>
       <c r="L30" s="22">
-        <f>IF(K30="","",IF(AND(K30&lt;&gt;"",ISNUMBER(入力!$F$33),入力!$F$33&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$33))*(K30-$T$3),K30))</f>
+        <f>IF(K30="","",IF(AND(K30&lt;&gt;"",ISNUMBER(入力!$F$33),入力!$F$33&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$33))*(K30-$W$3),K30))</f>
         <v>90.760319550211833</v>
       </c>
       <c r="M30" s="22">
@@ -44567,12 +44920,24 @@
         <f>IF(C30="","",設定!$C$26*C30/D30*100)</f>
         <v>71.07368421052632</v>
       </c>
-      <c r="U30">
+      <c r="S30" s="50" t="str">
+        <f>IF(Y30="","",IF(Y30&lt;=0,"達成済み",IF(Y30&lt;60,Y30&amp;"秒",INT(Y30/60)&amp;"分"&amp;TEXT(MOD(Y30,60),"00")&amp;"秒")))</f>
+        <v>39秒</v>
+      </c>
+      <c r="T30" s="26">
+        <f>IF(C30="","",D30/設定!$C$26-C30)</f>
+        <v>171.75</v>
+      </c>
+      <c r="X30">
         <f t="shared" si="8"/>
         <v>36234.030526315786</v>
       </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y30">
+        <f>IF(C30="","",ROUND(G30-設定!$C$26*60,0))</f>
+        <v>39.0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A31" s="48">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -44618,7 +44983,7 @@
         <v>80.89163346613546</v>
       </c>
       <c r="L31" s="22">
-        <f>IF(K31="","",IF(AND(K31&lt;&gt;"",ISNUMBER(入力!$F$34),入力!$F$34&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$34))*(K31-$T$3),K31))</f>
+        <f>IF(K31="","",IF(AND(K31&lt;&gt;"",ISNUMBER(入力!$F$34),入力!$F$34&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$34))*(K31-$W$3),K31))</f>
         <v>88.912906889449019</v>
       </c>
       <c r="M31" s="22">
@@ -44645,12 +45010,24 @@
         <f>IF(C31="","",設定!$C$26*C31/D31*100)</f>
         <v>69.4820717131474</v>
       </c>
-      <c r="U31">
+      <c r="S31" s="50" t="str">
+        <f>IF(Y31="","",IF(Y31&lt;=0,"達成済み",IF(Y31&lt;60,Y31&amp;"秒",INT(Y31/60)&amp;"分"&amp;TEXT(MOD(Y31,60),"00")&amp;"秒")))</f>
+        <v>42秒</v>
+      </c>
+      <c r="T31" s="26">
+        <f>IF(C31="","",D31/設定!$C$26-C31)</f>
+        <v>478.75</v>
+      </c>
+      <c r="X31">
         <f t="shared" si="8"/>
         <v>88171.880478087653</v>
       </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y31">
+        <f>IF(C31="","",ROUND(G31-設定!$C$26*60,0))</f>
+        <v>42.0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A32" s="48">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -44696,7 +45073,7 @@
         <v>80.289637058261704</v>
       </c>
       <c r="L32" s="22">
-        <f>IF(K32="","",IF(AND(K32&lt;&gt;"",ISNUMBER(入力!$F$35),入力!$F$35&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$35))*(K32-$T$3),K32))</f>
+        <f>IF(K32="","",IF(AND(K32&lt;&gt;"",ISNUMBER(入力!$F$35),入力!$F$35&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$35))*(K32-$W$3),K32))</f>
         <v>88.533376547012466</v>
       </c>
       <c r="M32" s="22">
@@ -44723,12 +45100,24 @@
         <f>IF(C32="","",設定!$C$26*C32/D32*100)</f>
         <v>65.55873925501433</v>
       </c>
-      <c r="U32">
+      <c r="S32" s="50" t="str">
+        <f>IF(Y32="","",IF(Y32&lt;=0,"達成済み",IF(Y32&lt;60,Y32&amp;"秒",INT(Y32/60)&amp;"分"&amp;TEXT(MOD(Y32,60),"00")&amp;"秒")))</f>
+        <v>50秒</v>
+      </c>
+      <c r="T32" s="26">
+        <f>IF(C32="","",D32/設定!$C$26-C32)</f>
+        <v>450.75</v>
+      </c>
+      <c r="X32">
         <f t="shared" si="8"/>
         <v>68888.508595988547</v>
       </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y32">
+        <f>IF(C32="","",ROUND(G32-設定!$C$26*60,0))</f>
+        <v>50.0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A33" s="48">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -44774,7 +45163,7 @@
         <v>79.358161350844284</v>
       </c>
       <c r="L33" s="22">
-        <f>IF(K33="","",IF(AND(K33&lt;&gt;"",ISNUMBER(入力!$F$36),入力!$F$36&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$36))*(K33-$T$3),K33))</f>
+        <f>IF(K33="","",IF(AND(K33&lt;&gt;"",ISNUMBER(入力!$F$36),入力!$F$36&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$36))*(K33-$W$3),K33))</f>
         <v>87.517454266205448</v>
       </c>
       <c r="M33" s="22">
@@ -44801,12 +45190,24 @@
         <f>IF(C33="","",設定!$C$26*C33/D33*100)</f>
         <v>66.76172607879926</v>
       </c>
-      <c r="U33">
+      <c r="S33" s="50" t="str">
+        <f>IF(Y33="","",IF(Y33&lt;=0,"達成済み",IF(Y33&lt;60,Y33&amp;"秒",INT(Y33/60)&amp;"分"&amp;TEXT(MOD(Y33,60),"00")&amp;"秒")))</f>
+        <v>48秒</v>
+      </c>
+      <c r="T33" s="26">
+        <f>IF(C33="","",D33/設定!$C$26-C33)</f>
+        <v>553.625</v>
+      </c>
+      <c r="X33">
         <f t="shared" si="8"/>
         <v>88246.275422138846</v>
       </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y33">
+        <f>IF(C33="","",ROUND(G33-設定!$C$26*60,0))</f>
+        <v>48.0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A34" s="48">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -44852,7 +45253,7 @@
         <v>56.602448979591827</v>
       </c>
       <c r="L34" s="22">
-        <f>IF(K34="","",IF(AND(K34&lt;&gt;"",ISNUMBER(入力!$F$37),入力!$F$37&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$37))*(K34-$T$3),K34))</f>
+        <f>IF(K34="","",IF(AND(K34&lt;&gt;"",ISNUMBER(入力!$F$37),入力!$F$37&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$37))*(K34-$W$3),K34))</f>
         <v>85.923353074085327</v>
       </c>
       <c r="M34" s="22">
@@ -44879,12 +45280,24 @@
         <f>IF(C34="","",設定!$C$26*C34/D34*100)</f>
         <v>48.3265306122449</v>
       </c>
-      <c r="U34">
+      <c r="S34" s="50" t="str">
+        <f>IF(Y34="","",IF(Y34&lt;=0,"達成済み",IF(Y34&lt;60,Y34&amp;"秒",INT(Y34/60)&amp;"分"&amp;TEXT(MOD(Y34,60),"00")&amp;"秒")))</f>
+        <v>1分43秒</v>
+      </c>
+      <c r="T34" s="26">
+        <f>IF(C34="","",D34/設定!$C$26-C34)</f>
+        <v>395.625</v>
+      </c>
+      <c r="X34">
         <f t="shared" si="8"/>
         <v>20942.906122448978</v>
       </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y34">
+        <f>IF(C34="","",ROUND(G34-設定!$C$26*60,0))</f>
+        <v>103.0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A35" s="48">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -44930,7 +45343,7 @@
         <v>74.630235602094231</v>
       </c>
       <c r="L35" s="22">
-        <f>IF(K35="","",IF(AND(K35&lt;&gt;"",ISNUMBER(入力!$F$38),入力!$F$38&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$38))*(K35-$T$3),K35))</f>
+        <f>IF(K35="","",IF(AND(K35&lt;&gt;"",ISNUMBER(入力!$F$38),入力!$F$38&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$38))*(K35-$W$3),K35))</f>
         <v>85.538485613185657</v>
       </c>
       <c r="M35" s="22">
@@ -44957,12 +45370,24 @@
         <f>IF(C35="","",設定!$C$26*C35/D35*100)</f>
         <v>56.75392670157068</v>
       </c>
-      <c r="U35">
+      <c r="S35" s="50" t="str">
+        <f>IF(Y35="","",IF(Y35&lt;=0,"達成済み",IF(Y35&lt;60,Y35&amp;"秒",INT(Y35/60)&amp;"分"&amp;TEXT(MOD(Y35,60),"00")&amp;"秒")))</f>
+        <v>1分13秒</v>
+      </c>
+      <c r="T35" s="26">
+        <f>IF(C35="","",D35/設定!$C$26-C35)</f>
+        <v>206.5</v>
+      </c>
+      <c r="X35">
         <f t="shared" si="8"/>
         <v>20224.793848167537</v>
       </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y35">
+        <f>IF(C35="","",ROUND(G35-設定!$C$26*60,0))</f>
+        <v>73.0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A36" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -45008,7 +45433,7 @@
         <v/>
       </c>
       <c r="L36" s="22" t="str">
-        <f>IF(K36="","",IF(AND(K36&lt;&gt;"",ISNUMBER(入力!$F$39),入力!$F$39&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$39))*(K36-$T$3),K36))</f>
+        <f>IF(K36="","",IF(AND(K36&lt;&gt;"",ISNUMBER(入力!$F$39),入力!$F$39&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$39))*(K36-$W$3),K36))</f>
         <v/>
       </c>
       <c r="M36" s="22" t="str">
@@ -45035,12 +45460,24 @@
         <f>IF(C36="","",設定!$C$26*C36/D36*100)</f>
         <v/>
       </c>
-      <c r="U36">
+      <c r="S36" s="50" t="str">
+        <f>IF(Y36="","",IF(Y36&lt;=0,"達成済み",IF(Y36&lt;60,Y36&amp;"秒",INT(Y36/60)&amp;"分"&amp;TEXT(MOD(Y36,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T36" s="26" t="str">
+        <f>IF(C36="","",D36/設定!$C$26-C36)</f>
+        <v/>
+      </c>
+      <c r="X36">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y36" t="str">
+        <f>IF(C36="","",ROUND(G36-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A37" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -45086,7 +45523,7 @@
         <v/>
       </c>
       <c r="L37" s="22" t="str">
-        <f>IF(K37="","",IF(AND(K37&lt;&gt;"",ISNUMBER(入力!$F$40),入力!$F$40&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$40))*(K37-$T$3),K37))</f>
+        <f>IF(K37="","",IF(AND(K37&lt;&gt;"",ISNUMBER(入力!$F$40),入力!$F$40&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$40))*(K37-$W$3),K37))</f>
         <v/>
       </c>
       <c r="M37" s="22" t="str">
@@ -45113,12 +45550,24 @@
         <f>IF(C37="","",設定!$C$26*C37/D37*100)</f>
         <v/>
       </c>
-      <c r="U37">
+      <c r="S37" s="50" t="str">
+        <f>IF(Y37="","",IF(Y37&lt;=0,"達成済み",IF(Y37&lt;60,Y37&amp;"秒",INT(Y37/60)&amp;"分"&amp;TEXT(MOD(Y37,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T37" s="26" t="str">
+        <f>IF(C37="","",D37/設定!$C$26-C37)</f>
+        <v/>
+      </c>
+      <c r="X37">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y37" t="str">
+        <f>IF(C37="","",ROUND(G37-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A38" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -45164,7 +45613,7 @@
         <v/>
       </c>
       <c r="L38" s="22" t="str">
-        <f>IF(K38="","",IF(AND(K38&lt;&gt;"",ISNUMBER(入力!$F$41),入力!$F$41&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$41))*(K38-$T$3),K38))</f>
+        <f>IF(K38="","",IF(AND(K38&lt;&gt;"",ISNUMBER(入力!$F$41),入力!$F$41&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$41))*(K38-$W$3),K38))</f>
         <v/>
       </c>
       <c r="M38" s="22" t="str">
@@ -45191,12 +45640,24 @@
         <f>IF(C38="","",設定!$C$26*C38/D38*100)</f>
         <v/>
       </c>
-      <c r="U38">
+      <c r="S38" s="50" t="str">
+        <f>IF(Y38="","",IF(Y38&lt;=0,"達成済み",IF(Y38&lt;60,Y38&amp;"秒",INT(Y38/60)&amp;"分"&amp;TEXT(MOD(Y38,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T38" s="26" t="str">
+        <f>IF(C38="","",D38/設定!$C$26-C38)</f>
+        <v/>
+      </c>
+      <c r="X38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y38" t="str">
+        <f>IF(C38="","",ROUND(G38-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A39" s="48" t="str">
         <f t="shared" ref="A39:A66" si="9">IF(R39="","",RANK(R39,$R$7:$R$66,0))</f>
         <v/>
@@ -45242,7 +45703,7 @@
         <v/>
       </c>
       <c r="L39" s="22" t="str">
-        <f>IF(K39="","",IF(AND(K39&lt;&gt;"",ISNUMBER(入力!$F$42),入力!$F$42&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$42))*(K39-$T$3),K39))</f>
+        <f>IF(K39="","",IF(AND(K39&lt;&gt;"",ISNUMBER(入力!$F$42),入力!$F$42&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$42))*(K39-$W$3),K39))</f>
         <v/>
       </c>
       <c r="M39" s="22" t="str">
@@ -45269,12 +45730,24 @@
         <f>IF(C39="","",設定!$C$26*C39/D39*100)</f>
         <v/>
       </c>
-      <c r="U39">
-        <f t="shared" ref="U39:U66" si="17">IF(K39="",0,K39*C39)</f>
+      <c r="S39" s="50" t="str">
+        <f>IF(Y39="","",IF(Y39&lt;=0,"達成済み",IF(Y39&lt;60,Y39&amp;"秒",INT(Y39/60)&amp;"分"&amp;TEXT(MOD(Y39,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T39" s="26" t="str">
+        <f>IF(C39="","",D39/設定!$C$26-C39)</f>
+        <v/>
+      </c>
+      <c r="X39">
+        <f t="shared" ref="X39:X66" si="17">IF(K39="",0,K39*C39)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y39" t="str">
+        <f>IF(C39="","",ROUND(G39-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A40" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -45320,7 +45793,7 @@
         <v/>
       </c>
       <c r="L40" s="22" t="str">
-        <f>IF(K40="","",IF(AND(K40&lt;&gt;"",ISNUMBER(入力!$F$43),入力!$F$43&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$43))*(K40-$T$3),K40))</f>
+        <f>IF(K40="","",IF(AND(K40&lt;&gt;"",ISNUMBER(入力!$F$43),入力!$F$43&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$43))*(K40-$W$3),K40))</f>
         <v/>
       </c>
       <c r="M40" s="22" t="str">
@@ -45347,12 +45820,24 @@
         <f>IF(C40="","",設定!$C$26*C40/D40*100)</f>
         <v/>
       </c>
-      <c r="U40">
+      <c r="S40" s="50" t="str">
+        <f>IF(Y40="","",IF(Y40&lt;=0,"達成済み",IF(Y40&lt;60,Y40&amp;"秒",INT(Y40/60)&amp;"分"&amp;TEXT(MOD(Y40,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T40" s="26" t="str">
+        <f>IF(C40="","",D40/設定!$C$26-C40)</f>
+        <v/>
+      </c>
+      <c r="X40">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y40" t="str">
+        <f>IF(C40="","",ROUND(G40-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A41" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -45398,7 +45883,7 @@
         <v/>
       </c>
       <c r="L41" s="22" t="str">
-        <f>IF(K41="","",IF(AND(K41&lt;&gt;"",ISNUMBER(入力!$F$44),入力!$F$44&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$44))*(K41-$T$3),K41))</f>
+        <f>IF(K41="","",IF(AND(K41&lt;&gt;"",ISNUMBER(入力!$F$44),入力!$F$44&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$44))*(K41-$W$3),K41))</f>
         <v/>
       </c>
       <c r="M41" s="22" t="str">
@@ -45425,12 +45910,24 @@
         <f>IF(C41="","",設定!$C$26*C41/D41*100)</f>
         <v/>
       </c>
-      <c r="U41">
+      <c r="S41" s="50" t="str">
+        <f>IF(Y41="","",IF(Y41&lt;=0,"達成済み",IF(Y41&lt;60,Y41&amp;"秒",INT(Y41/60)&amp;"分"&amp;TEXT(MOD(Y41,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T41" s="26" t="str">
+        <f>IF(C41="","",D41/設定!$C$26-C41)</f>
+        <v/>
+      </c>
+      <c r="X41">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y41" t="str">
+        <f>IF(C41="","",ROUND(G41-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A42" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -45476,7 +45973,7 @@
         <v/>
       </c>
       <c r="L42" s="22" t="str">
-        <f>IF(K42="","",IF(AND(K42&lt;&gt;"",ISNUMBER(入力!$F$45),入力!$F$45&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$45))*(K42-$T$3),K42))</f>
+        <f>IF(K42="","",IF(AND(K42&lt;&gt;"",ISNUMBER(入力!$F$45),入力!$F$45&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$45))*(K42-$W$3),K42))</f>
         <v/>
       </c>
       <c r="M42" s="22" t="str">
@@ -45503,12 +46000,24 @@
         <f>IF(C42="","",設定!$C$26*C42/D42*100)</f>
         <v/>
       </c>
-      <c r="U42">
+      <c r="S42" s="50" t="str">
+        <f>IF(Y42="","",IF(Y42&lt;=0,"達成済み",IF(Y42&lt;60,Y42&amp;"秒",INT(Y42/60)&amp;"分"&amp;TEXT(MOD(Y42,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T42" s="26" t="str">
+        <f>IF(C42="","",D42/設定!$C$26-C42)</f>
+        <v/>
+      </c>
+      <c r="X42">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y42" t="str">
+        <f>IF(C42="","",ROUND(G42-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A43" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -45554,7 +46063,7 @@
         <v/>
       </c>
       <c r="L43" s="22" t="str">
-        <f>IF(K43="","",IF(AND(K43&lt;&gt;"",ISNUMBER(入力!$F$46),入力!$F$46&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$46))*(K43-$T$3),K43))</f>
+        <f>IF(K43="","",IF(AND(K43&lt;&gt;"",ISNUMBER(入力!$F$46),入力!$F$46&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$46))*(K43-$W$3),K43))</f>
         <v/>
       </c>
       <c r="M43" s="22" t="str">
@@ -45581,12 +46090,24 @@
         <f>IF(C43="","",設定!$C$26*C43/D43*100)</f>
         <v/>
       </c>
-      <c r="U43">
+      <c r="S43" s="50" t="str">
+        <f>IF(Y43="","",IF(Y43&lt;=0,"達成済み",IF(Y43&lt;60,Y43&amp;"秒",INT(Y43/60)&amp;"分"&amp;TEXT(MOD(Y43,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T43" s="26" t="str">
+        <f>IF(C43="","",D43/設定!$C$26-C43)</f>
+        <v/>
+      </c>
+      <c r="X43">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y43" t="str">
+        <f>IF(C43="","",ROUND(G43-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A44" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -45632,7 +46153,7 @@
         <v/>
       </c>
       <c r="L44" s="22" t="str">
-        <f>IF(K44="","",IF(AND(K44&lt;&gt;"",ISNUMBER(入力!$F$47),入力!$F$47&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$47))*(K44-$T$3),K44))</f>
+        <f>IF(K44="","",IF(AND(K44&lt;&gt;"",ISNUMBER(入力!$F$47),入力!$F$47&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$47))*(K44-$W$3),K44))</f>
         <v/>
       </c>
       <c r="M44" s="22" t="str">
@@ -45659,12 +46180,24 @@
         <f>IF(C44="","",設定!$C$26*C44/D44*100)</f>
         <v/>
       </c>
-      <c r="U44">
+      <c r="S44" s="50" t="str">
+        <f>IF(Y44="","",IF(Y44&lt;=0,"達成済み",IF(Y44&lt;60,Y44&amp;"秒",INT(Y44/60)&amp;"分"&amp;TEXT(MOD(Y44,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T44" s="26" t="str">
+        <f>IF(C44="","",D44/設定!$C$26-C44)</f>
+        <v/>
+      </c>
+      <c r="X44">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y44" t="str">
+        <f>IF(C44="","",ROUND(G44-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A45" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -45710,7 +46243,7 @@
         <v/>
       </c>
       <c r="L45" s="22" t="str">
-        <f>IF(K45="","",IF(AND(K45&lt;&gt;"",ISNUMBER(入力!$F$48),入力!$F$48&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$48))*(K45-$T$3),K45))</f>
+        <f>IF(K45="","",IF(AND(K45&lt;&gt;"",ISNUMBER(入力!$F$48),入力!$F$48&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$48))*(K45-$W$3),K45))</f>
         <v/>
       </c>
       <c r="M45" s="22" t="str">
@@ -45737,12 +46270,24 @@
         <f>IF(C45="","",設定!$C$26*C45/D45*100)</f>
         <v/>
       </c>
-      <c r="U45">
+      <c r="S45" s="50" t="str">
+        <f>IF(Y45="","",IF(Y45&lt;=0,"達成済み",IF(Y45&lt;60,Y45&amp;"秒",INT(Y45/60)&amp;"分"&amp;TEXT(MOD(Y45,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T45" s="26" t="str">
+        <f>IF(C45="","",D45/設定!$C$26-C45)</f>
+        <v/>
+      </c>
+      <c r="X45">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y45" t="str">
+        <f>IF(C45="","",ROUND(G45-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A46" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -45788,7 +46333,7 @@
         <v/>
       </c>
       <c r="L46" s="22" t="str">
-        <f>IF(K46="","",IF(AND(K46&lt;&gt;"",ISNUMBER(入力!$F$49),入力!$F$49&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$49))*(K46-$T$3),K46))</f>
+        <f>IF(K46="","",IF(AND(K46&lt;&gt;"",ISNUMBER(入力!$F$49),入力!$F$49&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$49))*(K46-$W$3),K46))</f>
         <v/>
       </c>
       <c r="M46" s="22" t="str">
@@ -45815,12 +46360,24 @@
         <f>IF(C46="","",設定!$C$26*C46/D46*100)</f>
         <v/>
       </c>
-      <c r="U46">
+      <c r="S46" s="50" t="str">
+        <f>IF(Y46="","",IF(Y46&lt;=0,"達成済み",IF(Y46&lt;60,Y46&amp;"秒",INT(Y46/60)&amp;"分"&amp;TEXT(MOD(Y46,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T46" s="26" t="str">
+        <f>IF(C46="","",D46/設定!$C$26-C46)</f>
+        <v/>
+      </c>
+      <c r="X46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y46" t="str">
+        <f>IF(C46="","",ROUND(G46-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A47" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -45866,7 +46423,7 @@
         <v/>
       </c>
       <c r="L47" s="22" t="str">
-        <f>IF(K47="","",IF(AND(K47&lt;&gt;"",ISNUMBER(入力!$F$50),入力!$F$50&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$50))*(K47-$T$3),K47))</f>
+        <f>IF(K47="","",IF(AND(K47&lt;&gt;"",ISNUMBER(入力!$F$50),入力!$F$50&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$50))*(K47-$W$3),K47))</f>
         <v/>
       </c>
       <c r="M47" s="22" t="str">
@@ -45893,12 +46450,24 @@
         <f>IF(C47="","",設定!$C$26*C47/D47*100)</f>
         <v/>
       </c>
-      <c r="U47">
+      <c r="S47" s="50" t="str">
+        <f>IF(Y47="","",IF(Y47&lt;=0,"達成済み",IF(Y47&lt;60,Y47&amp;"秒",INT(Y47/60)&amp;"分"&amp;TEXT(MOD(Y47,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T47" s="26" t="str">
+        <f>IF(C47="","",D47/設定!$C$26-C47)</f>
+        <v/>
+      </c>
+      <c r="X47">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y47" t="str">
+        <f>IF(C47="","",ROUND(G47-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A48" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -45944,7 +46513,7 @@
         <v/>
       </c>
       <c r="L48" s="22" t="str">
-        <f>IF(K48="","",IF(AND(K48&lt;&gt;"",ISNUMBER(入力!$F$51),入力!$F$51&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$51))*(K48-$T$3),K48))</f>
+        <f>IF(K48="","",IF(AND(K48&lt;&gt;"",ISNUMBER(入力!$F$51),入力!$F$51&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$51))*(K48-$W$3),K48))</f>
         <v/>
       </c>
       <c r="M48" s="22" t="str">
@@ -45971,12 +46540,24 @@
         <f>IF(C48="","",設定!$C$26*C48/D48*100)</f>
         <v/>
       </c>
-      <c r="U48">
+      <c r="S48" s="50" t="str">
+        <f>IF(Y48="","",IF(Y48&lt;=0,"達成済み",IF(Y48&lt;60,Y48&amp;"秒",INT(Y48/60)&amp;"分"&amp;TEXT(MOD(Y48,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T48" s="26" t="str">
+        <f>IF(C48="","",D48/設定!$C$26-C48)</f>
+        <v/>
+      </c>
+      <c r="X48">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y48" t="str">
+        <f>IF(C48="","",ROUND(G48-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A49" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -46022,7 +46603,7 @@
         <v/>
       </c>
       <c r="L49" s="22" t="str">
-        <f>IF(K49="","",IF(AND(K49&lt;&gt;"",ISNUMBER(入力!$F$52),入力!$F$52&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$52))*(K49-$T$3),K49))</f>
+        <f>IF(K49="","",IF(AND(K49&lt;&gt;"",ISNUMBER(入力!$F$52),入力!$F$52&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$52))*(K49-$W$3),K49))</f>
         <v/>
       </c>
       <c r="M49" s="22" t="str">
@@ -46049,12 +46630,24 @@
         <f>IF(C49="","",設定!$C$26*C49/D49*100)</f>
         <v/>
       </c>
-      <c r="U49">
+      <c r="S49" s="50" t="str">
+        <f>IF(Y49="","",IF(Y49&lt;=0,"達成済み",IF(Y49&lt;60,Y49&amp;"秒",INT(Y49/60)&amp;"分"&amp;TEXT(MOD(Y49,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T49" s="26" t="str">
+        <f>IF(C49="","",D49/設定!$C$26-C49)</f>
+        <v/>
+      </c>
+      <c r="X49">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y49" t="str">
+        <f>IF(C49="","",ROUND(G49-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A50" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -46100,7 +46693,7 @@
         <v/>
       </c>
       <c r="L50" s="22" t="str">
-        <f>IF(K50="","",IF(AND(K50&lt;&gt;"",ISNUMBER(入力!$F$53),入力!$F$53&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$53))*(K50-$T$3),K50))</f>
+        <f>IF(K50="","",IF(AND(K50&lt;&gt;"",ISNUMBER(入力!$F$53),入力!$F$53&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$53))*(K50-$W$3),K50))</f>
         <v/>
       </c>
       <c r="M50" s="22" t="str">
@@ -46127,12 +46720,24 @@
         <f>IF(C50="","",設定!$C$26*C50/D50*100)</f>
         <v/>
       </c>
-      <c r="U50">
+      <c r="S50" s="50" t="str">
+        <f>IF(Y50="","",IF(Y50&lt;=0,"達成済み",IF(Y50&lt;60,Y50&amp;"秒",INT(Y50/60)&amp;"分"&amp;TEXT(MOD(Y50,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T50" s="26" t="str">
+        <f>IF(C50="","",D50/設定!$C$26-C50)</f>
+        <v/>
+      </c>
+      <c r="X50">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y50" t="str">
+        <f>IF(C50="","",ROUND(G50-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A51" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -46178,7 +46783,7 @@
         <v/>
       </c>
       <c r="L51" s="22" t="str">
-        <f>IF(K51="","",IF(AND(K51&lt;&gt;"",ISNUMBER(入力!$F$54),入力!$F$54&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$54))*(K51-$T$3),K51))</f>
+        <f>IF(K51="","",IF(AND(K51&lt;&gt;"",ISNUMBER(入力!$F$54),入力!$F$54&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$54))*(K51-$W$3),K51))</f>
         <v/>
       </c>
       <c r="M51" s="22" t="str">
@@ -46205,12 +46810,24 @@
         <f>IF(C51="","",設定!$C$26*C51/D51*100)</f>
         <v/>
       </c>
-      <c r="U51">
+      <c r="S51" s="50" t="str">
+        <f>IF(Y51="","",IF(Y51&lt;=0,"達成済み",IF(Y51&lt;60,Y51&amp;"秒",INT(Y51/60)&amp;"分"&amp;TEXT(MOD(Y51,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T51" s="26" t="str">
+        <f>IF(C51="","",D51/設定!$C$26-C51)</f>
+        <v/>
+      </c>
+      <c r="X51">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y51" t="str">
+        <f>IF(C51="","",ROUND(G51-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A52" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -46256,7 +46873,7 @@
         <v/>
       </c>
       <c r="L52" s="22" t="str">
-        <f>IF(K52="","",IF(AND(K52&lt;&gt;"",ISNUMBER(入力!$F$55),入力!$F$55&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$55))*(K52-$T$3),K52))</f>
+        <f>IF(K52="","",IF(AND(K52&lt;&gt;"",ISNUMBER(入力!$F$55),入力!$F$55&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$55))*(K52-$W$3),K52))</f>
         <v/>
       </c>
       <c r="M52" s="22" t="str">
@@ -46283,12 +46900,24 @@
         <f>IF(C52="","",設定!$C$26*C52/D52*100)</f>
         <v/>
       </c>
-      <c r="U52">
+      <c r="S52" s="50" t="str">
+        <f>IF(Y52="","",IF(Y52&lt;=0,"達成済み",IF(Y52&lt;60,Y52&amp;"秒",INT(Y52/60)&amp;"分"&amp;TEXT(MOD(Y52,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T52" s="26" t="str">
+        <f>IF(C52="","",D52/設定!$C$26-C52)</f>
+        <v/>
+      </c>
+      <c r="X52">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y52" t="str">
+        <f>IF(C52="","",ROUND(G52-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A53" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -46334,7 +46963,7 @@
         <v/>
       </c>
       <c r="L53" s="22" t="str">
-        <f>IF(K53="","",IF(AND(K53&lt;&gt;"",ISNUMBER(入力!$F$56),入力!$F$56&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$56))*(K53-$T$3),K53))</f>
+        <f>IF(K53="","",IF(AND(K53&lt;&gt;"",ISNUMBER(入力!$F$56),入力!$F$56&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$56))*(K53-$W$3),K53))</f>
         <v/>
       </c>
       <c r="M53" s="22" t="str">
@@ -46361,12 +46990,24 @@
         <f>IF(C53="","",設定!$C$26*C53/D53*100)</f>
         <v/>
       </c>
-      <c r="U53">
+      <c r="S53" s="50" t="str">
+        <f>IF(Y53="","",IF(Y53&lt;=0,"達成済み",IF(Y53&lt;60,Y53&amp;"秒",INT(Y53/60)&amp;"分"&amp;TEXT(MOD(Y53,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T53" s="26" t="str">
+        <f>IF(C53="","",D53/設定!$C$26-C53)</f>
+        <v/>
+      </c>
+      <c r="X53">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y53" t="str">
+        <f>IF(C53="","",ROUND(G53-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A54" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -46412,7 +47053,7 @@
         <v/>
       </c>
       <c r="L54" s="22" t="str">
-        <f>IF(K54="","",IF(AND(K54&lt;&gt;"",ISNUMBER(入力!$F$57),入力!$F$57&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$57))*(K54-$T$3),K54))</f>
+        <f>IF(K54="","",IF(AND(K54&lt;&gt;"",ISNUMBER(入力!$F$57),入力!$F$57&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$57))*(K54-$W$3),K54))</f>
         <v/>
       </c>
       <c r="M54" s="22" t="str">
@@ -46439,12 +47080,24 @@
         <f>IF(C54="","",設定!$C$26*C54/D54*100)</f>
         <v/>
       </c>
-      <c r="U54">
+      <c r="S54" s="50" t="str">
+        <f>IF(Y54="","",IF(Y54&lt;=0,"達成済み",IF(Y54&lt;60,Y54&amp;"秒",INT(Y54/60)&amp;"分"&amp;TEXT(MOD(Y54,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T54" s="26" t="str">
+        <f>IF(C54="","",D54/設定!$C$26-C54)</f>
+        <v/>
+      </c>
+      <c r="X54">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y54" t="str">
+        <f>IF(C54="","",ROUND(G54-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A55" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -46490,7 +47143,7 @@
         <v/>
       </c>
       <c r="L55" s="22" t="str">
-        <f>IF(K55="","",IF(AND(K55&lt;&gt;"",ISNUMBER(入力!$F$58),入力!$F$58&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$58))*(K55-$T$3),K55))</f>
+        <f>IF(K55="","",IF(AND(K55&lt;&gt;"",ISNUMBER(入力!$F$58),入力!$F$58&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$58))*(K55-$W$3),K55))</f>
         <v/>
       </c>
       <c r="M55" s="22" t="str">
@@ -46517,12 +47170,24 @@
         <f>IF(C55="","",設定!$C$26*C55/D55*100)</f>
         <v/>
       </c>
-      <c r="U55">
+      <c r="S55" s="50" t="str">
+        <f>IF(Y55="","",IF(Y55&lt;=0,"達成済み",IF(Y55&lt;60,Y55&amp;"秒",INT(Y55/60)&amp;"分"&amp;TEXT(MOD(Y55,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T55" s="26" t="str">
+        <f>IF(C55="","",D55/設定!$C$26-C55)</f>
+        <v/>
+      </c>
+      <c r="X55">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y55" t="str">
+        <f>IF(C55="","",ROUND(G55-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A56" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -46568,7 +47233,7 @@
         <v/>
       </c>
       <c r="L56" s="22" t="str">
-        <f>IF(K56="","",IF(AND(K56&lt;&gt;"",ISNUMBER(入力!$F$59),入力!$F$59&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$59))*(K56-$T$3),K56))</f>
+        <f>IF(K56="","",IF(AND(K56&lt;&gt;"",ISNUMBER(入力!$F$59),入力!$F$59&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$59))*(K56-$W$3),K56))</f>
         <v/>
       </c>
       <c r="M56" s="22" t="str">
@@ -46595,12 +47260,24 @@
         <f>IF(C56="","",設定!$C$26*C56/D56*100)</f>
         <v/>
       </c>
-      <c r="U56">
+      <c r="S56" s="50" t="str">
+        <f>IF(Y56="","",IF(Y56&lt;=0,"達成済み",IF(Y56&lt;60,Y56&amp;"秒",INT(Y56/60)&amp;"分"&amp;TEXT(MOD(Y56,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T56" s="26" t="str">
+        <f>IF(C56="","",D56/設定!$C$26-C56)</f>
+        <v/>
+      </c>
+      <c r="X56">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y56" t="str">
+        <f>IF(C56="","",ROUND(G56-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A57" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -46646,7 +47323,7 @@
         <v/>
       </c>
       <c r="L57" s="22" t="str">
-        <f>IF(K57="","",IF(AND(K57&lt;&gt;"",ISNUMBER(入力!$F$60),入力!$F$60&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$60))*(K57-$T$3),K57))</f>
+        <f>IF(K57="","",IF(AND(K57&lt;&gt;"",ISNUMBER(入力!$F$60),入力!$F$60&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$60))*(K57-$W$3),K57))</f>
         <v/>
       </c>
       <c r="M57" s="22" t="str">
@@ -46673,12 +47350,24 @@
         <f>IF(C57="","",設定!$C$26*C57/D57*100)</f>
         <v/>
       </c>
-      <c r="U57">
+      <c r="S57" s="50" t="str">
+        <f>IF(Y57="","",IF(Y57&lt;=0,"達成済み",IF(Y57&lt;60,Y57&amp;"秒",INT(Y57/60)&amp;"分"&amp;TEXT(MOD(Y57,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T57" s="26" t="str">
+        <f>IF(C57="","",D57/設定!$C$26-C57)</f>
+        <v/>
+      </c>
+      <c r="X57">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y57" t="str">
+        <f>IF(C57="","",ROUND(G57-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A58" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -46724,7 +47413,7 @@
         <v/>
       </c>
       <c r="L58" s="22" t="str">
-        <f>IF(K58="","",IF(AND(K58&lt;&gt;"",ISNUMBER(入力!$F$61),入力!$F$61&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$61))*(K58-$T$3),K58))</f>
+        <f>IF(K58="","",IF(AND(K58&lt;&gt;"",ISNUMBER(入力!$F$61),入力!$F$61&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$61))*(K58-$W$3),K58))</f>
         <v/>
       </c>
       <c r="M58" s="22" t="str">
@@ -46751,12 +47440,24 @@
         <f>IF(C58="","",設定!$C$26*C58/D58*100)</f>
         <v/>
       </c>
-      <c r="U58">
+      <c r="S58" s="50" t="str">
+        <f>IF(Y58="","",IF(Y58&lt;=0,"達成済み",IF(Y58&lt;60,Y58&amp;"秒",INT(Y58/60)&amp;"分"&amp;TEXT(MOD(Y58,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T58" s="26" t="str">
+        <f>IF(C58="","",D58/設定!$C$26-C58)</f>
+        <v/>
+      </c>
+      <c r="X58">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y58" t="str">
+        <f>IF(C58="","",ROUND(G58-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A59" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -46802,7 +47503,7 @@
         <v/>
       </c>
       <c r="L59" s="22" t="str">
-        <f>IF(K59="","",IF(AND(K59&lt;&gt;"",ISNUMBER(入力!$F$62),入力!$F$62&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$62))*(K59-$T$3),K59))</f>
+        <f>IF(K59="","",IF(AND(K59&lt;&gt;"",ISNUMBER(入力!$F$62),入力!$F$62&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$62))*(K59-$W$3),K59))</f>
         <v/>
       </c>
       <c r="M59" s="22" t="str">
@@ -46829,12 +47530,24 @@
         <f>IF(C59="","",設定!$C$26*C59/D59*100)</f>
         <v/>
       </c>
-      <c r="U59">
+      <c r="S59" s="50" t="str">
+        <f>IF(Y59="","",IF(Y59&lt;=0,"達成済み",IF(Y59&lt;60,Y59&amp;"秒",INT(Y59/60)&amp;"分"&amp;TEXT(MOD(Y59,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T59" s="26" t="str">
+        <f>IF(C59="","",D59/設定!$C$26-C59)</f>
+        <v/>
+      </c>
+      <c r="X59">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y59" t="str">
+        <f>IF(C59="","",ROUND(G59-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A60" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -46880,7 +47593,7 @@
         <v/>
       </c>
       <c r="L60" s="22" t="str">
-        <f>IF(K60="","",IF(AND(K60&lt;&gt;"",ISNUMBER(入力!$F$63),入力!$F$63&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$63))*(K60-$T$3),K60))</f>
+        <f>IF(K60="","",IF(AND(K60&lt;&gt;"",ISNUMBER(入力!$F$63),入力!$F$63&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$63))*(K60-$W$3),K60))</f>
         <v/>
       </c>
       <c r="M60" s="22" t="str">
@@ -46907,12 +47620,24 @@
         <f>IF(C60="","",設定!$C$26*C60/D60*100)</f>
         <v/>
       </c>
-      <c r="U60">
+      <c r="S60" s="50" t="str">
+        <f>IF(Y60="","",IF(Y60&lt;=0,"達成済み",IF(Y60&lt;60,Y60&amp;"秒",INT(Y60/60)&amp;"分"&amp;TEXT(MOD(Y60,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T60" s="26" t="str">
+        <f>IF(C60="","",D60/設定!$C$26-C60)</f>
+        <v/>
+      </c>
+      <c r="X60">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y60" t="str">
+        <f>IF(C60="","",ROUND(G60-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A61" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -46958,7 +47683,7 @@
         <v/>
       </c>
       <c r="L61" s="22" t="str">
-        <f>IF(K61="","",IF(AND(K61&lt;&gt;"",ISNUMBER(入力!$F$64),入力!$F$64&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$64))*(K61-$T$3),K61))</f>
+        <f>IF(K61="","",IF(AND(K61&lt;&gt;"",ISNUMBER(入力!$F$64),入力!$F$64&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$64))*(K61-$W$3),K61))</f>
         <v/>
       </c>
       <c r="M61" s="22" t="str">
@@ -46985,12 +47710,24 @@
         <f>IF(C61="","",設定!$C$26*C61/D61*100)</f>
         <v/>
       </c>
-      <c r="U61">
+      <c r="S61" s="50" t="str">
+        <f>IF(Y61="","",IF(Y61&lt;=0,"達成済み",IF(Y61&lt;60,Y61&amp;"秒",INT(Y61/60)&amp;"分"&amp;TEXT(MOD(Y61,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T61" s="26" t="str">
+        <f>IF(C61="","",D61/設定!$C$26-C61)</f>
+        <v/>
+      </c>
+      <c r="X61">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y61" t="str">
+        <f>IF(C61="","",ROUND(G61-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A62" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -47036,7 +47773,7 @@
         <v/>
       </c>
       <c r="L62" s="22" t="str">
-        <f>IF(K62="","",IF(AND(K62&lt;&gt;"",ISNUMBER(入力!$F$65),入力!$F$65&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$65))*(K62-$T$3),K62))</f>
+        <f>IF(K62="","",IF(AND(K62&lt;&gt;"",ISNUMBER(入力!$F$65),入力!$F$65&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$65))*(K62-$W$3),K62))</f>
         <v/>
       </c>
       <c r="M62" s="22" t="str">
@@ -47063,12 +47800,24 @@
         <f>IF(C62="","",設定!$C$26*C62/D62*100)</f>
         <v/>
       </c>
-      <c r="U62">
+      <c r="S62" s="50" t="str">
+        <f>IF(Y62="","",IF(Y62&lt;=0,"達成済み",IF(Y62&lt;60,Y62&amp;"秒",INT(Y62/60)&amp;"分"&amp;TEXT(MOD(Y62,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T62" s="26" t="str">
+        <f>IF(C62="","",D62/設定!$C$26-C62)</f>
+        <v/>
+      </c>
+      <c r="X62">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y62" t="str">
+        <f>IF(C62="","",ROUND(G62-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A63" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -47114,7 +47863,7 @@
         <v/>
       </c>
       <c r="L63" s="22" t="str">
-        <f>IF(K63="","",IF(AND(K63&lt;&gt;"",ISNUMBER(入力!$F$66),入力!$F$66&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$66))*(K63-$T$3),K63))</f>
+        <f>IF(K63="","",IF(AND(K63&lt;&gt;"",ISNUMBER(入力!$F$66),入力!$F$66&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$66))*(K63-$W$3),K63))</f>
         <v/>
       </c>
       <c r="M63" s="22" t="str">
@@ -47141,12 +47890,24 @@
         <f>IF(C63="","",設定!$C$26*C63/D63*100)</f>
         <v/>
       </c>
-      <c r="U63">
+      <c r="S63" s="50" t="str">
+        <f>IF(Y63="","",IF(Y63&lt;=0,"達成済み",IF(Y63&lt;60,Y63&amp;"秒",INT(Y63/60)&amp;"分"&amp;TEXT(MOD(Y63,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T63" s="26" t="str">
+        <f>IF(C63="","",D63/設定!$C$26-C63)</f>
+        <v/>
+      </c>
+      <c r="X63">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y63" t="str">
+        <f>IF(C63="","",ROUND(G63-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A64" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -47192,7 +47953,7 @@
         <v/>
       </c>
       <c r="L64" s="22" t="str">
-        <f>IF(K64="","",IF(AND(K64&lt;&gt;"",ISNUMBER(入力!$F$67),入力!$F$67&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$67))*(K64-$T$3),K64))</f>
+        <f>IF(K64="","",IF(AND(K64&lt;&gt;"",ISNUMBER(入力!$F$67),入力!$F$67&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$67))*(K64-$W$3),K64))</f>
         <v/>
       </c>
       <c r="M64" s="22" t="str">
@@ -47219,12 +47980,24 @@
         <f>IF(C64="","",設定!$C$26*C64/D64*100)</f>
         <v/>
       </c>
-      <c r="U64">
+      <c r="S64" s="50" t="str">
+        <f>IF(Y64="","",IF(Y64&lt;=0,"達成済み",IF(Y64&lt;60,Y64&amp;"秒",INT(Y64/60)&amp;"分"&amp;TEXT(MOD(Y64,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T64" s="26" t="str">
+        <f>IF(C64="","",D64/設定!$C$26-C64)</f>
+        <v/>
+      </c>
+      <c r="X64">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y64" t="str">
+        <f>IF(C64="","",ROUND(G64-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A65" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -47270,7 +48043,7 @@
         <v/>
       </c>
       <c r="L65" s="22" t="str">
-        <f>IF(K65="","",IF(AND(K65&lt;&gt;"",ISNUMBER(入力!$F$68),入力!$F$68&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$68))*(K65-$T$3),K65))</f>
+        <f>IF(K65="","",IF(AND(K65&lt;&gt;"",ISNUMBER(入力!$F$68),入力!$F$68&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$68))*(K65-$W$3),K65))</f>
         <v/>
       </c>
       <c r="M65" s="22" t="str">
@@ -47297,12 +48070,24 @@
         <f>IF(C65="","",設定!$C$26*C65/D65*100)</f>
         <v/>
       </c>
-      <c r="U65">
+      <c r="S65" s="50" t="str">
+        <f>IF(Y65="","",IF(Y65&lt;=0,"達成済み",IF(Y65&lt;60,Y65&amp;"秒",INT(Y65/60)&amp;"分"&amp;TEXT(MOD(Y65,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T65" s="26" t="str">
+        <f>IF(C65="","",D65/設定!$C$26-C65)</f>
+        <v/>
+      </c>
+      <c r="X65">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y65" t="str">
+        <f>IF(C65="","",ROUND(G65-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A66" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -47348,7 +48133,7 @@
         <v/>
       </c>
       <c r="L66" s="22" t="str">
-        <f>IF(K66="","",IF(AND(K66&lt;&gt;"",ISNUMBER(入力!$F$69),入力!$F$69&gt;0),$T$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$69))*(K66-$T$3),K66))</f>
+        <f>IF(K66="","",IF(AND(K66&lt;&gt;"",ISNUMBER(入力!$F$69),入力!$F$69&gt;0),$W$3+(設定!$D$14/(設定!$D$14+設定!$D$15/入力!$F$69))*(K66-$W$3),K66))</f>
         <v/>
       </c>
       <c r="M66" s="22" t="str">
@@ -47375,14 +48160,26 @@
         <f>IF(C66="","",設定!$C$26*C66/D66*100)</f>
         <v/>
       </c>
-      <c r="U66">
+      <c r="S66" s="50" t="str">
+        <f>IF(Y66="","",IF(Y66&lt;=0,"達成済み",IF(Y66&lt;60,Y66&amp;"秒",INT(Y66/60)&amp;"分"&amp;TEXT(MOD(Y66,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T66" s="26" t="str">
+        <f>IF(C66="","",D66/設定!$C$26-C66)</f>
+        <v/>
+      </c>
+      <c r="X66">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
+      <c r="Y66" t="str">
+        <f>IF(C66="","",ROUND(G66-設定!$C$26*60,0))</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="34"/>
-  <conditionalFormatting sqref="A7:R66">
+  <conditionalFormatting sqref="A7:T66">
     <cfRule type="expression" dxfId="5" priority="1">
       <formula>$O7="◎達成"</formula>
     </cfRule>
@@ -47415,7 +48212,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A2:U66"/>
+  <dimension ref="A2:Y66"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -47431,53 +48228,56 @@
     <col min="16" max="16" width="9" customWidth="1"/>
     <col min="17" max="17" width="10" customWidth="1"/>
     <col min="18" max="18" width="10" customWidth="1"/>
-    <col min="19" max="19" width="22" customWidth="1"/>
-    <col min="20" max="20" width="12" customWidth="1"/>
-    <col min="21" max="21" width="13" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="12" customWidth="1"/>
+    <col min="20" max="20" width="14" customWidth="1"/>
+    <col min="22" max="22" width="22" customWidth="1"/>
+    <col min="23" max="23" width="12" customWidth="1"/>
+    <col min="24" max="24" width="13" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:21" ht="17.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" ht="17.25" x14ac:dyDescent="0.2">
       <c r="B2" s="51" t="s">
         <v>189</v>
       </c>
-      <c r="S2" s="9" t="s">
+      <c r="V2" s="9" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:25" ht="14.25" x14ac:dyDescent="0.15">
       <c r="B3" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="S3" s="45" t="s">
+      <c r="V3" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="T3" s="46">
-        <f>IFERROR(SUM(U7:U66)/SUMIF(I7:I66,"&gt;0",C7:C66),"")</f>
+      <c r="W3" s="46">
+        <f>IFERROR(SUM(X7:X66)/SUMIF(I7:I66,"&gt;0",C7:C66),"")</f>
         <v>109.44372058095747</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.15">
       <c r="B4" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="S4" s="47" t="s">
+      <c r="V4" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="T4" s="21"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="W4" s="21"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.15">
       <c r="B5" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="S5" s="47" t="s">
+      <c r="V5" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="T5" s="26">
+      <c r="W5" s="26">
         <f>COUNT(L7:L66)</f>
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="20" t="s">
         <v>3</v>
       </c>
@@ -47535,17 +48335,29 @@
 %</t>
         </is>
       </c>
-      <c r="S6" s="47" t="inlineStr">
+      <c r="S6" s="20" t="inlineStr">
+        <is>
+          <t>目標まで
+あと</t>
+        </is>
+      </c>
+      <c r="T6" s="20" t="inlineStr">
+        <is>
+          <t>目標到達で
+増やせる件数</t>
+        </is>
+      </c>
+      <c r="V6" s="47" t="inlineStr">
         <is>
           <t>◎ 達成</t>
         </is>
       </c>
-      <c r="T6" s="26">
+      <c r="W6" s="26">
         <f>COUNTIF(O7:O66,"◎達成")</f>
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A7" s="48">
         <f t="shared" ref="A7:A38" si="0">IF(R7="","",RANK(R7,$R$7:$R$66,0))</f>
         <v>2</v>
@@ -47591,7 +48403,7 @@
         <v>149.67602924201614</v>
       </c>
       <c r="L7" s="22">
-        <f>IF(K7="","",IF(AND(K7&lt;&gt;"",ISNUMBER(入力!$J$10),入力!$J$10&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$10))*(K7-$T$3),K7))</f>
+        <f>IF(K7="","",IF(AND(K7&lt;&gt;"",ISNUMBER(入力!$J$10),入力!$J$10&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$10))*(K7-$W$3),K7))</f>
         <v>146.66177155707118</v>
       </c>
       <c r="M7" s="22">
@@ -47618,21 +48430,33 @@
         <f>IF(C7="","",設定!$C$27*C7/D7*100)</f>
         <v>153.47441323585994</v>
       </c>
-      <c r="S7" s="47" t="inlineStr">
+      <c r="S7" s="50" t="str">
+        <f>IF(Y7="","",IF(Y7&lt;=0,"達成済み",IF(Y7&lt;60,Y7&amp;"秒",INT(Y7/60)&amp;"分"&amp;TEXT(MOD(Y7,60),"00")&amp;"秒")))</f>
+        <v>達成済み</v>
+      </c>
+      <c r="T7" s="26">
+        <f>IF(C7="","",D7/設定!$C$27-C7)</f>
+        <v>-868.625</v>
+      </c>
+      <c r="V7" s="47" t="inlineStr">
         <is>
           <t>○ あと一歩</t>
         </is>
       </c>
-      <c r="T7" s="26">
+      <c r="W7" s="26">
         <f>COUNTIF(O7:O66,"○あと一歩")</f>
         <v>3</v>
       </c>
-      <c r="U7">
-        <f t="shared" ref="U7:U38" si="8">IF(K7="",0,K7*C7)</f>
+      <c r="X7">
+        <f t="shared" ref="X7:X38" si="8">IF(K7="",0,K7*C7)</f>
         <v>373142.34090034623</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y7">
+        <f>IF(C7="","",ROUND(G7-設定!$C$27*60,0))</f>
+        <v>-33.0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A8" s="48">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -47678,7 +48502,7 @@
         <v>94.524254742547413</v>
       </c>
       <c r="L8" s="22">
-        <f>IF(K8="","",IF(AND(K8&lt;&gt;"",ISNUMBER(入力!$J$11),入力!$J$11&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$11))*(K8-$T$3),K8))</f>
+        <f>IF(K8="","",IF(AND(K8&lt;&gt;"",ISNUMBER(入力!$J$11),入力!$J$11&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$11))*(K8-$W$3),K8))</f>
         <v>96.604008968531502</v>
       </c>
       <c r="M8" s="22">
@@ -47705,21 +48529,33 @@
         <f>IF(C8="","",設定!$C$27*C8/D8*100)</f>
         <v>82.47154471544717</v>
       </c>
-      <c r="S8" s="47" t="inlineStr">
+      <c r="S8" s="50" t="str">
+        <f>IF(Y8="","",IF(Y8&lt;=0,"達成済み",IF(Y8&lt;60,Y8&amp;"秒",INT(Y8/60)&amp;"分"&amp;TEXT(MOD(Y8,60),"00")&amp;"秒")))</f>
+        <v>20秒</v>
+      </c>
+      <c r="T8" s="26">
+        <f>IF(C8="","",D8/設定!$C$27-C8)</f>
+        <v>134.75</v>
+      </c>
+      <c r="V8" s="47" t="inlineStr">
         <is>
           <t>△ 要改善</t>
         </is>
       </c>
-      <c r="T8" s="26">
+      <c r="W8" s="26">
         <f>COUNTIF(O7:O66,"△要改善")</f>
         <v>4</v>
       </c>
-      <c r="U8">
+      <c r="X8">
         <f t="shared" si="8"/>
         <v>59928.377506775061</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y8">
+        <f>IF(C8="","",ROUND(G8-設定!$C$27*60,0))</f>
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A9" s="48">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -47765,7 +48601,7 @@
         <v>132.88643790849673</v>
       </c>
       <c r="L9" s="22">
-        <f>IF(K9="","",IF(AND(K9&lt;&gt;"",ISNUMBER(入力!$J$12),入力!$J$12&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$12))*(K9-$T$3),K9))</f>
+        <f>IF(K9="","",IF(AND(K9&lt;&gt;"",ISNUMBER(入力!$J$12),入力!$J$12&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$12))*(K9-$W$3),K9))</f>
         <v>131.04490021102978</v>
       </c>
       <c r="M9" s="22">
@@ -47792,21 +48628,33 @@
         <f>IF(C9="","",設定!$C$27*C9/D9*100)</f>
         <v>136.7843137254902</v>
       </c>
-      <c r="S9" s="47" t="inlineStr">
+      <c r="S9" s="50" t="str">
+        <f>IF(Y9="","",IF(Y9&lt;=0,"達成済み",IF(Y9&lt;60,Y9&amp;"秒",INT(Y9/60)&amp;"分"&amp;TEXT(MOD(Y9,60),"00")&amp;"秒")))</f>
+        <v>達成済み</v>
+      </c>
+      <c r="T9" s="26">
+        <f>IF(C9="","",D9/設定!$C$27-C9)</f>
+        <v>-703.5</v>
+      </c>
+      <c r="V9" s="47" t="inlineStr">
         <is>
           <t>✕ 要支援</t>
         </is>
       </c>
-      <c r="T9" s="26">
+      <c r="W9" s="26">
         <f>COUNTIF(O7:O66,"✕要支援")</f>
         <v>4</v>
       </c>
-      <c r="U9">
+      <c r="X9">
         <f t="shared" si="8"/>
         <v>347630.92156862747</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y9">
+        <f>IF(C9="","",ROUND(G9-設定!$C$27*60,0))</f>
+        <v>-26.0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A10" s="48">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -47852,7 +48700,7 @@
         <v>132.51857923497266</v>
       </c>
       <c r="L10" s="22">
-        <f>IF(K10="","",IF(AND(K10&lt;&gt;"",ISNUMBER(入力!$J$13),入力!$J$13&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$13))*(K10-$T$3),K10))</f>
+        <f>IF(K10="","",IF(AND(K10&lt;&gt;"",ISNUMBER(入力!$J$13),入力!$J$13&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$13))*(K10-$W$3),K10))</f>
         <v>128.1824773344137</v>
       </c>
       <c r="M10" s="22">
@@ -47879,19 +48727,31 @@
         <f>IF(C10="","",設定!$C$27*C10/D10*100)</f>
         <v>148.98360655737704</v>
       </c>
-      <c r="S10" s="47" t="s">
+      <c r="S10" s="50" t="str">
+        <f>IF(Y10="","",IF(Y10&lt;=0,"達成済み",IF(Y10&lt;60,Y10&amp;"秒",INT(Y10/60)&amp;"分"&amp;TEXT(MOD(Y10,60),"00")&amp;"秒")))</f>
+        <v>達成済み</v>
+      </c>
+      <c r="T10" s="26">
+        <f>IF(C10="","",D10/設定!$C$27-C10)</f>
+        <v>-93.375</v>
+      </c>
+      <c r="V10" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="T10" s="26">
+      <c r="W10" s="26">
         <f>SUMIF(I7:I66,"&gt;0",C7:C66)</f>
         <v>24467</v>
       </c>
-      <c r="U10">
+      <c r="X10">
         <f t="shared" si="8"/>
         <v>37635.276502732238</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y10">
+        <f>IF(C10="","",ROUND(G10-設定!$C$27*60,0))</f>
+        <v>-32.0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A11" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -47937,7 +48797,7 @@
         <v/>
       </c>
       <c r="L11" s="22" t="str">
-        <f>IF(K11="","",IF(AND(K11&lt;&gt;"",ISNUMBER(入力!$J$14),入力!$J$14&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$14))*(K11-$T$3),K11))</f>
+        <f>IF(K11="","",IF(AND(K11&lt;&gt;"",ISNUMBER(入力!$J$14),入力!$J$14&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$14))*(K11-$W$3),K11))</f>
         <v/>
       </c>
       <c r="M11" s="22" t="str">
@@ -47964,19 +48824,31 @@
         <f>IF(C11="","",設定!$C$27*C11/D11*100)</f>
         <v/>
       </c>
-      <c r="S11" s="47" t="s">
+      <c r="S11" s="50" t="str">
+        <f>IF(Y11="","",IF(Y11&lt;=0,"達成済み",IF(Y11&lt;60,Y11&amp;"秒",INT(Y11/60)&amp;"分"&amp;TEXT(MOD(Y11,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T11" s="26" t="str">
+        <f>IF(C11="","",D11/設定!$C$27-C11)</f>
+        <v/>
+      </c>
+      <c r="V11" s="47" t="s">
         <v>91</v>
       </c>
-      <c r="T11" s="26">
+      <c r="W11" s="26">
         <f>SUMIF(I7:I66,"&gt;0",E7:E66)</f>
         <v>7099</v>
       </c>
-      <c r="U11">
+      <c r="X11">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y11" t="str">
+        <f>IF(C11="","",ROUND(G11-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A12" s="48">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -48022,7 +48894,7 @@
         <v>80.326509661835729</v>
       </c>
       <c r="L12" s="22">
-        <f>IF(K12="","",IF(AND(K12&lt;&gt;"",ISNUMBER(入力!$J$15),入力!$J$15&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$15))*(K12-$T$3),K12))</f>
+        <f>IF(K12="","",IF(AND(K12&lt;&gt;"",ISNUMBER(入力!$J$15),入力!$J$15&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$15))*(K12-$W$3),K12))</f>
         <v>82.508009548320643</v>
       </c>
       <c r="M12" s="22">
@@ -48049,19 +48921,31 @@
         <f>IF(C12="","",設定!$C$27*C12/D12*100)</f>
         <v>82.37681159420289</v>
       </c>
-      <c r="S12" s="47" t="s">
+      <c r="S12" s="50" t="str">
+        <f>IF(Y12="","",IF(Y12&lt;=0,"達成済み",IF(Y12&lt;60,Y12&amp;"秒",INT(Y12/60)&amp;"分"&amp;TEXT(MOD(Y12,60),"00")&amp;"秒")))</f>
+        <v>21秒</v>
+      </c>
+      <c r="T12" s="26">
+        <f>IF(C12="","",D12/設定!$C$27-C12)</f>
+        <v>304.0</v>
+      </c>
+      <c r="V12" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="T12" s="26">
+      <c r="W12" s="26">
         <f>SUMIF(I7:I66,"&gt;0",D7:D66)</f>
         <v>38887</v>
       </c>
-      <c r="U12">
+      <c r="X12">
         <f t="shared" si="8"/>
         <v>114143.97022946857</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y12">
+        <f>IF(C12="","",ROUND(G12-設定!$C$27*60,0))</f>
+        <v>21.0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A13" s="48">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -48107,7 +48991,7 @@
         <v>81.792465753424665</v>
       </c>
       <c r="L13" s="22">
-        <f>IF(K13="","",IF(AND(K13&lt;&gt;"",ISNUMBER(入力!$J$16),入力!$J$16&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$16))*(K13-$T$3),K13))</f>
+        <f>IF(K13="","",IF(AND(K13&lt;&gt;"",ISNUMBER(入力!$J$16),入力!$J$16&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$16))*(K13-$W$3),K13))</f>
         <v>89.76235104145006</v>
       </c>
       <c r="M13" s="22">
@@ -48134,19 +49018,31 @@
         <f>IF(C13="","",設定!$C$27*C13/D13*100)</f>
         <v>82.1917808219178</v>
       </c>
-      <c r="S13" s="47" t="s">
+      <c r="S13" s="50" t="str">
+        <f>IF(Y13="","",IF(Y13&lt;=0,"達成済み",IF(Y13&lt;60,Y13&amp;"秒",INT(Y13/60)&amp;"分"&amp;TEXT(MOD(Y13,60),"00")&amp;"秒")))</f>
+        <v>21秒</v>
+      </c>
+      <c r="T13" s="26">
+        <f>IF(C13="","",D13/設定!$C$27-C13)</f>
+        <v>81.25</v>
+      </c>
+      <c r="V13" s="47" t="s">
         <v>187</v>
       </c>
-      <c r="T13" s="26">
+      <c r="W13" s="26">
         <f>SUMIF(I7:I66,"&gt;0",H7:H66)</f>
         <v>10896.964999999998</v>
       </c>
-      <c r="U13">
+      <c r="X13">
         <f t="shared" si="8"/>
         <v>30672.174657534248</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y13">
+        <f>IF(C13="","",ROUND(G13-設定!$C$27*60,0))</f>
+        <v>21.0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A14" s="48">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -48192,7 +49088,7 @@
         <v>121.13147824640211</v>
       </c>
       <c r="L14" s="22">
-        <f>IF(K14="","",IF(AND(K14&lt;&gt;"",ISNUMBER(入力!$J$17),入力!$J$17&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$17))*(K14-$T$3),K14))</f>
+        <f>IF(K14="","",IF(AND(K14&lt;&gt;"",ISNUMBER(入力!$J$17),入力!$J$17&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$17))*(K14-$W$3),K14))</f>
         <v>120.21334891697963</v>
       </c>
       <c r="M14" s="22">
@@ -48219,19 +49115,31 @@
         <f>IF(C14="","",設定!$C$27*C14/D14*100)</f>
         <v>115.03868230596457</v>
       </c>
-      <c r="S14" s="47" t="s">
+      <c r="S14" s="50" t="str">
+        <f>IF(Y14="","",IF(Y14&lt;=0,"達成済み",IF(Y14&lt;60,Y14&amp;"秒",INT(Y14/60)&amp;"分"&amp;TEXT(MOD(Y14,60),"00")&amp;"秒")))</f>
+        <v>達成済み</v>
+      </c>
+      <c r="T14" s="26">
+        <f>IF(C14="","",D14/設定!$C$27-C14)</f>
+        <v>-376.625</v>
+      </c>
+      <c r="V14" s="47" t="s">
         <v>188</v>
       </c>
-      <c r="T14" s="26">
+      <c r="W14" s="26">
         <f>SUM(I7:I66)</f>
         <v>39237.906666666662</v>
       </c>
-      <c r="U14">
+      <c r="X14">
         <f t="shared" si="8"/>
         <v>348979.78882788448</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y14">
+        <f>IF(C14="","",ROUND(G14-設定!$C$27*60,0))</f>
+        <v>-13.0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A15" s="48">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -48277,7 +49185,7 @@
         <v>93.863706034204569</v>
       </c>
       <c r="L15" s="22">
-        <f>IF(K15="","",IF(AND(K15&lt;&gt;"",ISNUMBER(入力!$J$18),入力!$J$18&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$18))*(K15-$T$3),K15))</f>
+        <f>IF(K15="","",IF(AND(K15&lt;&gt;"",ISNUMBER(入力!$J$18),入力!$J$18&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$18))*(K15-$W$3),K15))</f>
         <v>95.030981294859927</v>
       </c>
       <c r="M15" s="22">
@@ -48304,19 +49212,31 @@
         <f>IF(C15="","",設定!$C$27*C15/D15*100)</f>
         <v>93.78509196515006</v>
       </c>
-      <c r="S15" s="47" t="s">
+      <c r="S15" s="50" t="str">
+        <f>IF(Y15="","",IF(Y15&lt;=0,"達成済み",IF(Y15&lt;60,Y15&amp;"秒",INT(Y15/60)&amp;"分"&amp;TEXT(MOD(Y15,60),"00")&amp;"秒")))</f>
+        <v>6秒</v>
+      </c>
+      <c r="T15" s="26">
+        <f>IF(C15="","",D15/設定!$C$27-C15)</f>
+        <v>160.5</v>
+      </c>
+      <c r="V15" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="T15" s="23">
-        <f>IFERROR(T13/T14,"")</f>
+      <c r="W15" s="23">
+        <f>IFERROR(W13/W14,"")</f>
         <v>0.2777152484859029</v>
       </c>
-      <c r="U15">
+      <c r="X15">
         <f t="shared" si="8"/>
         <v>227337.89601484346</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y15">
+        <f>IF(C15="","",ROUND(G15-設定!$C$27*60,0))</f>
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A16" s="48">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -48362,7 +49282,7 @@
         <v>84.736739745403099</v>
       </c>
       <c r="L16" s="22">
-        <f>IF(K16="","",IF(AND(K16&lt;&gt;"",ISNUMBER(入力!$J$19),入力!$J$19&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$19))*(K16-$T$3),K16))</f>
+        <f>IF(K16="","",IF(AND(K16&lt;&gt;"",ISNUMBER(入力!$J$19),入力!$J$19&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$19))*(K16-$W$3),K16))</f>
         <v>86.587819371053342</v>
       </c>
       <c r="M16" s="22">
@@ -48389,19 +49309,31 @@
         <f>IF(C16="","",設定!$C$27*C16/D16*100)</f>
         <v>87.58132956152758</v>
       </c>
-      <c r="S16" s="47" t="s">
+      <c r="S16" s="50" t="str">
+        <f>IF(Y16="","",IF(Y16&lt;=0,"達成済み",IF(Y16&lt;60,Y16&amp;"秒",INT(Y16/60)&amp;"分"&amp;TEXT(MOD(Y16,60),"00")&amp;"秒")))</f>
+        <v>14秒</v>
+      </c>
+      <c r="T16" s="26">
+        <f>IF(C16="","",D16/設定!$C$27-C16)</f>
+        <v>219.5</v>
+      </c>
+      <c r="V16" s="47" t="s">
         <v>93</v>
       </c>
-      <c r="T16" s="27">
-        <f>IFERROR(T10/T11,"")</f>
+      <c r="W16" s="27">
+        <f>IFERROR(W10/W11,"")</f>
         <v>3.4465417664459781</v>
       </c>
-      <c r="U16">
+      <c r="X16">
         <f t="shared" si="8"/>
         <v>131172.47312588399</v>
       </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y16">
+        <f>IF(C16="","",ROUND(G16-設定!$C$27*60,0))</f>
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A17" s="48">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -48447,7 +49379,7 @@
         <v>171.96125541125542</v>
       </c>
       <c r="L17" s="22">
-        <f>IF(K17="","",IF(AND(K17&lt;&gt;"",ISNUMBER(入力!$J$20),入力!$J$20&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$20))*(K17-$T$3),K17))</f>
+        <f>IF(K17="","",IF(AND(K17&lt;&gt;"",ISNUMBER(入力!$J$20),入力!$J$20&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$20))*(K17-$W$3),K17))</f>
         <v>160.21330038970882</v>
       </c>
       <c r="M17" s="22">
@@ -48474,19 +49406,31 @@
         <f>IF(C17="","",設定!$C$27*C17/D17*100)</f>
         <v>184.93506493506493</v>
       </c>
-      <c r="S17" s="47" t="s">
+      <c r="S17" s="50" t="str">
+        <f>IF(Y17="","",IF(Y17&lt;=0,"達成済み",IF(Y17&lt;60,Y17&amp;"秒",INT(Y17/60)&amp;"分"&amp;TEXT(MOD(Y17,60),"00")&amp;"秒")))</f>
+        <v>達成済み</v>
+      </c>
+      <c r="T17" s="26">
+        <f>IF(C17="","",D17/設定!$C$27-C17)</f>
+        <v>-408.75</v>
+      </c>
+      <c r="V17" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="T17" s="22">
-        <f>IFERROR(T12*60/T10,"")</f>
+      <c r="W17" s="22">
+        <f>IFERROR(W12*60/W10,"")</f>
         <v>95.361916050190047</v>
       </c>
-      <c r="U17">
+      <c r="X17">
         <f t="shared" si="8"/>
         <v>153045.51731601733</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y17">
+        <f>IF(C17="","",ROUND(G17-設定!$C$27*60,0))</f>
+        <v>-44.0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A18" s="48">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -48532,7 +49476,7 @@
         <v>136.2250663632916</v>
       </c>
       <c r="L18" s="22">
-        <f>IF(K18="","",IF(AND(K18&lt;&gt;"",ISNUMBER(入力!$J$21),入力!$J$21&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$21))*(K18-$T$3),K18))</f>
+        <f>IF(K18="","",IF(AND(K18&lt;&gt;"",ISNUMBER(入力!$J$21),入力!$J$21&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$21))*(K18-$W$3),K18))</f>
         <v>133.25785675591538</v>
       </c>
       <c r="M18" s="22">
@@ -48559,12 +49503,33 @@
         <f>IF(C18="","",設定!$C$27*C18/D18*100)</f>
         <v>131.24004550625713</v>
       </c>
-      <c r="U18">
+      <c r="S18" s="50" t="str">
+        <f>IF(Y18="","",IF(Y18&lt;=0,"達成済み",IF(Y18&lt;60,Y18&amp;"秒",INT(Y18/60)&amp;"分"&amp;TEXT(MOD(Y18,60),"00")&amp;"秒")))</f>
+        <v>達成済み</v>
+      </c>
+      <c r="T18" s="26">
+        <f>IF(C18="","",D18/設定!$C$27-C18)</f>
+        <v>-343.25</v>
+      </c>
+      <c r="V18" s="47" t="inlineStr">
+        <is>
+          <t>1件あたり 目標まで(秒)</t>
+        </is>
+      </c>
+      <c r="W18" s="22">
+        <f>IFERROR(W17-設定!$C$27*60,"")</f>
+        <v>-0.6380839498098965</v>
+      </c>
+      <c r="X18">
         <f t="shared" si="8"/>
         <v>196436.54569586649</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y18">
+        <f>IF(C18="","",ROUND(G18-設定!$C$27*60,0))</f>
+        <v>-23.0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A19" s="48">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -48610,7 +49575,7 @@
         <v>66.904561403508765</v>
       </c>
       <c r="L19" s="22">
-        <f>IF(K19="","",IF(AND(K19&lt;&gt;"",ISNUMBER(入力!$J$22),入力!$J$22&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$22))*(K19-$T$3),K19))</f>
+        <f>IF(K19="","",IF(AND(K19&lt;&gt;"",ISNUMBER(入力!$J$22),入力!$J$22&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$22))*(K19-$W$3),K19))</f>
         <v>81.8195904305488</v>
       </c>
       <c r="M19" s="22">
@@ -48637,12 +49602,33 @@
         <f>IF(C19="","",設定!$C$27*C19/D19*100)</f>
         <v>75.45263157894738</v>
       </c>
-      <c r="U19">
+      <c r="S19" s="50" t="str">
+        <f>IF(Y19="","",IF(Y19&lt;=0,"達成済み",IF(Y19&lt;60,Y19&amp;"秒",INT(Y19/60)&amp;"分"&amp;TEXT(MOD(Y19,60),"00")&amp;"秒")))</f>
+        <v>31秒</v>
+      </c>
+      <c r="T19" s="26">
+        <f>IF(C19="","",D19/設定!$C$27-C19)</f>
+        <v>72.875</v>
+      </c>
+      <c r="V19" s="47" t="inlineStr">
+        <is>
+          <t>目標到達で増やせる件数</t>
+        </is>
+      </c>
+      <c r="W19" s="26">
+        <f>IFERROR(W12/設定!$C$27-W10,"")</f>
+        <v>-162.625</v>
+      </c>
+      <c r="X19">
         <f t="shared" si="8"/>
         <v>14986.621754385964</v>
       </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y19">
+        <f>IF(C19="","",ROUND(G19-設定!$C$27*60,0))</f>
+        <v>31.0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A20" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -48688,7 +49674,7 @@
         <v/>
       </c>
       <c r="L20" s="22" t="str">
-        <f>IF(K20="","",IF(AND(K20&lt;&gt;"",ISNUMBER(入力!$J$23),入力!$J$23&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$23))*(K20-$T$3),K20))</f>
+        <f>IF(K20="","",IF(AND(K20&lt;&gt;"",ISNUMBER(入力!$J$23),入力!$J$23&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$23))*(K20-$W$3),K20))</f>
         <v/>
       </c>
       <c r="M20" s="22" t="str">
@@ -48715,12 +49701,24 @@
         <f>IF(C20="","",設定!$C$27*C20/D20*100)</f>
         <v/>
       </c>
-      <c r="U20">
+      <c r="S20" s="50" t="str">
+        <f>IF(Y20="","",IF(Y20&lt;=0,"達成済み",IF(Y20&lt;60,Y20&amp;"秒",INT(Y20/60)&amp;"分"&amp;TEXT(MOD(Y20,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T20" s="26" t="str">
+        <f>IF(C20="","",D20/設定!$C$27-C20)</f>
+        <v/>
+      </c>
+      <c r="X20">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y20" t="str">
+        <f>IF(C20="","",ROUND(G20-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A21" s="48">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -48766,7 +49764,7 @@
         <v>52.277377892030849</v>
       </c>
       <c r="L21" s="22">
-        <f>IF(K21="","",IF(AND(K21&lt;&gt;"",ISNUMBER(入力!$J$24),入力!$J$24&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$24))*(K21-$T$3),K21))</f>
+        <f>IF(K21="","",IF(AND(K21&lt;&gt;"",ISNUMBER(入力!$J$24),入力!$J$24&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$24))*(K21-$W$3),K21))</f>
         <v>60.246292066240983</v>
       </c>
       <c r="M21" s="22">
@@ -48793,12 +49791,24 @@
         <f>IF(C21="","",設定!$C$27*C21/D21*100)</f>
         <v>51.82519280205655</v>
       </c>
-      <c r="U21">
+      <c r="S21" s="50" t="str">
+        <f>IF(Y21="","",IF(Y21&lt;=0,"達成済み",IF(Y21&lt;60,Y21&amp;"秒",INT(Y21/60)&amp;"分"&amp;TEXT(MOD(Y21,60),"00")&amp;"秒")))</f>
+        <v>1分29秒</v>
+      </c>
+      <c r="T21" s="26">
+        <f>IF(C21="","",D21/設定!$C$27-C21)</f>
+        <v>585.625</v>
+      </c>
+      <c r="X21">
         <f t="shared" si="8"/>
         <v>32934.748071979433</v>
       </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y21">
+        <f>IF(C21="","",ROUND(G21-設定!$C$27*60,0))</f>
+        <v>89.0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A22" s="48">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -48844,7 +49854,7 @@
         <v>116.41046228710461</v>
       </c>
       <c r="L22" s="22">
-        <f>IF(K22="","",IF(AND(K22&lt;&gt;"",ISNUMBER(入力!$J$25),入力!$J$25&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$25))*(K22-$T$3),K22))</f>
+        <f>IF(K22="","",IF(AND(K22&lt;&gt;"",ISNUMBER(入力!$J$25),入力!$J$25&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$25))*(K22-$W$3),K22))</f>
         <v>115.10131008792217</v>
       </c>
       <c r="M22" s="22">
@@ -48871,12 +49881,24 @@
         <f>IF(C22="","",設定!$C$27*C22/D22*100)</f>
         <v>138.5109489051095</v>
       </c>
-      <c r="U22">
+      <c r="S22" s="50" t="str">
+        <f>IF(Y22="","",IF(Y22&lt;=0,"達成済み",IF(Y22&lt;60,Y22&amp;"秒",INT(Y22/60)&amp;"分"&amp;TEXT(MOD(Y22,60),"00")&amp;"秒")))</f>
+        <v>達成済み</v>
+      </c>
+      <c r="T22" s="26">
+        <f>IF(C22="","",D22/設定!$C$27-C22)</f>
+        <v>-164.875</v>
+      </c>
+      <c r="X22">
         <f t="shared" si="8"/>
         <v>69031.404136253026</v>
       </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y22">
+        <f>IF(C22="","",ROUND(G22-設定!$C$27*60,0))</f>
+        <v>-27.0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A23" s="48">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -48922,7 +49944,7 @@
         <v>71.829549454417446</v>
       </c>
       <c r="L23" s="22">
-        <f>IF(K23="","",IF(AND(K23&lt;&gt;"",ISNUMBER(入力!$J$26),入力!$J$26&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$26))*(K23-$T$3),K23))</f>
+        <f>IF(K23="","",IF(AND(K23&lt;&gt;"",ISNUMBER(入力!$J$26),入力!$J$26&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$26))*(K23-$W$3),K23))</f>
         <v>74.647652818461978</v>
       </c>
       <c r="M23" s="22">
@@ -48949,12 +49971,24 @@
         <f>IF(C23="","",設定!$C$27*C23/D23*100)</f>
         <v>73.91763463569166</v>
       </c>
-      <c r="U23">
+      <c r="S23" s="50" t="str">
+        <f>IF(Y23="","",IF(Y23&lt;=0,"達成済み",IF(Y23&lt;60,Y23&amp;"秒",INT(Y23/60)&amp;"分"&amp;TEXT(MOD(Y23,60),"00")&amp;"秒")))</f>
+        <v>34秒</v>
+      </c>
+      <c r="T23" s="26">
+        <f>IF(C23="","",D23/設定!$C$27-C23)</f>
+        <v>617.5</v>
+      </c>
+      <c r="X23">
         <f t="shared" si="8"/>
         <v>125701.71154523053</v>
       </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y23">
+        <f>IF(C23="","",ROUND(G23-設定!$C$27*60,0))</f>
+        <v>34.0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A24" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -49000,7 +50034,7 @@
         <v/>
       </c>
       <c r="L24" s="22" t="str">
-        <f>IF(K24="","",IF(AND(K24&lt;&gt;"",ISNUMBER(入力!$J$27),入力!$J$27&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$27))*(K24-$T$3),K24))</f>
+        <f>IF(K24="","",IF(AND(K24&lt;&gt;"",ISNUMBER(入力!$J$27),入力!$J$27&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$27))*(K24-$W$3),K24))</f>
         <v/>
       </c>
       <c r="M24" s="22" t="str">
@@ -49027,12 +50061,24 @@
         <f>IF(C24="","",設定!$C$27*C24/D24*100)</f>
         <v/>
       </c>
-      <c r="U24">
+      <c r="S24" s="50" t="str">
+        <f>IF(Y24="","",IF(Y24&lt;=0,"達成済み",IF(Y24&lt;60,Y24&amp;"秒",INT(Y24/60)&amp;"分"&amp;TEXT(MOD(Y24,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T24" s="26" t="str">
+        <f>IF(C24="","",D24/設定!$C$27-C24)</f>
+        <v/>
+      </c>
+      <c r="X24">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y24" t="str">
+        <f>IF(C24="","",ROUND(G24-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A25" s="48">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -49078,7 +50124,7 @@
         <v>97.378246753246756</v>
       </c>
       <c r="L25" s="22">
-        <f>IF(K25="","",IF(AND(K25&lt;&gt;"",ISNUMBER(入力!$J$28),入力!$J$28&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$28))*(K25-$T$3),K25))</f>
+        <f>IF(K25="","",IF(AND(K25&lt;&gt;"",ISNUMBER(入力!$J$28),入力!$J$28&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$28))*(K25-$W$3),K25))</f>
         <v>98.813177530341235</v>
       </c>
       <c r="M25" s="22">
@@ -49105,12 +50151,24 @@
         <f>IF(C25="","",設定!$C$27*C25/D25*100)</f>
         <v>90.9090909090909</v>
       </c>
-      <c r="U25">
+      <c r="S25" s="50" t="str">
+        <f>IF(Y25="","",IF(Y25&lt;=0,"達成済み",IF(Y25&lt;60,Y25&amp;"秒",INT(Y25/60)&amp;"分"&amp;TEXT(MOD(Y25,60),"00")&amp;"秒")))</f>
+        <v>10秒</v>
+      </c>
+      <c r="T25" s="26">
+        <f>IF(C25="","",D25/設定!$C$27-C25)</f>
+        <v>105.0</v>
+      </c>
+      <c r="X25">
         <f t="shared" si="8"/>
         <v>102247.15909090909</v>
       </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y25">
+        <f>IF(C25="","",ROUND(G25-設定!$C$27*60,0))</f>
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A26" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -49156,7 +50214,7 @@
         <v/>
       </c>
       <c r="L26" s="22" t="str">
-        <f>IF(K26="","",IF(AND(K26&lt;&gt;"",ISNUMBER(入力!$J$29),入力!$J$29&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$29))*(K26-$T$3),K26))</f>
+        <f>IF(K26="","",IF(AND(K26&lt;&gt;"",ISNUMBER(入力!$J$29),入力!$J$29&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$29))*(K26-$W$3),K26))</f>
         <v/>
       </c>
       <c r="M26" s="22" t="str">
@@ -49183,12 +50241,24 @@
         <f>IF(C26="","",設定!$C$27*C26/D26*100)</f>
         <v/>
       </c>
-      <c r="U26">
+      <c r="S26" s="50" t="str">
+        <f>IF(Y26="","",IF(Y26&lt;=0,"達成済み",IF(Y26&lt;60,Y26&amp;"秒",INT(Y26/60)&amp;"分"&amp;TEXT(MOD(Y26,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T26" s="26" t="str">
+        <f>IF(C26="","",D26/設定!$C$27-C26)</f>
+        <v/>
+      </c>
+      <c r="X26">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y26" t="str">
+        <f>IF(C26="","",ROUND(G26-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A27" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -49234,7 +50304,7 @@
         <v/>
       </c>
       <c r="L27" s="22" t="str">
-        <f>IF(K27="","",IF(AND(K27&lt;&gt;"",ISNUMBER(入力!$J$30),入力!$J$30&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$30))*(K27-$T$3),K27))</f>
+        <f>IF(K27="","",IF(AND(K27&lt;&gt;"",ISNUMBER(入力!$J$30),入力!$J$30&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$30))*(K27-$W$3),K27))</f>
         <v/>
       </c>
       <c r="M27" s="22" t="str">
@@ -49261,12 +50331,24 @@
         <f>IF(C27="","",設定!$C$27*C27/D27*100)</f>
         <v/>
       </c>
-      <c r="U27">
+      <c r="S27" s="50" t="str">
+        <f>IF(Y27="","",IF(Y27&lt;=0,"達成済み",IF(Y27&lt;60,Y27&amp;"秒",INT(Y27/60)&amp;"分"&amp;TEXT(MOD(Y27,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T27" s="26" t="str">
+        <f>IF(C27="","",D27/設定!$C$27-C27)</f>
+        <v/>
+      </c>
+      <c r="X27">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y27" t="str">
+        <f>IF(C27="","",ROUND(G27-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A28" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -49312,7 +50394,7 @@
         <v/>
       </c>
       <c r="L28" s="22" t="str">
-        <f>IF(K28="","",IF(AND(K28&lt;&gt;"",ISNUMBER(入力!$J$31),入力!$J$31&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$31))*(K28-$T$3),K28))</f>
+        <f>IF(K28="","",IF(AND(K28&lt;&gt;"",ISNUMBER(入力!$J$31),入力!$J$31&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$31))*(K28-$W$3),K28))</f>
         <v/>
       </c>
       <c r="M28" s="22" t="str">
@@ -49339,12 +50421,24 @@
         <f>IF(C28="","",設定!$C$27*C28/D28*100)</f>
         <v/>
       </c>
-      <c r="U28">
+      <c r="S28" s="50" t="str">
+        <f>IF(Y28="","",IF(Y28&lt;=0,"達成済み",IF(Y28&lt;60,Y28&amp;"秒",INT(Y28/60)&amp;"分"&amp;TEXT(MOD(Y28,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T28" s="26" t="str">
+        <f>IF(C28="","",D28/設定!$C$27-C28)</f>
+        <v/>
+      </c>
+      <c r="X28">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y28" t="str">
+        <f>IF(C28="","",ROUND(G28-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A29" s="48">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -49390,7 +50484,7 @@
         <v>100.98448866067606</v>
       </c>
       <c r="L29" s="22">
-        <f>IF(K29="","",IF(AND(K29&lt;&gt;"",ISNUMBER(入力!$J$32),入力!$J$32&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$32))*(K29-$T$3),K29))</f>
+        <f>IF(K29="","",IF(AND(K29&lt;&gt;"",ISNUMBER(入力!$J$32),入力!$J$32&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$32))*(K29-$W$3),K29))</f>
         <v>102.27473325768686</v>
       </c>
       <c r="M29" s="22">
@@ -49417,12 +50511,24 @@
         <f>IF(C29="","",設定!$C$27*C29/D29*100)</f>
         <v>99.61489088575097</v>
       </c>
-      <c r="U29">
+      <c r="S29" s="50" t="str">
+        <f>IF(Y29="","",IF(Y29&lt;=0,"達成済み",IF(Y29&lt;60,Y29&amp;"秒",INT(Y29/60)&amp;"分"&amp;TEXT(MOD(Y29,60),"00")&amp;"秒")))</f>
+        <v>達成済み</v>
+      </c>
+      <c r="T29" s="26">
+        <f>IF(C29="","",D29/設定!$C$27-C29)</f>
+        <v>3.75</v>
+      </c>
+      <c r="X29">
         <f t="shared" si="8"/>
         <v>97954.954000855781</v>
       </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y29">
+        <f>IF(C29="","",ROUND(G29-設定!$C$27*60,0))</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A30" s="48">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -49468,7 +50574,7 @@
         <v>65.703477177483293</v>
       </c>
       <c r="L30" s="22">
-        <f>IF(K30="","",IF(AND(K30&lt;&gt;"",ISNUMBER(入力!$J$33),入力!$J$33&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$33))*(K30-$T$3),K30))</f>
+        <f>IF(K30="","",IF(AND(K30&lt;&gt;"",ISNUMBER(入力!$J$33),入力!$J$33&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$33))*(K30-$W$3),K30))</f>
         <v>69.508553165647555</v>
       </c>
       <c r="M30" s="22">
@@ -49495,12 +50601,24 @@
         <f>IF(C30="","",設定!$C$27*C30/D30*100)</f>
         <v>64.31532449881074</v>
       </c>
-      <c r="U30">
+      <c r="S30" s="50" t="str">
+        <f>IF(Y30="","",IF(Y30&lt;=0,"達成済み",IF(Y30&lt;60,Y30&amp;"秒",INT(Y30/60)&amp;"分"&amp;TEXT(MOD(Y30,60),"00")&amp;"秒")))</f>
+        <v>53秒</v>
+      </c>
+      <c r="T30" s="26">
+        <f>IF(C30="","",D30/設定!$C$27-C30)</f>
+        <v>656.375</v>
+      </c>
+      <c r="X30">
         <f t="shared" si="8"/>
         <v>77727.213500962738</v>
       </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y30">
+        <f>IF(C30="","",ROUND(G30-設定!$C$27*60,0))</f>
+        <v>53.0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A31" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -49546,7 +50664,7 @@
         <v/>
       </c>
       <c r="L31" s="22" t="str">
-        <f>IF(K31="","",IF(AND(K31&lt;&gt;"",ISNUMBER(入力!$J$34),入力!$J$34&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$34))*(K31-$T$3),K31))</f>
+        <f>IF(K31="","",IF(AND(K31&lt;&gt;"",ISNUMBER(入力!$J$34),入力!$J$34&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$34))*(K31-$W$3),K31))</f>
         <v/>
       </c>
       <c r="M31" s="22" t="str">
@@ -49573,12 +50691,24 @@
         <f>IF(C31="","",設定!$C$27*C31/D31*100)</f>
         <v/>
       </c>
-      <c r="U31">
+      <c r="S31" s="50" t="str">
+        <f>IF(Y31="","",IF(Y31&lt;=0,"達成済み",IF(Y31&lt;60,Y31&amp;"秒",INT(Y31/60)&amp;"分"&amp;TEXT(MOD(Y31,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T31" s="26" t="str">
+        <f>IF(C31="","",D31/設定!$C$27-C31)</f>
+        <v/>
+      </c>
+      <c r="X31">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y31" t="str">
+        <f>IF(C31="","",ROUND(G31-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A32" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -49624,7 +50754,7 @@
         <v/>
       </c>
       <c r="L32" s="22" t="str">
-        <f>IF(K32="","",IF(AND(K32&lt;&gt;"",ISNUMBER(入力!$J$35),入力!$J$35&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$35))*(K32-$T$3),K32))</f>
+        <f>IF(K32="","",IF(AND(K32&lt;&gt;"",ISNUMBER(入力!$J$35),入力!$J$35&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$35))*(K32-$W$3),K32))</f>
         <v/>
       </c>
       <c r="M32" s="22" t="str">
@@ -49651,12 +50781,24 @@
         <f>IF(C32="","",設定!$C$27*C32/D32*100)</f>
         <v/>
       </c>
-      <c r="U32">
+      <c r="S32" s="50" t="str">
+        <f>IF(Y32="","",IF(Y32&lt;=0,"達成済み",IF(Y32&lt;60,Y32&amp;"秒",INT(Y32/60)&amp;"分"&amp;TEXT(MOD(Y32,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T32" s="26" t="str">
+        <f>IF(C32="","",D32/設定!$C$27-C32)</f>
+        <v/>
+      </c>
+      <c r="X32">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y32" t="str">
+        <f>IF(C32="","",ROUND(G32-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A33" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -49702,7 +50844,7 @@
         <v/>
       </c>
       <c r="L33" s="22" t="str">
-        <f>IF(K33="","",IF(AND(K33&lt;&gt;"",ISNUMBER(入力!$J$36),入力!$J$36&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$36))*(K33-$T$3),K33))</f>
+        <f>IF(K33="","",IF(AND(K33&lt;&gt;"",ISNUMBER(入力!$J$36),入力!$J$36&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$36))*(K33-$W$3),K33))</f>
         <v/>
       </c>
       <c r="M33" s="22" t="str">
@@ -49729,12 +50871,24 @@
         <f>IF(C33="","",設定!$C$27*C33/D33*100)</f>
         <v/>
       </c>
-      <c r="U33">
+      <c r="S33" s="50" t="str">
+        <f>IF(Y33="","",IF(Y33&lt;=0,"達成済み",IF(Y33&lt;60,Y33&amp;"秒",INT(Y33/60)&amp;"分"&amp;TEXT(MOD(Y33,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T33" s="26" t="str">
+        <f>IF(C33="","",D33/設定!$C$27-C33)</f>
+        <v/>
+      </c>
+      <c r="X33">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y33" t="str">
+        <f>IF(C33="","",ROUND(G33-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A34" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -49780,7 +50934,7 @@
         <v/>
       </c>
       <c r="L34" s="22" t="str">
-        <f>IF(K34="","",IF(AND(K34&lt;&gt;"",ISNUMBER(入力!$J$37),入力!$J$37&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$37))*(K34-$T$3),K34))</f>
+        <f>IF(K34="","",IF(AND(K34&lt;&gt;"",ISNUMBER(入力!$J$37),入力!$J$37&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$37))*(K34-$W$3),K34))</f>
         <v/>
       </c>
       <c r="M34" s="22" t="str">
@@ -49807,12 +50961,24 @@
         <f>IF(C34="","",設定!$C$27*C34/D34*100)</f>
         <v/>
       </c>
-      <c r="U34">
+      <c r="S34" s="50" t="str">
+        <f>IF(Y34="","",IF(Y34&lt;=0,"達成済み",IF(Y34&lt;60,Y34&amp;"秒",INT(Y34/60)&amp;"分"&amp;TEXT(MOD(Y34,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T34" s="26" t="str">
+        <f>IF(C34="","",D34/設定!$C$27-C34)</f>
+        <v/>
+      </c>
+      <c r="X34">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y34" t="str">
+        <f>IF(C34="","",ROUND(G34-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A35" s="48">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -49858,7 +51024,7 @@
         <v>129.17098681218735</v>
       </c>
       <c r="L35" s="22">
-        <f>IF(K35="","",IF(AND(K35&lt;&gt;"",ISNUMBER(入力!$J$38),入力!$J$38&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$38))*(K35-$T$3),K35))</f>
+        <f>IF(K35="","",IF(AND(K35&lt;&gt;"",ISNUMBER(入力!$J$38),入力!$J$38&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$38))*(K35-$W$3),K35))</f>
         <v>126.82484924085423</v>
       </c>
       <c r="M35" s="22">
@@ -49885,12 +51051,24 @@
         <f>IF(C35="","",設定!$C$27*C35/D35*100)</f>
         <v>115.79809004092772</v>
       </c>
-      <c r="U35">
+      <c r="S35" s="50" t="str">
+        <f>IF(Y35="","",IF(Y35&lt;=0,"達成済み",IF(Y35&lt;60,Y35&amp;"秒",INT(Y35/60)&amp;"分"&amp;TEXT(MOD(Y35,60),"00")&amp;"秒")))</f>
+        <v>達成済み</v>
+      </c>
+      <c r="T35" s="26">
+        <f>IF(C35="","",D35/設定!$C$27-C35)</f>
+        <v>-144.75</v>
+      </c>
+      <c r="X35">
         <f t="shared" si="8"/>
         <v>137050.41700773078</v>
       </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y35">
+        <f>IF(C35="","",ROUND(G35-設定!$C$27*60,0))</f>
+        <v>-13.0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A36" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -49936,7 +51114,7 @@
         <v/>
       </c>
       <c r="L36" s="22" t="str">
-        <f>IF(K36="","",IF(AND(K36&lt;&gt;"",ISNUMBER(入力!$J$39),入力!$J$39&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$39))*(K36-$T$3),K36))</f>
+        <f>IF(K36="","",IF(AND(K36&lt;&gt;"",ISNUMBER(入力!$J$39),入力!$J$39&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$39))*(K36-$W$3),K36))</f>
         <v/>
       </c>
       <c r="M36" s="22" t="str">
@@ -49963,12 +51141,24 @@
         <f>IF(C36="","",設定!$C$27*C36/D36*100)</f>
         <v/>
       </c>
-      <c r="U36">
+      <c r="S36" s="50" t="str">
+        <f>IF(Y36="","",IF(Y36&lt;=0,"達成済み",IF(Y36&lt;60,Y36&amp;"秒",INT(Y36/60)&amp;"分"&amp;TEXT(MOD(Y36,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T36" s="26" t="str">
+        <f>IF(C36="","",D36/設定!$C$27-C36)</f>
+        <v/>
+      </c>
+      <c r="X36">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y36" t="str">
+        <f>IF(C36="","",ROUND(G36-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A37" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -50014,7 +51204,7 @@
         <v/>
       </c>
       <c r="L37" s="22" t="str">
-        <f>IF(K37="","",IF(AND(K37&lt;&gt;"",ISNUMBER(入力!$J$40),入力!$J$40&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$40))*(K37-$T$3),K37))</f>
+        <f>IF(K37="","",IF(AND(K37&lt;&gt;"",ISNUMBER(入力!$J$40),入力!$J$40&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$40))*(K37-$W$3),K37))</f>
         <v/>
       </c>
       <c r="M37" s="22" t="str">
@@ -50041,12 +51231,24 @@
         <f>IF(C37="","",設定!$C$27*C37/D37*100)</f>
         <v/>
       </c>
-      <c r="U37">
+      <c r="S37" s="50" t="str">
+        <f>IF(Y37="","",IF(Y37&lt;=0,"達成済み",IF(Y37&lt;60,Y37&amp;"秒",INT(Y37/60)&amp;"分"&amp;TEXT(MOD(Y37,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T37" s="26" t="str">
+        <f>IF(C37="","",D37/設定!$C$27-C37)</f>
+        <v/>
+      </c>
+      <c r="X37">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y37" t="str">
+        <f>IF(C37="","",ROUND(G37-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A38" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -50092,7 +51294,7 @@
         <v/>
       </c>
       <c r="L38" s="22" t="str">
-        <f>IF(K38="","",IF(AND(K38&lt;&gt;"",ISNUMBER(入力!$J$41),入力!$J$41&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$41))*(K38-$T$3),K38))</f>
+        <f>IF(K38="","",IF(AND(K38&lt;&gt;"",ISNUMBER(入力!$J$41),入力!$J$41&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$41))*(K38-$W$3),K38))</f>
         <v/>
       </c>
       <c r="M38" s="22" t="str">
@@ -50119,12 +51321,24 @@
         <f>IF(C38="","",設定!$C$27*C38/D38*100)</f>
         <v/>
       </c>
-      <c r="U38">
+      <c r="S38" s="50" t="str">
+        <f>IF(Y38="","",IF(Y38&lt;=0,"達成済み",IF(Y38&lt;60,Y38&amp;"秒",INT(Y38/60)&amp;"分"&amp;TEXT(MOD(Y38,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T38" s="26" t="str">
+        <f>IF(C38="","",D38/設定!$C$27-C38)</f>
+        <v/>
+      </c>
+      <c r="X38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y38" t="str">
+        <f>IF(C38="","",ROUND(G38-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A39" s="48" t="str">
         <f t="shared" ref="A39:A66" si="9">IF(R39="","",RANK(R39,$R$7:$R$66,0))</f>
         <v/>
@@ -50170,7 +51384,7 @@
         <v/>
       </c>
       <c r="L39" s="22" t="str">
-        <f>IF(K39="","",IF(AND(K39&lt;&gt;"",ISNUMBER(入力!$J$42),入力!$J$42&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$42))*(K39-$T$3),K39))</f>
+        <f>IF(K39="","",IF(AND(K39&lt;&gt;"",ISNUMBER(入力!$J$42),入力!$J$42&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$42))*(K39-$W$3),K39))</f>
         <v/>
       </c>
       <c r="M39" s="22" t="str">
@@ -50197,12 +51411,24 @@
         <f>IF(C39="","",設定!$C$27*C39/D39*100)</f>
         <v/>
       </c>
-      <c r="U39">
-        <f t="shared" ref="U39:U66" si="17">IF(K39="",0,K39*C39)</f>
+      <c r="S39" s="50" t="str">
+        <f>IF(Y39="","",IF(Y39&lt;=0,"達成済み",IF(Y39&lt;60,Y39&amp;"秒",INT(Y39/60)&amp;"分"&amp;TEXT(MOD(Y39,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T39" s="26" t="str">
+        <f>IF(C39="","",D39/設定!$C$27-C39)</f>
+        <v/>
+      </c>
+      <c r="X39">
+        <f t="shared" ref="X39:X66" si="17">IF(K39="",0,K39*C39)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y39" t="str">
+        <f>IF(C39="","",ROUND(G39-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A40" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -50248,7 +51474,7 @@
         <v/>
       </c>
       <c r="L40" s="22" t="str">
-        <f>IF(K40="","",IF(AND(K40&lt;&gt;"",ISNUMBER(入力!$J$43),入力!$J$43&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$43))*(K40-$T$3),K40))</f>
+        <f>IF(K40="","",IF(AND(K40&lt;&gt;"",ISNUMBER(入力!$J$43),入力!$J$43&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$43))*(K40-$W$3),K40))</f>
         <v/>
       </c>
       <c r="M40" s="22" t="str">
@@ -50275,12 +51501,24 @@
         <f>IF(C40="","",設定!$C$27*C40/D40*100)</f>
         <v/>
       </c>
-      <c r="U40">
+      <c r="S40" s="50" t="str">
+        <f>IF(Y40="","",IF(Y40&lt;=0,"達成済み",IF(Y40&lt;60,Y40&amp;"秒",INT(Y40/60)&amp;"分"&amp;TEXT(MOD(Y40,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T40" s="26" t="str">
+        <f>IF(C40="","",D40/設定!$C$27-C40)</f>
+        <v/>
+      </c>
+      <c r="X40">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y40" t="str">
+        <f>IF(C40="","",ROUND(G40-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A41" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -50326,7 +51564,7 @@
         <v/>
       </c>
       <c r="L41" s="22" t="str">
-        <f>IF(K41="","",IF(AND(K41&lt;&gt;"",ISNUMBER(入力!$J$44),入力!$J$44&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$44))*(K41-$T$3),K41))</f>
+        <f>IF(K41="","",IF(AND(K41&lt;&gt;"",ISNUMBER(入力!$J$44),入力!$J$44&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$44))*(K41-$W$3),K41))</f>
         <v/>
       </c>
       <c r="M41" s="22" t="str">
@@ -50353,12 +51591,24 @@
         <f>IF(C41="","",設定!$C$27*C41/D41*100)</f>
         <v/>
       </c>
-      <c r="U41">
+      <c r="S41" s="50" t="str">
+        <f>IF(Y41="","",IF(Y41&lt;=0,"達成済み",IF(Y41&lt;60,Y41&amp;"秒",INT(Y41/60)&amp;"分"&amp;TEXT(MOD(Y41,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T41" s="26" t="str">
+        <f>IF(C41="","",D41/設定!$C$27-C41)</f>
+        <v/>
+      </c>
+      <c r="X41">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y41" t="str">
+        <f>IF(C41="","",ROUND(G41-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A42" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -50404,7 +51654,7 @@
         <v/>
       </c>
       <c r="L42" s="22" t="str">
-        <f>IF(K42="","",IF(AND(K42&lt;&gt;"",ISNUMBER(入力!$J$45),入力!$J$45&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$45))*(K42-$T$3),K42))</f>
+        <f>IF(K42="","",IF(AND(K42&lt;&gt;"",ISNUMBER(入力!$J$45),入力!$J$45&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$45))*(K42-$W$3),K42))</f>
         <v/>
       </c>
       <c r="M42" s="22" t="str">
@@ -50431,12 +51681,24 @@
         <f>IF(C42="","",設定!$C$27*C42/D42*100)</f>
         <v/>
       </c>
-      <c r="U42">
+      <c r="S42" s="50" t="str">
+        <f>IF(Y42="","",IF(Y42&lt;=0,"達成済み",IF(Y42&lt;60,Y42&amp;"秒",INT(Y42/60)&amp;"分"&amp;TEXT(MOD(Y42,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T42" s="26" t="str">
+        <f>IF(C42="","",D42/設定!$C$27-C42)</f>
+        <v/>
+      </c>
+      <c r="X42">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y42" t="str">
+        <f>IF(C42="","",ROUND(G42-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A43" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -50482,7 +51744,7 @@
         <v/>
       </c>
       <c r="L43" s="22" t="str">
-        <f>IF(K43="","",IF(AND(K43&lt;&gt;"",ISNUMBER(入力!$J$46),入力!$J$46&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$46))*(K43-$T$3),K43))</f>
+        <f>IF(K43="","",IF(AND(K43&lt;&gt;"",ISNUMBER(入力!$J$46),入力!$J$46&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$46))*(K43-$W$3),K43))</f>
         <v/>
       </c>
       <c r="M43" s="22" t="str">
@@ -50509,12 +51771,24 @@
         <f>IF(C43="","",設定!$C$27*C43/D43*100)</f>
         <v/>
       </c>
-      <c r="U43">
+      <c r="S43" s="50" t="str">
+        <f>IF(Y43="","",IF(Y43&lt;=0,"達成済み",IF(Y43&lt;60,Y43&amp;"秒",INT(Y43/60)&amp;"分"&amp;TEXT(MOD(Y43,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T43" s="26" t="str">
+        <f>IF(C43="","",D43/設定!$C$27-C43)</f>
+        <v/>
+      </c>
+      <c r="X43">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y43" t="str">
+        <f>IF(C43="","",ROUND(G43-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A44" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -50560,7 +51834,7 @@
         <v/>
       </c>
       <c r="L44" s="22" t="str">
-        <f>IF(K44="","",IF(AND(K44&lt;&gt;"",ISNUMBER(入力!$J$47),入力!$J$47&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$47))*(K44-$T$3),K44))</f>
+        <f>IF(K44="","",IF(AND(K44&lt;&gt;"",ISNUMBER(入力!$J$47),入力!$J$47&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$47))*(K44-$W$3),K44))</f>
         <v/>
       </c>
       <c r="M44" s="22" t="str">
@@ -50587,12 +51861,24 @@
         <f>IF(C44="","",設定!$C$27*C44/D44*100)</f>
         <v/>
       </c>
-      <c r="U44">
+      <c r="S44" s="50" t="str">
+        <f>IF(Y44="","",IF(Y44&lt;=0,"達成済み",IF(Y44&lt;60,Y44&amp;"秒",INT(Y44/60)&amp;"分"&amp;TEXT(MOD(Y44,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T44" s="26" t="str">
+        <f>IF(C44="","",D44/設定!$C$27-C44)</f>
+        <v/>
+      </c>
+      <c r="X44">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y44" t="str">
+        <f>IF(C44="","",ROUND(G44-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A45" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -50638,7 +51924,7 @@
         <v/>
       </c>
       <c r="L45" s="22" t="str">
-        <f>IF(K45="","",IF(AND(K45&lt;&gt;"",ISNUMBER(入力!$J$48),入力!$J$48&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$48))*(K45-$T$3),K45))</f>
+        <f>IF(K45="","",IF(AND(K45&lt;&gt;"",ISNUMBER(入力!$J$48),入力!$J$48&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$48))*(K45-$W$3),K45))</f>
         <v/>
       </c>
       <c r="M45" s="22" t="str">
@@ -50665,12 +51951,24 @@
         <f>IF(C45="","",設定!$C$27*C45/D45*100)</f>
         <v/>
       </c>
-      <c r="U45">
+      <c r="S45" s="50" t="str">
+        <f>IF(Y45="","",IF(Y45&lt;=0,"達成済み",IF(Y45&lt;60,Y45&amp;"秒",INT(Y45/60)&amp;"分"&amp;TEXT(MOD(Y45,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T45" s="26" t="str">
+        <f>IF(C45="","",D45/設定!$C$27-C45)</f>
+        <v/>
+      </c>
+      <c r="X45">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y45" t="str">
+        <f>IF(C45="","",ROUND(G45-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A46" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -50716,7 +52014,7 @@
         <v/>
       </c>
       <c r="L46" s="22" t="str">
-        <f>IF(K46="","",IF(AND(K46&lt;&gt;"",ISNUMBER(入力!$J$49),入力!$J$49&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$49))*(K46-$T$3),K46))</f>
+        <f>IF(K46="","",IF(AND(K46&lt;&gt;"",ISNUMBER(入力!$J$49),入力!$J$49&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$49))*(K46-$W$3),K46))</f>
         <v/>
       </c>
       <c r="M46" s="22" t="str">
@@ -50743,12 +52041,24 @@
         <f>IF(C46="","",設定!$C$27*C46/D46*100)</f>
         <v/>
       </c>
-      <c r="U46">
+      <c r="S46" s="50" t="str">
+        <f>IF(Y46="","",IF(Y46&lt;=0,"達成済み",IF(Y46&lt;60,Y46&amp;"秒",INT(Y46/60)&amp;"分"&amp;TEXT(MOD(Y46,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T46" s="26" t="str">
+        <f>IF(C46="","",D46/設定!$C$27-C46)</f>
+        <v/>
+      </c>
+      <c r="X46">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y46" t="str">
+        <f>IF(C46="","",ROUND(G46-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A47" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -50794,7 +52104,7 @@
         <v/>
       </c>
       <c r="L47" s="22" t="str">
-        <f>IF(K47="","",IF(AND(K47&lt;&gt;"",ISNUMBER(入力!$J$50),入力!$J$50&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$50))*(K47-$T$3),K47))</f>
+        <f>IF(K47="","",IF(AND(K47&lt;&gt;"",ISNUMBER(入力!$J$50),入力!$J$50&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$50))*(K47-$W$3),K47))</f>
         <v/>
       </c>
       <c r="M47" s="22" t="str">
@@ -50821,12 +52131,24 @@
         <f>IF(C47="","",設定!$C$27*C47/D47*100)</f>
         <v/>
       </c>
-      <c r="U47">
+      <c r="S47" s="50" t="str">
+        <f>IF(Y47="","",IF(Y47&lt;=0,"達成済み",IF(Y47&lt;60,Y47&amp;"秒",INT(Y47/60)&amp;"分"&amp;TEXT(MOD(Y47,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T47" s="26" t="str">
+        <f>IF(C47="","",D47/設定!$C$27-C47)</f>
+        <v/>
+      </c>
+      <c r="X47">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y47" t="str">
+        <f>IF(C47="","",ROUND(G47-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A48" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -50872,7 +52194,7 @@
         <v/>
       </c>
       <c r="L48" s="22" t="str">
-        <f>IF(K48="","",IF(AND(K48&lt;&gt;"",ISNUMBER(入力!$J$51),入力!$J$51&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$51))*(K48-$T$3),K48))</f>
+        <f>IF(K48="","",IF(AND(K48&lt;&gt;"",ISNUMBER(入力!$J$51),入力!$J$51&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$51))*(K48-$W$3),K48))</f>
         <v/>
       </c>
       <c r="M48" s="22" t="str">
@@ -50899,12 +52221,24 @@
         <f>IF(C48="","",設定!$C$27*C48/D48*100)</f>
         <v/>
       </c>
-      <c r="U48">
+      <c r="S48" s="50" t="str">
+        <f>IF(Y48="","",IF(Y48&lt;=0,"達成済み",IF(Y48&lt;60,Y48&amp;"秒",INT(Y48/60)&amp;"分"&amp;TEXT(MOD(Y48,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T48" s="26" t="str">
+        <f>IF(C48="","",D48/設定!$C$27-C48)</f>
+        <v/>
+      </c>
+      <c r="X48">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y48" t="str">
+        <f>IF(C48="","",ROUND(G48-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A49" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -50950,7 +52284,7 @@
         <v/>
       </c>
       <c r="L49" s="22" t="str">
-        <f>IF(K49="","",IF(AND(K49&lt;&gt;"",ISNUMBER(入力!$J$52),入力!$J$52&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$52))*(K49-$T$3),K49))</f>
+        <f>IF(K49="","",IF(AND(K49&lt;&gt;"",ISNUMBER(入力!$J$52),入力!$J$52&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$52))*(K49-$W$3),K49))</f>
         <v/>
       </c>
       <c r="M49" s="22" t="str">
@@ -50977,12 +52311,24 @@
         <f>IF(C49="","",設定!$C$27*C49/D49*100)</f>
         <v/>
       </c>
-      <c r="U49">
+      <c r="S49" s="50" t="str">
+        <f>IF(Y49="","",IF(Y49&lt;=0,"達成済み",IF(Y49&lt;60,Y49&amp;"秒",INT(Y49/60)&amp;"分"&amp;TEXT(MOD(Y49,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T49" s="26" t="str">
+        <f>IF(C49="","",D49/設定!$C$27-C49)</f>
+        <v/>
+      </c>
+      <c r="X49">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y49" t="str">
+        <f>IF(C49="","",ROUND(G49-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A50" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -51028,7 +52374,7 @@
         <v/>
       </c>
       <c r="L50" s="22" t="str">
-        <f>IF(K50="","",IF(AND(K50&lt;&gt;"",ISNUMBER(入力!$J$53),入力!$J$53&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$53))*(K50-$T$3),K50))</f>
+        <f>IF(K50="","",IF(AND(K50&lt;&gt;"",ISNUMBER(入力!$J$53),入力!$J$53&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$53))*(K50-$W$3),K50))</f>
         <v/>
       </c>
       <c r="M50" s="22" t="str">
@@ -51055,12 +52401,24 @@
         <f>IF(C50="","",設定!$C$27*C50/D50*100)</f>
         <v/>
       </c>
-      <c r="U50">
+      <c r="S50" s="50" t="str">
+        <f>IF(Y50="","",IF(Y50&lt;=0,"達成済み",IF(Y50&lt;60,Y50&amp;"秒",INT(Y50/60)&amp;"分"&amp;TEXT(MOD(Y50,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T50" s="26" t="str">
+        <f>IF(C50="","",D50/設定!$C$27-C50)</f>
+        <v/>
+      </c>
+      <c r="X50">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y50" t="str">
+        <f>IF(C50="","",ROUND(G50-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A51" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -51106,7 +52464,7 @@
         <v/>
       </c>
       <c r="L51" s="22" t="str">
-        <f>IF(K51="","",IF(AND(K51&lt;&gt;"",ISNUMBER(入力!$J$54),入力!$J$54&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$54))*(K51-$T$3),K51))</f>
+        <f>IF(K51="","",IF(AND(K51&lt;&gt;"",ISNUMBER(入力!$J$54),入力!$J$54&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$54))*(K51-$W$3),K51))</f>
         <v/>
       </c>
       <c r="M51" s="22" t="str">
@@ -51133,12 +52491,24 @@
         <f>IF(C51="","",設定!$C$27*C51/D51*100)</f>
         <v/>
       </c>
-      <c r="U51">
+      <c r="S51" s="50" t="str">
+        <f>IF(Y51="","",IF(Y51&lt;=0,"達成済み",IF(Y51&lt;60,Y51&amp;"秒",INT(Y51/60)&amp;"分"&amp;TEXT(MOD(Y51,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T51" s="26" t="str">
+        <f>IF(C51="","",D51/設定!$C$27-C51)</f>
+        <v/>
+      </c>
+      <c r="X51">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y51" t="str">
+        <f>IF(C51="","",ROUND(G51-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A52" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -51184,7 +52554,7 @@
         <v/>
       </c>
       <c r="L52" s="22" t="str">
-        <f>IF(K52="","",IF(AND(K52&lt;&gt;"",ISNUMBER(入力!$J$55),入力!$J$55&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$55))*(K52-$T$3),K52))</f>
+        <f>IF(K52="","",IF(AND(K52&lt;&gt;"",ISNUMBER(入力!$J$55),入力!$J$55&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$55))*(K52-$W$3),K52))</f>
         <v/>
       </c>
       <c r="M52" s="22" t="str">
@@ -51211,12 +52581,24 @@
         <f>IF(C52="","",設定!$C$27*C52/D52*100)</f>
         <v/>
       </c>
-      <c r="U52">
+      <c r="S52" s="50" t="str">
+        <f>IF(Y52="","",IF(Y52&lt;=0,"達成済み",IF(Y52&lt;60,Y52&amp;"秒",INT(Y52/60)&amp;"分"&amp;TEXT(MOD(Y52,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T52" s="26" t="str">
+        <f>IF(C52="","",D52/設定!$C$27-C52)</f>
+        <v/>
+      </c>
+      <c r="X52">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y52" t="str">
+        <f>IF(C52="","",ROUND(G52-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A53" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -51262,7 +52644,7 @@
         <v/>
       </c>
       <c r="L53" s="22" t="str">
-        <f>IF(K53="","",IF(AND(K53&lt;&gt;"",ISNUMBER(入力!$J$56),入力!$J$56&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$56))*(K53-$T$3),K53))</f>
+        <f>IF(K53="","",IF(AND(K53&lt;&gt;"",ISNUMBER(入力!$J$56),入力!$J$56&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$56))*(K53-$W$3),K53))</f>
         <v/>
       </c>
       <c r="M53" s="22" t="str">
@@ -51289,12 +52671,24 @@
         <f>IF(C53="","",設定!$C$27*C53/D53*100)</f>
         <v/>
       </c>
-      <c r="U53">
+      <c r="S53" s="50" t="str">
+        <f>IF(Y53="","",IF(Y53&lt;=0,"達成済み",IF(Y53&lt;60,Y53&amp;"秒",INT(Y53/60)&amp;"分"&amp;TEXT(MOD(Y53,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T53" s="26" t="str">
+        <f>IF(C53="","",D53/設定!$C$27-C53)</f>
+        <v/>
+      </c>
+      <c r="X53">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y53" t="str">
+        <f>IF(C53="","",ROUND(G53-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A54" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -51340,7 +52734,7 @@
         <v/>
       </c>
       <c r="L54" s="22" t="str">
-        <f>IF(K54="","",IF(AND(K54&lt;&gt;"",ISNUMBER(入力!$J$57),入力!$J$57&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$57))*(K54-$T$3),K54))</f>
+        <f>IF(K54="","",IF(AND(K54&lt;&gt;"",ISNUMBER(入力!$J$57),入力!$J$57&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$57))*(K54-$W$3),K54))</f>
         <v/>
       </c>
       <c r="M54" s="22" t="str">
@@ -51367,12 +52761,24 @@
         <f>IF(C54="","",設定!$C$27*C54/D54*100)</f>
         <v/>
       </c>
-      <c r="U54">
+      <c r="S54" s="50" t="str">
+        <f>IF(Y54="","",IF(Y54&lt;=0,"達成済み",IF(Y54&lt;60,Y54&amp;"秒",INT(Y54/60)&amp;"分"&amp;TEXT(MOD(Y54,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T54" s="26" t="str">
+        <f>IF(C54="","",D54/設定!$C$27-C54)</f>
+        <v/>
+      </c>
+      <c r="X54">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y54" t="str">
+        <f>IF(C54="","",ROUND(G54-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A55" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -51418,7 +52824,7 @@
         <v/>
       </c>
       <c r="L55" s="22" t="str">
-        <f>IF(K55="","",IF(AND(K55&lt;&gt;"",ISNUMBER(入力!$J$58),入力!$J$58&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$58))*(K55-$T$3),K55))</f>
+        <f>IF(K55="","",IF(AND(K55&lt;&gt;"",ISNUMBER(入力!$J$58),入力!$J$58&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$58))*(K55-$W$3),K55))</f>
         <v/>
       </c>
       <c r="M55" s="22" t="str">
@@ -51445,12 +52851,24 @@
         <f>IF(C55="","",設定!$C$27*C55/D55*100)</f>
         <v/>
       </c>
-      <c r="U55">
+      <c r="S55" s="50" t="str">
+        <f>IF(Y55="","",IF(Y55&lt;=0,"達成済み",IF(Y55&lt;60,Y55&amp;"秒",INT(Y55/60)&amp;"分"&amp;TEXT(MOD(Y55,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T55" s="26" t="str">
+        <f>IF(C55="","",D55/設定!$C$27-C55)</f>
+        <v/>
+      </c>
+      <c r="X55">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y55" t="str">
+        <f>IF(C55="","",ROUND(G55-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A56" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -51496,7 +52914,7 @@
         <v/>
       </c>
       <c r="L56" s="22" t="str">
-        <f>IF(K56="","",IF(AND(K56&lt;&gt;"",ISNUMBER(入力!$J$59),入力!$J$59&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$59))*(K56-$T$3),K56))</f>
+        <f>IF(K56="","",IF(AND(K56&lt;&gt;"",ISNUMBER(入力!$J$59),入力!$J$59&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$59))*(K56-$W$3),K56))</f>
         <v/>
       </c>
       <c r="M56" s="22" t="str">
@@ -51523,12 +52941,24 @@
         <f>IF(C56="","",設定!$C$27*C56/D56*100)</f>
         <v/>
       </c>
-      <c r="U56">
+      <c r="S56" s="50" t="str">
+        <f>IF(Y56="","",IF(Y56&lt;=0,"達成済み",IF(Y56&lt;60,Y56&amp;"秒",INT(Y56/60)&amp;"分"&amp;TEXT(MOD(Y56,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T56" s="26" t="str">
+        <f>IF(C56="","",D56/設定!$C$27-C56)</f>
+        <v/>
+      </c>
+      <c r="X56">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y56" t="str">
+        <f>IF(C56="","",ROUND(G56-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A57" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -51574,7 +53004,7 @@
         <v/>
       </c>
       <c r="L57" s="22" t="str">
-        <f>IF(K57="","",IF(AND(K57&lt;&gt;"",ISNUMBER(入力!$J$60),入力!$J$60&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$60))*(K57-$T$3),K57))</f>
+        <f>IF(K57="","",IF(AND(K57&lt;&gt;"",ISNUMBER(入力!$J$60),入力!$J$60&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$60))*(K57-$W$3),K57))</f>
         <v/>
       </c>
       <c r="M57" s="22" t="str">
@@ -51601,12 +53031,24 @@
         <f>IF(C57="","",設定!$C$27*C57/D57*100)</f>
         <v/>
       </c>
-      <c r="U57">
+      <c r="S57" s="50" t="str">
+        <f>IF(Y57="","",IF(Y57&lt;=0,"達成済み",IF(Y57&lt;60,Y57&amp;"秒",INT(Y57/60)&amp;"分"&amp;TEXT(MOD(Y57,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T57" s="26" t="str">
+        <f>IF(C57="","",D57/設定!$C$27-C57)</f>
+        <v/>
+      </c>
+      <c r="X57">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y57" t="str">
+        <f>IF(C57="","",ROUND(G57-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A58" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -51652,7 +53094,7 @@
         <v/>
       </c>
       <c r="L58" s="22" t="str">
-        <f>IF(K58="","",IF(AND(K58&lt;&gt;"",ISNUMBER(入力!$J$61),入力!$J$61&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$61))*(K58-$T$3),K58))</f>
+        <f>IF(K58="","",IF(AND(K58&lt;&gt;"",ISNUMBER(入力!$J$61),入力!$J$61&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$61))*(K58-$W$3),K58))</f>
         <v/>
       </c>
       <c r="M58" s="22" t="str">
@@ -51679,12 +53121,24 @@
         <f>IF(C58="","",設定!$C$27*C58/D58*100)</f>
         <v/>
       </c>
-      <c r="U58">
+      <c r="S58" s="50" t="str">
+        <f>IF(Y58="","",IF(Y58&lt;=0,"達成済み",IF(Y58&lt;60,Y58&amp;"秒",INT(Y58/60)&amp;"分"&amp;TEXT(MOD(Y58,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T58" s="26" t="str">
+        <f>IF(C58="","",D58/設定!$C$27-C58)</f>
+        <v/>
+      </c>
+      <c r="X58">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y58" t="str">
+        <f>IF(C58="","",ROUND(G58-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A59" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -51730,7 +53184,7 @@
         <v/>
       </c>
       <c r="L59" s="22" t="str">
-        <f>IF(K59="","",IF(AND(K59&lt;&gt;"",ISNUMBER(入力!$J$62),入力!$J$62&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$62))*(K59-$T$3),K59))</f>
+        <f>IF(K59="","",IF(AND(K59&lt;&gt;"",ISNUMBER(入力!$J$62),入力!$J$62&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$62))*(K59-$W$3),K59))</f>
         <v/>
       </c>
       <c r="M59" s="22" t="str">
@@ -51757,12 +53211,24 @@
         <f>IF(C59="","",設定!$C$27*C59/D59*100)</f>
         <v/>
       </c>
-      <c r="U59">
+      <c r="S59" s="50" t="str">
+        <f>IF(Y59="","",IF(Y59&lt;=0,"達成済み",IF(Y59&lt;60,Y59&amp;"秒",INT(Y59/60)&amp;"分"&amp;TEXT(MOD(Y59,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T59" s="26" t="str">
+        <f>IF(C59="","",D59/設定!$C$27-C59)</f>
+        <v/>
+      </c>
+      <c r="X59">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y59" t="str">
+        <f>IF(C59="","",ROUND(G59-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A60" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -51808,7 +53274,7 @@
         <v/>
       </c>
       <c r="L60" s="22" t="str">
-        <f>IF(K60="","",IF(AND(K60&lt;&gt;"",ISNUMBER(入力!$J$63),入力!$J$63&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$63))*(K60-$T$3),K60))</f>
+        <f>IF(K60="","",IF(AND(K60&lt;&gt;"",ISNUMBER(入力!$J$63),入力!$J$63&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$63))*(K60-$W$3),K60))</f>
         <v/>
       </c>
       <c r="M60" s="22" t="str">
@@ -51835,12 +53301,24 @@
         <f>IF(C60="","",設定!$C$27*C60/D60*100)</f>
         <v/>
       </c>
-      <c r="U60">
+      <c r="S60" s="50" t="str">
+        <f>IF(Y60="","",IF(Y60&lt;=0,"達成済み",IF(Y60&lt;60,Y60&amp;"秒",INT(Y60/60)&amp;"分"&amp;TEXT(MOD(Y60,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T60" s="26" t="str">
+        <f>IF(C60="","",D60/設定!$C$27-C60)</f>
+        <v/>
+      </c>
+      <c r="X60">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y60" t="str">
+        <f>IF(C60="","",ROUND(G60-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A61" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -51886,7 +53364,7 @@
         <v/>
       </c>
       <c r="L61" s="22" t="str">
-        <f>IF(K61="","",IF(AND(K61&lt;&gt;"",ISNUMBER(入力!$J$64),入力!$J$64&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$64))*(K61-$T$3),K61))</f>
+        <f>IF(K61="","",IF(AND(K61&lt;&gt;"",ISNUMBER(入力!$J$64),入力!$J$64&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$64))*(K61-$W$3),K61))</f>
         <v/>
       </c>
       <c r="M61" s="22" t="str">
@@ -51913,12 +53391,24 @@
         <f>IF(C61="","",設定!$C$27*C61/D61*100)</f>
         <v/>
       </c>
-      <c r="U61">
+      <c r="S61" s="50" t="str">
+        <f>IF(Y61="","",IF(Y61&lt;=0,"達成済み",IF(Y61&lt;60,Y61&amp;"秒",INT(Y61/60)&amp;"分"&amp;TEXT(MOD(Y61,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T61" s="26" t="str">
+        <f>IF(C61="","",D61/設定!$C$27-C61)</f>
+        <v/>
+      </c>
+      <c r="X61">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y61" t="str">
+        <f>IF(C61="","",ROUND(G61-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A62" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -51964,7 +53454,7 @@
         <v/>
       </c>
       <c r="L62" s="22" t="str">
-        <f>IF(K62="","",IF(AND(K62&lt;&gt;"",ISNUMBER(入力!$J$65),入力!$J$65&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$65))*(K62-$T$3),K62))</f>
+        <f>IF(K62="","",IF(AND(K62&lt;&gt;"",ISNUMBER(入力!$J$65),入力!$J$65&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$65))*(K62-$W$3),K62))</f>
         <v/>
       </c>
       <c r="M62" s="22" t="str">
@@ -51991,12 +53481,24 @@
         <f>IF(C62="","",設定!$C$27*C62/D62*100)</f>
         <v/>
       </c>
-      <c r="U62">
+      <c r="S62" s="50" t="str">
+        <f>IF(Y62="","",IF(Y62&lt;=0,"達成済み",IF(Y62&lt;60,Y62&amp;"秒",INT(Y62/60)&amp;"分"&amp;TEXT(MOD(Y62,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T62" s="26" t="str">
+        <f>IF(C62="","",D62/設定!$C$27-C62)</f>
+        <v/>
+      </c>
+      <c r="X62">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y62" t="str">
+        <f>IF(C62="","",ROUND(G62-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A63" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -52042,7 +53544,7 @@
         <v/>
       </c>
       <c r="L63" s="22" t="str">
-        <f>IF(K63="","",IF(AND(K63&lt;&gt;"",ISNUMBER(入力!$J$66),入力!$J$66&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$66))*(K63-$T$3),K63))</f>
+        <f>IF(K63="","",IF(AND(K63&lt;&gt;"",ISNUMBER(入力!$J$66),入力!$J$66&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$66))*(K63-$W$3),K63))</f>
         <v/>
       </c>
       <c r="M63" s="22" t="str">
@@ -52069,12 +53571,24 @@
         <f>IF(C63="","",設定!$C$27*C63/D63*100)</f>
         <v/>
       </c>
-      <c r="U63">
+      <c r="S63" s="50" t="str">
+        <f>IF(Y63="","",IF(Y63&lt;=0,"達成済み",IF(Y63&lt;60,Y63&amp;"秒",INT(Y63/60)&amp;"分"&amp;TEXT(MOD(Y63,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T63" s="26" t="str">
+        <f>IF(C63="","",D63/設定!$C$27-C63)</f>
+        <v/>
+      </c>
+      <c r="X63">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y63" t="str">
+        <f>IF(C63="","",ROUND(G63-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A64" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -52120,7 +53634,7 @@
         <v/>
       </c>
       <c r="L64" s="22" t="str">
-        <f>IF(K64="","",IF(AND(K64&lt;&gt;"",ISNUMBER(入力!$J$67),入力!$J$67&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$67))*(K64-$T$3),K64))</f>
+        <f>IF(K64="","",IF(AND(K64&lt;&gt;"",ISNUMBER(入力!$J$67),入力!$J$67&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$67))*(K64-$W$3),K64))</f>
         <v/>
       </c>
       <c r="M64" s="22" t="str">
@@ -52147,12 +53661,24 @@
         <f>IF(C64="","",設定!$C$27*C64/D64*100)</f>
         <v/>
       </c>
-      <c r="U64">
+      <c r="S64" s="50" t="str">
+        <f>IF(Y64="","",IF(Y64&lt;=0,"達成済み",IF(Y64&lt;60,Y64&amp;"秒",INT(Y64/60)&amp;"分"&amp;TEXT(MOD(Y64,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T64" s="26" t="str">
+        <f>IF(C64="","",D64/設定!$C$27-C64)</f>
+        <v/>
+      </c>
+      <c r="X64">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y64" t="str">
+        <f>IF(C64="","",ROUND(G64-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A65" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -52198,7 +53724,7 @@
         <v/>
       </c>
       <c r="L65" s="22" t="str">
-        <f>IF(K65="","",IF(AND(K65&lt;&gt;"",ISNUMBER(入力!$J$68),入力!$J$68&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$68))*(K65-$T$3),K65))</f>
+        <f>IF(K65="","",IF(AND(K65&lt;&gt;"",ISNUMBER(入力!$J$68),入力!$J$68&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$68))*(K65-$W$3),K65))</f>
         <v/>
       </c>
       <c r="M65" s="22" t="str">
@@ -52225,12 +53751,24 @@
         <f>IF(C65="","",設定!$C$27*C65/D65*100)</f>
         <v/>
       </c>
-      <c r="U65">
+      <c r="S65" s="50" t="str">
+        <f>IF(Y65="","",IF(Y65&lt;=0,"達成済み",IF(Y65&lt;60,Y65&amp;"秒",INT(Y65/60)&amp;"分"&amp;TEXT(MOD(Y65,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T65" s="26" t="str">
+        <f>IF(C65="","",D65/設定!$C$27-C65)</f>
+        <v/>
+      </c>
+      <c r="X65">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="Y65" t="str">
+        <f>IF(C65="","",ROUND(G65-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A66" s="48" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -52276,7 +53814,7 @@
         <v/>
       </c>
       <c r="L66" s="22" t="str">
-        <f>IF(K66="","",IF(AND(K66&lt;&gt;"",ISNUMBER(入力!$J$69),入力!$J$69&gt;0),$T$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$69))*(K66-$T$3),K66))</f>
+        <f>IF(K66="","",IF(AND(K66&lt;&gt;"",ISNUMBER(入力!$J$69),入力!$J$69&gt;0),$W$3+(設定!$D$17/(設定!$D$17+設定!$D$18/入力!$J$69))*(K66-$W$3),K66))</f>
         <v/>
       </c>
       <c r="M66" s="22" t="str">
@@ -52303,14 +53841,26 @@
         <f>IF(C66="","",設定!$C$27*C66/D66*100)</f>
         <v/>
       </c>
-      <c r="U66">
+      <c r="S66" s="50" t="str">
+        <f>IF(Y66="","",IF(Y66&lt;=0,"達成済み",IF(Y66&lt;60,Y66&amp;"秒",INT(Y66/60)&amp;"分"&amp;TEXT(MOD(Y66,60),"00")&amp;"秒")))</f>
+        <v/>
+      </c>
+      <c r="T66" s="26" t="str">
+        <f>IF(C66="","",D66/設定!$C$27-C66)</f>
+        <v/>
+      </c>
+      <c r="X66">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
+      <c r="Y66" t="str">
+        <f>IF(C66="","",ROUND(G66-設定!$C$27*60,0))</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="34"/>
-  <conditionalFormatting sqref="A7:R66">
+  <conditionalFormatting sqref="A7:T66">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>$O7="◎達成"</formula>
     </cfRule>
@@ -63758,11 +65308,11 @@
         <v>146.66177155707118</v>
       </c>
       <c r="E8" s="22">
-        <f>IF(C8="","",C8-ピッキング!$T$3)</f>
+        <f>IF(C8="","",C8-ピッキング!$W$3)</f>
         <v>24.437291214163963</v>
       </c>
       <c r="F8" s="22">
-        <f>IF(D8="","",D8-梱包!$T$3)</f>
+        <f>IF(D8="","",D8-梱包!$W$3)</f>
         <v>37.218050976113702</v>
       </c>
       <c r="G8" s="50" t="str">
@@ -63788,11 +65338,11 @@
         <v>96.604008968531502</v>
       </c>
       <c r="E9" s="22">
-        <f>IF(C9="","",C9-ピッキング!$T$3)</f>
+        <f>IF(C9="","",C9-ピッキング!$W$3)</f>
         <v>7.0113310314659572</v>
       </c>
       <c r="F9" s="22">
-        <f>IF(D9="","",D9-梱包!$T$3)</f>
+        <f>IF(D9="","",D9-梱包!$W$3)</f>
         <v>-12.839711612425972</v>
       </c>
       <c r="G9" s="50" t="str">
@@ -63818,11 +65368,11 @@
         <v>131.04490021102978</v>
       </c>
       <c r="E10" s="22">
-        <f>IF(C10="","",C10-ピッキング!$T$3)</f>
+        <f>IF(C10="","",C10-ピッキング!$W$3)</f>
         <v>18.079594229522868</v>
       </c>
       <c r="F10" s="22">
-        <f>IF(D10="","",D10-梱包!$T$3)</f>
+        <f>IF(D10="","",D10-梱包!$W$3)</f>
         <v>21.601179630072309</v>
       </c>
       <c r="G10" s="50" t="str">
@@ -63848,11 +65398,11 @@
         <v>128.1824773344137</v>
       </c>
       <c r="E11" s="22">
-        <f>IF(C11="","",C11-ピッキング!$T$3)</f>
+        <f>IF(C11="","",C11-ピッキング!$W$3)</f>
         <v>17.145274134618148</v>
       </c>
       <c r="F11" s="22">
-        <f>IF(D11="","",D11-梱包!$T$3)</f>
+        <f>IF(D11="","",D11-梱包!$W$3)</f>
         <v>18.738756753456229</v>
       </c>
       <c r="G11" s="50" t="str">
@@ -63878,11 +65428,11 @@
         <v/>
       </c>
       <c r="E12" s="22">
-        <f>IF(C12="","",C12-ピッキング!$T$3)</f>
+        <f>IF(C12="","",C12-ピッキング!$W$3)</f>
         <v>8.6867294231761178</v>
       </c>
       <c r="F12" s="22" t="str">
-        <f>IF(D12="","",D12-梱包!$T$3)</f>
+        <f>IF(D12="","",D12-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G12" s="50" t="str">
@@ -63908,11 +65458,11 @@
         <v>82.508009548320643</v>
       </c>
       <c r="E13" s="22">
-        <f>IF(C13="","",C13-ピッキング!$T$3)</f>
+        <f>IF(C13="","",C13-ピッキング!$W$3)</f>
         <v>6.6607990776026753</v>
       </c>
       <c r="F13" s="22">
-        <f>IF(D13="","",D13-梱包!$T$3)</f>
+        <f>IF(D13="","",D13-梱包!$W$3)</f>
         <v>-26.935711032636831</v>
       </c>
       <c r="G13" s="50" t="str">
@@ -63938,11 +65488,11 @@
         <v>89.76235104145006</v>
       </c>
       <c r="E14" s="22">
-        <f>IF(C14="","",C14-ピッキング!$T$3)</f>
+        <f>IF(C14="","",C14-ピッキング!$W$3)</f>
         <v>5.5993024581563873</v>
       </c>
       <c r="F14" s="22">
-        <f>IF(D14="","",D14-梱包!$T$3)</f>
+        <f>IF(D14="","",D14-梱包!$W$3)</f>
         <v>-19.681369539507415</v>
       </c>
       <c r="G14" s="50" t="str">
@@ -63968,11 +65518,11 @@
         <v>120.21334891697963</v>
       </c>
       <c r="E15" s="22">
-        <f>IF(C15="","",C15-ピッキング!$T$3)</f>
+        <f>IF(C15="","",C15-ピッキング!$W$3)</f>
         <v>3.8889665684425268</v>
       </c>
       <c r="F15" s="22">
-        <f>IF(D15="","",D15-梱包!$T$3)</f>
+        <f>IF(D15="","",D15-梱包!$W$3)</f>
         <v>10.769628336022151</v>
       </c>
       <c r="G15" s="50" t="str">
@@ -63998,11 +65548,11 @@
         <v>95.030981294859927</v>
       </c>
       <c r="E16" s="22">
-        <f>IF(C16="","",C16-ピッキング!$T$3)</f>
+        <f>IF(C16="","",C16-ピッキング!$W$3)</f>
         <v>2.922596627308053</v>
       </c>
       <c r="F16" s="22">
-        <f>IF(D16="","",D16-梱包!$T$3)</f>
+        <f>IF(D16="","",D16-梱包!$W$3)</f>
         <v>-14.412739286097548</v>
       </c>
       <c r="G16" s="50" t="str">
@@ -64028,11 +65578,11 @@
         <v>86.587819371053342</v>
       </c>
       <c r="E17" s="22">
-        <f>IF(C17="","",C17-ピッキング!$T$3)</f>
+        <f>IF(C17="","",C17-ピッキング!$W$3)</f>
         <v>2.6814242562379746</v>
       </c>
       <c r="F17" s="22">
-        <f>IF(D17="","",D17-梱包!$T$3)</f>
+        <f>IF(D17="","",D17-梱包!$W$3)</f>
         <v>-22.855901209904133</v>
       </c>
       <c r="G17" s="50" t="str">
@@ -64058,11 +65608,11 @@
         <v>160.21330038970882</v>
       </c>
       <c r="E18" s="22">
-        <f>IF(C18="","",C18-ピッキング!$T$3)</f>
+        <f>IF(C18="","",C18-ピッキング!$W$3)</f>
         <v>2.2322535269012036</v>
       </c>
       <c r="F18" s="22">
-        <f>IF(D18="","",D18-梱包!$T$3)</f>
+        <f>IF(D18="","",D18-梱包!$W$3)</f>
         <v>50.769579808751345</v>
       </c>
       <c r="G18" s="50" t="str">
@@ -64088,11 +65638,11 @@
         <v>133.25785675591538</v>
       </c>
       <c r="E19" s="22">
-        <f>IF(C19="","",C19-ピッキング!$T$3)</f>
+        <f>IF(C19="","",C19-ピッキング!$W$3)</f>
         <v>-0.39790061674973742</v>
       </c>
       <c r="F19" s="22">
-        <f>IF(D19="","",D19-梱包!$T$3)</f>
+        <f>IF(D19="","",D19-梱包!$W$3)</f>
         <v>23.814136174957909</v>
       </c>
       <c r="G19" s="50" t="str">
@@ -64118,11 +65668,11 @@
         <v>81.8195904305488</v>
       </c>
       <c r="E20" s="22">
-        <f>IF(C20="","",C20-ピッキング!$T$3)</f>
+        <f>IF(C20="","",C20-ピッキング!$W$3)</f>
         <v>-0.49607990964638304</v>
       </c>
       <c r="F20" s="22">
-        <f>IF(D20="","",D20-梱包!$T$3)</f>
+        <f>IF(D20="","",D20-梱包!$W$3)</f>
         <v>-27.624130150408675</v>
       </c>
       <c r="G20" s="50" t="str">
@@ -64148,11 +65698,11 @@
         <v/>
       </c>
       <c r="E21" s="22">
-        <f>IF(C21="","",C21-ピッキング!$T$3)</f>
+        <f>IF(C21="","",C21-ピッキング!$W$3)</f>
         <v>-1.0667589950255376</v>
       </c>
       <c r="F21" s="22" t="str">
-        <f>IF(D21="","",D21-梱包!$T$3)</f>
+        <f>IF(D21="","",D21-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G21" s="50" t="str">
@@ -64178,11 +65728,11 @@
         <v>60.246292066240983</v>
       </c>
       <c r="E22" s="22">
-        <f>IF(C22="","",C22-ピッキング!$T$3)</f>
+        <f>IF(C22="","",C22-ピッキング!$W$3)</f>
         <v>-1.8182763534614992</v>
       </c>
       <c r="F22" s="22">
-        <f>IF(D22="","",D22-梱包!$T$3)</f>
+        <f>IF(D22="","",D22-梱包!$W$3)</f>
         <v>-49.197428514716492</v>
       </c>
       <c r="G22" s="50" t="str">
@@ -64208,11 +65758,11 @@
         <v>115.10131008792217</v>
       </c>
       <c r="E23" s="22">
-        <f>IF(C23="","",C23-ピッキング!$T$3)</f>
+        <f>IF(C23="","",C23-ピッキング!$W$3)</f>
         <v>-2.062523970885394</v>
       </c>
       <c r="F23" s="22">
-        <f>IF(D23="","",D23-梱包!$T$3)</f>
+        <f>IF(D23="","",D23-梱包!$W$3)</f>
         <v>5.6575895069646975</v>
       </c>
       <c r="G23" s="50" t="str">
@@ -64238,11 +65788,11 @@
         <v>74.647652818461978</v>
       </c>
       <c r="E24" s="22">
-        <f>IF(C24="","",C24-ピッキング!$T$3)</f>
+        <f>IF(C24="","",C24-ピッキング!$W$3)</f>
         <v>-2.051714391405369</v>
       </c>
       <c r="F24" s="22">
-        <f>IF(D24="","",D24-梱包!$T$3)</f>
+        <f>IF(D24="","",D24-梱包!$W$3)</f>
         <v>-34.796067762495497</v>
       </c>
       <c r="G24" s="50" t="str">
@@ -64268,11 +65818,11 @@
         <v/>
       </c>
       <c r="E25" s="22">
-        <f>IF(C25="","",C25-ピッキング!$T$3)</f>
+        <f>IF(C25="","",C25-ピッキング!$W$3)</f>
         <v>-3.3631863186712252</v>
       </c>
       <c r="F25" s="22" t="str">
-        <f>IF(D25="","",D25-梱包!$T$3)</f>
+        <f>IF(D25="","",D25-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G25" s="50" t="str">
@@ -64298,11 +65848,11 @@
         <v>98.813177530341235</v>
       </c>
       <c r="E26" s="22">
-        <f>IF(C26="","",C26-ピッキング!$T$3)</f>
+        <f>IF(C26="","",C26-ピッキング!$W$3)</f>
         <v>-3.5545167724201434</v>
       </c>
       <c r="F26" s="22">
-        <f>IF(D26="","",D26-梱包!$T$3)</f>
+        <f>IF(D26="","",D26-梱包!$W$3)</f>
         <v>-10.630543050616239</v>
       </c>
       <c r="G26" s="50" t="str">
@@ -64328,11 +65878,11 @@
         <v/>
       </c>
       <c r="E27" s="22">
-        <f>IF(C27="","",C27-ピッキング!$T$3)</f>
+        <f>IF(C27="","",C27-ピッキング!$W$3)</f>
         <v>-7.946214363132313</v>
       </c>
       <c r="F27" s="22" t="str">
-        <f>IF(D27="","",D27-梱包!$T$3)</f>
+        <f>IF(D27="","",D27-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G27" s="50" t="str">
@@ -64358,11 +65908,11 @@
         <v/>
       </c>
       <c r="E28" s="22">
-        <f>IF(C28="","",C28-ピッキング!$T$3)</f>
+        <f>IF(C28="","",C28-ピッキング!$W$3)</f>
         <v>-9.3216595231954358</v>
       </c>
       <c r="F28" s="22" t="str">
-        <f>IF(D28="","",D28-梱包!$T$3)</f>
+        <f>IF(D28="","",D28-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G28" s="50" t="str">
@@ -64388,11 +65938,11 @@
         <v/>
       </c>
       <c r="E29" s="22">
-        <f>IF(C29="","",C29-ピッキング!$T$3)</f>
+        <f>IF(C29="","",C29-ピッキング!$W$3)</f>
         <v>-9.186134887989482</v>
       </c>
       <c r="F29" s="22" t="str">
-        <f>IF(D29="","",D29-梱包!$T$3)</f>
+        <f>IF(D29="","",D29-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G29" s="50" t="str">
@@ -64418,11 +65968,11 @@
         <v>102.27473325768686</v>
       </c>
       <c r="E30" s="22">
-        <f>IF(C30="","",C30-ピッキング!$T$3)</f>
+        <f>IF(C30="","",C30-ピッキング!$W$3)</f>
         <v>-11.622223393628843</v>
       </c>
       <c r="F30" s="22">
-        <f>IF(D30="","",D30-梱包!$T$3)</f>
+        <f>IF(D30="","",D30-梱包!$W$3)</f>
         <v>-7.1689873232706134</v>
       </c>
       <c r="G30" s="50" t="str">
@@ -64448,11 +65998,11 @@
         <v>69.508553165647555</v>
       </c>
       <c r="E31" s="22">
-        <f>IF(C31="","",C31-ピッキング!$T$3)</f>
+        <f>IF(C31="","",C31-ピッキング!$W$3)</f>
         <v>-11.836996433921215</v>
       </c>
       <c r="F31" s="22">
-        <f>IF(D31="","",D31-梱包!$T$3)</f>
+        <f>IF(D31="","",D31-梱包!$W$3)</f>
         <v>-39.93516741530992</v>
       </c>
       <c r="G31" s="50" t="str">
@@ -64478,11 +66028,11 @@
         <v/>
       </c>
       <c r="E32" s="22">
-        <f>IF(C32="","",C32-ピッキング!$T$3)</f>
+        <f>IF(C32="","",C32-ピッキング!$W$3)</f>
         <v>-13.684409094684028</v>
       </c>
       <c r="F32" s="22" t="str">
-        <f>IF(D32="","",D32-梱包!$T$3)</f>
+        <f>IF(D32="","",D32-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G32" s="50" t="str">
@@ -64508,11 +66058,11 @@
         <v/>
       </c>
       <c r="E33" s="22">
-        <f>IF(C33="","",C33-ピッキング!$T$3)</f>
+        <f>IF(C33="","",C33-ピッキング!$W$3)</f>
         <v>-14.063939437120581</v>
       </c>
       <c r="F33" s="22" t="str">
-        <f>IF(D33="","",D33-梱包!$T$3)</f>
+        <f>IF(D33="","",D33-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G33" s="50" t="str">
@@ -64538,11 +66088,11 @@
         <v/>
       </c>
       <c r="E34" s="22">
-        <f>IF(C34="","",C34-ピッキング!$T$3)</f>
+        <f>IF(C34="","",C34-ピッキング!$W$3)</f>
         <v>-15.079861717927599</v>
       </c>
       <c r="F34" s="22" t="str">
-        <f>IF(D34="","",D34-梱包!$T$3)</f>
+        <f>IF(D34="","",D34-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G34" s="50" t="str">
@@ -64568,11 +66118,11 @@
         <v/>
       </c>
       <c r="E35" s="22">
-        <f>IF(C35="","",C35-ピッキング!$T$3)</f>
+        <f>IF(C35="","",C35-ピッキング!$W$3)</f>
         <v>-16.67396291004772</v>
       </c>
       <c r="F35" s="22" t="str">
-        <f>IF(D35="","",D35-梱包!$T$3)</f>
+        <f>IF(D35="","",D35-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G35" s="50" t="str">
@@ -64598,11 +66148,11 @@
         <v>126.82484924085423</v>
       </c>
       <c r="E36" s="22">
-        <f>IF(C36="","",C36-ピッキング!$T$3)</f>
+        <f>IF(C36="","",C36-ピッキング!$W$3)</f>
         <v>-17.058830370947391</v>
       </c>
       <c r="F36" s="22">
-        <f>IF(D36="","",D36-梱包!$T$3)</f>
+        <f>IF(D36="","",D36-梱包!$W$3)</f>
         <v>17.38112865989676</v>
       </c>
       <c r="G36" s="50" t="str">
@@ -64628,11 +66178,11 @@
         <v/>
       </c>
       <c r="E37" s="22" t="str">
-        <f>IF(C37="","",C37-ピッキング!$T$3)</f>
+        <f>IF(C37="","",C37-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F37" s="22" t="str">
-        <f>IF(D37="","",D37-梱包!$T$3)</f>
+        <f>IF(D37="","",D37-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G37" s="50" t="str">
@@ -64658,11 +66208,11 @@
         <v/>
       </c>
       <c r="E38" s="22" t="str">
-        <f>IF(C38="","",C38-ピッキング!$T$3)</f>
+        <f>IF(C38="","",C38-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F38" s="22" t="str">
-        <f>IF(D38="","",D38-梱包!$T$3)</f>
+        <f>IF(D38="","",D38-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G38" s="50" t="str">
@@ -64688,11 +66238,11 @@
         <v/>
       </c>
       <c r="E39" s="22" t="str">
-        <f>IF(C39="","",C39-ピッキング!$T$3)</f>
+        <f>IF(C39="","",C39-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F39" s="22" t="str">
-        <f>IF(D39="","",D39-梱包!$T$3)</f>
+        <f>IF(D39="","",D39-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G39" s="50" t="str">
@@ -64718,11 +66268,11 @@
         <v/>
       </c>
       <c r="E40" s="22" t="str">
-        <f>IF(C40="","",C40-ピッキング!$T$3)</f>
+        <f>IF(C40="","",C40-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F40" s="22" t="str">
-        <f>IF(D40="","",D40-梱包!$T$3)</f>
+        <f>IF(D40="","",D40-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G40" s="50" t="str">
@@ -64748,11 +66298,11 @@
         <v/>
       </c>
       <c r="E41" s="22" t="str">
-        <f>IF(C41="","",C41-ピッキング!$T$3)</f>
+        <f>IF(C41="","",C41-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F41" s="22" t="str">
-        <f>IF(D41="","",D41-梱包!$T$3)</f>
+        <f>IF(D41="","",D41-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G41" s="50" t="str">
@@ -64778,11 +66328,11 @@
         <v/>
       </c>
       <c r="E42" s="22" t="str">
-        <f>IF(C42="","",C42-ピッキング!$T$3)</f>
+        <f>IF(C42="","",C42-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F42" s="22" t="str">
-        <f>IF(D42="","",D42-梱包!$T$3)</f>
+        <f>IF(D42="","",D42-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G42" s="50" t="str">
@@ -64808,11 +66358,11 @@
         <v/>
       </c>
       <c r="E43" s="22" t="str">
-        <f>IF(C43="","",C43-ピッキング!$T$3)</f>
+        <f>IF(C43="","",C43-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F43" s="22" t="str">
-        <f>IF(D43="","",D43-梱包!$T$3)</f>
+        <f>IF(D43="","",D43-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G43" s="50" t="str">
@@ -64838,11 +66388,11 @@
         <v/>
       </c>
       <c r="E44" s="22" t="str">
-        <f>IF(C44="","",C44-ピッキング!$T$3)</f>
+        <f>IF(C44="","",C44-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F44" s="22" t="str">
-        <f>IF(D44="","",D44-梱包!$T$3)</f>
+        <f>IF(D44="","",D44-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G44" s="50" t="str">
@@ -64868,11 +66418,11 @@
         <v/>
       </c>
       <c r="E45" s="22" t="str">
-        <f>IF(C45="","",C45-ピッキング!$T$3)</f>
+        <f>IF(C45="","",C45-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F45" s="22" t="str">
-        <f>IF(D45="","",D45-梱包!$T$3)</f>
+        <f>IF(D45="","",D45-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G45" s="50" t="str">
@@ -64898,11 +66448,11 @@
         <v/>
       </c>
       <c r="E46" s="22" t="str">
-        <f>IF(C46="","",C46-ピッキング!$T$3)</f>
+        <f>IF(C46="","",C46-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F46" s="22" t="str">
-        <f>IF(D46="","",D46-梱包!$T$3)</f>
+        <f>IF(D46="","",D46-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G46" s="50" t="str">
@@ -64928,11 +66478,11 @@
         <v/>
       </c>
       <c r="E47" s="22" t="str">
-        <f>IF(C47="","",C47-ピッキング!$T$3)</f>
+        <f>IF(C47="","",C47-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F47" s="22" t="str">
-        <f>IF(D47="","",D47-梱包!$T$3)</f>
+        <f>IF(D47="","",D47-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G47" s="50" t="str">
@@ -64958,11 +66508,11 @@
         <v/>
       </c>
       <c r="E48" s="22" t="str">
-        <f>IF(C48="","",C48-ピッキング!$T$3)</f>
+        <f>IF(C48="","",C48-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F48" s="22" t="str">
-        <f>IF(D48="","",D48-梱包!$T$3)</f>
+        <f>IF(D48="","",D48-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G48" s="50" t="str">
@@ -64988,11 +66538,11 @@
         <v/>
       </c>
       <c r="E49" s="22" t="str">
-        <f>IF(C49="","",C49-ピッキング!$T$3)</f>
+        <f>IF(C49="","",C49-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F49" s="22" t="str">
-        <f>IF(D49="","",D49-梱包!$T$3)</f>
+        <f>IF(D49="","",D49-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G49" s="50" t="str">
@@ -65018,11 +66568,11 @@
         <v/>
       </c>
       <c r="E50" s="22" t="str">
-        <f>IF(C50="","",C50-ピッキング!$T$3)</f>
+        <f>IF(C50="","",C50-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F50" s="22" t="str">
-        <f>IF(D50="","",D50-梱包!$T$3)</f>
+        <f>IF(D50="","",D50-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G50" s="50" t="str">
@@ -65048,11 +66598,11 @@
         <v/>
       </c>
       <c r="E51" s="22" t="str">
-        <f>IF(C51="","",C51-ピッキング!$T$3)</f>
+        <f>IF(C51="","",C51-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F51" s="22" t="str">
-        <f>IF(D51="","",D51-梱包!$T$3)</f>
+        <f>IF(D51="","",D51-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G51" s="50" t="str">
@@ -65078,11 +66628,11 @@
         <v/>
       </c>
       <c r="E52" s="22" t="str">
-        <f>IF(C52="","",C52-ピッキング!$T$3)</f>
+        <f>IF(C52="","",C52-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F52" s="22" t="str">
-        <f>IF(D52="","",D52-梱包!$T$3)</f>
+        <f>IF(D52="","",D52-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G52" s="50" t="str">
@@ -65108,11 +66658,11 @@
         <v/>
       </c>
       <c r="E53" s="22" t="str">
-        <f>IF(C53="","",C53-ピッキング!$T$3)</f>
+        <f>IF(C53="","",C53-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F53" s="22" t="str">
-        <f>IF(D53="","",D53-梱包!$T$3)</f>
+        <f>IF(D53="","",D53-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G53" s="50" t="str">
@@ -65138,11 +66688,11 @@
         <v/>
       </c>
       <c r="E54" s="22" t="str">
-        <f>IF(C54="","",C54-ピッキング!$T$3)</f>
+        <f>IF(C54="","",C54-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F54" s="22" t="str">
-        <f>IF(D54="","",D54-梱包!$T$3)</f>
+        <f>IF(D54="","",D54-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G54" s="50" t="str">
@@ -65168,11 +66718,11 @@
         <v/>
       </c>
       <c r="E55" s="22" t="str">
-        <f>IF(C55="","",C55-ピッキング!$T$3)</f>
+        <f>IF(C55="","",C55-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F55" s="22" t="str">
-        <f>IF(D55="","",D55-梱包!$T$3)</f>
+        <f>IF(D55="","",D55-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G55" s="50" t="str">
@@ -65198,11 +66748,11 @@
         <v/>
       </c>
       <c r="E56" s="22" t="str">
-        <f>IF(C56="","",C56-ピッキング!$T$3)</f>
+        <f>IF(C56="","",C56-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F56" s="22" t="str">
-        <f>IF(D56="","",D56-梱包!$T$3)</f>
+        <f>IF(D56="","",D56-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G56" s="50" t="str">
@@ -65228,11 +66778,11 @@
         <v/>
       </c>
       <c r="E57" s="22" t="str">
-        <f>IF(C57="","",C57-ピッキング!$T$3)</f>
+        <f>IF(C57="","",C57-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F57" s="22" t="str">
-        <f>IF(D57="","",D57-梱包!$T$3)</f>
+        <f>IF(D57="","",D57-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G57" s="50" t="str">
@@ -65258,11 +66808,11 @@
         <v/>
       </c>
       <c r="E58" s="22" t="str">
-        <f>IF(C58="","",C58-ピッキング!$T$3)</f>
+        <f>IF(C58="","",C58-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F58" s="22" t="str">
-        <f>IF(D58="","",D58-梱包!$T$3)</f>
+        <f>IF(D58="","",D58-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G58" s="50" t="str">
@@ -65288,11 +66838,11 @@
         <v/>
       </c>
       <c r="E59" s="22" t="str">
-        <f>IF(C59="","",C59-ピッキング!$T$3)</f>
+        <f>IF(C59="","",C59-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F59" s="22" t="str">
-        <f>IF(D59="","",D59-梱包!$T$3)</f>
+        <f>IF(D59="","",D59-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G59" s="50" t="str">
@@ -65318,11 +66868,11 @@
         <v/>
       </c>
       <c r="E60" s="22" t="str">
-        <f>IF(C60="","",C60-ピッキング!$T$3)</f>
+        <f>IF(C60="","",C60-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F60" s="22" t="str">
-        <f>IF(D60="","",D60-梱包!$T$3)</f>
+        <f>IF(D60="","",D60-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G60" s="50" t="str">
@@ -65348,11 +66898,11 @@
         <v/>
       </c>
       <c r="E61" s="22" t="str">
-        <f>IF(C61="","",C61-ピッキング!$T$3)</f>
+        <f>IF(C61="","",C61-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F61" s="22" t="str">
-        <f>IF(D61="","",D61-梱包!$T$3)</f>
+        <f>IF(D61="","",D61-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G61" s="50" t="str">
@@ -65378,11 +66928,11 @@
         <v/>
       </c>
       <c r="E62" s="22" t="str">
-        <f>IF(C62="","",C62-ピッキング!$T$3)</f>
+        <f>IF(C62="","",C62-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F62" s="22" t="str">
-        <f>IF(D62="","",D62-梱包!$T$3)</f>
+        <f>IF(D62="","",D62-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G62" s="50" t="str">
@@ -65408,11 +66958,11 @@
         <v/>
       </c>
       <c r="E63" s="22" t="str">
-        <f>IF(C63="","",C63-ピッキング!$T$3)</f>
+        <f>IF(C63="","",C63-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F63" s="22" t="str">
-        <f>IF(D63="","",D63-梱包!$T$3)</f>
+        <f>IF(D63="","",D63-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G63" s="50" t="str">
@@ -65438,11 +66988,11 @@
         <v/>
       </c>
       <c r="E64" s="22" t="str">
-        <f>IF(C64="","",C64-ピッキング!$T$3)</f>
+        <f>IF(C64="","",C64-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F64" s="22" t="str">
-        <f>IF(D64="","",D64-梱包!$T$3)</f>
+        <f>IF(D64="","",D64-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G64" s="50" t="str">
@@ -65468,11 +67018,11 @@
         <v/>
       </c>
       <c r="E65" s="22" t="str">
-        <f>IF(C65="","",C65-ピッキング!$T$3)</f>
+        <f>IF(C65="","",C65-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F65" s="22" t="str">
-        <f>IF(D65="","",D65-梱包!$T$3)</f>
+        <f>IF(D65="","",D65-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G65" s="50" t="str">
@@ -65498,11 +67048,11 @@
         <v/>
       </c>
       <c r="E66" s="22" t="str">
-        <f>IF(C66="","",C66-ピッキング!$T$3)</f>
+        <f>IF(C66="","",C66-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F66" s="22" t="str">
-        <f>IF(D66="","",D66-梱包!$T$3)</f>
+        <f>IF(D66="","",D66-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G66" s="50" t="str">
@@ -65528,11 +67078,11 @@
         <v/>
       </c>
       <c r="E67" s="22" t="str">
-        <f>IF(C67="","",C67-ピッキング!$T$3)</f>
+        <f>IF(C67="","",C67-ピッキング!$W$3)</f>
         <v/>
       </c>
       <c r="F67" s="22" t="str">
-        <f>IF(D67="","",D67-梱包!$T$3)</f>
+        <f>IF(D67="","",D67-梱包!$W$3)</f>
         <v/>
       </c>
       <c r="G67" s="50" t="str">

--- a/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
+++ b/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
@@ -20765,9 +20765,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tbl_PK" displayName="Tbl_PK" ref="A6:T66" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A6:T66"/>
-  <tableColumns count="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tbl_PK" displayName="Tbl_PK" ref="A6:U66" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A6:U66"/>
+  <tableColumns count="21">
     <tableColumn id="1" name="順位"/>
     <tableColumn id="2" name="担当者名"/>
     <tableColumn id="3" name="件数"/>
@@ -20788,15 +20788,16 @@
     <tableColumn id="18" name="目標達成率&#10;%"/>
     <tableColumn id="19" name="目標まで&#10;あと"/>
     <tableColumn id="20" name="目標到達で&#10;増やせる件数"/>
+    <tableColumn id="21" name="目標到達で&#10;減らせる人件費(円)"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tbl_KP" displayName="Tbl_KP" ref="A6:T66" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A6:T66"/>
-  <tableColumns count="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tbl_KP" displayName="Tbl_KP" ref="A6:U66" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A6:U66"/>
+  <tableColumns count="21">
     <tableColumn id="1" name="順位"/>
     <tableColumn id="2" name="担当者名"/>
     <tableColumn id="3" name="件数"/>
@@ -20817,6 +20818,7 @@
     <tableColumn id="18" name="目標達成率&#10;%"/>
     <tableColumn id="19" name="目標まで&#10;あと"/>
     <tableColumn id="20" name="目標到達で&#10;増やせる件数"/>
+    <tableColumn id="21" name="目標到達で&#10;減らせる人件費(円)"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -26742,6 +26744,26 @@
         <v>96</v>
       </c>
     </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>時給換算の単価</t>
+        </is>
+      </c>
+      <c r="C28" s="56">
+        <v>1500</v>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>円/時</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>金額の列（ピッキング・梱包シート）はこの単価で計算します。変えると全員の金額が追随します</t>
+        </is>
+      </c>
+    </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B29" s="20" t="inlineStr">
         <is>
@@ -27096,7 +27118,7 @@
       </c>
       <c r="C34" s="93" t="inlineStr">
         <is>
-          <t>同じ時間で目標ペースなら処理できたはずの件数と、実績との差。マイナスは、目標ペースより先行している分です。</t>
+          <t>同じ時間で目標ペースなら処理できたはずの件数と、実績との差。マイナスは、目標ペースより先行している分です。隣の人件費(円)は、この差の時間を時給換算の単価（設定シート、現在1,500円/時）で金額にしたものです。</t>
         </is>
       </c>
       <c r="D34" s="74"/>
@@ -42549,6 +42571,7 @@
     <col min="18" max="18" width="10" customWidth="1"/>
     <col min="19" max="19" width="12" customWidth="1"/>
     <col min="20" max="20" width="14" customWidth="1"/>
+    <col min="21" max="21" width="16" customWidth="1"/>
     <col min="22" max="22" width="22" customWidth="1"/>
     <col min="23" max="23" width="12" customWidth="1"/>
     <col min="24" max="24" width="13" hidden="1" customWidth="1"/>
@@ -42666,6 +42689,12 @@
 増やせる件数</t>
         </is>
       </c>
+      <c r="U6" s="20" t="inlineStr">
+        <is>
+          <t>目標到達で
+減らせる人件費(円)</t>
+        </is>
+      </c>
       <c r="V6" s="47" t="inlineStr">
         <is>
           <t>◎ 達成</t>
@@ -42757,6 +42786,10 @@
         <f>IF(C7="","",D7/設定!$C$26-C7)</f>
         <v>-186.5</v>
       </c>
+      <c r="U7" s="26">
+        <f>IF(C7="","",(D7-C7*設定!$C$26)/60*設定!$C$28)</f>
+        <v>-7460.000000000002</v>
+      </c>
       <c r="V7" s="47" t="inlineStr">
         <is>
           <t>○ あと一歩</t>
@@ -42856,6 +42889,10 @@
         <f>IF(C8="","",D8/設定!$C$26-C8)</f>
         <v>-11.875</v>
       </c>
+      <c r="U8" s="26">
+        <f>IF(C8="","",(D8-C8*設定!$C$26)/60*設定!$C$28)</f>
+        <v>-475.0</v>
+      </c>
       <c r="V8" s="47" t="inlineStr">
         <is>
           <t>△ 要改善</t>
@@ -42955,6 +42992,10 @@
         <f>IF(C9="","",D9/設定!$C$26-C9)</f>
         <v>-21.625</v>
       </c>
+      <c r="U9" s="26">
+        <f>IF(C9="","",(D9-C9*設定!$C$26)/60*設定!$C$28)</f>
+        <v>-865.0000000000035</v>
+      </c>
       <c r="V9" s="47" t="inlineStr">
         <is>
           <t>✕ 要支援</t>
@@ -43054,6 +43095,10 @@
         <f>IF(C10="","",D10/設定!$C$26-C10)</f>
         <v>-160.75</v>
       </c>
+      <c r="U10" s="26">
+        <f>IF(C10="","",(D10-C10*設定!$C$26)/60*設定!$C$28)</f>
+        <v>-6430.000000000001</v>
+      </c>
       <c r="V10" s="47" t="s">
         <v>89</v>
       </c>
@@ -43151,6 +43196,10 @@
         <f>IF(C11="","",D11/設定!$C$26-C11)</f>
         <v>9.25</v>
       </c>
+      <c r="U11" s="26">
+        <f>IF(C11="","",(D11-C11*設定!$C$26)/60*設定!$C$28)</f>
+        <v>369.9999999999996</v>
+      </c>
       <c r="V11" s="47" t="s">
         <v>91</v>
       </c>
@@ -43248,6 +43297,10 @@
         <f>IF(C12="","",D12/設定!$C$26-C12)</f>
         <v>233.625</v>
       </c>
+      <c r="U12" s="26">
+        <f>IF(C12="","",(D12-C12*設定!$C$26)/60*設定!$C$28)</f>
+        <v>9344.999999999993</v>
+      </c>
       <c r="V12" s="47" t="s">
         <v>186</v>
       </c>
@@ -43345,6 +43398,10 @@
         <f>IF(C13="","",D13/設定!$C$26-C13)</f>
         <v>-4.0</v>
       </c>
+      <c r="U13" s="26">
+        <f>IF(C13="","",(D13-C13*設定!$C$26)/60*設定!$C$28)</f>
+        <v>-160.00000000000014</v>
+      </c>
       <c r="V13" s="47" t="s">
         <v>187</v>
       </c>
@@ -43442,6 +43499,10 @@
         <f>IF(C14="","",D14/設定!$C$26-C14)</f>
         <v>-35.75</v>
       </c>
+      <c r="U14" s="26">
+        <f>IF(C14="","",(D14-C14*設定!$C$26)/60*設定!$C$28)</f>
+        <v>-1430.0000000000011</v>
+      </c>
       <c r="V14" s="47" t="s">
         <v>188</v>
       </c>
@@ -43539,6 +43600,10 @@
         <f>IF(C15="","",D15/設定!$C$26-C15)</f>
         <v>112.125</v>
       </c>
+      <c r="U15" s="26">
+        <f>IF(C15="","",(D15-C15*設定!$C$26)/60*設定!$C$28)</f>
+        <v>4484.999999999996</v>
+      </c>
       <c r="V15" s="47" t="s">
         <v>50</v>
       </c>
@@ -43636,6 +43701,10 @@
         <f>IF(C16="","",D16/設定!$C$26-C16)</f>
         <v>114.125</v>
       </c>
+      <c r="U16" s="26">
+        <f>IF(C16="","",(D16-C16*設定!$C$26)/60*設定!$C$28)</f>
+        <v>4564.999999999997</v>
+      </c>
       <c r="V16" s="47" t="s">
         <v>93</v>
       </c>
@@ -43733,6 +43802,10 @@
         <f>IF(C17="","",D17/設定!$C$26-C17)</f>
         <v>-4.75</v>
       </c>
+      <c r="U17" s="26">
+        <f>IF(C17="","",(D17-C17*設定!$C$26)/60*設定!$C$28)</f>
+        <v>-190.00000000000344</v>
+      </c>
       <c r="V17" s="47" t="s">
         <v>100</v>
       </c>
@@ -43830,6 +43903,10 @@
         <f>IF(C18="","",D18/設定!$C$26-C18)</f>
         <v>157.625</v>
       </c>
+      <c r="U18" s="26">
+        <f>IF(C18="","",(D18-C18*設定!$C$26)/60*設定!$C$28)</f>
+        <v>6304.999999999998</v>
+      </c>
       <c r="V18" s="47" t="inlineStr">
         <is>
           <t>1件あたり 目標まで(秒)</t>
@@ -43929,6 +44006,10 @@
         <f>IF(C19="","",D19/設定!$C$26-C19)</f>
         <v>266.375</v>
       </c>
+      <c r="U19" s="26">
+        <f>IF(C19="","",(D19-C19*設定!$C$26)/60*設定!$C$28)</f>
+        <v>10654.999999999995</v>
+      </c>
       <c r="V19" s="47" t="inlineStr">
         <is>
           <t>目標到達で増やせる件数</t>
@@ -44028,6 +44109,19 @@
         <f>IF(C20="","",D20/設定!$C$26-C20)</f>
         <v>85.25</v>
       </c>
+      <c r="U20" s="26">
+        <f>IF(C20="","",(D20-C20*設定!$C$26)/60*設定!$C$28)</f>
+        <v>3409.999999999997</v>
+      </c>
+      <c r="V20" s="47" t="inlineStr">
+        <is>
+          <t>目標到達で減らせる人件費(円)</t>
+        </is>
+      </c>
+      <c r="W20" s="26">
+        <f>IFERROR((W12-W10*設定!$C$26)/60*設定!$C$28,"")</f>
+        <v>169614.99999999997</v>
+      </c>
       <c r="X20">
         <f t="shared" si="8"/>
         <v>85101.35436241611</v>
@@ -44118,6 +44212,10 @@
         <f>IF(C21="","",D21/設定!$C$26-C21)</f>
         <v>63.25</v>
       </c>
+      <c r="U21" s="26">
+        <f>IF(C21="","",(D21-C21*設定!$C$26)/60*設定!$C$28)</f>
+        <v>2530.0</v>
+      </c>
       <c r="X21">
         <f t="shared" si="8"/>
         <v>21412.202222222222</v>
@@ -44208,6 +44306,10 @@
         <f>IF(C22="","",D22/設定!$C$26-C22)</f>
         <v>65.0</v>
       </c>
+      <c r="U22" s="26">
+        <f>IF(C22="","",(D22-C22*設定!$C$26)/60*設定!$C$28)</f>
+        <v>2600.0</v>
+      </c>
       <c r="X22">
         <f t="shared" si="8"/>
         <v>27472.717391304352</v>
@@ -44298,6 +44400,10 @@
         <f>IF(C23="","",D23/設定!$C$26-C23)</f>
         <v>181.5</v>
       </c>
+      <c r="U23" s="26">
+        <f>IF(C23="","",(D23-C23*設定!$C$26)/60*設定!$C$28)</f>
+        <v>7259.999999999997</v>
+      </c>
       <c r="X23">
         <f t="shared" si="8"/>
         <v>68853.744627507156</v>
@@ -44388,6 +44494,10 @@
         <f>IF(C24="","",D24/設定!$C$26-C24)</f>
         <v>162.125</v>
       </c>
+      <c r="U24" s="26">
+        <f>IF(C24="","",(D24-C24*設定!$C$26)/60*設定!$C$28)</f>
+        <v>6485.0</v>
+      </c>
       <c r="X24">
         <f t="shared" si="8"/>
         <v>38001.03783783783</v>
@@ -44478,6 +44588,10 @@
         <f>IF(C25="","",D25/設定!$C$26-C25)</f>
         <v>84.625</v>
       </c>
+      <c r="U25" s="26">
+        <f>IF(C25="","",(D25-C25*設定!$C$26)/60*設定!$C$28)</f>
+        <v>3384.9999999999995</v>
+      </c>
       <c r="X25">
         <f t="shared" si="8"/>
         <v>22301.334653465346</v>
@@ -44568,6 +44682,10 @@
         <f>IF(C26="","",D26/設定!$C$26-C26)</f>
         <v>306.5</v>
       </c>
+      <c r="U26" s="26">
+        <f>IF(C26="","",(D26-C26*設定!$C$26)/60*設定!$C$28)</f>
+        <v>12259.999999999995</v>
+      </c>
       <c r="X26">
         <f t="shared" si="8"/>
         <v>77934.229744136479</v>
@@ -44658,6 +44776,10 @@
         <f>IF(C27="","",D27/設定!$C$26-C27)</f>
         <v>60.25</v>
       </c>
+      <c r="U27" s="26">
+        <f>IF(C27="","",(D27-C27*設定!$C$26)/60*設定!$C$28)</f>
+        <v>2409.9999999999995</v>
+      </c>
       <c r="X27">
         <f t="shared" si="8"/>
         <v>5074.3217821782182</v>
@@ -44748,6 +44870,10 @@
         <f>IF(C28="","",D28/設定!$C$26-C28)</f>
         <v>394.5</v>
       </c>
+      <c r="U28" s="26">
+        <f>IF(C28="","",(D28-C28*設定!$C$26)/60*設定!$C$28)</f>
+        <v>15779.999999999996</v>
+      </c>
       <c r="X28">
         <f t="shared" si="8"/>
         <v>73766.309837728186</v>
@@ -44838,6 +44964,10 @@
         <f>IF(C29="","",D29/設定!$C$26-C29)</f>
         <v>112.5</v>
       </c>
+      <c r="U29" s="26">
+        <f>IF(C29="","",(D29-C29*設定!$C$26)/60*設定!$C$28)</f>
+        <v>4500.0</v>
+      </c>
       <c r="X29">
         <f t="shared" si="8"/>
         <v>27433.739525139663</v>
@@ -44928,6 +45058,10 @@
         <f>IF(C30="","",D30/設定!$C$26-C30)</f>
         <v>171.75</v>
       </c>
+      <c r="U30" s="26">
+        <f>IF(C30="","",(D30-C30*設定!$C$26)/60*設定!$C$28)</f>
+        <v>6869.999999999999</v>
+      </c>
       <c r="X30">
         <f t="shared" si="8"/>
         <v>36234.030526315786</v>
@@ -45018,6 +45152,10 @@
         <f>IF(C31="","",D31/設定!$C$26-C31)</f>
         <v>478.75</v>
       </c>
+      <c r="U31" s="26">
+        <f>IF(C31="","",(D31-C31*設定!$C$26)/60*設定!$C$28)</f>
+        <v>19150.0</v>
+      </c>
       <c r="X31">
         <f t="shared" si="8"/>
         <v>88171.880478087653</v>
@@ -45108,6 +45246,10 @@
         <f>IF(C32="","",D32/設定!$C$26-C32)</f>
         <v>450.75</v>
       </c>
+      <c r="U32" s="26">
+        <f>IF(C32="","",(D32-C32*設定!$C$26)/60*設定!$C$28)</f>
+        <v>18029.999999999996</v>
+      </c>
       <c r="X32">
         <f t="shared" si="8"/>
         <v>68888.508595988547</v>
@@ -45198,6 +45340,10 @@
         <f>IF(C33="","",D33/設定!$C$26-C33)</f>
         <v>553.625</v>
       </c>
+      <c r="U33" s="26">
+        <f>IF(C33="","",(D33-C33*設定!$C$26)/60*設定!$C$28)</f>
+        <v>22144.999999999996</v>
+      </c>
       <c r="X33">
         <f t="shared" si="8"/>
         <v>88246.275422138846</v>
@@ -45288,6 +45434,10 @@
         <f>IF(C34="","",D34/設定!$C$26-C34)</f>
         <v>395.625</v>
       </c>
+      <c r="U34" s="26">
+        <f>IF(C34="","",(D34-C34*設定!$C$26)/60*設定!$C$28)</f>
+        <v>15825.000000000002</v>
+      </c>
       <c r="X34">
         <f t="shared" si="8"/>
         <v>20942.906122448978</v>
@@ -45378,6 +45528,10 @@
         <f>IF(C35="","",D35/設定!$C$26-C35)</f>
         <v>206.5</v>
       </c>
+      <c r="U35" s="26">
+        <f>IF(C35="","",(D35-C35*設定!$C$26)/60*設定!$C$28)</f>
+        <v>8259.999999999998</v>
+      </c>
       <c r="X35">
         <f t="shared" si="8"/>
         <v>20224.793848167537</v>
@@ -45468,6 +45622,10 @@
         <f>IF(C36="","",D36/設定!$C$26-C36)</f>
         <v/>
       </c>
+      <c r="U36" s="26" t="str">
+        <f>IF(C36="","",(D36-C36*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X36">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -45558,6 +45716,10 @@
         <f>IF(C37="","",D37/設定!$C$26-C37)</f>
         <v/>
       </c>
+      <c r="U37" s="26" t="str">
+        <f>IF(C37="","",(D37-C37*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X37">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -45648,6 +45810,10 @@
         <f>IF(C38="","",D38/設定!$C$26-C38)</f>
         <v/>
       </c>
+      <c r="U38" s="26" t="str">
+        <f>IF(C38="","",(D38-C38*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X38">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -45738,6 +45904,10 @@
         <f>IF(C39="","",D39/設定!$C$26-C39)</f>
         <v/>
       </c>
+      <c r="U39" s="26" t="str">
+        <f>IF(C39="","",(D39-C39*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X39">
         <f t="shared" ref="X39:X66" si="17">IF(K39="",0,K39*C39)</f>
         <v>0</v>
@@ -45828,6 +45998,10 @@
         <f>IF(C40="","",D40/設定!$C$26-C40)</f>
         <v/>
       </c>
+      <c r="U40" s="26" t="str">
+        <f>IF(C40="","",(D40-C40*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X40">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -45918,6 +46092,10 @@
         <f>IF(C41="","",D41/設定!$C$26-C41)</f>
         <v/>
       </c>
+      <c r="U41" s="26" t="str">
+        <f>IF(C41="","",(D41-C41*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X41">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -46008,6 +46186,10 @@
         <f>IF(C42="","",D42/設定!$C$26-C42)</f>
         <v/>
       </c>
+      <c r="U42" s="26" t="str">
+        <f>IF(C42="","",(D42-C42*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X42">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -46098,6 +46280,10 @@
         <f>IF(C43="","",D43/設定!$C$26-C43)</f>
         <v/>
       </c>
+      <c r="U43" s="26" t="str">
+        <f>IF(C43="","",(D43-C43*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X43">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -46188,6 +46374,10 @@
         <f>IF(C44="","",D44/設定!$C$26-C44)</f>
         <v/>
       </c>
+      <c r="U44" s="26" t="str">
+        <f>IF(C44="","",(D44-C44*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X44">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -46278,6 +46468,10 @@
         <f>IF(C45="","",D45/設定!$C$26-C45)</f>
         <v/>
       </c>
+      <c r="U45" s="26" t="str">
+        <f>IF(C45="","",(D45-C45*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X45">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -46368,6 +46562,10 @@
         <f>IF(C46="","",D46/設定!$C$26-C46)</f>
         <v/>
       </c>
+      <c r="U46" s="26" t="str">
+        <f>IF(C46="","",(D46-C46*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X46">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -46458,6 +46656,10 @@
         <f>IF(C47="","",D47/設定!$C$26-C47)</f>
         <v/>
       </c>
+      <c r="U47" s="26" t="str">
+        <f>IF(C47="","",(D47-C47*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X47">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -46548,6 +46750,10 @@
         <f>IF(C48="","",D48/設定!$C$26-C48)</f>
         <v/>
       </c>
+      <c r="U48" s="26" t="str">
+        <f>IF(C48="","",(D48-C48*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X48">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -46638,6 +46844,10 @@
         <f>IF(C49="","",D49/設定!$C$26-C49)</f>
         <v/>
       </c>
+      <c r="U49" s="26" t="str">
+        <f>IF(C49="","",(D49-C49*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X49">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -46728,6 +46938,10 @@
         <f>IF(C50="","",D50/設定!$C$26-C50)</f>
         <v/>
       </c>
+      <c r="U50" s="26" t="str">
+        <f>IF(C50="","",(D50-C50*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X50">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -46818,6 +47032,10 @@
         <f>IF(C51="","",D51/設定!$C$26-C51)</f>
         <v/>
       </c>
+      <c r="U51" s="26" t="str">
+        <f>IF(C51="","",(D51-C51*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X51">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -46908,6 +47126,10 @@
         <f>IF(C52="","",D52/設定!$C$26-C52)</f>
         <v/>
       </c>
+      <c r="U52" s="26" t="str">
+        <f>IF(C52="","",(D52-C52*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X52">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -46998,6 +47220,10 @@
         <f>IF(C53="","",D53/設定!$C$26-C53)</f>
         <v/>
       </c>
+      <c r="U53" s="26" t="str">
+        <f>IF(C53="","",(D53-C53*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X53">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -47088,6 +47314,10 @@
         <f>IF(C54="","",D54/設定!$C$26-C54)</f>
         <v/>
       </c>
+      <c r="U54" s="26" t="str">
+        <f>IF(C54="","",(D54-C54*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X54">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -47178,6 +47408,10 @@
         <f>IF(C55="","",D55/設定!$C$26-C55)</f>
         <v/>
       </c>
+      <c r="U55" s="26" t="str">
+        <f>IF(C55="","",(D55-C55*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X55">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -47268,6 +47502,10 @@
         <f>IF(C56="","",D56/設定!$C$26-C56)</f>
         <v/>
       </c>
+      <c r="U56" s="26" t="str">
+        <f>IF(C56="","",(D56-C56*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X56">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -47358,6 +47596,10 @@
         <f>IF(C57="","",D57/設定!$C$26-C57)</f>
         <v/>
       </c>
+      <c r="U57" s="26" t="str">
+        <f>IF(C57="","",(D57-C57*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X57">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -47448,6 +47690,10 @@
         <f>IF(C58="","",D58/設定!$C$26-C58)</f>
         <v/>
       </c>
+      <c r="U58" s="26" t="str">
+        <f>IF(C58="","",(D58-C58*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X58">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -47538,6 +47784,10 @@
         <f>IF(C59="","",D59/設定!$C$26-C59)</f>
         <v/>
       </c>
+      <c r="U59" s="26" t="str">
+        <f>IF(C59="","",(D59-C59*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X59">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -47628,6 +47878,10 @@
         <f>IF(C60="","",D60/設定!$C$26-C60)</f>
         <v/>
       </c>
+      <c r="U60" s="26" t="str">
+        <f>IF(C60="","",(D60-C60*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X60">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -47718,6 +47972,10 @@
         <f>IF(C61="","",D61/設定!$C$26-C61)</f>
         <v/>
       </c>
+      <c r="U61" s="26" t="str">
+        <f>IF(C61="","",(D61-C61*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X61">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -47808,6 +48066,10 @@
         <f>IF(C62="","",D62/設定!$C$26-C62)</f>
         <v/>
       </c>
+      <c r="U62" s="26" t="str">
+        <f>IF(C62="","",(D62-C62*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X62">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -47898,6 +48160,10 @@
         <f>IF(C63="","",D63/設定!$C$26-C63)</f>
         <v/>
       </c>
+      <c r="U63" s="26" t="str">
+        <f>IF(C63="","",(D63-C63*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X63">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -47988,6 +48254,10 @@
         <f>IF(C64="","",D64/設定!$C$26-C64)</f>
         <v/>
       </c>
+      <c r="U64" s="26" t="str">
+        <f>IF(C64="","",(D64-C64*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X64">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -48078,6 +48348,10 @@
         <f>IF(C65="","",D65/設定!$C$26-C65)</f>
         <v/>
       </c>
+      <c r="U65" s="26" t="str">
+        <f>IF(C65="","",(D65-C65*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X65">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -48168,6 +48442,10 @@
         <f>IF(C66="","",D66/設定!$C$26-C66)</f>
         <v/>
       </c>
+      <c r="U66" s="26" t="str">
+        <f>IF(C66="","",(D66-C66*設定!$C$26)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X66">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -48179,7 +48457,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="34"/>
-  <conditionalFormatting sqref="A7:T66">
+  <conditionalFormatting sqref="A7:U66">
     <cfRule type="expression" dxfId="5" priority="1">
       <formula>$O7="◎達成"</formula>
     </cfRule>
@@ -48230,6 +48508,7 @@
     <col min="18" max="18" width="10" customWidth="1"/>
     <col min="19" max="19" width="12" customWidth="1"/>
     <col min="20" max="20" width="14" customWidth="1"/>
+    <col min="21" max="21" width="16" customWidth="1"/>
     <col min="22" max="22" width="22" customWidth="1"/>
     <col min="23" max="23" width="12" customWidth="1"/>
     <col min="24" max="24" width="13" hidden="1" customWidth="1"/>
@@ -48347,6 +48626,12 @@
 増やせる件数</t>
         </is>
       </c>
+      <c r="U6" s="20" t="inlineStr">
+        <is>
+          <t>目標到達で
+減らせる人件費(円)</t>
+        </is>
+      </c>
       <c r="V6" s="47" t="inlineStr">
         <is>
           <t>◎ 達成</t>
@@ -48438,6 +48723,10 @@
         <f>IF(C7="","",D7/設定!$C$27-C7)</f>
         <v>-868.625</v>
       </c>
+      <c r="U7" s="26">
+        <f>IF(C7="","",(D7-C7*設定!$C$27)/60*設定!$C$28)</f>
+        <v>-34745.00000000001</v>
+      </c>
       <c r="V7" s="47" t="inlineStr">
         <is>
           <t>○ あと一歩</t>
@@ -48537,6 +48826,10 @@
         <f>IF(C8="","",D8/設定!$C$27-C8)</f>
         <v>134.75</v>
       </c>
+      <c r="U8" s="26">
+        <f>IF(C8="","",(D8-C8*設定!$C$27)/60*設定!$C$28)</f>
+        <v>5389.999999999998</v>
+      </c>
       <c r="V8" s="47" t="inlineStr">
         <is>
           <t>△ 要改善</t>
@@ -48636,6 +48929,10 @@
         <f>IF(C9="","",D9/設定!$C$27-C9)</f>
         <v>-703.5</v>
       </c>
+      <c r="U9" s="26">
+        <f>IF(C9="","",(D9-C9*設定!$C$27)/60*設定!$C$28)</f>
+        <v>-28140.000000000007</v>
+      </c>
       <c r="V9" s="47" t="inlineStr">
         <is>
           <t>✕ 要支援</t>
@@ -48735,6 +49032,10 @@
         <f>IF(C10="","",D10/設定!$C$27-C10)</f>
         <v>-93.375</v>
       </c>
+      <c r="U10" s="26">
+        <f>IF(C10="","",(D10-C10*設定!$C$27)/60*設定!$C$28)</f>
+        <v>-3735.000000000001</v>
+      </c>
       <c r="V10" s="47" t="s">
         <v>89</v>
       </c>
@@ -48830,6 +49131,10 @@
       </c>
       <c r="T11" s="26" t="str">
         <f>IF(C11="","",D11/設定!$C$27-C11)</f>
+        <v/>
+      </c>
+      <c r="U11" s="26" t="str">
+        <f>IF(C11="","",(D11-C11*設定!$C$27)/60*設定!$C$28)</f>
         <v/>
       </c>
       <c r="V11" s="47" t="s">
@@ -48929,6 +49234,10 @@
         <f>IF(C12="","",D12/設定!$C$27-C12)</f>
         <v>304.0</v>
       </c>
+      <c r="U12" s="26">
+        <f>IF(C12="","",(D12-C12*設定!$C$27)/60*設定!$C$28)</f>
+        <v>12160.000000000002</v>
+      </c>
       <c r="V12" s="47" t="s">
         <v>186</v>
       </c>
@@ -49026,6 +49335,10 @@
         <f>IF(C13="","",D13/設定!$C$27-C13)</f>
         <v>81.25</v>
       </c>
+      <c r="U13" s="26">
+        <f>IF(C13="","",(D13-C13*設定!$C$27)/60*設定!$C$28)</f>
+        <v>3250.0</v>
+      </c>
       <c r="V13" s="47" t="s">
         <v>187</v>
       </c>
@@ -49123,6 +49436,10 @@
         <f>IF(C14="","",D14/設定!$C$27-C14)</f>
         <v>-376.625</v>
       </c>
+      <c r="U14" s="26">
+        <f>IF(C14="","",(D14-C14*設定!$C$27)/60*設定!$C$28)</f>
+        <v>-15065.000000000011</v>
+      </c>
       <c r="V14" s="47" t="s">
         <v>188</v>
       </c>
@@ -49220,6 +49537,10 @@
         <f>IF(C15="","",D15/設定!$C$27-C15)</f>
         <v>160.5</v>
       </c>
+      <c r="U15" s="26">
+        <f>IF(C15="","",(D15-C15*設定!$C$27)/60*設定!$C$28)</f>
+        <v>6419.999999999994</v>
+      </c>
       <c r="V15" s="47" t="s">
         <v>50</v>
       </c>
@@ -49317,6 +49638,10 @@
         <f>IF(C16="","",D16/設定!$C$27-C16)</f>
         <v>219.5</v>
       </c>
+      <c r="U16" s="26">
+        <f>IF(C16="","",(D16-C16*設定!$C$27)/60*設定!$C$28)</f>
+        <v>8779.999999999995</v>
+      </c>
       <c r="V16" s="47" t="s">
         <v>93</v>
       </c>
@@ -49414,6 +49739,10 @@
         <f>IF(C17="","",D17/設定!$C$27-C17)</f>
         <v>-408.75</v>
       </c>
+      <c r="U17" s="26">
+        <f>IF(C17="","",(D17-C17*設定!$C$27)/60*設定!$C$28)</f>
+        <v>-16350.0</v>
+      </c>
       <c r="V17" s="47" t="s">
         <v>100</v>
       </c>
@@ -49511,6 +49840,10 @@
         <f>IF(C18="","",D18/設定!$C$27-C18)</f>
         <v>-343.25</v>
       </c>
+      <c r="U18" s="26">
+        <f>IF(C18="","",(D18-C18*設定!$C$27)/60*設定!$C$28)</f>
+        <v>-13730.000000000007</v>
+      </c>
       <c r="V18" s="47" t="inlineStr">
         <is>
           <t>1件あたり 目標まで(秒)</t>
@@ -49610,6 +49943,10 @@
         <f>IF(C19="","",D19/設定!$C$27-C19)</f>
         <v>72.875</v>
       </c>
+      <c r="U19" s="26">
+        <f>IF(C19="","",(D19-C19*設定!$C$27)/60*設定!$C$28)</f>
+        <v>2914.999999999999</v>
+      </c>
       <c r="V19" s="47" t="inlineStr">
         <is>
           <t>目標到達で増やせる件数</t>
@@ -49709,6 +50046,19 @@
         <f>IF(C20="","",D20/設定!$C$27-C20)</f>
         <v/>
       </c>
+      <c r="U20" s="26" t="str">
+        <f>IF(C20="","",(D20-C20*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
+      <c r="V20" s="47" t="inlineStr">
+        <is>
+          <t>目標到達で減らせる人件費(円)</t>
+        </is>
+      </c>
+      <c r="W20" s="26">
+        <f>IFERROR((W12-W10*設定!$C$27)/60*設定!$C$28,"")</f>
+        <v>-6505.000000000109</v>
+      </c>
       <c r="X20">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -49799,6 +50149,10 @@
         <f>IF(C21="","",D21/設定!$C$27-C21)</f>
         <v>585.625</v>
       </c>
+      <c r="U21" s="26">
+        <f>IF(C21="","",(D21-C21*設定!$C$27)/60*設定!$C$28)</f>
+        <v>23425.0</v>
+      </c>
       <c r="X21">
         <f t="shared" si="8"/>
         <v>32934.748071979433</v>
@@ -49889,6 +50243,10 @@
         <f>IF(C22="","",D22/設定!$C$27-C22)</f>
         <v>-164.875</v>
       </c>
+      <c r="U22" s="26">
+        <f>IF(C22="","",(D22-C22*設定!$C$27)/60*設定!$C$28)</f>
+        <v>-6595.000000000001</v>
+      </c>
       <c r="X22">
         <f t="shared" si="8"/>
         <v>69031.404136253026</v>
@@ -49979,6 +50337,10 @@
         <f>IF(C23="","",D23/設定!$C$27-C23)</f>
         <v>617.5</v>
       </c>
+      <c r="U23" s="26">
+        <f>IF(C23="","",(D23-C23*設定!$C$27)/60*設定!$C$28)</f>
+        <v>24699.999999999996</v>
+      </c>
       <c r="X23">
         <f t="shared" si="8"/>
         <v>125701.71154523053</v>
@@ -50067,6 +50429,10 @@
       </c>
       <c r="T24" s="26" t="str">
         <f>IF(C24="","",D24/設定!$C$27-C24)</f>
+        <v/>
+      </c>
+      <c r="U24" s="26" t="str">
+        <f>IF(C24="","",(D24-C24*設定!$C$27)/60*設定!$C$28)</f>
         <v/>
       </c>
       <c r="X24">
@@ -50159,6 +50525,10 @@
         <f>IF(C25="","",D25/設定!$C$27-C25)</f>
         <v>105.0</v>
       </c>
+      <c r="U25" s="26">
+        <f>IF(C25="","",(D25-C25*設定!$C$27)/60*設定!$C$28)</f>
+        <v>4200.0</v>
+      </c>
       <c r="X25">
         <f t="shared" si="8"/>
         <v>102247.15909090909</v>
@@ -50249,6 +50619,10 @@
         <f>IF(C26="","",D26/設定!$C$27-C26)</f>
         <v/>
       </c>
+      <c r="U26" s="26" t="str">
+        <f>IF(C26="","",(D26-C26*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X26">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -50339,6 +50713,10 @@
         <f>IF(C27="","",D27/設定!$C$27-C27)</f>
         <v/>
       </c>
+      <c r="U27" s="26" t="str">
+        <f>IF(C27="","",(D27-C27*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X27">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -50427,6 +50805,10 @@
       </c>
       <c r="T28" s="26" t="str">
         <f>IF(C28="","",D28/設定!$C$27-C28)</f>
+        <v/>
+      </c>
+      <c r="U28" s="26" t="str">
+        <f>IF(C28="","",(D28-C28*設定!$C$27)/60*設定!$C$28)</f>
         <v/>
       </c>
       <c r="X28">
@@ -50519,6 +50901,10 @@
         <f>IF(C29="","",D29/設定!$C$27-C29)</f>
         <v>3.75</v>
       </c>
+      <c r="U29" s="26">
+        <f>IF(C29="","",(D29-C29*設定!$C$27)/60*設定!$C$28)</f>
+        <v>150.0</v>
+      </c>
       <c r="X29">
         <f t="shared" si="8"/>
         <v>97954.954000855781</v>
@@ -50609,6 +50995,10 @@
         <f>IF(C30="","",D30/設定!$C$27-C30)</f>
         <v>656.375</v>
       </c>
+      <c r="U30" s="26">
+        <f>IF(C30="","",(D30-C30*設定!$C$27)/60*設定!$C$28)</f>
+        <v>26254.999999999996</v>
+      </c>
       <c r="X30">
         <f t="shared" si="8"/>
         <v>77727.213500962738</v>
@@ -50699,6 +51089,10 @@
         <f>IF(C31="","",D31/設定!$C$27-C31)</f>
         <v/>
       </c>
+      <c r="U31" s="26" t="str">
+        <f>IF(C31="","",(D31-C31*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X31">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -50789,6 +51183,10 @@
         <f>IF(C32="","",D32/設定!$C$27-C32)</f>
         <v/>
       </c>
+      <c r="U32" s="26" t="str">
+        <f>IF(C32="","",(D32-C32*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X32">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -50879,6 +51277,10 @@
         <f>IF(C33="","",D33/設定!$C$27-C33)</f>
         <v/>
       </c>
+      <c r="U33" s="26" t="str">
+        <f>IF(C33="","",(D33-C33*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X33">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -50967,6 +51369,10 @@
       </c>
       <c r="T34" s="26" t="str">
         <f>IF(C34="","",D34/設定!$C$27-C34)</f>
+        <v/>
+      </c>
+      <c r="U34" s="26" t="str">
+        <f>IF(C34="","",(D34-C34*設定!$C$27)/60*設定!$C$28)</f>
         <v/>
       </c>
       <c r="X34">
@@ -51059,6 +51465,10 @@
         <f>IF(C35="","",D35/設定!$C$27-C35)</f>
         <v>-144.75</v>
       </c>
+      <c r="U35" s="26">
+        <f>IF(C35="","",(D35-C35*設定!$C$27)/60*設定!$C$28)</f>
+        <v>-5790.000000000003</v>
+      </c>
       <c r="X35">
         <f t="shared" si="8"/>
         <v>137050.41700773078</v>
@@ -51149,6 +51559,10 @@
         <f>IF(C36="","",D36/設定!$C$27-C36)</f>
         <v/>
       </c>
+      <c r="U36" s="26" t="str">
+        <f>IF(C36="","",(D36-C36*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X36">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -51239,6 +51653,10 @@
         <f>IF(C37="","",D37/設定!$C$27-C37)</f>
         <v/>
       </c>
+      <c r="U37" s="26" t="str">
+        <f>IF(C37="","",(D37-C37*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X37">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -51329,6 +51747,10 @@
         <f>IF(C38="","",D38/設定!$C$27-C38)</f>
         <v/>
       </c>
+      <c r="U38" s="26" t="str">
+        <f>IF(C38="","",(D38-C38*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X38">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -51419,6 +51841,10 @@
         <f>IF(C39="","",D39/設定!$C$27-C39)</f>
         <v/>
       </c>
+      <c r="U39" s="26" t="str">
+        <f>IF(C39="","",(D39-C39*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X39">
         <f t="shared" ref="X39:X66" si="17">IF(K39="",0,K39*C39)</f>
         <v>0</v>
@@ -51509,6 +51935,10 @@
         <f>IF(C40="","",D40/設定!$C$27-C40)</f>
         <v/>
       </c>
+      <c r="U40" s="26" t="str">
+        <f>IF(C40="","",(D40-C40*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X40">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -51599,6 +52029,10 @@
         <f>IF(C41="","",D41/設定!$C$27-C41)</f>
         <v/>
       </c>
+      <c r="U41" s="26" t="str">
+        <f>IF(C41="","",(D41-C41*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X41">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -51689,6 +52123,10 @@
         <f>IF(C42="","",D42/設定!$C$27-C42)</f>
         <v/>
       </c>
+      <c r="U42" s="26" t="str">
+        <f>IF(C42="","",(D42-C42*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X42">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -51779,6 +52217,10 @@
         <f>IF(C43="","",D43/設定!$C$27-C43)</f>
         <v/>
       </c>
+      <c r="U43" s="26" t="str">
+        <f>IF(C43="","",(D43-C43*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X43">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -51869,6 +52311,10 @@
         <f>IF(C44="","",D44/設定!$C$27-C44)</f>
         <v/>
       </c>
+      <c r="U44" s="26" t="str">
+        <f>IF(C44="","",(D44-C44*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X44">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -51959,6 +52405,10 @@
         <f>IF(C45="","",D45/設定!$C$27-C45)</f>
         <v/>
       </c>
+      <c r="U45" s="26" t="str">
+        <f>IF(C45="","",(D45-C45*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X45">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -52049,6 +52499,10 @@
         <f>IF(C46="","",D46/設定!$C$27-C46)</f>
         <v/>
       </c>
+      <c r="U46" s="26" t="str">
+        <f>IF(C46="","",(D46-C46*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X46">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -52139,6 +52593,10 @@
         <f>IF(C47="","",D47/設定!$C$27-C47)</f>
         <v/>
       </c>
+      <c r="U47" s="26" t="str">
+        <f>IF(C47="","",(D47-C47*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X47">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -52229,6 +52687,10 @@
         <f>IF(C48="","",D48/設定!$C$27-C48)</f>
         <v/>
       </c>
+      <c r="U48" s="26" t="str">
+        <f>IF(C48="","",(D48-C48*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X48">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -52319,6 +52781,10 @@
         <f>IF(C49="","",D49/設定!$C$27-C49)</f>
         <v/>
       </c>
+      <c r="U49" s="26" t="str">
+        <f>IF(C49="","",(D49-C49*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X49">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -52409,6 +52875,10 @@
         <f>IF(C50="","",D50/設定!$C$27-C50)</f>
         <v/>
       </c>
+      <c r="U50" s="26" t="str">
+        <f>IF(C50="","",(D50-C50*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X50">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -52499,6 +52969,10 @@
         <f>IF(C51="","",D51/設定!$C$27-C51)</f>
         <v/>
       </c>
+      <c r="U51" s="26" t="str">
+        <f>IF(C51="","",(D51-C51*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X51">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -52589,6 +53063,10 @@
         <f>IF(C52="","",D52/設定!$C$27-C52)</f>
         <v/>
       </c>
+      <c r="U52" s="26" t="str">
+        <f>IF(C52="","",(D52-C52*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X52">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -52679,6 +53157,10 @@
         <f>IF(C53="","",D53/設定!$C$27-C53)</f>
         <v/>
       </c>
+      <c r="U53" s="26" t="str">
+        <f>IF(C53="","",(D53-C53*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X53">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -52769,6 +53251,10 @@
         <f>IF(C54="","",D54/設定!$C$27-C54)</f>
         <v/>
       </c>
+      <c r="U54" s="26" t="str">
+        <f>IF(C54="","",(D54-C54*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X54">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -52859,6 +53345,10 @@
         <f>IF(C55="","",D55/設定!$C$27-C55)</f>
         <v/>
       </c>
+      <c r="U55" s="26" t="str">
+        <f>IF(C55="","",(D55-C55*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X55">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -52949,6 +53439,10 @@
         <f>IF(C56="","",D56/設定!$C$27-C56)</f>
         <v/>
       </c>
+      <c r="U56" s="26" t="str">
+        <f>IF(C56="","",(D56-C56*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X56">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -53039,6 +53533,10 @@
         <f>IF(C57="","",D57/設定!$C$27-C57)</f>
         <v/>
       </c>
+      <c r="U57" s="26" t="str">
+        <f>IF(C57="","",(D57-C57*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X57">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -53129,6 +53627,10 @@
         <f>IF(C58="","",D58/設定!$C$27-C58)</f>
         <v/>
       </c>
+      <c r="U58" s="26" t="str">
+        <f>IF(C58="","",(D58-C58*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X58">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -53219,6 +53721,10 @@
         <f>IF(C59="","",D59/設定!$C$27-C59)</f>
         <v/>
       </c>
+      <c r="U59" s="26" t="str">
+        <f>IF(C59="","",(D59-C59*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X59">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -53309,6 +53815,10 @@
         <f>IF(C60="","",D60/設定!$C$27-C60)</f>
         <v/>
       </c>
+      <c r="U60" s="26" t="str">
+        <f>IF(C60="","",(D60-C60*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X60">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -53399,6 +53909,10 @@
         <f>IF(C61="","",D61/設定!$C$27-C61)</f>
         <v/>
       </c>
+      <c r="U61" s="26" t="str">
+        <f>IF(C61="","",(D61-C61*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X61">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -53489,6 +54003,10 @@
         <f>IF(C62="","",D62/設定!$C$27-C62)</f>
         <v/>
       </c>
+      <c r="U62" s="26" t="str">
+        <f>IF(C62="","",(D62-C62*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X62">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -53579,6 +54097,10 @@
         <f>IF(C63="","",D63/設定!$C$27-C63)</f>
         <v/>
       </c>
+      <c r="U63" s="26" t="str">
+        <f>IF(C63="","",(D63-C63*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X63">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -53669,6 +54191,10 @@
         <f>IF(C64="","",D64/設定!$C$27-C64)</f>
         <v/>
       </c>
+      <c r="U64" s="26" t="str">
+        <f>IF(C64="","",(D64-C64*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X64">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -53759,6 +54285,10 @@
         <f>IF(C65="","",D65/設定!$C$27-C65)</f>
         <v/>
       </c>
+      <c r="U65" s="26" t="str">
+        <f>IF(C65="","",(D65-C65*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X65">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -53849,6 +54379,10 @@
         <f>IF(C66="","",D66/設定!$C$27-C66)</f>
         <v/>
       </c>
+      <c r="U66" s="26" t="str">
+        <f>IF(C66="","",(D66-C66*設定!$C$27)/60*設定!$C$28)</f>
+        <v/>
+      </c>
       <c r="X66">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -53860,7 +54394,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="34"/>
-  <conditionalFormatting sqref="A7:T66">
+  <conditionalFormatting sqref="A7:U66">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>$O7="◎達成"</formula>
     </cfRule>

--- a/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
+++ b/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
@@ -3643,7 +3643,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -3656,11 +3656,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -3703,122 +3698,6 @@
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>本吉有美子</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="7"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="2E75B6"/>
-              </a:solidFill>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:dLbls>
-            <c:dLbl>
-              <c:idx val="0"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-9.1503267973856214E-3"/>
-                  <c:y val="-1.2226120557446657E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:dLblPos val="r"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="1"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000069-79D4-48A9-8F10-910E96FCBD2E}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="600"/>
-                </a:pPr>
-                <a:endParaRPr lang="ja-JP"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="t"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="1"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:xVal>
-            <c:numRef>
-              <c:f>印刷用データ!$AH$4</c:f>
-              <c:numCache>
-                <c:formatCode>0.0"%"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>118.482043063774</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>印刷用データ!$AI$4</c:f>
-              <c:numCache>
-                <c:formatCode>0.0"%"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>149.676029242016</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-79D4-48A9-8F10-910E96FCBD2E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>印刷用データ!$AG$5</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>中村美佳</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3853,7 +3732,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -3866,32 +3745,27 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>印刷用データ!$AH$5</c:f>
+              <c:f>印刷用データ!$AH$4</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>106.304166666667</c:v>
+                  <c:v>118.482043063774</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>印刷用データ!$AI$5</c:f>
+              <c:f>印刷用データ!$AI$4</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>81.7924657534247</c:v>
+                  <c:v>149.676029242016</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3899,20 +3773,20 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-79D4-48A9-8F10-910E96FCBD2E}"/>
+              <c16:uniqueId val="{00000001-79D4-48A9-8F10-910E96FCBD2E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
+          <c:idx val="2"/>
+          <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>印刷用データ!$AG$6</c:f>
+              <c:f>印刷用データ!$AG$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>晩田恵美</c:v>
+                  <c:v>中村美佳</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3947,7 +3821,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -3960,32 +3834,27 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>印刷用データ!$AH$6</c:f>
+              <c:f>印刷用データ!$AH$5</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>98.1287147102526</c:v>
+                  <c:v>106.304166666667</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>印刷用データ!$AI$6</c:f>
+              <c:f>印刷用データ!$AI$5</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>121.131478246402</c:v>
+                  <c:v>81.7924657534247</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3993,20 +3862,20 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-79D4-48A9-8F10-910E96FCBD2E}"/>
+              <c16:uniqueId val="{00000002-79D4-48A9-8F10-910E96FCBD2E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
+          <c:idx val="3"/>
+          <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>印刷用データ!$AG$7</c:f>
+              <c:f>印刷用データ!$AG$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>大江美記子</c:v>
+                  <c:v>晩田恵美</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4041,12 +3910,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
+            <c:dLblPos val="t"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -4054,32 +3923,27 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>印刷用データ!$AH$7</c:f>
+              <c:f>印刷用データ!$AH$6</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>109.79766558089</c:v>
+                  <c:v>98.1287147102526</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>印刷用データ!$AI$7</c:f>
+              <c:f>印刷用データ!$AI$6</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>132.886437908497</c:v>
+                  <c:v>121.131478246402</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4087,20 +3951,20 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-79D4-48A9-8F10-910E96FCBD2E}"/>
+              <c16:uniqueId val="{00000003-79D4-48A9-8F10-910E96FCBD2E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
+          <c:idx val="4"/>
+          <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>印刷用データ!$AG$8</c:f>
+              <c:f>印刷用データ!$AG$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>澤田凌</c:v>
+                  <c:v>大江美記子</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4135,12 +3999,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
+            <c:dLblPos val="t"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -4148,32 +4012,27 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>印刷用データ!$AH$8</c:f>
+              <c:f>印刷用データ!$AH$7</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>114.09203480589</c:v>
+                  <c:v>109.79766558089</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>印刷用データ!$AI$8</c:f>
+              <c:f>印刷用データ!$AI$7</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>94.5242547425474</c:v>
+                  <c:v>132.886437908497</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4181,20 +4040,20 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-79D4-48A9-8F10-910E96FCBD2E}"/>
+              <c16:uniqueId val="{00000004-79D4-48A9-8F10-910E96FCBD2E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="6"/>
-          <c:order val="6"/>
+          <c:idx val="5"/>
+          <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>印刷用データ!$AG$9</c:f>
+              <c:f>印刷用データ!$AG$8</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>佐々木千恵</c:v>
+                  <c:v>澤田凌</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4229,12 +4088,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="b"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -4242,32 +4101,27 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>印刷用データ!$AH$9</c:f>
+              <c:f>印刷用データ!$AH$8</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>95.7935150955021</c:v>
+                  <c:v>114.09203480589</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>印刷用データ!$AI$9</c:f>
+              <c:f>印刷用データ!$AI$8</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>171.961255411255</c:v>
+                  <c:v>94.5242547425474</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4275,20 +4129,20 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-79D4-48A9-8F10-910E96FCBD2E}"/>
+              <c16:uniqueId val="{00000005-79D4-48A9-8F10-910E96FCBD2E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="7"/>
-          <c:order val="7"/>
+          <c:idx val="6"/>
+          <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>印刷用データ!$AG$10</c:f>
+              <c:f>印刷用データ!$AG$9</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>山本祥吉</c:v>
+                  <c:v>佐々木千恵</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4323,7 +4177,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -4336,32 +4190,27 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>印刷用データ!$AH$10</c:f>
+              <c:f>印刷用データ!$AH$9</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>93.9004365189932</c:v>
+                  <c:v>95.7935150955021</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>印刷用データ!$AI$10</c:f>
+              <c:f>印刷用データ!$AI$9</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>84.7367397454031</c:v>
+                  <c:v>171.961255411255</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4369,133 +4218,20 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-79D4-48A9-8F10-910E96FCBD2E}"/>
+              <c16:uniqueId val="{00000006-79D4-48A9-8F10-910E96FCBD2E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="8"/>
-          <c:order val="8"/>
+          <c:idx val="7"/>
+          <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>印刷用データ!$AG$11</c:f>
+              <c:f>印刷用データ!$AG$10</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>春谷智子</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="7"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="2E75B6"/>
-              </a:solidFill>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:dLbls>
-            <c:dLbl>
-              <c:idx val="0"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-5.6209150326797387E-2"/>
-                  <c:y val="-4.2167640289969083E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:dLblPos val="r"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="1"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000068-79D4-48A9-8F10-910E96FCBD2E}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="600"/>
-                </a:pPr>
-                <a:endParaRPr lang="ja-JP"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="t"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="1"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:xVal>
-            <c:numRef>
-              <c:f>印刷用データ!$AH$11</c:f>
-              <c:numCache>
-                <c:formatCode>0.0"%"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>105.673412698413</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>印刷用データ!$AI$11</c:f>
-              <c:numCache>
-                <c:formatCode>0.0"%"</c:formatCode>
-                <c:ptCount val="1"/>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-79D4-48A9-8F10-910E96FCBD2E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="9"/>
-          <c:order val="9"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>印刷用データ!$AG$12</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>石戸谷亜子</c:v>
+                  <c:v>山本祥吉</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4530,7 +4266,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -4543,50 +4279,48 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>印刷用データ!$AH$12</c:f>
+              <c:f>印刷用データ!$AH$10</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>89.2211409395973</c:v>
+                  <c:v>93.9004365189932</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>印刷用データ!$AI$12</c:f>
+              <c:f>印刷用データ!$AI$10</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>84.7367397454031</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000009-79D4-48A9-8F10-910E96FCBD2E}"/>
+              <c16:uniqueId val="{00000007-79D4-48A9-8F10-910E96FCBD2E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="10"/>
-          <c:order val="10"/>
+          <c:idx val="8"/>
+          <c:order val="8"/>
           <c:tx>
             <c:strRef>
-              <c:f>印刷用データ!$AG$13</c:f>
+              <c:f>印刷用データ!$AG$11</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>後藤克行</c:v>
+                  <c:v>春谷智子</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4621,7 +4355,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -4634,53 +4368,45 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>印刷用データ!$AH$13</c:f>
+              <c:f>印刷用データ!$AH$11</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>95.5281961878196</c:v>
+                  <c:v>105.673412698413</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>印刷用データ!$AI$13</c:f>
+              <c:f>印刷用データ!$AI$11</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>80.3265096618357</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000A-79D4-48A9-8F10-910E96FCBD2E}"/>
+              <c16:uniqueId val="{00000008-79D4-48A9-8F10-910E96FCBD2E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="11"/>
-          <c:order val="11"/>
+          <c:idx val="9"/>
+          <c:order val="9"/>
           <c:tx>
             <c:strRef>
-              <c:f>印刷用データ!$AG$14</c:f>
+              <c:f>印刷用データ!$AG$12</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>高橋佐織</c:v>
+                  <c:v>石戸谷亜子</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4715,7 +4441,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -4728,53 +4454,45 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>印刷用データ!$AH$14</c:f>
+              <c:f>印刷用データ!$AH$12</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>92.5416419386746</c:v>
+                  <c:v>89.2211409395973</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>印刷用データ!$AI$14</c:f>
+              <c:f>印刷用データ!$AI$12</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>93.8637060342046</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000B-79D4-48A9-8F10-910E96FCBD2E}"/>
+              <c16:uniqueId val="{00000009-79D4-48A9-8F10-910E96FCBD2E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="12"/>
-          <c:order val="12"/>
+          <c:idx val="10"/>
+          <c:order val="10"/>
           <c:tx>
             <c:strRef>
-              <c:f>印刷用データ!$AG$15</c:f>
+              <c:f>印刷用データ!$AG$13</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>河野忠</c:v>
+                  <c:v>後藤克行</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4809,12 +4527,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="b"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -4822,32 +4540,27 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>印刷用データ!$AH$15</c:f>
+              <c:f>印刷用データ!$AH$13</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>84.7287137681159</c:v>
+                  <c:v>95.5281961878196</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>印刷用データ!$AI$15</c:f>
+              <c:f>印刷用データ!$AI$13</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>116.410462287105</c:v>
+                  <c:v>80.3265096618357</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4855,20 +4568,20 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000C-79D4-48A9-8F10-910E96FCBD2E}"/>
+              <c16:uniqueId val="{0000000A-79D4-48A9-8F10-910E96FCBD2E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="13"/>
-          <c:order val="13"/>
+          <c:idx val="11"/>
+          <c:order val="11"/>
           <c:tx>
             <c:strRef>
-              <c:f>印刷用データ!$AG$16</c:f>
+              <c:f>印刷用データ!$AG$14</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>中納沙織</c:v>
+                  <c:v>高橋佐織</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4903,12 +4616,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
+            <c:dLblPos val="b"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -4916,32 +4629,27 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>印刷用データ!$AH$16</c:f>
+              <c:f>印刷用データ!$AH$14</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>86.8991869918699</c:v>
+                  <c:v>92.5416419386746</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>印刷用データ!$AI$16</c:f>
+              <c:f>印刷用データ!$AI$14</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>66.9045614035088</c:v>
+                  <c:v>93.8637060342046</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4949,20 +4657,20 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000D-79D4-48A9-8F10-910E96FCBD2E}"/>
+              <c16:uniqueId val="{0000000B-79D4-48A9-8F10-910E96FCBD2E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="14"/>
-          <c:order val="14"/>
+          <c:idx val="12"/>
+          <c:order val="12"/>
           <c:tx>
             <c:strRef>
-              <c:f>印刷用データ!$AG$17</c:f>
+              <c:f>印刷用データ!$AG$15</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>木村千鶴</c:v>
+                  <c:v>河野忠</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4997,7 +4705,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -5010,32 +4718,27 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>印刷用データ!$AH$17</c:f>
+              <c:f>印刷用データ!$AH$15</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>85.0531876790831</c:v>
+                  <c:v>84.7287137681159</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>印刷用データ!$AI$17</c:f>
+              <c:f>印刷用データ!$AI$15</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>71.8295494544175</c:v>
+                  <c:v>116.410462287105</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5043,20 +4746,20 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000E-79D4-48A9-8F10-910E96FCBD2E}"/>
+              <c16:uniqueId val="{0000000C-79D4-48A9-8F10-910E96FCBD2E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="15"/>
-          <c:order val="15"/>
+          <c:idx val="13"/>
+          <c:order val="13"/>
           <c:tx>
             <c:strRef>
-              <c:f>印刷用データ!$AG$18</c:f>
+              <c:f>印刷用データ!$AG$16</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>森田美加</c:v>
+                  <c:v>中納沙織</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5091,7 +4794,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -5104,32 +4807,27 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>印刷用データ!$AH$18</c:f>
+              <c:f>印刷用データ!$AH$16</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>83.6675925925926</c:v>
+                  <c:v>86.8991869918699</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>印刷用データ!$AI$18</c:f>
+              <c:f>印刷用データ!$AI$16</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>52.2773778920309</c:v>
+                  <c:v>66.9045614035088</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5137,20 +4835,20 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000F-79D4-48A9-8F10-910E96FCBD2E}"/>
+              <c16:uniqueId val="{0000000D-79D4-48A9-8F10-910E96FCBD2E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="16"/>
-          <c:order val="16"/>
+          <c:idx val="14"/>
+          <c:order val="14"/>
           <c:tx>
             <c:strRef>
-              <c:f>印刷用データ!$AG$19</c:f>
+              <c:f>印刷用データ!$AG$17</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>森本久美</c:v>
+                  <c:v>木村千鶴</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5185,7 +4883,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -5198,32 +4896,27 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>印刷用データ!$AH$19</c:f>
+              <c:f>印刷用データ!$AH$17</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>72.9128258845438</c:v>
+                  <c:v>85.0531876790831</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>印刷用データ!$AI$19</c:f>
+              <c:f>印刷用データ!$AI$17</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>100.984488660676</c:v>
+                  <c:v>71.8295494544175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5231,20 +4924,20 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000010-79D4-48A9-8F10-910E96FCBD2E}"/>
+              <c16:uniqueId val="{0000000E-79D4-48A9-8F10-910E96FCBD2E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="17"/>
-          <c:order val="17"/>
+          <c:idx val="15"/>
+          <c:order val="15"/>
           <c:tx>
             <c:strRef>
-              <c:f>印刷用データ!$AG$20</c:f>
+              <c:f>印刷用データ!$AG$18</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>北田倫子</c:v>
+                  <c:v>森田美加</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5279,12 +4972,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
+            <c:dLblPos val="t"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -5292,32 +4985,27 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>印刷用データ!$AH$20</c:f>
+              <c:f>印刷用データ!$AH$18</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>85.1329503829504</c:v>
+                  <c:v>83.6675925925926</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>印刷用データ!$AI$20</c:f>
+              <c:f>印刷用データ!$AI$18</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>136.225066363292</c:v>
+                  <c:v>52.2773778920309</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5325,20 +5013,20 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000011-79D4-48A9-8F10-910E96FCBD2E}"/>
+              <c16:uniqueId val="{0000000F-79D4-48A9-8F10-910E96FCBD2E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="18"/>
-          <c:order val="18"/>
+          <c:idx val="16"/>
+          <c:order val="16"/>
           <c:tx>
             <c:strRef>
-              <c:f>印刷用データ!$AG$21</c:f>
+              <c:f>印刷用データ!$AG$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>向井ひかり</c:v>
+                  <c:v>森本久美</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5373,12 +5061,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="b"/>
+            <c:dLblPos val="t"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -5386,236 +5074,48 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>印刷用データ!$AH$21</c:f>
+              <c:f>印刷用データ!$AH$19</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>77.5346926083866</c:v>
+                  <c:v>72.9128258845438</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>印刷用データ!$AI$21</c:f>
+              <c:f>印刷用データ!$AI$19</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>100.984488660676</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000012-79D4-48A9-8F10-910E96FCBD2E}"/>
+              <c16:uniqueId val="{00000010-79D4-48A9-8F10-910E96FCBD2E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="19"/>
-          <c:order val="19"/>
+          <c:idx val="17"/>
+          <c:order val="17"/>
           <c:tx>
             <c:strRef>
-              <c:f>印刷用データ!$AG$22</c:f>
+              <c:f>印刷用データ!$AG$20</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>鈴木香織</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="7"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="2E75B6"/>
-              </a:solidFill>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>印刷用データ!$AH$22</c:f>
-              <c:numCache>
-                <c:formatCode>0.0"%"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>81.3135313531353</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>印刷用データ!$AI$22</c:f>
-              <c:numCache>
-                <c:formatCode>0.0"%"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>97.3782467532468</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000013-79D4-48A9-8F10-910E96FCBD2E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="20"/>
-          <c:order val="20"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>印刷用データ!$AG$23</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>奥野愛海</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="7"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="2E75B6"/>
-              </a:solidFill>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>印刷用データ!$AH$23</c:f>
-              <c:numCache>
-                <c:formatCode>0.0"%"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>77.7730630630631</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>印刷用データ!$AI$23</c:f>
-              <c:numCache>
-                <c:formatCode>0.0"%"</c:formatCode>
-                <c:ptCount val="1"/>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000014-79D4-48A9-8F10-910E96FCBD2E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="21"/>
-          <c:order val="21"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>印刷用データ!$AG$24</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>菊池敬</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="7"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="2E75B6"/>
-              </a:solidFill>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>印刷用データ!$AH$24</c:f>
-              <c:numCache>
-                <c:formatCode>0.0"%"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>74.1621929824561</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>印刷用データ!$AI$24</c:f>
-              <c:numCache>
-                <c:formatCode>0.0"%"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>65.7034771774833</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000015-79D4-48A9-8F10-910E96FCBD2E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="22"/>
-          <c:order val="22"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>印刷用データ!$AG$25</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>高橋正美</c:v>
+                  <c:v>北田倫子</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5650,7 +5150,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -5663,353 +5163,48 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>印刷用データ!$AH$25</c:f>
+              <c:f>印刷用データ!$AH$20</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>70.6463479415671</c:v>
+                  <c:v>85.1329503829504</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>印刷用データ!$AI$25</c:f>
+              <c:f>印刷用データ!$AI$20</c:f>
               <c:numCache>
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>136.225066363292</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000016-79D4-48A9-8F10-910E96FCBD2E}"/>
+              <c16:uniqueId val="{00000011-79D4-48A9-8F10-910E96FCBD2E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="23"/>
-          <c:order val="23"/>
+          <c:idx val="18"/>
+          <c:order val="18"/>
           <c:tx>
             <c:strRef>
-              <c:f>印刷用データ!$AG$26</c:f>
+              <c:f>印刷用データ!$AG$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>廣瀬こずえ</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="7"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="2E75B6"/>
-              </a:solidFill>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>印刷用データ!$AH$26</c:f>
-              <c:numCache>
-                <c:formatCode>0.0"%"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>74.5292004732928</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>印刷用データ!$AI$26</c:f>
-              <c:numCache>
-                <c:formatCode>0.0"%"</c:formatCode>
-                <c:ptCount val="1"/>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000017-79D4-48A9-8F10-910E96FCBD2E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="24"/>
-          <c:order val="24"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>印刷用データ!$AG$27</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>上村和恵</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="7"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="2E75B6"/>
-              </a:solidFill>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>印刷用データ!$AH$27</c:f>
-              <c:numCache>
-                <c:formatCode>0.0"%"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>68.8745778611632</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>印刷用データ!$AI$27</c:f>
-              <c:numCache>
-                <c:formatCode>0.0"%"</c:formatCode>
-                <c:ptCount val="1"/>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000018-79D4-48A9-8F10-910E96FCBD2E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="25"/>
-          <c:order val="25"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>印刷用データ!$AG$28</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>秋草文恵</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="7"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="2E75B6"/>
-              </a:solidFill>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>印刷用データ!$AH$28</c:f>
-              <c:numCache>
-                <c:formatCode>0.0"%"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>69.0706383317415</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>印刷用データ!$AI$28</c:f>
-              <c:numCache>
-                <c:formatCode>0.0"%"</c:formatCode>
-                <c:ptCount val="1"/>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000019-79D4-48A9-8F10-910E96FCBD2E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="26"/>
-          <c:order val="26"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>印刷用データ!$AG$29</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>飯田由加里</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="7"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="2E75B6"/>
-              </a:solidFill>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>印刷用データ!$AH$29</c:f>
-              <c:numCache>
-                <c:formatCode>0.0"%"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>62.9124127399651</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>印刷用データ!$AI$29</c:f>
-              <c:numCache>
-                <c:formatCode>0.0"%"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>129.170986812187</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000001A-79D4-48A9-8F10-910E96FCBD2E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="27"/>
-          <c:order val="27"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>印刷用データ!$AG$30</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>片岡達也</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="7"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="2E75B6"/>
-              </a:solidFill>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>印刷用データ!$AH$30</c:f>
-              <c:numCache>
-                <c:formatCode>0.0"%"</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>62.9038778877888</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>印刷用データ!$AI$30</c:f>
-              <c:numCache>
-                <c:formatCode>0.0"%"</c:formatCode>
-                <c:ptCount val="1"/>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000001B-79D4-48A9-8F10-910E96FCBD2E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="28"/>
-          <c:order val="28"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>印刷用データ!$AG$31</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>平田学</c:v>
+                  <c:v>向井ひかり</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6044,7 +5239,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -6057,11 +5252,875 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$AH$21</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>77.5346926083866</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$AI$21</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000012-79D4-48A9-8F10-910E96FCBD2E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="19"/>
+          <c:order val="19"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$AG$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>鈴木香織</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="b"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$AH$22</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>81.3135313531353</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$AI$22</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>97.3782467532468</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000013-79D4-48A9-8F10-910E96FCBD2E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="20"/>
+          <c:order val="20"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$AG$23</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>奥野愛海</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$AH$23</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>77.7730630630631</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$AI$23</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000014-79D4-48A9-8F10-910E96FCBD2E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="21"/>
+          <c:order val="21"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$AG$24</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>菊池敬</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="b"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$AH$24</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>74.1621929824561</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$AI$24</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>65.7034771774833</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000015-79D4-48A9-8F10-910E96FCBD2E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="22"/>
+          <c:order val="22"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$AG$25</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>高橋正美</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$AH$25</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>70.6463479415671</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$AI$25</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000016-79D4-48A9-8F10-910E96FCBD2E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="23"/>
+          <c:order val="23"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$AG$26</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>廣瀬こずえ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$AH$26</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>74.5292004732928</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$AI$26</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000017-79D4-48A9-8F10-910E96FCBD2E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="24"/>
+          <c:order val="24"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$AG$27</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>上村和恵</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$AH$27</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>68.8745778611632</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$AI$27</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000018-79D4-48A9-8F10-910E96FCBD2E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="25"/>
+          <c:order val="25"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$AG$28</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>秋草文恵</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$AH$28</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>69.0706383317415</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$AI$28</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000019-79D4-48A9-8F10-910E96FCBD2E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="26"/>
+          <c:order val="26"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$AG$29</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>飯田由加里</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$AH$29</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>62.9124127399651</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$AI$29</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>129.170986812187</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000001A-79D4-48A9-8F10-910E96FCBD2E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="27"/>
+          <c:order val="27"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$AG$30</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>片岡達也</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>印刷用データ!$AH$30</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>62.9038778877888</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>印刷用データ!$AI$30</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000001B-79D4-48A9-8F10-910E96FCBD2E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="28"/>
+          <c:order val="28"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>印刷用データ!$AG$31</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>平田学</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -6132,7 +6191,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -6145,11 +6204,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -6213,7 +6267,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -6226,11 +6280,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -6294,7 +6343,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -6307,11 +6356,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -6375,7 +6419,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -6388,11 +6432,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -6456,7 +6495,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -6469,11 +6508,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -6537,7 +6571,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -6550,11 +6584,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -6618,7 +6647,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -6631,11 +6660,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -6699,7 +6723,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -6712,11 +6736,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -6780,7 +6799,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -6793,11 +6812,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -6861,7 +6875,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -6874,11 +6888,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -6942,7 +6951,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -6955,11 +6964,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -7023,7 +7027,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -7036,11 +7040,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -7104,7 +7103,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -7117,11 +7116,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -7185,7 +7179,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -7198,11 +7192,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -7266,7 +7255,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -7279,11 +7268,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -7347,7 +7331,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -7360,11 +7344,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -7428,7 +7407,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -7441,11 +7420,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -7509,7 +7483,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -7522,11 +7496,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -7590,7 +7559,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -7603,11 +7572,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -7671,7 +7635,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -7684,11 +7648,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -7752,7 +7711,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -7765,11 +7724,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -7812,6 +7766,32 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
           <c:marker>
             <c:symbol val="triangle"/>
             <c:size val="7"/>
@@ -7865,6 +7845,32 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
           <c:marker>
             <c:symbol val="triangle"/>
             <c:size val="7"/>
@@ -7918,6 +7924,32 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
           <c:marker>
             <c:symbol val="triangle"/>
             <c:size val="7"/>
@@ -7971,6 +8003,32 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
           <c:marker>
             <c:symbol val="triangle"/>
             <c:size val="7"/>
@@ -8024,6 +8082,32 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
           <c:marker>
             <c:symbol val="triangle"/>
             <c:size val="7"/>
@@ -8077,6 +8161,32 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
           <c:marker>
             <c:symbol val="triangle"/>
             <c:size val="7"/>
@@ -8130,6 +8240,32 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
           <c:marker>
             <c:symbol val="triangle"/>
             <c:size val="7"/>
@@ -8183,6 +8319,32 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
           <c:marker>
             <c:symbol val="triangle"/>
             <c:size val="7"/>
@@ -8236,6 +8398,32 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
           <c:marker>
             <c:symbol val="triangle"/>
             <c:size val="7"/>
@@ -8260,7 +8448,7 @@
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>27.0</c:v>
+                  <c:v>30.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8292,6 +8480,32 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
           <c:marker>
             <c:symbol val="triangle"/>
             <c:size val="7"/>
@@ -8316,7 +8530,7 @@
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>22.0</c:v>
+                  <c:v>24.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8348,6 +8562,32 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
           <c:marker>
             <c:symbol val="triangle"/>
             <c:size val="7"/>
@@ -8401,6 +8641,32 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
           <c:marker>
             <c:symbol val="triangle"/>
             <c:size val="7"/>
@@ -8454,6 +8720,32 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
           <c:marker>
             <c:symbol val="triangle"/>
             <c:size val="7"/>
@@ -8507,6 +8799,32 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
           <c:marker>
             <c:symbol val="triangle"/>
             <c:size val="7"/>
@@ -8573,16 +8891,6 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
-            <c:dLbl>
-              <c:idx val="0"/>
-              <c:delete val="1"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000000-61FE-4DD7-A2D7-6E0C56A1C909}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -8594,7 +8902,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -8607,11 +8915,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -8654,6 +8957,32 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
           <c:marker>
             <c:symbol val="triangle"/>
             <c:size val="7"/>
@@ -8707,6 +9036,32 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
           <c:marker>
             <c:symbol val="triangle"/>
             <c:size val="7"/>
@@ -8760,6 +9115,32 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
           <c:marker>
             <c:symbol val="triangle"/>
             <c:size val="7"/>
@@ -8813,6 +9194,32 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700"/>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
           <c:marker>
             <c:symbol val="triangle"/>
             <c:size val="7"/>
@@ -8893,12 +9300,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
+            <c:dLblPos val="t"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -8906,11 +9313,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -8981,12 +9383,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
+            <c:dLblPos val="t"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -8994,11 +9396,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -9019,7 +9416,7 @@
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>17.0</c:v>
+                  <c:v>18.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9075,12 +9472,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
+            <c:dLblPos val="t"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -9088,11 +9485,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -9163,7 +9555,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -9176,11 +9568,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -9201,7 +9588,7 @@
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>32.0</c:v>
+                  <c:v>36.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9257,7 +9644,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -9270,11 +9657,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -9295,7 +9677,7 @@
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>37.0</c:v>
+                  <c:v>42.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9351,12 +9733,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
+            <c:dLblPos val="t"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -9364,11 +9746,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -9389,7 +9766,7 @@
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>22.0</c:v>
+                  <c:v>24.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9445,12 +9822,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
+            <c:dLblPos val="t"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -9458,11 +9835,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -9483,7 +9855,7 @@
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>27.0</c:v>
+                  <c:v>30.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9539,12 +9911,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
+            <c:dLblPos val="t"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -9552,11 +9924,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -9627,12 +9994,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
+            <c:dLblPos val="t"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -9640,11 +10007,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -9665,7 +10027,7 @@
                 <c:formatCode>0.0"%"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>17.0</c:v>
+                  <c:v>18.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9721,7 +10083,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -9734,11 +10096,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -9812,7 +10169,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -9825,11 +10182,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -9893,7 +10245,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -9906,11 +10258,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -9974,7 +10321,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -9987,11 +10334,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -10055,7 +10397,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -10068,11 +10410,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -10136,7 +10473,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -10149,11 +10486,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -10217,7 +10549,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -10230,11 +10562,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -10298,7 +10625,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -10311,11 +10638,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -10379,7 +10701,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -10392,11 +10714,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -10460,7 +10777,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -10473,11 +10790,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -10541,7 +10853,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -10554,11 +10866,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -10622,7 +10929,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -10635,11 +10942,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -10703,7 +11005,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -10716,11 +11018,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -10784,7 +11081,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -10797,11 +11094,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -10865,7 +11157,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -10878,11 +11170,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -10946,7 +11233,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -10959,11 +11246,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -11027,7 +11309,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -11040,11 +11322,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -11108,7 +11385,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -11121,11 +11398,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -11189,7 +11461,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -11202,11 +11474,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -11270,7 +11537,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -11283,11 +11550,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -11351,7 +11613,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -11364,11 +11626,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -11432,7 +11689,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="600"/>
+                  <a:defRPr sz="700"/>
                 </a:pPr>
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
@@ -11445,11 +11702,6 @@
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
@@ -11511,7 +11763,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>40.0</c:v>
+                  <c:v>10.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>190.0</c:v>
@@ -11553,7 +11805,7 @@
                   <c:v>40.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>190.0</c:v>
+                  <c:v>160.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11595,8 +11847,8 @@
         <c:axId val="10"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="190"/>
-          <c:min val="10"/>
+          <c:max val="160"/>
+          <c:min val="40"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -26122,7 +26374,7 @@
         <v>100</v>
       </c>
       <c r="X2" s="61">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="Y2" s="61">
         <v>40</v>
@@ -26316,7 +26568,7 @@
         <v>190</v>
       </c>
       <c r="Y3" s="61">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="Z3" s="61">
         <v>100</v>
@@ -26405,11 +26657,11 @@
         <v>100</v>
       </c>
       <c r="AW3" s="62" t="str">
-        <f t="shared" ref="AW3:AW34" si="31">IF($AY3="","",IF($AK3="PKのみ",$AH3,CHOOSE(MOD($AY3-1,6)+1,12,17,22,27,32,37)))</f>
+        <f t="shared" ref="AW3:AW34" si="31">IF($AY3="","",IF($AK3="PKのみ",$AH3,CHOOSE(MOD($AY3-1,6)+1,12,18,24,30,36,42)))</f>
         <v/>
       </c>
       <c r="AX3" s="62" t="str">
-        <f t="shared" ref="AX3:AX34" si="32">IF($AY3="","",IF($AK3="PKのみ",CHOOSE(MOD($AY3-1,6)+1,12,17,22,27,32,37),$AI3))</f>
+        <f t="shared" ref="AX3:AX34" si="32">IF($AY3="","",IF($AK3="PKのみ",CHOOSE(MOD($AY3-1,6)+1,12,18,24,30,36,42),$AI3))</f>
         <v/>
       </c>
       <c r="AY3" s="62" t="str">
@@ -26429,7 +26681,7 @@
         <v>190</v>
       </c>
       <c r="BD3" s="62">
-        <f t="shared" ref="BD3:BD34" si="34">IF($AG3="","",IF(OR(AND(ISNUMBER($AH3),OR($AH3&lt;10,$AH3&gt;190)),AND(ISNUMBER($AI3),OR($AI3&lt;10,$AI3&gt;190))),1,0))</f>
+        <f t="shared" ref="BD3:BD34" si="34">IF($AG3="","",IF(OR(AND(ISNUMBER($AH3),OR($AH3&lt;40,$AH3&gt;160)),AND(ISNUMBER($AI3),OR($AI3&lt;10,$AI3&gt;190))),1,0))</f>
         <v>0</v>
       </c>
       <c r="BF3" s="61" t="str">
@@ -28071,7 +28323,7 @@
       </c>
       <c r="AX11" s="62">
         <f t="shared" si="32"/>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AY11" s="62">
         <f t="shared" si="33"/>
@@ -28278,7 +28530,7 @@
       </c>
       <c r="AX12" s="62">
         <f t="shared" si="32"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AY12" s="62">
         <f t="shared" si="33"/>
@@ -30527,7 +30779,7 @@
       </c>
       <c r="AX23" s="62">
         <f t="shared" si="32"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY23" s="62">
         <f t="shared" si="33"/>
@@ -30895,7 +31147,7 @@
       </c>
       <c r="AX25" s="62">
         <f t="shared" si="32"/>
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AY25" s="62">
         <f t="shared" si="33"/>
@@ -31079,7 +31331,7 @@
       </c>
       <c r="AX26" s="62">
         <f t="shared" si="32"/>
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AY26" s="62">
         <f t="shared" si="33"/>
@@ -31263,7 +31515,7 @@
       </c>
       <c r="AX27" s="62">
         <f t="shared" si="32"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AY27" s="62">
         <f t="shared" si="33"/>
@@ -31447,7 +31699,7 @@
       </c>
       <c r="AX28" s="62">
         <f t="shared" si="32"/>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AY28" s="62">
         <f t="shared" si="33"/>
@@ -31815,7 +32067,7 @@
       </c>
       <c r="AX30" s="62">
         <f t="shared" si="32"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY30" s="62">
         <f t="shared" si="33"/>
@@ -32730,11 +32982,11 @@
         <v/>
       </c>
       <c r="AW35" s="62" t="str">
-        <f t="shared" ref="AW35:AW62" si="70">IF($AY35="","",IF($AK35="PKのみ",$AH35,CHOOSE(MOD($AY35-1,6)+1,12,17,22,27,32,37)))</f>
+        <f t="shared" ref="AW35:AW62" si="70">IF($AY35="","",IF($AK35="PKのみ",$AH35,CHOOSE(MOD($AY35-1,6)+1,12,18,24,30,36,42)))</f>
         <v/>
       </c>
       <c r="AX35" s="62" t="str">
-        <f t="shared" ref="AX35:AX62" si="71">IF($AY35="","",IF($AK35="PKのみ",CHOOSE(MOD($AY35-1,6)+1,12,17,22,27,32,37),$AI35))</f>
+        <f t="shared" ref="AX35:AX62" si="71">IF($AY35="","",IF($AK35="PKのみ",CHOOSE(MOD($AY35-1,6)+1,12,18,24,30,36,42),$AI35))</f>
         <v/>
       </c>
       <c r="AY35" s="62" t="str">
@@ -32742,7 +32994,7 @@
         <v/>
       </c>
       <c r="BD35" s="62" t="str">
-        <f t="shared" ref="BD35:BD62" si="73">IF($AG35="","",IF(OR(AND(ISNUMBER($AH35),OR($AH35&lt;10,$AH35&gt;190)),AND(ISNUMBER($AI35),OR($AI35&lt;10,$AI35&gt;190))),1,0))</f>
+        <f t="shared" ref="BD35:BD62" si="73">IF($AG35="","",IF(OR(AND(ISNUMBER($AH35),OR($AH35&lt;40,$AH35&gt;160)),AND(ISNUMBER($AI35),OR($AI35&lt;10,$AI35&gt;190))),1,0))</f>
         <v/>
       </c>
     </row>

--- a/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
+++ b/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
@@ -4280,7 +4280,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="b"/>
+            <c:dLblPos val="l"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -4630,7 +4630,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="b"/>
+            <c:dLblPos val="t"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -4897,7 +4897,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="b"/>
+            <c:dLblPos val="t"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -4986,7 +4986,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="b"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -5502,7 +5502,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="b"/>
+            <c:dLblPos val="t"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -7792,7 +7792,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -7871,7 +7871,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -7950,7 +7950,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -8029,7 +8029,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -8108,7 +8108,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -8187,7 +8187,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -8266,7 +8266,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -8345,7 +8345,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -8424,7 +8424,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -8506,7 +8506,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -8588,7 +8588,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -8667,7 +8667,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -8746,7 +8746,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -8825,7 +8825,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -8916,7 +8916,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -8983,7 +8983,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -9062,7 +9062,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -9141,7 +9141,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -9220,7 +9220,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -9314,7 +9314,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -9397,7 +9397,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -9486,7 +9486,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -9569,7 +9569,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -9658,7 +9658,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -9747,7 +9747,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -9836,7 +9836,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -9925,7 +9925,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -10008,7 +10008,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -10097,7 +10097,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -10183,7 +10183,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -10259,7 +10259,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -10335,7 +10335,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -10411,7 +10411,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -10487,7 +10487,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -10563,7 +10563,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -10639,7 +10639,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -10715,7 +10715,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -10791,7 +10791,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -10867,7 +10867,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -10943,7 +10943,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -11019,7 +11019,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -11095,7 +11095,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -11171,7 +11171,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -11247,7 +11247,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -11323,7 +11323,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -11399,7 +11399,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -11475,7 +11475,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -11551,7 +11551,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -11627,7 +11627,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -11703,7 +11703,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>

--- a/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
+++ b/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
@@ -37974,6 +37974,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B1:AA63"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
@@ -40089,7 +40092,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="8" scale="120" fitToHeight="2" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="8" scale="120" fitToWidth="1" fitToHeight="2" orientation="landscape" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="36" max="16383" man="1"/>
   </rowBreaks>

--- a/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
+++ b/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="508">
   <si>
     <t>▼ グラフ用データ　消したり非表示にしたりしないでください</t>
   </si>
@@ -1626,6 +1626,15 @@
   </si>
   <si>
     <t>・そのため同姓同名の方がいても正しく対応します。隠し列「入力行」は削除しないでください。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自動計算です。入力は「入力」シートで行ってください。判定は会社目標（1.6分/件）に対する達成率で決めます（◎○△の境目は「設定」シート）。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⑧ 印刷用（A3横・2枚）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">・「印刷用」シートを開いて印刷してください。A3 横 2 枚に収まる設定済みです（1枚目にグラフ①②③と順位1〜32、2枚目に残りの順位と注記）。</t>
   </si>
 </sst>
 </file>
@@ -20620,7 +20629,7 @@
         <v>43</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>44</v>
+        <v>506</v>
       </c>
       <c r="T6">
         <v>4</v>
@@ -26192,7 +26201,7 @@
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B43" s="94" t="s">
-        <v>402</v>
+        <v>507</v>
       </c>
       <c r="C43" s="79"/>
       <c r="D43" s="79"/>
@@ -41617,7 +41626,7 @@
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.15">
       <c r="B4" s="3" t="s">
-        <v>164</v>
+        <v>505</v>
       </c>
       <c r="W4" s="47" t="s">
         <v>165</v>
@@ -47776,7 +47785,7 @@
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.15">
       <c r="B4" s="3" t="s">
-        <v>164</v>
+        <v>505</v>
       </c>
       <c r="W4" s="47" t="s">
         <v>165</v>

--- a/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
+++ b/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="518">
   <si>
     <t>▼ グラフ用データ　消したり非表示にしたりしないでください</t>
   </si>
@@ -1635,6 +1635,36 @@
   </si>
   <si>
     <t xml:space="preserve">・「印刷用」シートを開いて印刷してください。A3 横 2 枚に収まる設定済みです（1枚目にグラフ①②③と順位1〜32、2枚目に残りの順位と注記）。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　 記録日数が少ない人ほど大きく動きます（縦軸が動いた量）。少ない日数の数字で人を評価しないための補正です。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">※ ②の p 値は、このブックの「入力」シートの企業数からその場で計算しています。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　 ただし相関が完全には消えていない分は、補正しきれていない可能性として説明書にも書いています。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　 入力データを差し替えると、この r・p も自動で計算し直されます。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">記録日数が空欄の人は、縮小後効率と95%信頼区間が出ません（判定は達成率だけで付きます）。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黄色のセルだけ入力してください。空欄の行は自動で無視されます（最大60名。印刷用の表とグラフに載るのは50名まで）。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">参考値（縮小後効率・信頼区間）の設定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PK 縮小後効率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">梱包 縮小後効率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">いまの全体平均（自動）。改善を織り込むなら数字を上書き</t>
   </si>
 </sst>
 </file>
@@ -11999,7 +12029,7 @@
             </a:r>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>a=92.1 b=75.6</a:t>
+              <a:t>a=56.05 b=75.6</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -13938,91 +13968,91 @@
               <c:strCache>
                 <c:ptCount val="60"/>
                 <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>18</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>11</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="6">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>16</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="12">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>10</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="20">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="21">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>12</c:v>
                 </c:pt>
-                <c:pt idx="20">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="23">
                   <c:v>12</c:v>
                 </c:pt>
-                <c:pt idx="22">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>17</c:v>
-                </c:pt>
                 <c:pt idx="24">
-                  <c:v>12</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>13</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>11</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -14163,91 +14193,91 @@
               <c:strCache>
                 <c:ptCount val="60"/>
                 <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>18</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>11</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="6">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>16</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="12">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>10</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="20">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="21">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>12</c:v>
                 </c:pt>
-                <c:pt idx="20">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="23">
                   <c:v>12</c:v>
                 </c:pt>
-                <c:pt idx="22">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>17</c:v>
-                </c:pt>
                 <c:pt idx="24">
-                  <c:v>12</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>13</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>11</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -16171,76 +16201,73 @@
             </c:strRef>
           </c:cat>
           <c:val>
-            <c:numRef>
-              <c:f>印刷用データ!$AV$3:$AV$23</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
-                <c:pt idx="0">
-                  <c:v>100.0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>100.0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>100.0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>100.0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>100.0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>100.0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>100.0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>100.0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>100.0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>100.0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>100.0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>100.0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>100.0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>100.0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>100.0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>100.0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>100.0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>100.0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>100.0</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>100.0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>100.0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="21"/>
+              <c:pt idx="0">
+                <c:v>100</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>100</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>100</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>100</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>100</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>100</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>100</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>100</c:v>
+              </c:pt>
+              <c:pt idx="8">
+                <c:v>100</c:v>
+              </c:pt>
+              <c:pt idx="9">
+                <c:v>100</c:v>
+              </c:pt>
+              <c:pt idx="10">
+                <c:v>100</c:v>
+              </c:pt>
+              <c:pt idx="11">
+                <c:v>100</c:v>
+              </c:pt>
+              <c:pt idx="12">
+                <c:v>100</c:v>
+              </c:pt>
+              <c:pt idx="13">
+                <c:v>100</c:v>
+              </c:pt>
+              <c:pt idx="14">
+                <c:v>100</c:v>
+              </c:pt>
+              <c:pt idx="15">
+                <c:v>100</c:v>
+              </c:pt>
+              <c:pt idx="16">
+                <c:v>100</c:v>
+              </c:pt>
+              <c:pt idx="17">
+                <c:v>100</c:v>
+              </c:pt>
+              <c:pt idx="18">
+                <c:v>100</c:v>
+              </c:pt>
+              <c:pt idx="19">
+                <c:v>100</c:v>
+              </c:pt>
+              <c:pt idx="20">
+                <c:v>100</c:v>
+              </c:pt>
+            </c:numLit>
           </c:val>
           <c:smooth val="0"/>
           <c:extLst>
@@ -16463,13 +16490,13 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>段取り　233.2h・34.3%</c:v>
+                  <c:v>段取り　141.6h・24.1%</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>移動　223.1h・32.8%</c:v>
+                  <c:v>移動　223.1h・38%</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>ピック　223.1h・32.8%</c:v>
+                  <c:v>ピック　223.1h・38%</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -16481,13 +16508,13 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>233.2</c:v>
+                  <c:v>141.588527777778</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>223.1</c:v>
+                  <c:v>223.1145</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>223.1</c:v>
+                  <c:v>223.1145</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -20259,8 +20286,9 @@
       <c r="B3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="84" t="s">
-        <v>30</v>
+      <c r="G3" s="84" t="str">
+        <f>"対象 "&amp;ピッキング!$X$5&amp;"名・"&amp;TEXT(ピッキング!$X$10+梱包!$X$10,"#,##0")&amp;"件・完全記録 "&amp;COUNT(日次!$P$8:$P$28)&amp;"日分"</f>
+        <v>対象 29名・45,716件・完全記録 21日分</v>
       </c>
       <c r="H3" s="76"/>
       <c r="I3" s="76"/>
@@ -20364,15 +20392,16 @@
         <v>31</v>
       </c>
       <c r="AX3" s="5">
-        <v>233.2</v>
+        <f>ピッキング!$X$13/60</f>
+        <v>141.588527777778</v>
       </c>
       <c r="AY3" s="6">
         <f>IFERROR(AX3/SUM($AX$3:$AX$5),"")</f>
-        <v>0.343244038857816</v>
+        <v>0.240871564876685</v>
       </c>
       <c r="AZ3" t="str">
         <f>AW3&amp;"　"&amp;ROUND(AX3,1)&amp;"h・"&amp;ROUND(AY3*100,1)&amp;"%"</f>
-        <v>段取り　233.2h・34.3%</v>
+        <v>段取り　141.6h・24.1%</v>
       </c>
     </row>
     <row r="4" spans="2:52" x14ac:dyDescent="0.15">
@@ -20478,15 +20507,16 @@
         <v>33</v>
       </c>
       <c r="AX4" s="5">
-        <v>223.1</v>
+        <f>設定!$E$7/2*ピッキング!$X$10/3600</f>
+        <v>223.1145</v>
       </c>
       <c r="AY4" s="6">
         <f>IFERROR(AX4/SUM($AX$3:$AX$5),"")</f>
-        <v>0.328377980571092</v>
+        <v>0.379564217561657</v>
       </c>
       <c r="AZ4" t="str">
         <f>AW4&amp;"　"&amp;ROUND(AX4,1)&amp;"h・"&amp;ROUND(AY4*100,1)&amp;"%"</f>
-        <v>移動　223.1h・32.8%</v>
+        <v>移動　223.1h・38%</v>
       </c>
     </row>
     <row r="5" spans="2:52" x14ac:dyDescent="0.15">
@@ -20589,15 +20619,16 @@
         <v>34</v>
       </c>
       <c r="AX5" s="5">
-        <v>223.1</v>
+        <f>設定!$E$7/2*ピッキング!$X$10/3600</f>
+        <v>223.1145</v>
       </c>
       <c r="AY5" s="6">
         <f>IFERROR(AX5/SUM($AX$3:$AX$5),"")</f>
-        <v>0.328377980571092</v>
+        <v>0.379564217561657</v>
       </c>
       <c r="AZ5" t="str">
         <f>AW5&amp;"　"&amp;ROUND(AX5,1)&amp;"h・"&amp;ROUND(AY5*100,1)&amp;"%"</f>
-        <v>ピック　223.1h・32.8%</v>
+        <v>ピック　223.1h・38%</v>
       </c>
     </row>
     <row r="6" spans="2:52" ht="24" customHeight="1" x14ac:dyDescent="0.15">
@@ -20825,8 +20856,9 @@
       </c>
     </row>
     <row r="8" spans="2:52" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="B8" s="85" t="s">
-        <v>45</v>
+      <c r="B8" s="85" t="str">
+        <f>"●　1社ごとの段取りが "&amp;TEXT(AX3,"0.0")&amp;" 時間。ピッキング標準時間の "&amp;TEXT(AY3,"0.0%")&amp;" を占めています。"</f>
+        <v>●　1社ごとの段取りが 141.6 時間。ピッキング標準時間の 24.1% を占めています。</v>
       </c>
       <c r="C8" s="79"/>
       <c r="D8" s="79"/>
@@ -21250,15 +21282,11 @@
       </c>
     </row>
     <row r="12" spans="2:52" x14ac:dyDescent="0.15">
-      <c r="B12" s="74">
-        <v>0.29399999999999998</v>
-      </c>
+      <c r="B12" s="74"/>
       <c r="C12" s="69"/>
       <c r="D12" s="69"/>
       <c r="E12" s="69"/>
-      <c r="F12" s="68">
-        <v>6.7000000000000004E-2</v>
-      </c>
+      <c r="F12" s="68"/>
       <c r="G12" s="69"/>
       <c r="H12" s="69"/>
       <c r="I12" s="69"/>
@@ -21359,8 +21387,9 @@
       </c>
     </row>
     <row r="13" spans="2:52" x14ac:dyDescent="0.15">
-      <c r="B13" s="72" t="s">
-        <v>48</v>
+      <c r="B13" s="72" t="str">
+        <f>"ピッキング "&amp;TEXT(ピッキング!$X$10,"#,##0")&amp;"件 ＋ 梱包 "&amp;TEXT(梱包!$X$10,"#,##0")&amp;"件。物量は需要であって成績ではない"</f>
+        <v>ピッキング 21,249件 ＋ 梱包 24,467件。物量は需要であって成績ではない</v>
       </c>
       <c r="C13" s="69"/>
       <c r="D13" s="69"/>
@@ -21729,15 +21758,11 @@
       </c>
     </row>
     <row r="17" spans="2:40" x14ac:dyDescent="0.15">
-      <c r="B17" s="73">
-        <v>9.5000000000000001E-2</v>
-      </c>
+      <c r="B17" s="73"/>
       <c r="C17" s="69"/>
       <c r="D17" s="69"/>
       <c r="E17" s="69"/>
-      <c r="F17" s="74">
-        <v>0.23799999999999999</v>
-      </c>
+      <c r="F17" s="74"/>
       <c r="G17" s="69"/>
       <c r="H17" s="69"/>
       <c r="I17" s="69"/>
@@ -21810,14 +21835,16 @@
       </c>
     </row>
     <row r="18" spans="2:40" x14ac:dyDescent="0.15">
-      <c r="B18" s="72" t="s">
-        <v>52</v>
+      <c r="B18" s="72" t="str">
+        <f>"段取り "&amp;TEXT(ピッキング!$X$13/60,"0.0")&amp;"h ÷ ピッキング実働 "&amp;TEXT(ピッキング!$X$12/60,"0.0")&amp;"h。下がるのは良いこと"</f>
+        <v>段取り 141.6h ÷ ピッキング実働 679.7h。下がるのは良いこと</v>
       </c>
       <c r="C18" s="69"/>
       <c r="D18" s="69"/>
       <c r="E18" s="69"/>
-      <c r="F18" s="72" t="s">
-        <v>53</v>
+      <c r="F18" s="72" t="str">
+        <f>"ピッキング "&amp;TEXT(ピッキング!$X$12/60,"0.0")&amp;"h ＋ 梱包 "&amp;TEXT(梱包!$X$12/60,"0.0")&amp;"h"</f>
+        <v>ピッキング 679.7h ＋ 梱包 648.1h</v>
       </c>
       <c r="G18" s="69"/>
       <c r="H18" s="69"/>
@@ -25010,8 +25037,9 @@
       </c>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B98" s="3" t="s">
-        <v>68</v>
+      <c r="B98" s="3" t="str">
+        <f>"ピッキングの標準時間 "&amp;TEXT(ピッキング!$X$14/60,"0.0")&amp;" 時間を作業単位で分解。手を動かしているのは約"&amp;TEXT(AY5*10,"0")&amp;"割です。（移動とピックは b="&amp;設定!$E$7&amp;"秒/件 を半分ずつと仮定した内訳で、実測ではありません）"</f>
+        <v>ピッキングの標準時間 587.8 時間を作業単位で分解。手を動かしているのは約4割です。（移動とピックは b=75.6秒/件 を半分ずつと仮定した内訳で、実測ではありません）</v>
       </c>
     </row>
     <row r="99" spans="2:10" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
@@ -25020,7 +25048,7 @@
       </c>
       <c r="E99" s="19">
         <f>IFERROR(AY5,"")</f>
-        <v>0.328377980571092</v>
+        <v>0.379564217561657</v>
       </c>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.15">
@@ -25044,11 +25072,11 @@
       </c>
       <c r="H102" s="22">
         <f t="shared" si="16"/>
-        <v>233.2</v>
+        <v>141.588527777778</v>
       </c>
       <c r="I102" s="23">
         <f t="shared" si="16"/>
-        <v>0.343244038857816</v>
+        <v>0.240871564876685</v>
       </c>
       <c r="J102" s="24" t="s">
         <v>73</v>
@@ -25061,11 +25089,11 @@
       </c>
       <c r="H103" s="22">
         <f t="shared" si="16"/>
-        <v>223.1</v>
+        <v>223.1145</v>
       </c>
       <c r="I103" s="23">
         <f t="shared" si="16"/>
-        <v>0.328377980571092</v>
+        <v>0.379564217561657</v>
       </c>
       <c r="J103" s="24" t="s">
         <v>74</v>
@@ -25078,11 +25106,11 @@
       </c>
       <c r="H104" s="22">
         <f t="shared" si="16"/>
-        <v>223.1</v>
+        <v>223.1145</v>
       </c>
       <c r="I104" s="23">
         <f t="shared" si="16"/>
-        <v>0.328377980571092</v>
+        <v>0.379564217561657</v>
       </c>
       <c r="J104" s="24" t="s">
         <v>75</v>
@@ -25117,11 +25145,13 @@
       </c>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B150" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D150" s="7" t="s">
-        <v>81</v>
+      <c r="B150" s="7" t="str">
+        <f>"→ ピッキング "&amp;ピッキング!$X$5&amp;"名の明細"</f>
+        <v>→ ピッキング 29名の明細</v>
+      </c>
+      <c r="D150" s="7" t="str">
+        <f>"→ 梱包 "&amp;梱包!$X$5&amp;"名の明細"</f>
+        <v>→ 梱包 19名の明細</v>
       </c>
     </row>
     <row r="152" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -25427,8 +25457,9 @@
       </c>
     </row>
     <row r="235" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B235" s="3" t="s">
-        <v>104</v>
+      <c r="B235" s="3" t="str">
+        <f>"対象 "&amp;ピッキング!$X$5&amp;"名・"&amp;TEXT(ピッキング!$X$10+梱包!$X$10,"#,##0")&amp;"件・完全記録 "&amp;COUNT(日次!$P$8:$P$28)&amp;"日分　／　梱包の a="&amp;設定!$E$8&amp;" は統計的に0と区別できない（値より不安定さが実態）"</f>
+        <v>対象 29名・45,716件・完全記録 21日分　／　梱包の a=92.1 は統計的に0と区別できない（値より不安定さが実態）</v>
       </c>
     </row>
   </sheetData>
@@ -25613,7 +25644,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B11" s="9" t="s">
-        <v>359</v>
+        <v>514</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.15">
@@ -26666,7 +26697,7 @@
         <v>100</v>
       </c>
       <c r="AW3" s="62" t="str">
-        <f t="shared" ref="AW3:AW34" si="31">IF($AY3="","",IF($AK3="PKのみ",$AH3,CHOOSE(MOD($AY3-1,6)+1,12,18,24,30,36,42)))</f>
+        <f t="shared" ref="AW3:AW34" si="31">IF($AY3="","",IF($AK3="PKのみ",$AH3,0))</f>
         <v/>
       </c>
       <c r="AX3" s="62" t="str">
@@ -26690,7 +26721,7 @@
         <v>190</v>
       </c>
       <c r="BD3" s="62">
-        <f t="shared" ref="BD3:BD34" si="34">IF($AG3="","",IF(OR(AND(ISNUMBER($AH3),OR($AH3&lt;40,$AH3&gt;160)),AND(ISNUMBER($AI3),OR($AI3&lt;10,$AI3&gt;190))),1,0))</f>
+        <f t="shared" ref="BD3:BD34" si="34">IF($AG3="","",IF(OR(AND(ISNUMBER($AH3),OR($AH3&lt;40,$AH3&gt;160)),AND(ISNUMBER($AI3),OR($AI3&lt;10,$AI3&gt;190)),$AK3="梱包のみ"),1,0))</f>
         <v>0</v>
       </c>
       <c r="BF3" s="61" t="str">
@@ -32991,7 +33022,7 @@
         <v/>
       </c>
       <c r="AW35" s="62" t="str">
-        <f t="shared" ref="AW35:AW62" si="70">IF($AY35="","",IF($AK35="PKのみ",$AH35,CHOOSE(MOD($AY35-1,6)+1,12,18,24,30,36,42)))</f>
+        <f t="shared" ref="AW35:AW62" si="70">IF($AY35="","",IF($AK35="PKのみ",$AH35,0))</f>
         <v/>
       </c>
       <c r="AX35" s="62" t="str">
@@ -33003,7 +33034,7 @@
         <v/>
       </c>
       <c r="BD35" s="62" t="str">
-        <f t="shared" ref="BD35:BD62" si="73">IF($AG35="","",IF(OR(AND(ISNUMBER($AH35),OR($AH35&lt;40,$AH35&gt;160)),AND(ISNUMBER($AI35),OR($AI35&lt;10,$AI35&gt;190))),1,0))</f>
+        <f t="shared" ref="BD35:BD62" si="73">IF($AG35="","",IF(OR(AND(ISNUMBER($AH35),OR($AH35&lt;40,$AH35&gt;160)),AND(ISNUMBER($AI35),OR($AI35&lt;10,$AI35&gt;190)),$AK35="梱包のみ"),1,0))</f>
         <v/>
       </c>
     </row>
@@ -40018,8 +40049,8 @@
     </row>
     <row r="62" spans="2:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="89" t="str">
-        <f>"※ ①③④ は実績のある全員 "&amp;COUNT(印刷用データ!AS3:AS62)&amp;" 名。② は改善優先の上位 "&amp;MIN(20,COUNT(印刷用データ!$AS$3:$AS$62))&amp;" 名です（全員の順位は④の表）。「工程」が PKのみ／梱包のみ の人は、その工程だけの標準時間 ÷ 実測時間です。③ でもう一方の実績が無い "&amp;(COUNT(印刷用データ!AS3:AS62)-COUNT(印刷用データ!N3:N62))&amp;" 名は、下の帯に灰色の三角で並べています。出典: 2026年4月 実績。"&amp;IF(SUM(印刷用データ!BD3:BD62)&gt;0,"　【要確認】③ は縦横とも 10〜190% の範囲で描いています。範囲外のため図に出ていない人が "&amp;SUM(印刷用データ!BD3:BD62)&amp;" 名います。","")</f>
-        <v>※ ①③④ は実績のある全員 29 名。② は改善優先の上位 20 名です（全員の順位は④の表）。「工程」が PKのみ／梱包のみ の人は、その工程だけの標準時間 ÷ 実測時間です。③ でもう一方の実績が無い 10 名は、下の帯に灰色の三角で並べています。出典: 2026年4月 実績。</v>
+        <f>"※ ①③④ は実績のある全員 "&amp;COUNT(印刷用データ!AS3:AS62)&amp;" 名。② は改善優先の上位 "&amp;MIN(20,COUNT(印刷用データ!$AS$3:$AS$62))&amp;" 名です（全員の順位は④の表）。「工程」が PKのみ／梱包のみ の人は、その工程だけの標準時間 ÷ 実測時間です。③ でピッキングの実績しか無い "&amp;COUNTIF(印刷用データ!AK3:AK62,"PKのみ")&amp;" 名は、下の帯に灰色の三角で並べています。出典: 2026年4月 実績。"&amp;IF(SUM(印刷用データ!BD3:BD62)&gt;0,"　【要確認】③ は横 40〜160%・縦 10〜190% の範囲で描いています。範囲外または梱包のみのため図に出ていない人が "&amp;SUM(印刷用データ!BD3:BD62)&amp;" 名います。","")&amp;IF(COUNT(印刷用データ!AS3:AS62)&gt;50,"　【要確認】印刷用の表とグラフに載るのは 50 名までです。51 人目以降は載りません。","")</f>
+        <v>※ ①③④ は実績のある全員 29 名。② は改善優先の上位 20 名です（全員の順位は④の表）。「工程」が PKのみ／梱包のみ の人は、その工程だけの標準時間 ÷ 実測時間です。③ でピッキングの実績しか無い 10 名は、下の帯に灰色の三角で並べています。出典: 2026年4月 実績。</v>
       </c>
       <c r="C62" s="79"/>
       <c r="D62" s="79"/>
@@ -40131,7 +40162,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B3" s="3" t="s">
-        <v>114</v>
+        <v>513</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.15">
@@ -40432,7 +40463,7 @@
         <v>4</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>136</v>
+        <v>512</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.15">
@@ -55230,8 +55261,8 @@
         <v>810</v>
       </c>
       <c r="AY8">
-        <f>IF(AND(ISNUMBER(入力!$F$10),入力!$F$10&gt;0),入力!$F$10,"")</f>
-        <v>18</v>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$7)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$7),""),"")</f>
+        <v>10</v>
       </c>
       <c r="AZ8">
         <f>IF(ピッキング!$K$7="","",ピッキング!$K$7)</f>
@@ -55267,7 +55298,7 @@
       </c>
       <c r="BJ8">
         <f t="shared" ref="BJ8:BJ39" si="16">IFERROR(INDEX($AY$8:$AY$67,MATCH(AB8,$BI$8:$BI$67,0)),"")</f>
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="BK8">
         <f t="shared" ref="BK8:BK39" si="17">IFERROR(INDEX($AZ$8:$AZ$67,MATCH(AB8,$BI$8:$BI$67,0)),"")</f>
@@ -55414,8 +55445,8 @@
         <v>2028</v>
       </c>
       <c r="AY9">
-        <f>IF(AND(ISNUMBER(入力!$F$11),入力!$F$11&gt;0),入力!$F$11,"")</f>
-        <v>11</v>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$8)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$8),""),"")</f>
+        <v>18</v>
       </c>
       <c r="AZ9">
         <f>IF(ピッキング!$K$8="","",ピッキング!$K$8)</f>
@@ -55451,7 +55482,7 @@
       </c>
       <c r="BJ9">
         <f t="shared" si="16"/>
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="BK9">
         <f t="shared" si="17"/>
@@ -55590,8 +55621,8 @@
         <v>120</v>
       </c>
       <c r="AY10">
-        <f>IF(AND(ISNUMBER(入力!$F$12),入力!$F$12&gt;0),入力!$F$12,"")</f>
-        <v>16</v>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$9)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$9),""),"")</f>
+        <v>3</v>
       </c>
       <c r="AZ10">
         <f>IF(ピッキング!$K$9="","",ピッキング!$K$9)</f>
@@ -55627,7 +55658,7 @@
       </c>
       <c r="BJ10">
         <f t="shared" si="16"/>
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="BK10">
         <f t="shared" si="17"/>
@@ -55758,8 +55789,8 @@
         <v>1346</v>
       </c>
       <c r="AY11">
-        <f>IF(AND(ISNUMBER(入力!$F$13),入力!$F$13&gt;0),入力!$F$13,"")</f>
-        <v>10</v>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$10)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$10),""),"")</f>
+        <v>14</v>
       </c>
       <c r="AZ11">
         <f>IF(ピッキング!$K$10="","",ピッキング!$K$10)</f>
@@ -55795,7 +55826,7 @@
       </c>
       <c r="BJ11">
         <f t="shared" si="16"/>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BK11">
         <f t="shared" si="17"/>
@@ -55926,8 +55957,8 @@
         <v>1535</v>
       </c>
       <c r="AY12">
-        <f>IF(AND(ISNUMBER(入力!$F$14),入力!$F$14&gt;0),入力!$F$14,"")</f>
-        <v>4</v>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$11)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$11),""),"")</f>
+        <v>16</v>
       </c>
       <c r="AZ12">
         <f>IF(ピッキング!$K$11="","",ピッキング!$K$11)</f>
@@ -55963,7 +55994,7 @@
       </c>
       <c r="BJ12">
         <f t="shared" si="16"/>
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="BK12">
         <f t="shared" si="17"/>
@@ -56094,8 +56125,8 @@
         <v>1245</v>
       </c>
       <c r="AY13">
-        <f>IF(AND(ISNUMBER(入力!$F$15),入力!$F$15&gt;0),入力!$F$15,"")</f>
-        <v>20</v>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$12)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$12),""),"")</f>
+        <v>11</v>
       </c>
       <c r="AZ13">
         <f>IF(ピッキング!$K$12="","",ピッキング!$K$12)</f>
@@ -56131,7 +56162,7 @@
       </c>
       <c r="BJ13">
         <f t="shared" si="16"/>
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="BK13">
         <f t="shared" si="17"/>
@@ -56262,8 +56293,8 @@
         <v>1082</v>
       </c>
       <c r="AY14">
-        <f>IF(AND(ISNUMBER(入力!$F$16),入力!$F$16&gt;0),入力!$F$16,"")</f>
-        <v>3</v>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$13)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$13),""),"")</f>
+        <v>10</v>
       </c>
       <c r="AZ14">
         <f>IF(ピッキング!$K$13="","",ピッキング!$K$13)</f>
@@ -56299,7 +56330,7 @@
       </c>
       <c r="BJ14">
         <f t="shared" si="16"/>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="BK14">
         <f t="shared" si="17"/>
@@ -56423,8 +56454,8 @@
         <v>3589</v>
       </c>
       <c r="AY15">
-        <f>IF(AND(ISNUMBER(入力!$F$17),入力!$F$17&gt;0),入力!$F$17,"")</f>
-        <v>14</v>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$14)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$14),""),"")</f>
+        <v>20</v>
       </c>
       <c r="AZ15">
         <f>IF(ピッキング!$K$14="","",ピッキング!$K$14)</f>
@@ -56460,7 +56491,7 @@
       </c>
       <c r="BJ15">
         <f t="shared" si="16"/>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="BK15">
         <f t="shared" si="17"/>
@@ -56587,8 +56618,8 @@
         <v>210</v>
       </c>
       <c r="AY16">
-        <f>IF(AND(ISNUMBER(入力!$F$18),入力!$F$18&gt;0),入力!$F$18,"")</f>
-        <v>16</v>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$15)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$15),""),"")</f>
+        <v>4</v>
       </c>
       <c r="AZ16">
         <f>IF(ピッキング!$K$15="","",ピッキング!$K$15)</f>
@@ -56624,7 +56655,7 @@
       </c>
       <c r="BJ16">
         <f t="shared" si="16"/>
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="BK16">
         <f t="shared" si="17"/>
@@ -56754,8 +56785,8 @@
         <v>1490</v>
       </c>
       <c r="AY17">
-        <f>IF(AND(ISNUMBER(入力!$F$19),入力!$F$19&gt;0),入力!$F$19,"")</f>
-        <v>20</v>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$16)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$16),""),"")</f>
+        <v>8</v>
       </c>
       <c r="AZ17">
         <f>IF(ピッキング!$K$16="","",ピッキング!$K$16)</f>
@@ -56791,7 +56822,7 @@
       </c>
       <c r="BJ17">
         <f t="shared" si="16"/>
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="BK17">
         <f t="shared" si="17"/>
@@ -56922,8 +56953,8 @@
         <v>3585</v>
       </c>
       <c r="AY18">
-        <f>IF(AND(ISNUMBER(入力!$F$20),入力!$F$20&gt;0),入力!$F$20,"")</f>
-        <v>10</v>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$17)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$17),""),"")</f>
+        <v>20</v>
       </c>
       <c r="AZ18">
         <f>IF(ピッキング!$K$17="","",ピッキング!$K$17)</f>
@@ -56959,7 +56990,7 @@
       </c>
       <c r="BJ18">
         <f t="shared" si="16"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="BK18">
         <f t="shared" si="17"/>
@@ -57090,8 +57121,8 @@
         <v>1685</v>
       </c>
       <c r="AY19">
-        <f>IF(AND(ISNUMBER(入力!$F$21),入力!$F$21&gt;0),入力!$F$21,"")</f>
-        <v>14</v>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$18)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$18),""),"")</f>
+        <v>16</v>
       </c>
       <c r="AZ19">
         <f>IF(ピッキング!$K$18="","",ピッキング!$K$18)</f>
@@ -57127,7 +57158,7 @@
       </c>
       <c r="BJ19">
         <f t="shared" si="16"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BK19">
         <f t="shared" si="17"/>
@@ -57258,8 +57289,8 @@
         <v>552</v>
       </c>
       <c r="AY20">
-        <f>IF(AND(ISNUMBER(入力!$F$22),入力!$F$22&gt;0),入力!$F$22,"")</f>
-        <v>9</v>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$19)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$19),""),"")</f>
+        <v>6</v>
       </c>
       <c r="AZ20">
         <f>IF(ピッキング!$K$19="","",ピッキング!$K$19)</f>
@@ -57295,7 +57326,7 @@
       </c>
       <c r="BJ20">
         <f t="shared" si="16"/>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BK20">
         <f t="shared" si="17"/>
@@ -57426,8 +57457,8 @@
         <v>2255</v>
       </c>
       <c r="AY21">
-        <f>IF(AND(ISNUMBER(入力!$F$23),入力!$F$23&gt;0),入力!$F$23,"")</f>
-        <v>8</v>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$20)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$20),""),"")</f>
+        <v>9</v>
       </c>
       <c r="AZ21">
         <f>IF(ピッキング!$K$20="","",ピッキング!$K$20)</f>
@@ -57463,7 +57494,7 @@
       </c>
       <c r="BJ21">
         <f t="shared" si="16"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BK21">
         <f t="shared" si="17"/>
@@ -57594,8 +57625,8 @@
         <v>1396</v>
       </c>
       <c r="AY22">
-        <f>IF(AND(ISNUMBER(入力!$F$24),入力!$F$24&gt;0),入力!$F$24,"")</f>
-        <v>5</v>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$21)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$21),""),"")</f>
+        <v>16</v>
       </c>
       <c r="AZ22">
         <f>IF(ピッキング!$K$21="","",ピッキング!$K$21)</f>
@@ -57631,7 +57662,7 @@
       </c>
       <c r="BJ22">
         <f t="shared" si="16"/>
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="BK22">
         <f t="shared" si="17"/>
@@ -57762,8 +57793,8 @@
         <v>450</v>
       </c>
       <c r="AY23">
-        <f>IF(AND(ISNUMBER(入力!$F$25),入力!$F$25&gt;0),入力!$F$25,"")</f>
-        <v>6</v>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$22)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$22),""),"")</f>
+        <v>5</v>
       </c>
       <c r="AZ23">
         <f>IF(ピッキング!$K$22="","",ピッキング!$K$22)</f>
@@ -57799,7 +57830,7 @@
       </c>
       <c r="BJ23">
         <f t="shared" si="16"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BK23">
         <f t="shared" si="17"/>
@@ -57923,8 +57954,8 @@
         <v>716</v>
       </c>
       <c r="AY24">
-        <f>IF(AND(ISNUMBER(入力!$F$26),入力!$F$26&gt;0),入力!$F$26,"")</f>
-        <v>16</v>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$23)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$23),""),"")</f>
+        <v>9</v>
       </c>
       <c r="AZ24">
         <f>IF(ピッキング!$K$23="","",ピッキング!$K$23)</f>
@@ -57960,7 +57991,7 @@
       </c>
       <c r="BJ24">
         <f t="shared" si="16"/>
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="BK24">
         <f t="shared" si="17"/>
@@ -58087,8 +58118,8 @@
         <v>1001</v>
       </c>
       <c r="AY25">
-        <f>IF(AND(ISNUMBER(入力!$F$27),入力!$F$27&gt;0),入力!$F$27,"")</f>
-        <v>3</v>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$24)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$24),""),"")</f>
+        <v>14</v>
       </c>
       <c r="AZ25">
         <f>IF(ピッキング!$K$24="","",ピッキング!$K$24)</f>
@@ -58124,7 +58155,7 @@
       </c>
       <c r="BJ25">
         <f t="shared" si="16"/>
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="BK25">
         <f t="shared" si="17"/>
@@ -58254,8 +58285,8 @@
         <v>1876</v>
       </c>
       <c r="AY26">
-        <f>IF(AND(ISNUMBER(入力!$F$28),入力!$F$28&gt;0),入力!$F$28,"")</f>
-        <v>10</v>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$25)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$25),""),"")</f>
+        <v>12</v>
       </c>
       <c r="AZ26">
         <f>IF(ピッキング!$K$25="","",ピッキング!$K$25)</f>
@@ -58291,7 +58322,7 @@
       </c>
       <c r="BJ26">
         <f t="shared" si="16"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BK26">
         <f t="shared" si="17"/>
@@ -58422,8 +58453,8 @@
         <v>505</v>
       </c>
       <c r="AY27">
-        <f>IF(AND(ISNUMBER(入力!$F$29),入力!$F$29&gt;0),入力!$F$29,"")</f>
-        <v>12</v>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$26)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$26),""),"")</f>
+        <v>10</v>
       </c>
       <c r="AZ27">
         <f>IF(ピッキング!$K$26="","",ピッキング!$K$26)</f>
@@ -58459,7 +58490,7 @@
       </c>
       <c r="BJ27">
         <f t="shared" si="16"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BK27">
         <f t="shared" si="17"/>
@@ -58590,8 +58621,8 @@
         <v>925</v>
       </c>
       <c r="AY28">
-        <f>IF(AND(ISNUMBER(入力!$F$30),入力!$F$30&gt;0),入力!$F$30,"")</f>
-        <v>4</v>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$27)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$27),""),"")</f>
+        <v>3</v>
       </c>
       <c r="AZ28">
         <f>IF(ピッキング!$K$27="","",ピッキング!$K$27)</f>
@@ -58627,7 +58658,7 @@
       </c>
       <c r="BJ28">
         <f t="shared" si="16"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BK28">
         <f t="shared" si="17"/>
@@ -58758,8 +58789,8 @@
         <v>950</v>
       </c>
       <c r="AY29">
-        <f>IF(AND(ISNUMBER(入力!$F$31),入力!$F$31&gt;0),入力!$F$31,"")</f>
-        <v>12</v>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$28)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$28),""),"")</f>
+        <v>17</v>
       </c>
       <c r="AZ29">
         <f>IF(ピッキング!$K$28="","",ピッキング!$K$28)</f>
@@ -58795,7 +58826,7 @@
       </c>
       <c r="BJ29">
         <f t="shared" si="16"/>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="BK29">
         <f t="shared" si="17"/>
@@ -58926,8 +58957,8 @@
         <v>2510</v>
       </c>
       <c r="AY30">
-        <f>IF(AND(ISNUMBER(入力!$F$32),入力!$F$32&gt;0),入力!$F$32,"")</f>
-        <v>9</v>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$29)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$29),""),"")</f>
+        <v>12</v>
       </c>
       <c r="AZ30">
         <f>IF(ピッキング!$K$29="","",ピッキング!$K$29)</f>
@@ -58963,7 +58994,7 @@
       </c>
       <c r="BJ30">
         <f t="shared" si="16"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BK30">
         <f t="shared" si="17"/>
@@ -59094,8 +59125,8 @@
         <v>1972</v>
       </c>
       <c r="AY31">
-        <f>IF(AND(ISNUMBER(入力!$F$33),入力!$F$33&gt;0),入力!$F$33,"")</f>
-        <v>17</v>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$30)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$30),""),"")</f>
+        <v>12</v>
       </c>
       <c r="AZ31">
         <f>IF(ピッキング!$K$30="","",ピッキング!$K$30)</f>
@@ -59131,7 +59162,7 @@
       </c>
       <c r="BJ31">
         <f t="shared" si="16"/>
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BK31">
         <f t="shared" si="17"/>
@@ -59262,8 +59293,8 @@
         <v>2665</v>
       </c>
       <c r="AY32">
-        <f>IF(AND(ISNUMBER(入力!$F$34),入力!$F$34&gt;0),入力!$F$34,"")</f>
-        <v>12</v>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$31)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$31),""),"")</f>
+        <v>13</v>
       </c>
       <c r="AZ32">
         <f>IF(ピッキング!$K$31="","",ピッキング!$K$31)</f>
@@ -59299,7 +59330,7 @@
       </c>
       <c r="BJ32">
         <f t="shared" si="16"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BK32">
         <f t="shared" si="17"/>
@@ -59423,7 +59454,7 @@
         <v>2094</v>
       </c>
       <c r="AY33">
-        <f>IF(AND(ISNUMBER(入力!$F$35),入力!$F$35&gt;0),入力!$F$35,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$32)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$32),""),"")</f>
         <v>12</v>
       </c>
       <c r="AZ33">
@@ -59587,8 +59618,8 @@
         <v>764</v>
       </c>
       <c r="AY34">
-        <f>IF(AND(ISNUMBER(入力!$F$36),入力!$F$36&gt;0),入力!$F$36,"")</f>
-        <v>13</v>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$33)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$33),""),"")</f>
+        <v>11</v>
       </c>
       <c r="AZ34">
         <f>IF(ピッキング!$K$33="","",ピッキング!$K$33)</f>
@@ -59624,7 +59655,7 @@
       </c>
       <c r="BJ34">
         <f t="shared" si="16"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BK34">
         <f t="shared" si="17"/>
@@ -59754,7 +59785,7 @@
         <v>202</v>
       </c>
       <c r="AY35">
-        <f>IF(AND(ISNUMBER(入力!$F$37),入力!$F$37&gt;0),入力!$F$37,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$34)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$34),""),"")</f>
         <v>4</v>
       </c>
       <c r="AZ35">
@@ -59922,8 +59953,8 @@
         <v>1225</v>
       </c>
       <c r="AY36">
-        <f>IF(AND(ISNUMBER(入力!$F$38),入力!$F$38&gt;0),入力!$F$38,"")</f>
-        <v>11</v>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$35)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$35),""),"")</f>
+        <v>4</v>
       </c>
       <c r="AZ36">
         <f>IF(ピッキング!$K$35="","",ピッキング!$K$35)</f>
@@ -59959,7 +59990,7 @@
       </c>
       <c r="BJ36">
         <f t="shared" si="16"/>
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="BK36">
         <f t="shared" si="17"/>
@@ -60090,7 +60121,7 @@
         <v/>
       </c>
       <c r="AY37" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$39),入力!$F$39&gt;0),入力!$F$39,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$36)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$36),""),"")</f>
         <v/>
       </c>
       <c r="AZ37" t="str">
@@ -60258,7 +60289,7 @@
         <v/>
       </c>
       <c r="AY38" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$40),入力!$F$40&gt;0),入力!$F$40,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$37)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$37),""),"")</f>
         <v/>
       </c>
       <c r="AZ38" t="str">
@@ -60426,7 +60457,7 @@
         <v/>
       </c>
       <c r="AY39" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$41),入力!$F$41&gt;0),入力!$F$41,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$38)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$38),""),"")</f>
         <v/>
       </c>
       <c r="AZ39" t="str">
@@ -60594,7 +60625,7 @@
         <v/>
       </c>
       <c r="AY40" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$42),入力!$F$42&gt;0),入力!$F$42,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$39)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$39),""),"")</f>
         <v/>
       </c>
       <c r="AZ40" t="str">
@@ -60762,7 +60793,7 @@
         <v/>
       </c>
       <c r="AY41" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$43),入力!$F$43&gt;0),入力!$F$43,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$40)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$40),""),"")</f>
         <v/>
       </c>
       <c r="AZ41" t="str">
@@ -60923,7 +60954,7 @@
         <v/>
       </c>
       <c r="AY42" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$44),入力!$F$44&gt;0),入力!$F$44,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$41)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$41),""),"")</f>
         <v/>
       </c>
       <c r="AZ42" t="str">
@@ -61087,7 +61118,7 @@
         <v/>
       </c>
       <c r="AY43" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$45),入力!$F$45&gt;0),入力!$F$45,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$42)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$42),""),"")</f>
         <v/>
       </c>
       <c r="AZ43" t="str">
@@ -61254,7 +61285,7 @@
         <v/>
       </c>
       <c r="AY44" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$46),入力!$F$46&gt;0),入力!$F$46,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$43)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$43),""),"")</f>
         <v/>
       </c>
       <c r="AZ44" t="str">
@@ -61422,7 +61453,7 @@
         <v/>
       </c>
       <c r="AY45" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$47),入力!$F$47&gt;0),入力!$F$47,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$44)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$44),""),"")</f>
         <v/>
       </c>
       <c r="AZ45" t="str">
@@ -61590,7 +61621,7 @@
         <v/>
       </c>
       <c r="AY46" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$48),入力!$F$48&gt;0),入力!$F$48,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$45)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$45),""),"")</f>
         <v/>
       </c>
       <c r="AZ46" t="str">
@@ -61758,7 +61789,7 @@
         <v/>
       </c>
       <c r="AY47" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$49),入力!$F$49&gt;0),入力!$F$49,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$46)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$46),""),"")</f>
         <v/>
       </c>
       <c r="AZ47" t="str">
@@ -61926,7 +61957,7 @@
         <v/>
       </c>
       <c r="AY48" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$50),入力!$F$50&gt;0),入力!$F$50,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$47)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$47),""),"")</f>
         <v/>
       </c>
       <c r="AZ48" t="str">
@@ -62094,7 +62125,7 @@
         <v/>
       </c>
       <c r="AY49" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$51),入力!$F$51&gt;0),入力!$F$51,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$48)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$48),""),"")</f>
         <v/>
       </c>
       <c r="AZ49" t="str">
@@ -62262,7 +62293,7 @@
         <v/>
       </c>
       <c r="AY50" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$52),入力!$F$52&gt;0),入力!$F$52,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$49)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$49),""),"")</f>
         <v/>
       </c>
       <c r="AZ50" t="str">
@@ -62423,7 +62454,7 @@
         <v/>
       </c>
       <c r="AY51" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$53),入力!$F$53&gt;0),入力!$F$53,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$50)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$50),""),"")</f>
         <v/>
       </c>
       <c r="AZ51" t="str">
@@ -62587,7 +62618,7 @@
         <v/>
       </c>
       <c r="AY52" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$54),入力!$F$54&gt;0),入力!$F$54,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$51)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$51),""),"")</f>
         <v/>
       </c>
       <c r="AZ52" t="str">
@@ -62640,8 +62671,9 @@
       </c>
     </row>
     <row r="53" spans="2:65" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B53" s="92" t="s">
-        <v>281</v>
+      <c r="B53" s="92" t="str">
+        <f>"横軸 記録日数　縦軸 引き寄せ量。相関 r="&amp;TEXT(C55,"0.00")&amp;"（p="&amp;TEXT(C59,"0.00")&amp;"）。引き寄せ量は「記録日数」と「平均からの距離」の両方で決まるため、一直線にはなりません。"</f>
+        <v>横軸 記録日数　縦軸 引き寄せ量。相関 r=-0.46（p=0.01）。引き寄せ量は「記録日数」と「平均からの距離」の両方で決まるため、一直線にはなりません。</v>
       </c>
       <c r="C53" s="79"/>
       <c r="D53" s="79"/>
@@ -62754,7 +62786,7 @@
         <v/>
       </c>
       <c r="AY53" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$55),入力!$F$55&gt;0),入力!$F$55,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$52)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$52),""),"")</f>
         <v/>
       </c>
       <c r="AZ53" t="str">
@@ -62922,7 +62954,7 @@
         <v/>
       </c>
       <c r="AY54" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$56),入力!$F$56&gt;0),入力!$F$56,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$53)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$53),""),"")</f>
         <v/>
       </c>
       <c r="AZ54" t="str">
@@ -62980,7 +63012,7 @@
       </c>
       <c r="C55" s="52">
         <f>IFERROR(CORREL($BJ$8:$BJ$67,$BM$8:$BM$67),"")</f>
-        <v>0.146320789548666</v>
+        <v>-0.455031674411662</v>
       </c>
       <c r="T55" t="str">
         <f>IF(ピッキング!$B$54="","",ピッキング!$B$54)</f>
@@ -63090,7 +63122,7 @@
         <v/>
       </c>
       <c r="AY55" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$57),入力!$F$57&gt;0),入力!$F$57,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$54)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$54),""),"")</f>
         <v/>
       </c>
       <c r="AZ55" t="str">
@@ -63148,7 +63180,7 @@
       </c>
       <c r="C56" s="52">
         <f>IFERROR(RSQ($BM$8:$BM$67,$BJ$8:$BJ$67),"")</f>
-        <v>0.021409773454145</v>
+        <v>0.207053824717881</v>
       </c>
       <c r="T56" t="str">
         <f>IF(ピッキング!$B$55="","",ピッキング!$B$55)</f>
@@ -63258,7 +63290,7 @@
         <v/>
       </c>
       <c r="AY56" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$58),入力!$F$58&gt;0),入力!$F$58,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$55)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$55),""),"")</f>
         <v/>
       </c>
       <c r="AZ56" t="str">
@@ -63316,7 +63348,7 @@
       </c>
       <c r="C57" s="22">
         <f>IFERROR(SLOPE($BM$8:$BM$67,$BJ$8:$BJ$67),"")</f>
-        <v>0.19455681220194</v>
+        <v>-0.605037139954739</v>
       </c>
       <c r="T57" t="str">
         <f>IF(ピッキング!$B$56="","",ピッキング!$B$56)</f>
@@ -63426,7 +63458,7 @@
         <v/>
       </c>
       <c r="AY57" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$59),入力!$F$59&gt;0),入力!$F$59,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$56)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$56),""),"")</f>
         <v/>
       </c>
       <c r="AZ57" t="str">
@@ -63484,7 +63516,7 @@
       </c>
       <c r="C58" s="22">
         <f>IFERROR(INTERCEPT($BM$8:$BM$67,$BJ$8:$BJ$67),"")</f>
-        <v>6.1303933486651</v>
+        <v>14.9259268223886</v>
       </c>
       <c r="T58" t="str">
         <f>IF(ピッキング!$B$57="","",ピッキング!$B$57)</f>
@@ -63594,7 +63626,7 @@
         <v/>
       </c>
       <c r="AY58" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$60),入力!$F$60&gt;0),入力!$F$60,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$57)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$57),""),"")</f>
         <v/>
       </c>
       <c r="AZ58" t="str">
@@ -63652,7 +63684,7 @@
       </c>
       <c r="C59" s="53">
         <f>IFERROR(TDIST(ABS(C55)*SQRT((C54-2)/(1-C55^2)),C54-2,2),"")</f>
-        <v>0.448815252713156</v>
+        <v>0.0131313250085232</v>
       </c>
       <c r="T59" t="str">
         <f>IF(ピッキング!$B$58="","",ピッキング!$B$58)</f>
@@ -63762,7 +63794,7 @@
         <v/>
       </c>
       <c r="AY59" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$61),入力!$F$61&gt;0),入力!$F$61,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$58)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$58),""),"")</f>
         <v/>
       </c>
       <c r="AZ59" t="str">
@@ -63923,7 +63955,7 @@
         <v/>
       </c>
       <c r="AY60" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$62),入力!$F$62&gt;0),入力!$F$62,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$59)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$59),""),"")</f>
         <v/>
       </c>
       <c r="AZ60" t="str">
@@ -64084,7 +64116,7 @@
         <v/>
       </c>
       <c r="AY61" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$63),入力!$F$63&gt;0),入力!$F$63,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$60)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$60),""),"")</f>
         <v/>
       </c>
       <c r="AZ61" t="str">
@@ -64245,7 +64277,7 @@
         <v/>
       </c>
       <c r="AY62" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$64),入力!$F$64&gt;0),入力!$F$64,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$61)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$61),""),"")</f>
         <v/>
       </c>
       <c r="AZ62" t="str">
@@ -64406,7 +64438,7 @@
         <v/>
       </c>
       <c r="AY63" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$65),入力!$F$65&gt;0),入力!$F$65,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$62)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$62),""),"")</f>
         <v/>
       </c>
       <c r="AZ63" t="str">
@@ -64567,7 +64599,7 @@
         <v/>
       </c>
       <c r="AY64" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$66),入力!$F$66&gt;0),入力!$F$66,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$63)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$63),""),"")</f>
         <v/>
       </c>
       <c r="AZ64" t="str">
@@ -64728,7 +64760,7 @@
         <v/>
       </c>
       <c r="AY65" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$67),入力!$F$67&gt;0),入力!$F$67,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$64)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$64),""),"")</f>
         <v/>
       </c>
       <c r="AZ65" t="str">
@@ -64889,7 +64921,7 @@
         <v/>
       </c>
       <c r="AY66" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$68),入力!$F$68&gt;0),入力!$F$68,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$65)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$65),""),"")</f>
         <v/>
       </c>
       <c r="AZ66" t="str">
@@ -65050,7 +65082,7 @@
         <v/>
       </c>
       <c r="AY67" t="str">
-        <f>IF(AND(ISNUMBER(入力!$F$69),入力!$F$69&gt;0),入力!$F$69,"")</f>
+        <f>IFERROR(IF(INDEX(入力!$F:$F,ピッキング!$V$66)&gt;0,INDEX(入力!$F:$F,ピッキング!$V$66),""),"")</f>
         <v/>
       </c>
       <c r="AZ67" t="str">
@@ -65189,7 +65221,7 @@
     </row>
     <row r="148" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B148" s="54" t="s">
-        <v>296</v>
+        <v>508</v>
       </c>
     </row>
     <row r="149" spans="2:2" x14ac:dyDescent="0.15">
@@ -65198,8 +65230,9 @@
       </c>
     </row>
     <row r="150" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B150" s="54" t="s">
-        <v>298</v>
+      <c r="B150" s="54" t="str">
+        <f>"　 日数との相関は r="&amp;TEXT(C55,"0.00")&amp;"。日数が少ないほど大きく動きますが、一直線にはなりません。"</f>
+        <v>　 日数との相関は r=-0.46。日数が少ないほど大きく動きますが、一直線にはなりません。</v>
       </c>
     </row>
     <row r="151" spans="2:2" x14ac:dyDescent="0.15">
@@ -65207,22 +65240,23 @@
     </row>
     <row r="152" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B152" s="54" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
     </row>
     <row r="153" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B153" s="54" t="s">
-        <v>300</v>
+      <c r="B153" s="54" t="str">
+        <f>"　 現在の値は r="&amp;TEXT(C19,"0.00")&amp;"、p="&amp;TEXT(C23,"0.00")&amp;"。0.05 を上回るので、統計的には「傾きは無いと言ってよい」範囲です。"</f>
+        <v>　 現在の値は r=0.25、p=0.18。0.05 を上回るので、統計的には「傾きは無いと言ってよい」範囲です。</v>
       </c>
     </row>
     <row r="154" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B154" s="54" t="s">
-        <v>301</v>
+        <v>510</v>
       </c>
     </row>
     <row r="155" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B155" s="54" t="s">
-        <v>302</v>
+        <v>511</v>
       </c>
     </row>
   </sheetData>
@@ -65276,10 +65310,10 @@
         <v>118</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>305</v>
+        <v>515</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>306</v>
+        <v>516</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>307</v>
@@ -67186,13 +67220,15 @@
         <v>319</v>
       </c>
       <c r="C10" s="56">
-        <v>103.4</v>
+        <f>ROUND(ピッキング!$X$3,1)</f>
+        <v>89.7</v>
       </c>
       <c r="D10" s="56">
-        <v>109.2</v>
+        <f>ROUND(梱包!$X$3,1)</f>
+        <v>109.4</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>320</v>
+        <v>517</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.15">
@@ -67298,11 +67334,11 @@
       </c>
       <c r="C19" s="57">
         <f>IFERROR(C18/(C10/100),"")</f>
-        <v>425.921142159485</v>
+        <v>490.972643247389</v>
       </c>
       <c r="D19" s="57">
         <f>IFERROR(D18/(D10/100),"")</f>
-        <v>4.87455666027095</v>
+        <v>4.86564522213517</v>
       </c>
       <c r="E19" s="24" t="s">
         <v>333</v>
@@ -67314,11 +67350,11 @@
       </c>
       <c r="C20" s="46">
         <f>IFERROR(C19/C11,"")</f>
-        <v>3.04229387256775</v>
+        <v>3.50694745176706</v>
       </c>
       <c r="D20" s="46">
         <f>IFERROR(D19/D11,"")</f>
-        <v>0.0406213055022579</v>
+        <v>0.0405470435177931</v>
       </c>
       <c r="E20" s="24" t="s">
         <v>335</v>
@@ -67399,7 +67435,7 @@
       </c>
       <c r="H27" s="22">
         <f t="shared" ref="H27:H34" si="3">IFERROR(F27/($C$10/100)/$C$11,"")</f>
-        <v>4.02728711890946</v>
+        <v>4.64238002335828</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.15">
@@ -67428,7 +67464,7 @@
       </c>
       <c r="H28" s="22">
         <f t="shared" si="3"/>
-        <v>3.4557478278223</v>
+        <v>3.983548778114</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.15">
@@ -67457,7 +67493,7 @@
       </c>
       <c r="H29" s="22">
         <f t="shared" si="3"/>
-        <v>3.16997818227871</v>
+        <v>3.65413315549185</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.15">
@@ -67486,7 +67522,7 @@
       </c>
       <c r="H30" s="22">
         <f t="shared" si="3"/>
-        <v>3.04229387256775</v>
+        <v>3.50694745176706</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.15">
@@ -67515,7 +67551,7 @@
       </c>
       <c r="H31" s="22">
         <f t="shared" si="3"/>
-        <v>2.88420853673513</v>
+        <v>3.32471753286971</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.15">
@@ -67544,7 +67580,7 @@
       </c>
       <c r="H32" s="22">
         <f t="shared" si="3"/>
-        <v>2.74132371396334</v>
+        <v>3.16000972155863</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.15">
@@ -67573,7 +67609,7 @@
       </c>
       <c r="H33" s="22">
         <f t="shared" si="3"/>
-        <v>2.65559282030027</v>
+        <v>3.06118503477199</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.15">
@@ -67602,7 +67638,7 @@
       </c>
       <c r="H34" s="22">
         <f t="shared" si="3"/>
-        <v>2.48413103297412</v>
+        <v>2.8635356611987</v>
       </c>
     </row>
   </sheetData>

--- a/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
+++ b/ピッキング_梱包_公平評価ツール_2026年4月.xlsx
@@ -19562,69 +19562,6 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9007" name="TextBox 9007">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002F230000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF">
-            <a:alpha val="88000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="7F7F7F"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="14000" tIns="8000" rIns="14000" bIns="8000" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="ja-JP" sz="600" b="1">
-              <a:solidFill>
-                <a:srgbClr val="595959"/>
-              </a:solidFill>
-              <a:latin typeface="游ゴシック"/>
-              <a:ea typeface="游ゴシック"/>
-            </a:rPr>
-            <a:t>▲ もう一方の工程は実績なし</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -26721,7 +26658,7 @@
         <v>190</v>
       </c>
       <c r="BD3" s="62">
-        <f t="shared" ref="BD3:BD34" si="34">IF($AG3="","",IF(OR(AND(ISNUMBER($AH3),OR($AH3&lt;40,$AH3&gt;160)),AND(ISNUMBER($AI3),OR($AI3&lt;10,$AI3&gt;190)),$AK3="梱包のみ"),1,0))</f>
+        <f t="shared" ref="BD3:BD34" si="34">IF($AG3="","",IF(OR(AND(ISNUMBER($AH3),OR($AH3&lt;40,$AH3&gt;160)),AND(ISNUMBER($AI3),OR($AI3&lt;10,$AI3&gt;190)),AND(ISNUMBER($AW3),OR($AW3&lt;40,$AW3&gt;160)),AND(ISNUMBER($AX3),OR($AX3&lt;10,$AX3&gt;190))),1,0))</f>
         <v>0</v>
       </c>
       <c r="BF3" s="61" t="str">
@@ -33034,7 +32971,7 @@
         <v/>
       </c>
       <c r="BD35" s="62" t="str">
-        <f t="shared" ref="BD35:BD62" si="73">IF($AG35="","",IF(OR(AND(ISNUMBER($AH35),OR($AH35&lt;40,$AH35&gt;160)),AND(ISNUMBER($AI35),OR($AI35&lt;10,$AI35&gt;190)),$AK35="梱包のみ"),1,0))</f>
+        <f t="shared" ref="BD35:BD62" si="73">IF($AG35="","",IF(OR(AND(ISNUMBER($AH35),OR($AH35&lt;40,$AH35&gt;160)),AND(ISNUMBER($AI35),OR($AI35&lt;10,$AI35&gt;190)),AND(ISNUMBER($AW35),OR($AW35&lt;40,$AW35&gt;160)),AND(ISNUMBER($AX35),OR($AX35&lt;10,$AX35&gt;190))),1,0))</f>
         <v/>
       </c>
     </row>
@@ -38613,8 +38550,8 @@
         <v>梱包手順を改善</v>
       </c>
       <c r="T17" s="88" t="str">
-        <f>"③ 改善優先度マトリクス（全員 "&amp;COUNT(印刷用データ!$AS$3:$AS$62)&amp;"名）"</f>
-        <v>③ 改善優先度マトリクス（全員 29名）</v>
+        <f>"③ 改善優先度マトリクス（全員 "&amp;COUNT(印刷用データ!$AS$3:$AS$62)&amp;"名）　▲＝梱包の実績が無い人（下の帯）"</f>
+        <v>③ 改善優先度マトリクス（全員 29名）　▲＝梱包の実績が無い人（下の帯）</v>
       </c>
       <c r="U17" s="79"/>
       <c r="V17" s="79"/>
@@ -40131,7 +40068,7 @@
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.5" bottom="0.5" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="8" scale="120" fitToWidth="1" fitToHeight="2" orientation="landscape" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="36" max="16383" man="1"/>
